--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="250">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1125,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP147"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ3">
         <v>0.5</v>
@@ -4140,7 +4140,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5785,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23">
         <v>0.71</v>
@@ -7848,7 +7848,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ33">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR33">
         <v>1.9</v>
@@ -10317,7 +10317,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ45">
         <v>1.25</v>
@@ -11968,7 +11968,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ53">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR53">
         <v>1.35</v>
@@ -15673,7 +15673,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -17118,7 +17118,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ78">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -18557,7 +18557,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85">
         <v>1</v>
@@ -21856,7 +21856,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ101">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR101">
         <v>1.36</v>
@@ -22471,7 +22471,7 @@
         <v>0.25</v>
       </c>
       <c r="AP104">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104">
         <v>0.71</v>
@@ -25564,7 +25564,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ119">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR119">
         <v>1.94</v>
@@ -26797,7 +26797,7 @@
         <v>0.17</v>
       </c>
       <c r="AP125">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ125">
         <v>0.25</v>
@@ -27624,7 +27624,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ129">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR129">
         <v>1.61</v>
@@ -31407,6 +31407,212 @@
         <v>3.02</v>
       </c>
       <c r="BP147">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7834470</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45862.79166666666</v>
+      </c>
+      <c r="F148">
+        <v>16</v>
+      </c>
+      <c r="G148" t="s">
+        <v>71</v>
+      </c>
+      <c r="H148" t="s">
+        <v>73</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148" t="s">
+        <v>93</v>
+      </c>
+      <c r="P148" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q148">
+        <v>5</v>
+      </c>
+      <c r="R148">
+        <v>1.94</v>
+      </c>
+      <c r="S148">
+        <v>2.61</v>
+      </c>
+      <c r="T148">
+        <v>1.56</v>
+      </c>
+      <c r="U148">
+        <v>2.5</v>
+      </c>
+      <c r="V148">
+        <v>3.6</v>
+      </c>
+      <c r="W148">
+        <v>1.25</v>
+      </c>
+      <c r="X148">
+        <v>8</v>
+      </c>
+      <c r="Y148">
+        <v>1.04</v>
+      </c>
+      <c r="Z148">
+        <v>3.75</v>
+      </c>
+      <c r="AA148">
+        <v>3.05</v>
+      </c>
+      <c r="AB148">
+        <v>1.95</v>
+      </c>
+      <c r="AC148">
+        <v>1.06</v>
+      </c>
+      <c r="AD148">
+        <v>6.5</v>
+      </c>
+      <c r="AE148">
+        <v>1.54</v>
+      </c>
+      <c r="AF148">
+        <v>2.54</v>
+      </c>
+      <c r="AG148">
+        <v>2.45</v>
+      </c>
+      <c r="AH148">
+        <v>1.5</v>
+      </c>
+      <c r="AI148">
+        <v>2.05</v>
+      </c>
+      <c r="AJ148">
+        <v>1.67</v>
+      </c>
+      <c r="AK148">
+        <v>1.3</v>
+      </c>
+      <c r="AL148">
+        <v>1.35</v>
+      </c>
+      <c r="AM148">
+        <v>1.2</v>
+      </c>
+      <c r="AN148">
+        <v>1.57</v>
+      </c>
+      <c r="AO148">
+        <v>0.57</v>
+      </c>
+      <c r="AP148">
+        <v>1.38</v>
+      </c>
+      <c r="AQ148">
+        <v>0.88</v>
+      </c>
+      <c r="AR148">
+        <v>1.51</v>
+      </c>
+      <c r="AS148">
+        <v>1.28</v>
+      </c>
+      <c r="AT148">
+        <v>2.79</v>
+      </c>
+      <c r="AU148">
+        <v>0</v>
+      </c>
+      <c r="AV148">
+        <v>4</v>
+      </c>
+      <c r="AW148">
+        <v>9</v>
+      </c>
+      <c r="AX148">
+        <v>13</v>
+      </c>
+      <c r="AY148">
+        <v>9</v>
+      </c>
+      <c r="AZ148">
+        <v>17</v>
+      </c>
+      <c r="BA148">
+        <v>4</v>
+      </c>
+      <c r="BB148">
+        <v>8</v>
+      </c>
+      <c r="BC148">
+        <v>12</v>
+      </c>
+      <c r="BD148">
+        <v>2.25</v>
+      </c>
+      <c r="BE148">
+        <v>7</v>
+      </c>
+      <c r="BF148">
+        <v>1.95</v>
+      </c>
+      <c r="BG148">
+        <v>1.25</v>
+      </c>
+      <c r="BH148">
+        <v>3.3</v>
+      </c>
+      <c r="BI148">
+        <v>1.49</v>
+      </c>
+      <c r="BJ148">
+        <v>2.3</v>
+      </c>
+      <c r="BK148">
+        <v>1.85</v>
+      </c>
+      <c r="BL148">
+        <v>1.85</v>
+      </c>
+      <c r="BM148">
+        <v>2.45</v>
+      </c>
+      <c r="BN148">
+        <v>1.55</v>
+      </c>
+      <c r="BO148">
+        <v>2.92</v>
+      </c>
+      <c r="BP148">
         <v>1.33</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="258">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,7 +532,7 @@
     <t>['53', '90+7']</t>
   </si>
   <si>
-    <t>['33', '25', '54', '77']</t>
+    <t>['25', '33', '54', '77']</t>
   </si>
   <si>
     <t>['12', '49']</t>
@@ -568,7 +568,7 @@
     <t>['36']</t>
   </si>
   <si>
-    <t>['90+4', '54']</t>
+    <t>['54', '90+4']</t>
   </si>
   <si>
     <t>['90+1']</t>
@@ -589,10 +589,16 @@
     <t>['3']</t>
   </si>
   <si>
-    <t>['45+3']</t>
+    <t>['24', '59', '90+1']</t>
+  </si>
+  <si>
+    <t>['27', '58', '90+3']</t>
   </si>
   <si>
     <t>['75']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
   </si>
   <si>
     <t>['21']</t>
@@ -769,7 +775,7 @@
     <t>['16', '22']</t>
   </si>
   <si>
-    <t>['90+9', '89']</t>
+    <t>['89', '90+9']</t>
   </si>
   <si>
     <t>['9', '75']</t>
@@ -779,6 +785,9 @@
   </si>
   <si>
     <t>['79', '88']</t>
+  </si>
+  <si>
+    <t>['39', '60']</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1474,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ2">
         <v>0.25</v>
@@ -1602,7 +1611,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
@@ -1680,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ3">
         <v>1.25</v>
@@ -1808,7 +1817,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1889,7 +1898,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2095,7 +2104,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2504,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ7">
         <v>0.88</v>
@@ -2838,7 +2847,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -3044,7 +3053,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3122,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10">
         <v>0.78</v>
@@ -3250,7 +3259,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3331,7 +3340,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ11">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3743,7 +3752,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4280,7 +4289,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4564,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17">
         <v>1.5</v>
@@ -4692,7 +4701,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -4898,7 +4907,7 @@
         <v>105</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -5310,7 +5319,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5516,7 +5525,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -5597,7 +5606,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ22">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.18</v>
@@ -6310,7 +6319,7 @@
         <v>45760.66666666666</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="s">
         <v>78</v>
@@ -6340,7 +6349,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6418,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ26">
         <v>1.25</v>
@@ -6546,7 +6555,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6624,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ27">
         <v>1.5</v>
@@ -6752,7 +6761,7 @@
         <v>90</v>
       </c>
       <c r="P28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7370,7 +7379,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7657,7 +7666,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ32">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR32">
         <v>1.51</v>
@@ -7782,7 +7791,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7988,7 +7997,7 @@
         <v>90</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8194,7 +8203,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8478,7 +8487,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ36">
         <v>2.57</v>
@@ -8606,7 +8615,7 @@
         <v>90</v>
       </c>
       <c r="P37" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q37">
         <v>2.82</v>
@@ -8687,7 +8696,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR37">
         <v>0.99</v>
@@ -9096,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ39">
         <v>0</v>
@@ -9305,7 +9314,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR40">
         <v>2.4</v>
@@ -9508,7 +9517,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ41">
         <v>1.14</v>
@@ -9636,7 +9645,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10254,7 +10263,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10460,7 +10469,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q46">
         <v>2.81</v>
@@ -10538,7 +10547,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ46">
         <v>0.78</v>
@@ -10872,7 +10881,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -11078,7 +11087,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11568,10 +11577,10 @@
         <v>0.5</v>
       </c>
       <c r="AP51">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ51">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.54</v>
@@ -11774,7 +11783,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52">
         <v>0</v>
@@ -11902,7 +11911,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q53">
         <v>3.8</v>
@@ -11983,7 +11992,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR53">
         <v>1.85</v>
@@ -12108,7 +12117,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12601,7 +12610,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR56">
         <v>2.27</v>
@@ -12804,7 +12813,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ57">
         <v>0.78</v>
@@ -13216,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR59">
         <v>1.41</v>
@@ -13344,7 +13353,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13550,7 +13559,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -13834,7 +13843,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62">
         <v>0.5</v>
@@ -14374,7 +14383,7 @@
         <v>141</v>
       </c>
       <c r="P65" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q65">
         <v>2.95</v>
@@ -14658,7 +14667,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ66">
         <v>1.38</v>
@@ -14992,7 +15001,7 @@
         <v>90</v>
       </c>
       <c r="P68" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q68">
         <v>5.7</v>
@@ -15198,7 +15207,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15276,7 +15285,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ69">
         <v>1.86</v>
@@ -15610,7 +15619,7 @@
         <v>90</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15691,7 +15700,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR71">
         <v>1.79</v>
@@ -16022,7 +16031,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16228,7 +16237,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q74">
         <v>2.75</v>
@@ -16309,7 +16318,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR74">
         <v>1.47</v>
@@ -16434,7 +16443,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q75">
         <v>3.37</v>
@@ -16718,7 +16727,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ76">
         <v>1.14</v>
@@ -16846,7 +16855,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17258,7 +17267,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -17339,7 +17348,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR79">
         <v>2.54</v>
@@ -17751,7 +17760,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ81">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.87</v>
@@ -18288,7 +18297,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18366,7 +18375,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>0.63</v>
@@ -18494,7 +18503,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18575,7 +18584,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR85">
         <v>1.75</v>
@@ -18778,7 +18787,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ86">
         <v>0.5600000000000001</v>
@@ -19190,7 +19199,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ88">
         <v>1.38</v>
@@ -19318,7 +19327,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19602,10 +19611,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19808,7 +19817,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91">
         <v>1.25</v>
@@ -19936,7 +19945,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20017,7 +20026,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ92">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR92">
         <v>1.88</v>
@@ -20142,7 +20151,7 @@
         <v>90</v>
       </c>
       <c r="P93" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20220,7 +20229,7 @@
         <v>0.6</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ93">
         <v>1.25</v>
@@ -20966,7 +20975,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21172,7 +21181,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21378,7 +21387,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21868,7 +21877,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ101">
         <v>0.88</v>
@@ -21996,7 +22005,7 @@
         <v>90</v>
       </c>
       <c r="P102" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22408,7 +22417,7 @@
         <v>90</v>
       </c>
       <c r="P104" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q104">
         <v>3.4</v>
@@ -22614,7 +22623,7 @@
         <v>90</v>
       </c>
       <c r="P105" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q105">
         <v>3.5</v>
@@ -22898,7 +22907,7 @@
         <v>0.6</v>
       </c>
       <c r="AP106">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ106">
         <v>0.5</v>
@@ -23232,7 +23241,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23313,7 +23322,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR108">
         <v>1.34</v>
@@ -23516,7 +23525,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ109">
         <v>2.57</v>
@@ -23644,7 +23653,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23722,10 +23731,10 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR110">
         <v>2.29</v>
@@ -23931,7 +23940,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ111">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR111">
         <v>1.95</v>
@@ -24056,7 +24065,7 @@
         <v>90</v>
       </c>
       <c r="P112" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24468,7 +24477,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24880,7 +24889,7 @@
         <v>106</v>
       </c>
       <c r="P116" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -24958,10 +24967,10 @@
         <v>0</v>
       </c>
       <c r="AP116">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ116">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25262,7 +25271,7 @@
         <v>45850.6875</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G118" t="s">
         <v>85</v>
@@ -25370,7 +25379,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ118">
         <v>0.5600000000000001</v>
@@ -25391,16 +25400,16 @@
         <v>5</v>
       </c>
       <c r="AW118">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AX118">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY118">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AZ118">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA118">
         <v>2</v>
@@ -25468,7 +25477,7 @@
         <v>45850.6875</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G119" t="s">
         <v>75</v>
@@ -25576,7 +25585,7 @@
         <v>0.6</v>
       </c>
       <c r="AP119">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ119">
         <v>0.88</v>
@@ -25591,31 +25600,31 @@
         <v>3.26</v>
       </c>
       <c r="AU119">
+        <v>11</v>
+      </c>
+      <c r="AV119">
+        <v>0</v>
+      </c>
+      <c r="AW119">
+        <v>4</v>
+      </c>
+      <c r="AX119">
+        <v>4</v>
+      </c>
+      <c r="AY119">
+        <v>15</v>
+      </c>
+      <c r="AZ119">
+        <v>4</v>
+      </c>
+      <c r="BA119">
         <v>7</v>
       </c>
-      <c r="AV119">
-        <v>0</v>
-      </c>
-      <c r="AW119">
-        <v>11</v>
-      </c>
-      <c r="AX119">
-        <v>6</v>
-      </c>
-      <c r="AY119">
-        <v>18</v>
-      </c>
-      <c r="AZ119">
-        <v>6</v>
-      </c>
-      <c r="BA119">
-        <v>5</v>
-      </c>
       <c r="BB119">
         <v>1</v>
       </c>
       <c r="BC119">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD119">
         <v>1.24</v>
@@ -25674,7 +25683,7 @@
         <v>45850.77083333334</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G120" t="s">
         <v>77</v>
@@ -25704,7 +25713,7 @@
         <v>90</v>
       </c>
       <c r="P120" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25803,16 +25812,16 @@
         <v>7</v>
       </c>
       <c r="AW120">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX120">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AY120">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ120">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA120">
         <v>5</v>
@@ -25880,7 +25889,7 @@
         <v>45850.875</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G121" t="s">
         <v>78</v>
@@ -25988,10 +25997,10 @@
         <v>1.33</v>
       </c>
       <c r="AP121">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR121">
         <v>1.43</v>
@@ -26009,16 +26018,16 @@
         <v>3</v>
       </c>
       <c r="AW121">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX121">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY121">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ121">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA121">
         <v>4</v>
@@ -26086,7 +26095,7 @@
         <v>45851.79166666666</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G122" t="s">
         <v>81</v>
@@ -26116,7 +26125,7 @@
         <v>113</v>
       </c>
       <c r="P122" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26212,19 +26221,19 @@
         <v>9</v>
       </c>
       <c r="AV122">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW122">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX122">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY122">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ122">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA122">
         <v>10</v>
@@ -26292,7 +26301,7 @@
         <v>45851.85416666666</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" t="s">
         <v>71</v>
@@ -26400,7 +26409,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ123">
         <v>0.63</v>
@@ -26421,16 +26430,16 @@
         <v>3</v>
       </c>
       <c r="AW123">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX123">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY123">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ123">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA123">
         <v>6</v>
@@ -26498,7 +26507,7 @@
         <v>45851.85416666666</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G124" t="s">
         <v>73</v>
@@ -26528,7 +26537,7 @@
         <v>90</v>
       </c>
       <c r="P124" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q124">
         <v>3.17</v>
@@ -26609,7 +26618,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ124">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.81</v>
@@ -26627,13 +26636,13 @@
         <v>4</v>
       </c>
       <c r="AW124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX124">
         <v>8</v>
       </c>
       <c r="AY124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ124">
         <v>12</v>
@@ -26704,7 +26713,7 @@
         <v>45852.83333333334</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G125" t="s">
         <v>74</v>
@@ -26833,16 +26842,16 @@
         <v>6</v>
       </c>
       <c r="AW125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX125">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AY125">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ125">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BA125">
         <v>1</v>
@@ -26910,7 +26919,7 @@
         <v>45854.79166666666</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G126" t="s">
         <v>76</v>
@@ -26940,7 +26949,7 @@
         <v>95</v>
       </c>
       <c r="P126" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q126">
         <v>1.96</v>
@@ -27039,16 +27048,16 @@
         <v>2</v>
       </c>
       <c r="AW126">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY126">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ126">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA126">
         <v>7</v>
@@ -27116,7 +27125,7 @@
         <v>45854.8125</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s">
         <v>80</v>
@@ -27146,7 +27155,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27245,13 +27254,13 @@
         <v>3</v>
       </c>
       <c r="AW127">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AX127">
         <v>3</v>
       </c>
       <c r="AY127">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ127">
         <v>6</v>
@@ -27322,7 +27331,7 @@
         <v>45854.83333333334</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
         <v>89</v>
@@ -27451,16 +27460,16 @@
         <v>6</v>
       </c>
       <c r="AW128">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY128">
+        <v>7</v>
+      </c>
+      <c r="AZ128">
         <v>9</v>
-      </c>
-      <c r="AZ128">
-        <v>11</v>
       </c>
       <c r="BA128">
         <v>3</v>
@@ -27528,7 +27537,7 @@
         <v>45854.89583333334</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s">
         <v>79</v>
@@ -27558,7 +27567,7 @@
         <v>175</v>
       </c>
       <c r="P129" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q129">
         <v>2.84</v>
@@ -27645,10 +27654,10 @@
         <v>1.61</v>
       </c>
       <c r="AS129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AT129">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="AU129">
         <v>4</v>
@@ -27657,16 +27666,16 @@
         <v>6</v>
       </c>
       <c r="AW129">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AX129">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY129">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ129">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA129">
         <v>6</v>
@@ -27734,7 +27743,7 @@
         <v>45854.89583333334</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s">
         <v>82</v>
@@ -27851,10 +27860,10 @@
         <v>1.98</v>
       </c>
       <c r="AS130">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT130">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="AU130">
         <v>9</v>
@@ -27863,16 +27872,16 @@
         <v>2</v>
       </c>
       <c r="AW130">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AX130">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AY130">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ130">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA130">
         <v>6</v>
@@ -27940,7 +27949,7 @@
         <v>45855.8125</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s">
         <v>84</v>
@@ -27970,7 +27979,7 @@
         <v>90</v>
       </c>
       <c r="P131" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q131">
         <v>2.9</v>
@@ -28069,13 +28078,13 @@
         <v>6</v>
       </c>
       <c r="AW131">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AX131">
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ131">
         <v>9</v>
@@ -28146,7 +28155,7 @@
         <v>45857.66666666666</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G132" t="s">
         <v>73</v>
@@ -28176,7 +28185,7 @@
         <v>168</v>
       </c>
       <c r="P132" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q132">
         <v>3.3</v>
@@ -28260,13 +28269,13 @@
         <v>1.14</v>
       </c>
       <c r="AR132">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AS132">
         <v>1.38</v>
       </c>
       <c r="AT132">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="AU132">
         <v>3</v>
@@ -28275,16 +28284,16 @@
         <v>5</v>
       </c>
       <c r="AW132">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX132">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AY132">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ132">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA132">
         <v>9</v>
@@ -28352,7 +28361,7 @@
         <v>45857.72916666666</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G133" t="s">
         <v>77</v>
@@ -28382,7 +28391,7 @@
         <v>136</v>
       </c>
       <c r="P133" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q133">
         <v>2.82</v>
@@ -28466,13 +28475,13 @@
         <v>0.63</v>
       </c>
       <c r="AR133">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AS133">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AT133">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="AU133">
         <v>8</v>
@@ -28481,16 +28490,16 @@
         <v>5</v>
       </c>
       <c r="AW133">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AX133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY133">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AZ133">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA133">
         <v>12</v>
@@ -28558,7 +28567,7 @@
         <v>45857.77083333334</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G134" t="s">
         <v>88</v>
@@ -28681,22 +28690,22 @@
         <v>2.88</v>
       </c>
       <c r="AU134">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV134">
         <v>0</v>
       </c>
       <c r="AW134">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY134">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA134">
         <v>9</v>
@@ -28764,7 +28773,7 @@
         <v>45857.875</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G135" t="s">
         <v>70</v>
@@ -28872,7 +28881,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135">
         <v>0.78</v>
@@ -28893,16 +28902,16 @@
         <v>4</v>
       </c>
       <c r="AW135">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX135">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY135">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ135">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA135">
         <v>6</v>
@@ -29078,19 +29087,19 @@
         <v>0.83</v>
       </c>
       <c r="AP136">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ136">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AR136">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AS136">
         <v>1.25</v>
       </c>
       <c r="AT136">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="AU136">
         <v>5</v>
@@ -29284,19 +29293,19 @@
         <v>0</v>
       </c>
       <c r="AP137">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AQ137">
         <v>0</v>
       </c>
       <c r="AR137">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AS137">
         <v>0.85</v>
       </c>
       <c r="AT137">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AU137">
         <v>8</v>
@@ -29705,10 +29714,10 @@
         <v>1.75</v>
       </c>
       <c r="AS139">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AT139">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="AU139">
         <v>6</v>
@@ -29824,7 +29833,7 @@
         <v>181</v>
       </c>
       <c r="P140" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q140">
         <v>2.36</v>
@@ -29905,16 +29914,16 @@
         <v>1.75</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR140">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS140">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AT140">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="AU140">
         <v>8</v>
@@ -30108,19 +30117,19 @@
         <v>1.17</v>
       </c>
       <c r="AP141">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR141">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AS141">
         <v>1.22</v>
       </c>
       <c r="AT141">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AU141">
         <v>4</v>
@@ -30236,7 +30245,7 @@
         <v>183</v>
       </c>
       <c r="P142" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q142">
         <v>3.53</v>
@@ -30320,13 +30329,13 @@
         <v>2.57</v>
       </c>
       <c r="AR142">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AS142">
         <v>1.52</v>
       </c>
       <c r="AT142">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="AU142">
         <v>2</v>
@@ -30442,7 +30451,7 @@
         <v>90</v>
       </c>
       <c r="P143" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30526,13 +30535,13 @@
         <v>1.25</v>
       </c>
       <c r="AR143">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AS143">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AT143">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AU143">
         <v>9</v>
@@ -30732,13 +30741,13 @@
         <v>1.5</v>
       </c>
       <c r="AR144">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AS144">
         <v>1.51</v>
       </c>
       <c r="AT144">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="AU144">
         <v>5</v>
@@ -30854,7 +30863,7 @@
         <v>184</v>
       </c>
       <c r="P145" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q145">
         <v>3</v>
@@ -30941,10 +30950,10 @@
         <v>1.49</v>
       </c>
       <c r="AS145">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AT145">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AU145">
         <v>12</v>
@@ -31060,7 +31069,7 @@
         <v>185</v>
       </c>
       <c r="P146" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q146">
         <v>3.2</v>
@@ -31144,13 +31153,13 @@
         <v>0.88</v>
       </c>
       <c r="AR146">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AS146">
         <v>1.32</v>
       </c>
       <c r="AT146">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AU146">
         <v>8</v>
@@ -31266,7 +31275,7 @@
         <v>186</v>
       </c>
       <c r="P147" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q147">
         <v>4.8</v>
@@ -31350,13 +31359,13 @@
         <v>1.86</v>
       </c>
       <c r="AR147">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AS147">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AT147">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="AU147">
         <v>3</v>
@@ -31556,13 +31565,13 @@
         <v>0.88</v>
       </c>
       <c r="AR148">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AS148">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AT148">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="AU148">
         <v>0</v>
@@ -31678,7 +31687,7 @@
         <v>157</v>
       </c>
       <c r="P149" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q149">
         <v>2.3</v>
@@ -31762,13 +31771,13 @@
         <v>0.78</v>
       </c>
       <c r="AR149">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AS149">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AT149">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AU149">
         <v>4</v>
@@ -31884,7 +31893,7 @@
         <v>187</v>
       </c>
       <c r="P150" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q150">
         <v>2.3</v>
@@ -31968,13 +31977,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR150">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AS150">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AT150">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="AU150">
         <v>8</v>
@@ -32090,7 +32099,7 @@
         <v>188</v>
       </c>
       <c r="P151" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q151">
         <v>3.48</v>
@@ -32177,10 +32186,10 @@
         <v>1.71</v>
       </c>
       <c r="AS151">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AT151">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AU151">
         <v>5</v>
@@ -32380,13 +32389,13 @@
         <v>1.63</v>
       </c>
       <c r="AR152">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AS152">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AT152">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="AU152">
         <v>10</v>
@@ -32586,13 +32595,13 @@
         <v>0.63</v>
       </c>
       <c r="AR153">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AS153">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AT153">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="AU153">
         <v>4</v>
@@ -32659,6 +32668,1036 @@
       </c>
       <c r="BP153">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7834476</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45865.66666666666</v>
+      </c>
+      <c r="F154">
+        <v>17</v>
+      </c>
+      <c r="G154" t="s">
+        <v>71</v>
+      </c>
+      <c r="H154" t="s">
+        <v>80</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <v>2</v>
+      </c>
+      <c r="N154">
+        <v>3</v>
+      </c>
+      <c r="O154" t="s">
+        <v>133</v>
+      </c>
+      <c r="P154" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q154">
+        <v>1.93</v>
+      </c>
+      <c r="R154">
+        <v>2.15</v>
+      </c>
+      <c r="S154">
+        <v>7</v>
+      </c>
+      <c r="T154">
+        <v>1.43</v>
+      </c>
+      <c r="U154">
+        <v>2.54</v>
+      </c>
+      <c r="V154">
+        <v>3</v>
+      </c>
+      <c r="W154">
+        <v>1.33</v>
+      </c>
+      <c r="X154">
+        <v>7.5</v>
+      </c>
+      <c r="Y154">
+        <v>1.03</v>
+      </c>
+      <c r="Z154">
+        <v>1.34</v>
+      </c>
+      <c r="AA154">
+        <v>3.95</v>
+      </c>
+      <c r="AB154">
+        <v>8.1</v>
+      </c>
+      <c r="AC154">
+        <v>1.05</v>
+      </c>
+      <c r="AD154">
+        <v>7.75</v>
+      </c>
+      <c r="AE154">
+        <v>1.32</v>
+      </c>
+      <c r="AF154">
+        <v>2.88</v>
+      </c>
+      <c r="AG154">
+        <v>2.15</v>
+      </c>
+      <c r="AH154">
+        <v>1.65</v>
+      </c>
+      <c r="AI154">
+        <v>2.5</v>
+      </c>
+      <c r="AJ154">
+        <v>1.47</v>
+      </c>
+      <c r="AK154">
+        <v>1.22</v>
+      </c>
+      <c r="AL154">
+        <v>1.23</v>
+      </c>
+      <c r="AM154">
+        <v>2.7</v>
+      </c>
+      <c r="AN154">
+        <v>2.75</v>
+      </c>
+      <c r="AO154">
+        <v>0.71</v>
+      </c>
+      <c r="AP154">
+        <v>2.44</v>
+      </c>
+      <c r="AQ154">
+        <v>1</v>
+      </c>
+      <c r="AR154">
+        <v>1.73</v>
+      </c>
+      <c r="AS154">
+        <v>1.26</v>
+      </c>
+      <c r="AT154">
+        <v>2.99</v>
+      </c>
+      <c r="AU154">
+        <v>6</v>
+      </c>
+      <c r="AV154">
+        <v>4</v>
+      </c>
+      <c r="AW154">
+        <v>11</v>
+      </c>
+      <c r="AX154">
+        <v>6</v>
+      </c>
+      <c r="AY154">
+        <v>17</v>
+      </c>
+      <c r="AZ154">
+        <v>10</v>
+      </c>
+      <c r="BA154">
+        <v>10</v>
+      </c>
+      <c r="BB154">
+        <v>3</v>
+      </c>
+      <c r="BC154">
+        <v>13</v>
+      </c>
+      <c r="BD154">
+        <v>1.27</v>
+      </c>
+      <c r="BE154">
+        <v>10.25</v>
+      </c>
+      <c r="BF154">
+        <v>3.45</v>
+      </c>
+      <c r="BG154">
+        <v>1.25</v>
+      </c>
+      <c r="BH154">
+        <v>3.6</v>
+      </c>
+      <c r="BI154">
+        <v>1.42</v>
+      </c>
+      <c r="BJ154">
+        <v>2.62</v>
+      </c>
+      <c r="BK154">
+        <v>1.67</v>
+      </c>
+      <c r="BL154">
+        <v>2.25</v>
+      </c>
+      <c r="BM154">
+        <v>2.1</v>
+      </c>
+      <c r="BN154">
+        <v>1.67</v>
+      </c>
+      <c r="BO154">
+        <v>2.62</v>
+      </c>
+      <c r="BP154">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7834474</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45865.66666666666</v>
+      </c>
+      <c r="F155">
+        <v>17</v>
+      </c>
+      <c r="G155" t="s">
+        <v>70</v>
+      </c>
+      <c r="H155" t="s">
+        <v>84</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>3</v>
+      </c>
+      <c r="M155">
+        <v>1</v>
+      </c>
+      <c r="N155">
+        <v>4</v>
+      </c>
+      <c r="O155" t="s">
+        <v>191</v>
+      </c>
+      <c r="P155" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q155">
+        <v>3.14</v>
+      </c>
+      <c r="R155">
+        <v>1.92</v>
+      </c>
+      <c r="S155">
+        <v>4.1</v>
+      </c>
+      <c r="T155">
+        <v>1.66</v>
+      </c>
+      <c r="U155">
+        <v>2.29</v>
+      </c>
+      <c r="V155">
+        <v>3.68</v>
+      </c>
+      <c r="W155">
+        <v>1.23</v>
+      </c>
+      <c r="X155">
+        <v>11</v>
+      </c>
+      <c r="Y155">
+        <v>1.02</v>
+      </c>
+      <c r="Z155">
+        <v>2.27</v>
+      </c>
+      <c r="AA155">
+        <v>3</v>
+      </c>
+      <c r="AB155">
+        <v>3.5</v>
+      </c>
+      <c r="AC155">
+        <v>1.08</v>
+      </c>
+      <c r="AD155">
+        <v>6.2</v>
+      </c>
+      <c r="AE155">
+        <v>1.63</v>
+      </c>
+      <c r="AF155">
+        <v>2.25</v>
+      </c>
+      <c r="AG155">
+        <v>2.7</v>
+      </c>
+      <c r="AH155">
+        <v>1.4</v>
+      </c>
+      <c r="AI155">
+        <v>2.27</v>
+      </c>
+      <c r="AJ155">
+        <v>1.55</v>
+      </c>
+      <c r="AK155">
+        <v>1.4</v>
+      </c>
+      <c r="AL155">
+        <v>1.33</v>
+      </c>
+      <c r="AM155">
+        <v>1.62</v>
+      </c>
+      <c r="AN155">
+        <v>1.5</v>
+      </c>
+      <c r="AO155">
+        <v>1</v>
+      </c>
+      <c r="AP155">
+        <v>1.67</v>
+      </c>
+      <c r="AQ155">
+        <v>0.88</v>
+      </c>
+      <c r="AR155">
+        <v>1.42</v>
+      </c>
+      <c r="AS155">
+        <v>1.15</v>
+      </c>
+      <c r="AT155">
+        <v>2.57</v>
+      </c>
+      <c r="AU155">
+        <v>10</v>
+      </c>
+      <c r="AV155">
+        <v>2</v>
+      </c>
+      <c r="AW155">
+        <v>6</v>
+      </c>
+      <c r="AX155">
+        <v>6</v>
+      </c>
+      <c r="AY155">
+        <v>16</v>
+      </c>
+      <c r="AZ155">
+        <v>8</v>
+      </c>
+      <c r="BA155">
+        <v>7</v>
+      </c>
+      <c r="BB155">
+        <v>3</v>
+      </c>
+      <c r="BC155">
+        <v>10</v>
+      </c>
+      <c r="BD155">
+        <v>1.67</v>
+      </c>
+      <c r="BE155">
+        <v>6.5</v>
+      </c>
+      <c r="BF155">
+        <v>2.38</v>
+      </c>
+      <c r="BG155">
+        <v>1.24</v>
+      </c>
+      <c r="BH155">
+        <v>3.22</v>
+      </c>
+      <c r="BI155">
+        <v>1.52</v>
+      </c>
+      <c r="BJ155">
+        <v>2.37</v>
+      </c>
+      <c r="BK155">
+        <v>1.8</v>
+      </c>
+      <c r="BL155">
+        <v>1.83</v>
+      </c>
+      <c r="BM155">
+        <v>2.34</v>
+      </c>
+      <c r="BN155">
+        <v>1.55</v>
+      </c>
+      <c r="BO155">
+        <v>3.15</v>
+      </c>
+      <c r="BP155">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7834477</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45865.77083333334</v>
+      </c>
+      <c r="F156">
+        <v>17</v>
+      </c>
+      <c r="G156" t="s">
+        <v>85</v>
+      </c>
+      <c r="H156" t="s">
+        <v>77</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>2</v>
+      </c>
+      <c r="O156" t="s">
+        <v>185</v>
+      </c>
+      <c r="P156" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q156">
+        <v>2.1</v>
+      </c>
+      <c r="R156">
+        <v>2.23</v>
+      </c>
+      <c r="S156">
+        <v>5.8</v>
+      </c>
+      <c r="T156">
+        <v>1.38</v>
+      </c>
+      <c r="U156">
+        <v>3.15</v>
+      </c>
+      <c r="V156">
+        <v>2.95</v>
+      </c>
+      <c r="W156">
+        <v>1.42</v>
+      </c>
+      <c r="X156">
+        <v>6.75</v>
+      </c>
+      <c r="Y156">
+        <v>1.05</v>
+      </c>
+      <c r="Z156">
+        <v>1.55</v>
+      </c>
+      <c r="AA156">
+        <v>3.7</v>
+      </c>
+      <c r="AB156">
+        <v>5.75</v>
+      </c>
+      <c r="AC156">
+        <v>1.02</v>
+      </c>
+      <c r="AD156">
+        <v>9.5</v>
+      </c>
+      <c r="AE156">
+        <v>1.32</v>
+      </c>
+      <c r="AF156">
+        <v>3.4</v>
+      </c>
+      <c r="AG156">
+        <v>1.93</v>
+      </c>
+      <c r="AH156">
+        <v>1.85</v>
+      </c>
+      <c r="AI156">
+        <v>1.83</v>
+      </c>
+      <c r="AJ156">
+        <v>1.85</v>
+      </c>
+      <c r="AK156">
+        <v>1.11</v>
+      </c>
+      <c r="AL156">
+        <v>1.26</v>
+      </c>
+      <c r="AM156">
+        <v>2.3</v>
+      </c>
+      <c r="AN156">
+        <v>1.86</v>
+      </c>
+      <c r="AO156">
+        <v>0.5</v>
+      </c>
+      <c r="AP156">
+        <v>1.75</v>
+      </c>
+      <c r="AQ156">
+        <v>0.57</v>
+      </c>
+      <c r="AR156">
+        <v>2</v>
+      </c>
+      <c r="AS156">
+        <v>1.55</v>
+      </c>
+      <c r="AT156">
+        <v>3.55</v>
+      </c>
+      <c r="AU156">
+        <v>9</v>
+      </c>
+      <c r="AV156">
+        <v>6</v>
+      </c>
+      <c r="AW156">
+        <v>19</v>
+      </c>
+      <c r="AX156">
+        <v>10</v>
+      </c>
+      <c r="AY156">
+        <v>28</v>
+      </c>
+      <c r="AZ156">
+        <v>16</v>
+      </c>
+      <c r="BA156">
+        <v>10</v>
+      </c>
+      <c r="BB156">
+        <v>5</v>
+      </c>
+      <c r="BC156">
+        <v>15</v>
+      </c>
+      <c r="BD156">
+        <v>1.44</v>
+      </c>
+      <c r="BE156">
+        <v>7.25</v>
+      </c>
+      <c r="BF156">
+        <v>3.3</v>
+      </c>
+      <c r="BG156">
+        <v>1.24</v>
+      </c>
+      <c r="BH156">
+        <v>3.6</v>
+      </c>
+      <c r="BI156">
+        <v>1.44</v>
+      </c>
+      <c r="BJ156">
+        <v>2.5</v>
+      </c>
+      <c r="BK156">
+        <v>1.83</v>
+      </c>
+      <c r="BL156">
+        <v>1.85</v>
+      </c>
+      <c r="BM156">
+        <v>2.28</v>
+      </c>
+      <c r="BN156">
+        <v>1.65</v>
+      </c>
+      <c r="BO156">
+        <v>2.65</v>
+      </c>
+      <c r="BP156">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7834478</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45865.77083333334</v>
+      </c>
+      <c r="F157">
+        <v>17</v>
+      </c>
+      <c r="G157" t="s">
+        <v>78</v>
+      </c>
+      <c r="H157" t="s">
+        <v>74</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157">
+        <v>3</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>192</v>
+      </c>
+      <c r="P157" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q157">
+        <v>1.71</v>
+      </c>
+      <c r="R157">
+        <v>2.55</v>
+      </c>
+      <c r="S157">
+        <v>7.5</v>
+      </c>
+      <c r="T157">
+        <v>1.3</v>
+      </c>
+      <c r="U157">
+        <v>3.25</v>
+      </c>
+      <c r="V157">
+        <v>2.45</v>
+      </c>
+      <c r="W157">
+        <v>1.5</v>
+      </c>
+      <c r="X157">
+        <v>5.25</v>
+      </c>
+      <c r="Y157">
+        <v>1.12</v>
+      </c>
+      <c r="Z157">
+        <v>1.29</v>
+      </c>
+      <c r="AA157">
+        <v>5.75</v>
+      </c>
+      <c r="AB157">
+        <v>9.75</v>
+      </c>
+      <c r="AC157">
+        <v>1.03</v>
+      </c>
+      <c r="AD157">
+        <v>12.5</v>
+      </c>
+      <c r="AE157">
+        <v>1.16</v>
+      </c>
+      <c r="AF157">
+        <v>4.25</v>
+      </c>
+      <c r="AG157">
+        <v>1.76</v>
+      </c>
+      <c r="AH157">
+        <v>2.15</v>
+      </c>
+      <c r="AI157">
+        <v>2.23</v>
+      </c>
+      <c r="AJ157">
+        <v>1.61</v>
+      </c>
+      <c r="AK157">
+        <v>1.17</v>
+      </c>
+      <c r="AL157">
+        <v>1.21</v>
+      </c>
+      <c r="AM157">
+        <v>3.53</v>
+      </c>
+      <c r="AN157">
+        <v>2.43</v>
+      </c>
+      <c r="AO157">
+        <v>0</v>
+      </c>
+      <c r="AP157">
+        <v>2.5</v>
+      </c>
+      <c r="AQ157">
+        <v>0</v>
+      </c>
+      <c r="AR157">
+        <v>1.49</v>
+      </c>
+      <c r="AS157">
+        <v>0.83</v>
+      </c>
+      <c r="AT157">
+        <v>2.32</v>
+      </c>
+      <c r="AU157">
+        <v>9</v>
+      </c>
+      <c r="AV157">
+        <v>0</v>
+      </c>
+      <c r="AW157">
+        <v>9</v>
+      </c>
+      <c r="AX157">
+        <v>4</v>
+      </c>
+      <c r="AY157">
+        <v>18</v>
+      </c>
+      <c r="AZ157">
+        <v>4</v>
+      </c>
+      <c r="BA157">
+        <v>2</v>
+      </c>
+      <c r="BB157">
+        <v>1</v>
+      </c>
+      <c r="BC157">
+        <v>3</v>
+      </c>
+      <c r="BD157">
+        <v>1.17</v>
+      </c>
+      <c r="BE157">
+        <v>8.5</v>
+      </c>
+      <c r="BF157">
+        <v>6</v>
+      </c>
+      <c r="BG157">
+        <v>1.25</v>
+      </c>
+      <c r="BH157">
+        <v>3.75</v>
+      </c>
+      <c r="BI157">
+        <v>1.36</v>
+      </c>
+      <c r="BJ157">
+        <v>2.79</v>
+      </c>
+      <c r="BK157">
+        <v>1.67</v>
+      </c>
+      <c r="BL157">
+        <v>2.1</v>
+      </c>
+      <c r="BM157">
+        <v>2.1</v>
+      </c>
+      <c r="BN157">
+        <v>1.66</v>
+      </c>
+      <c r="BO157">
+        <v>2.6</v>
+      </c>
+      <c r="BP157">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7834471</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45865.85416666666</v>
+      </c>
+      <c r="F158">
+        <v>17</v>
+      </c>
+      <c r="G158" t="s">
+        <v>75</v>
+      </c>
+      <c r="H158" t="s">
+        <v>83</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>1</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>1</v>
+      </c>
+      <c r="O158" t="s">
+        <v>193</v>
+      </c>
+      <c r="P158" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q158">
+        <v>2</v>
+      </c>
+      <c r="R158">
+        <v>2.2</v>
+      </c>
+      <c r="S158">
+        <v>7.5</v>
+      </c>
+      <c r="T158">
+        <v>1.46</v>
+      </c>
+      <c r="U158">
+        <v>2.7</v>
+      </c>
+      <c r="V158">
+        <v>3.05</v>
+      </c>
+      <c r="W158">
+        <v>1.35</v>
+      </c>
+      <c r="X158">
+        <v>6.75</v>
+      </c>
+      <c r="Y158">
+        <v>1.05</v>
+      </c>
+      <c r="Z158">
+        <v>1.61</v>
+      </c>
+      <c r="AA158">
+        <v>3.39</v>
+      </c>
+      <c r="AB158">
+        <v>4.9</v>
+      </c>
+      <c r="AC158">
+        <v>1.06</v>
+      </c>
+      <c r="AD158">
+        <v>7.5</v>
+      </c>
+      <c r="AE158">
+        <v>1.37</v>
+      </c>
+      <c r="AF158">
+        <v>2.85</v>
+      </c>
+      <c r="AG158">
+        <v>2.13</v>
+      </c>
+      <c r="AH158">
+        <v>1.63</v>
+      </c>
+      <c r="AI158">
+        <v>2.4</v>
+      </c>
+      <c r="AJ158">
+        <v>1.56</v>
+      </c>
+      <c r="AK158">
+        <v>1.1</v>
+      </c>
+      <c r="AL158">
+        <v>1.22</v>
+      </c>
+      <c r="AM158">
+        <v>2.55</v>
+      </c>
+      <c r="AN158">
+        <v>2.5</v>
+      </c>
+      <c r="AO158">
+        <v>1</v>
+      </c>
+      <c r="AP158">
+        <v>2.56</v>
+      </c>
+      <c r="AQ158">
+        <v>0.89</v>
+      </c>
+      <c r="AR158">
+        <v>1.9</v>
+      </c>
+      <c r="AS158">
+        <v>1.65</v>
+      </c>
+      <c r="AT158">
+        <v>3.55</v>
+      </c>
+      <c r="AU158">
+        <v>7</v>
+      </c>
+      <c r="AV158">
+        <v>6</v>
+      </c>
+      <c r="AW158">
+        <v>10</v>
+      </c>
+      <c r="AX158">
+        <v>8</v>
+      </c>
+      <c r="AY158">
+        <v>17</v>
+      </c>
+      <c r="AZ158">
+        <v>14</v>
+      </c>
+      <c r="BA158">
+        <v>5</v>
+      </c>
+      <c r="BB158">
+        <v>7</v>
+      </c>
+      <c r="BC158">
+        <v>12</v>
+      </c>
+      <c r="BD158">
+        <v>1.27</v>
+      </c>
+      <c r="BE158">
+        <v>13</v>
+      </c>
+      <c r="BF158">
+        <v>5.85</v>
+      </c>
+      <c r="BG158">
+        <v>1.26</v>
+      </c>
+      <c r="BH158">
+        <v>3.2</v>
+      </c>
+      <c r="BI158">
+        <v>1.55</v>
+      </c>
+      <c r="BJ158">
+        <v>2.39</v>
+      </c>
+      <c r="BK158">
+        <v>1.8</v>
+      </c>
+      <c r="BL158">
+        <v>1.85</v>
+      </c>
+      <c r="BM158">
+        <v>2.3</v>
+      </c>
+      <c r="BN158">
+        <v>1.55</v>
+      </c>
+      <c r="BO158">
+        <v>3.25</v>
+      </c>
+      <c r="BP158">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP158"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.89</v>
@@ -4838,7 +4838,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.86</v>
@@ -8762,7 +8762,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR38" t="n">
         <v>0.79</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.88</v>
@@ -12468,7 +12468,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR55" t="n">
         <v>1.78</v>
@@ -13994,7 +13994,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR62" t="n">
         <v>1.28</v>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.78</v>
@@ -16825,7 +16825,7 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.63</v>
@@ -18572,7 +18572,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR83" t="n">
         <v>1.28</v>
@@ -21185,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.14</v>
@@ -23586,7 +23586,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR106" t="n">
         <v>1.87</v>
@@ -25545,7 +25545,7 @@
         <v>0.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.78</v>
@@ -34998,6 +34998,224 @@
       </c>
       <c r="BP158" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>7834447</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45867.85416666666</v>
+      </c>
+      <c r="F159" t="n">
+        <v>14</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>2</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" t="n">
+        <v>3</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>3</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>['12', '17']</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S159" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V159" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X159" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -35158,16 +35158,16 @@
         <v>4</v>
       </c>
       <c r="AW159" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX159" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY159" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ159" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA159" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
@@ -938,10 +938,10 @@
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
         <v>6</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
@@ -1156,10 +1156,10 @@
         <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
         <v>2</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW4" t="n">
         <v>7</v>
@@ -1374,10 +1374,10 @@
         <v>15</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
         <v>1</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>2</v>
@@ -1592,10 +1592,10 @@
         <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
         <v>5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6</v>
       </c>
       <c r="AW6" t="n">
         <v>5</v>
@@ -1810,10 +1810,10 @@
         <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
         <v>3</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
         <v>12</v>
@@ -2028,10 +2028,10 @@
         <v>2</v>
       </c>
       <c r="AY7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
         <v>4</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
         <v>10</v>
@@ -2246,10 +2246,10 @@
         <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>7</v>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
         <v>2</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
         <v>9</v>
@@ -2682,10 +2682,10 @@
         <v>5</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA10" t="n">
         <v>3</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="n">
         <v>11</v>
@@ -2900,10 +2900,10 @@
         <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
         <v>9</v>
@@ -3094,7 +3094,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW12" t="n">
         <v>6</v>
@@ -3118,10 +3118,10 @@
         <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>3</v>
@@ -3312,7 +3312,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3324,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
         <v>3</v>
@@ -3336,10 +3336,10 @@
         <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
         <v>1</v>
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW14" t="n">
         <v>10</v>
@@ -3554,10 +3554,10 @@
         <v>12</v>
       </c>
       <c r="AY14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
         <v>3</v>
@@ -3760,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
         <v>19</v>
@@ -3772,10 +3772,10 @@
         <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA15" t="n">
         <v>12</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.63</v>
@@ -3978,10 +3978,10 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
         <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>6</v>
@@ -4196,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
         <v>13</v>
@@ -4208,10 +4208,10 @@
         <v>5</v>
       </c>
       <c r="AY17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA17" t="n">
         <v>9</v>
@@ -4414,10 +4414,10 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
         <v>2</v>
@@ -4426,10 +4426,10 @@
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
         <v>2</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>2.57</v>
@@ -4632,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW19" t="n">
         <v>7</v>
@@ -4644,10 +4644,10 @@
         <v>3</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA19" t="n">
         <v>6</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.43</v>
@@ -4850,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
         <v>15</v>
@@ -4862,10 +4862,10 @@
         <v>4</v>
       </c>
       <c r="AY20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
         <v>8</v>
@@ -5056,7 +5056,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5068,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW21" t="n">
         <v>15</v>
@@ -5080,10 +5080,10 @@
         <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
         <v>9</v>
@@ -5277,19 +5277,19 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW22" t="n">
         <v>14</v>
@@ -5298,10 +5298,10 @@
         <v>7</v>
       </c>
       <c r="AY22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA22" t="n">
         <v>4</v>
@@ -5495,19 +5495,19 @@
         <v>1.38</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="AU23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW23" t="n">
         <v>6</v>
@@ -5516,10 +5516,10 @@
         <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>3</v>
@@ -5713,19 +5713,19 @@
         <v>0.78</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW24" t="n">
         <v>8</v>
@@ -5734,10 +5734,10 @@
         <v>7</v>
       </c>
       <c r="AY24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>1</v>
@@ -5931,19 +5931,19 @@
         <v>0.25</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW25" t="n">
         <v>4</v>
@@ -5952,10 +5952,10 @@
         <v>16</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA25" t="n">
         <v>1</v>
@@ -6149,19 +6149,19 @@
         <v>1.25</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AU26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV26" t="n">
         <v>3</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>4</v>
       </c>
       <c r="AW26" t="n">
         <v>7</v>
@@ -6170,10 +6170,10 @@
         <v>2</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA26" t="n">
         <v>10</v>
@@ -6367,19 +6367,19 @@
         <v>1.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.74</v>
+        <v>0.61</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AU27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW27" t="n">
         <v>9</v>
@@ -6388,10 +6388,10 @@
         <v>12</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -6585,19 +6585,19 @@
         <v>1.86</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="AU28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
         <v>8</v>
@@ -6606,10 +6606,10 @@
         <v>4</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
         <v>3</v>
@@ -6797,25 +6797,25 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.78</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW29" t="n">
         <v>9</v>
@@ -6824,10 +6824,10 @@
         <v>3</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
         <v>3</v>
@@ -7021,16 +7021,16 @@
         <v>0.88</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="n">
         <v>0</v>
@@ -7039,13 +7039,13 @@
         <v>9</v>
       </c>
       <c r="AX30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA30" t="n">
         <v>5</v>
@@ -7239,19 +7239,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.17</v>
+        <v>3.91</v>
       </c>
       <c r="AU31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW31" t="n">
         <v>23</v>
@@ -7260,10 +7260,10 @@
         <v>5</v>
       </c>
       <c r="AY31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AZ31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA31" t="n">
         <v>16</v>
@@ -7454,22 +7454,22 @@
         <v>1.63</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV32" t="n">
         <v>3</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>4</v>
       </c>
       <c r="AW32" t="n">
         <v>9</v>
@@ -7478,10 +7478,10 @@
         <v>8</v>
       </c>
       <c r="AY32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA32" t="n">
         <v>1</v>
@@ -7675,19 +7675,19 @@
         <v>0.88</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AU33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW33" t="n">
         <v>14</v>
@@ -7696,10 +7696,10 @@
         <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA33" t="n">
         <v>9</v>
@@ -7887,25 +7887,25 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.63</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AU34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV34" t="n">
         <v>7</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>8</v>
       </c>
       <c r="AW34" t="n">
         <v>15</v>
@@ -7914,10 +7914,10 @@
         <v>9</v>
       </c>
       <c r="AY34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
         <v>9</v>
@@ -8105,25 +8105,25 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.79</v>
+        <v>3.53</v>
       </c>
       <c r="AU35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW35" t="n">
         <v>5</v>
@@ -8132,10 +8132,10 @@
         <v>10</v>
       </c>
       <c r="AY35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA35" t="n">
         <v>2</v>
@@ -8329,19 +8329,19 @@
         <v>2.57</v>
       </c>
       <c r="AR36" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.07</v>
+        <v>3.81</v>
       </c>
       <c r="AU36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW36" t="n">
         <v>9</v>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="AY36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>13</v>
       </c>
       <c r="BA36" t="n">
         <v>1</v>
@@ -8547,19 +8547,19 @@
         <v>0.88</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AU37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW37" t="n">
         <v>8</v>
@@ -8568,10 +8568,10 @@
         <v>4</v>
       </c>
       <c r="AY37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA37" t="n">
         <v>7</v>
@@ -8765,19 +8765,19 @@
         <v>0.43</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AU38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW38" t="n">
         <v>7</v>
@@ -8786,10 +8786,10 @@
         <v>5</v>
       </c>
       <c r="AY38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA38" t="n">
         <v>5</v>
@@ -8983,19 +8983,19 @@
         <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW39" t="n">
         <v>10</v>
@@ -9004,10 +9004,10 @@
         <v>3</v>
       </c>
       <c r="AY39" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA39" t="n">
         <v>6</v>
@@ -9201,19 +9201,19 @@
         <v>0.89</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.84</v>
+        <v>4.56</v>
       </c>
       <c r="AU40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
         <v>6</v>
@@ -9222,10 +9222,10 @@
         <v>12</v>
       </c>
       <c r="AY40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA40" t="n">
         <v>3</v>
@@ -9416,22 +9416,22 @@
         <v>2.44</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AU41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW41" t="n">
         <v>7</v>
@@ -9440,10 +9440,10 @@
         <v>6</v>
       </c>
       <c r="AY41" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA41" t="n">
         <v>4</v>
@@ -9637,19 +9637,19 @@
         <v>0.25</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AU42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW42" t="n">
         <v>13</v>
@@ -9658,10 +9658,10 @@
         <v>8</v>
       </c>
       <c r="AY42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA42" t="n">
         <v>5</v>
@@ -9855,19 +9855,19 @@
         <v>1.86</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW43" t="n">
         <v>5</v>
@@ -9876,10 +9876,10 @@
         <v>10</v>
       </c>
       <c r="AY43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA43" t="n">
         <v>2</v>
@@ -10073,19 +10073,19 @@
         <v>0.88</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AU44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW44" t="n">
         <v>6</v>
@@ -10094,10 +10094,10 @@
         <v>9</v>
       </c>
       <c r="AY44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA44" t="n">
         <v>3</v>
@@ -10291,19 +10291,19 @@
         <v>1.25</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AU45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW45" t="n">
         <v>15</v>
@@ -10312,10 +10312,10 @@
         <v>19</v>
       </c>
       <c r="AY45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA45" t="n">
         <v>5</v>
@@ -10509,19 +10509,19 @@
         <v>0.78</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="AU46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW46" t="n">
         <v>3</v>
@@ -10530,10 +10530,10 @@
         <v>12</v>
       </c>
       <c r="AY46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA46" t="n">
         <v>5</v>
@@ -10727,19 +10727,19 @@
         <v>1.38</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT47" t="n">
-        <v>4.43</v>
+        <v>4.16</v>
       </c>
       <c r="AU47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW47" t="n">
         <v>7</v>
@@ -10748,10 +10748,10 @@
         <v>5</v>
       </c>
       <c r="AY47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA47" t="n">
         <v>8</v>
@@ -10945,19 +10945,19 @@
         <v>2.57</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AU48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW48" t="n">
         <v>7</v>
@@ -10966,10 +10966,10 @@
         <v>2</v>
       </c>
       <c r="AY48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA48" t="n">
         <v>8</v>
@@ -11157,25 +11157,25 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW49" t="n">
         <v>6</v>
@@ -11184,10 +11184,10 @@
         <v>4</v>
       </c>
       <c r="AY49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA49" t="n">
         <v>6</v>
@@ -11381,19 +11381,19 @@
         <v>1.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AU50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW50" t="n">
         <v>13</v>
@@ -11402,10 +11402,10 @@
         <v>8</v>
       </c>
       <c r="AY50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA50" t="n">
         <v>4</v>
@@ -11599,19 +11599,19 @@
         <v>1</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="AU51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW51" t="n">
         <v>9</v>
@@ -11620,10 +11620,10 @@
         <v>8</v>
       </c>
       <c r="AY51" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA51" t="n">
         <v>3</v>
@@ -11817,19 +11817,19 @@
         <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.04</v>
+        <v>0.9</v>
       </c>
       <c r="AT52" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AU52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW52" t="n">
         <v>6</v>
@@ -11838,10 +11838,10 @@
         <v>3</v>
       </c>
       <c r="AY52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA52" t="n">
         <v>9</v>
@@ -12029,25 +12029,25 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.89</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AT53" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AU53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW53" t="n">
         <v>14</v>
@@ -12056,10 +12056,10 @@
         <v>11</v>
       </c>
       <c r="AY53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA53" t="n">
         <v>9</v>
@@ -12253,19 +12253,19 @@
         <v>0.88</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW54" t="n">
         <v>5</v>
@@ -12274,10 +12274,10 @@
         <v>10</v>
       </c>
       <c r="AY54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA54" t="n">
         <v>3</v>
@@ -12465,25 +12465,25 @@
         <v>0.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.43</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW55" t="n">
         <v>8</v>
@@ -12492,10 +12492,10 @@
         <v>9</v>
       </c>
       <c r="AY55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA55" t="n">
         <v>6</v>
@@ -12689,19 +12689,19 @@
         <v>0.88</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.63</v>
+        <v>3.35</v>
       </c>
       <c r="AU56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW56" t="n">
         <v>8</v>
@@ -12710,10 +12710,10 @@
         <v>7</v>
       </c>
       <c r="AY56" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA56" t="n">
         <v>6</v>
@@ -12907,19 +12907,19 @@
         <v>0.78</v>
       </c>
       <c r="AR57" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="AU57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW57" t="n">
         <v>11</v>
@@ -12928,10 +12928,10 @@
         <v>6</v>
       </c>
       <c r="AY57" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA57" t="n">
         <v>10</v>
@@ -13122,22 +13122,22 @@
         <v>1.75</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AU58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW58" t="n">
         <v>19</v>
@@ -13146,10 +13146,10 @@
         <v>6</v>
       </c>
       <c r="AY58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA58" t="n">
         <v>6</v>
@@ -13340,22 +13340,22 @@
         <v>2.44</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AU59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW59" t="n">
         <v>8</v>
@@ -13364,10 +13364,10 @@
         <v>10</v>
       </c>
       <c r="AY59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA59" t="n">
         <v>4</v>
@@ -13558,22 +13558,22 @@
         <v>1.5</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW60" t="n">
         <v>11</v>
@@ -13582,10 +13582,10 @@
         <v>4</v>
       </c>
       <c r="AY60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA60" t="n">
         <v>6</v>
@@ -13779,19 +13779,19 @@
         <v>1.63</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="AU61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW61" t="n">
         <v>16</v>
@@ -13800,10 +13800,10 @@
         <v>10</v>
       </c>
       <c r="AY61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ61" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA61" t="n">
         <v>6</v>
@@ -13997,19 +13997,19 @@
         <v>0.43</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="AU62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW62" t="n">
         <v>10</v>
@@ -14018,10 +14018,10 @@
         <v>16</v>
       </c>
       <c r="AY62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ62" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA62" t="n">
         <v>5</v>
@@ -14209,25 +14209,25 @@
         <v>0.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.25</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW63" t="n">
         <v>12</v>
@@ -14236,10 +14236,10 @@
         <v>6</v>
       </c>
       <c r="AY63" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA63" t="n">
         <v>10</v>
@@ -14433,19 +14433,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="AU64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW64" t="n">
         <v>10</v>
@@ -14454,10 +14454,10 @@
         <v>9</v>
       </c>
       <c r="AY64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ64" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA64" t="n">
         <v>3</v>
@@ -14651,19 +14651,19 @@
         <v>0.88</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.03</v>
+        <v>0.93</v>
       </c>
       <c r="AT65" t="n">
-        <v>2.39</v>
+        <v>2.16</v>
       </c>
       <c r="AU65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW65" t="n">
         <v>14</v>
@@ -14672,10 +14672,10 @@
         <v>4</v>
       </c>
       <c r="AY65" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA65" t="n">
         <v>3</v>
@@ -14869,19 +14869,19 @@
         <v>1.38</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="AU66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW66" t="n">
         <v>7</v>
@@ -14890,10 +14890,10 @@
         <v>12</v>
       </c>
       <c r="AY66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA66" t="n">
         <v>3</v>
@@ -15087,19 +15087,19 @@
         <v>0.78</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT67" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AU67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW67" t="n">
         <v>4</v>
@@ -15108,10 +15108,10 @@
         <v>12</v>
       </c>
       <c r="AY67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ67" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA67" t="n">
         <v>3</v>
@@ -15305,19 +15305,19 @@
         <v>2.57</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="AU68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW68" t="n">
         <v>7</v>
@@ -15326,10 +15326,10 @@
         <v>14</v>
       </c>
       <c r="AY68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ68" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA68" t="n">
         <v>7</v>
@@ -15523,19 +15523,19 @@
         <v>1.86</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AT69" t="n">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="AU69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW69" t="n">
         <v>7</v>
@@ -15544,10 +15544,10 @@
         <v>2</v>
       </c>
       <c r="AY69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA69" t="n">
         <v>6</v>
@@ -15741,19 +15741,19 @@
         <v>1.25</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.65</v>
+        <v>3.39</v>
       </c>
       <c r="AU70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW70" t="n">
         <v>11</v>
@@ -15762,10 +15762,10 @@
         <v>9</v>
       </c>
       <c r="AY70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA70" t="n">
         <v>4</v>
@@ -15959,19 +15959,19 @@
         <v>0.89</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS71" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AT71" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="AU71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW71" t="n">
         <v>9</v>
@@ -15980,10 +15980,10 @@
         <v>22</v>
       </c>
       <c r="AY71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ71" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BA71" t="n">
         <v>3</v>
@@ -16177,19 +16177,19 @@
         <v>0</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS72" t="n">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="AU72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW72" t="n">
         <v>7</v>
@@ -16198,10 +16198,10 @@
         <v>3</v>
       </c>
       <c r="AY72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA72" t="n">
         <v>5</v>
@@ -16389,25 +16389,25 @@
         <v>0.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.78</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AU73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW73" t="n">
         <v>8</v>
@@ -16416,10 +16416,10 @@
         <v>7</v>
       </c>
       <c r="AY73" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA73" t="n">
         <v>4</v>
@@ -16610,22 +16610,22 @@
         <v>1.5</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="AU74" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV74" t="n">
         <v>5</v>
-      </c>
-      <c r="AV74" t="n">
-        <v>6</v>
       </c>
       <c r="AW74" t="n">
         <v>8</v>
@@ -16634,10 +16634,10 @@
         <v>12</v>
       </c>
       <c r="AY74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ74" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA74" t="n">
         <v>6</v>
@@ -16831,19 +16831,19 @@
         <v>1.63</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AT75" t="n">
-        <v>3.03</v>
+        <v>2.76</v>
       </c>
       <c r="AU75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW75" t="n">
         <v>13</v>
@@ -16852,10 +16852,10 @@
         <v>8</v>
       </c>
       <c r="AY75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA75" t="n">
         <v>6</v>
@@ -17046,22 +17046,22 @@
         <v>2.56</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT76" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW76" t="n">
         <v>11</v>
@@ -17070,10 +17070,10 @@
         <v>4</v>
       </c>
       <c r="AY76" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA76" t="n">
         <v>8</v>
@@ -17261,25 +17261,25 @@
         <v>0.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.5</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AT77" t="n">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="AU77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW77" t="n">
         <v>7</v>
@@ -17288,10 +17288,10 @@
         <v>11</v>
       </c>
       <c r="AY77" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ77" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA77" t="n">
         <v>7</v>
@@ -17485,19 +17485,19 @@
         <v>0.88</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT78" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AU78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW78" t="n">
         <v>13</v>
@@ -17506,10 +17506,10 @@
         <v>2</v>
       </c>
       <c r="AY78" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA78" t="n">
         <v>10</v>
@@ -17703,19 +17703,19 @@
         <v>0.88</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT79" t="n">
-        <v>3.77</v>
+        <v>3.51</v>
       </c>
       <c r="AU79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW79" t="n">
         <v>9</v>
@@ -17724,10 +17724,10 @@
         <v>3</v>
       </c>
       <c r="AY79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA79" t="n">
         <v>10</v>
@@ -17921,19 +17921,19 @@
         <v>0.88</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="AU80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW80" t="n">
         <v>7</v>
@@ -17942,10 +17942,10 @@
         <v>14</v>
       </c>
       <c r="AY80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ80" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA80" t="n">
         <v>2</v>
@@ -18139,19 +18139,19 @@
         <v>1</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT81" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AU81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW81" t="n">
         <v>13</v>
@@ -18160,10 +18160,10 @@
         <v>7</v>
       </c>
       <c r="AY81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA81" t="n">
         <v>9</v>
@@ -18357,19 +18357,19 @@
         <v>0.25</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="AU82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV82" t="n">
         <v>4</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>5</v>
       </c>
       <c r="AW82" t="n">
         <v>4</v>
@@ -18378,10 +18378,10 @@
         <v>5</v>
       </c>
       <c r="AY82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA82" t="n">
         <v>5</v>
@@ -18575,19 +18575,19 @@
         <v>0.43</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="AU83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW83" t="n">
         <v>7</v>
@@ -18596,10 +18596,10 @@
         <v>7</v>
       </c>
       <c r="AY83" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA83" t="n">
         <v>4</v>
@@ -18790,22 +18790,22 @@
         <v>1.67</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT84" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW84" t="n">
         <v>15</v>
@@ -18814,10 +18814,10 @@
         <v>0</v>
       </c>
       <c r="AY84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA84" t="n">
         <v>8</v>
@@ -19011,19 +19011,19 @@
         <v>0.88</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="AU85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW85" t="n">
         <v>7</v>
@@ -19032,10 +19032,10 @@
         <v>10</v>
       </c>
       <c r="AY85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA85" t="n">
         <v>5</v>
@@ -19229,19 +19229,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW86" t="n">
         <v>6</v>
@@ -19250,10 +19250,10 @@
         <v>15</v>
       </c>
       <c r="AY86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA86" t="n">
         <v>1</v>
@@ -19447,19 +19447,19 @@
         <v>0.78</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW87" t="n">
         <v>9</v>
@@ -19468,10 +19468,10 @@
         <v>5</v>
       </c>
       <c r="AY87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA87" t="n">
         <v>5</v>
@@ -19665,19 +19665,19 @@
         <v>1.38</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="AU88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW88" t="n">
         <v>13</v>
@@ -19686,10 +19686,10 @@
         <v>7</v>
       </c>
       <c r="AY88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA88" t="n">
         <v>7</v>
@@ -19883,19 +19883,19 @@
         <v>2.57</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="AU89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW89" t="n">
         <v>7</v>
@@ -19904,10 +19904,10 @@
         <v>10</v>
       </c>
       <c r="AY89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ89" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA89" t="n">
         <v>8</v>
@@ -20101,19 +20101,19 @@
         <v>0.89</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS90" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="AU90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW90" t="n">
         <v>15</v>
@@ -20122,10 +20122,10 @@
         <v>4</v>
       </c>
       <c r="AY90" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA90" t="n">
         <v>15</v>
@@ -20319,19 +20319,19 @@
         <v>1.25</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW91" t="n">
         <v>14</v>
@@ -20340,10 +20340,10 @@
         <v>6</v>
       </c>
       <c r="AY91" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA91" t="n">
         <v>6</v>
@@ -20531,25 +20531,25 @@
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT92" t="n">
-        <v>3.53</v>
+        <v>3.26</v>
       </c>
       <c r="AU92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW92" t="n">
         <v>12</v>
@@ -20558,10 +20558,10 @@
         <v>5</v>
       </c>
       <c r="AY92" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA92" t="n">
         <v>6</v>
@@ -20755,19 +20755,19 @@
         <v>1.25</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT93" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW93" t="n">
         <v>9</v>
@@ -20776,10 +20776,10 @@
         <v>4</v>
       </c>
       <c r="AY93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA93" t="n">
         <v>5</v>
@@ -20973,16 +20973,16 @@
         <v>0.78</v>
       </c>
       <c r="AR94" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT94" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="AU94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV94" t="n">
         <v>0</v>
@@ -20991,13 +20991,13 @@
         <v>11</v>
       </c>
       <c r="AX94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA94" t="n">
         <v>1</v>
@@ -21188,22 +21188,22 @@
         <v>1.88</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="AU95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV95" t="n">
         <v>3</v>
-      </c>
-      <c r="AV95" t="n">
-        <v>4</v>
       </c>
       <c r="AW95" t="n">
         <v>7</v>
@@ -21212,10 +21212,10 @@
         <v>13</v>
       </c>
       <c r="AY95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA95" t="n">
         <v>4</v>
@@ -21403,25 +21403,25 @@
         <v>0.6</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.88</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AU96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW96" t="n">
         <v>9</v>
@@ -21430,10 +21430,10 @@
         <v>13</v>
       </c>
       <c r="AY96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ96" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA96" t="n">
         <v>6</v>
@@ -21627,19 +21627,19 @@
         <v>1.86</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="AU97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW97" t="n">
         <v>10</v>
@@ -21648,10 +21648,10 @@
         <v>4</v>
       </c>
       <c r="AY97" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA97" t="n">
         <v>3</v>
@@ -21845,19 +21845,19 @@
         <v>0.78</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AU98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW98" t="n">
         <v>12</v>
@@ -21866,10 +21866,10 @@
         <v>6</v>
       </c>
       <c r="AY98" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA98" t="n">
         <v>5</v>
@@ -22063,19 +22063,19 @@
         <v>1.5</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="AU99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW99" t="n">
         <v>9</v>
@@ -22084,10 +22084,10 @@
         <v>9</v>
       </c>
       <c r="AY99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ99" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA99" t="n">
         <v>6</v>
@@ -22281,19 +22281,19 @@
         <v>0</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AS100" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="AU100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW100" t="n">
         <v>7</v>
@@ -22302,10 +22302,10 @@
         <v>5</v>
       </c>
       <c r="AY100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA100" t="n">
         <v>6</v>
@@ -22499,19 +22499,19 @@
         <v>0.88</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="AU101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW101" t="n">
         <v>6</v>
@@ -22520,10 +22520,10 @@
         <v>10</v>
       </c>
       <c r="AY101" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ101" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ101" t="n">
-        <v>15</v>
       </c>
       <c r="BA101" t="n">
         <v>5</v>
@@ -22717,19 +22717,19 @@
         <v>1.63</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW102" t="n">
         <v>16</v>
@@ -22738,10 +22738,10 @@
         <v>1</v>
       </c>
       <c r="AY102" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA102" t="n">
         <v>7</v>
@@ -22929,25 +22929,25 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.25</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW103" t="n">
         <v>8</v>
@@ -22956,10 +22956,10 @@
         <v>6</v>
       </c>
       <c r="AY103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA103" t="n">
         <v>2</v>
@@ -23153,19 +23153,19 @@
         <v>1.38</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT104" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW104" t="n">
         <v>13</v>
@@ -23174,10 +23174,10 @@
         <v>9</v>
       </c>
       <c r="AY104" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA104" t="n">
         <v>5</v>
@@ -23368,22 +23368,22 @@
         <v>1.38</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW105" t="n">
         <v>9</v>
@@ -23392,10 +23392,10 @@
         <v>12</v>
       </c>
       <c r="AY105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ105" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA105" t="n">
         <v>5</v>
@@ -23589,19 +23589,19 @@
         <v>0.43</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU106" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW106" t="n">
         <v>3</v>
@@ -23610,10 +23610,10 @@
         <v>8</v>
       </c>
       <c r="AY106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA106" t="n">
         <v>2</v>
@@ -23807,19 +23807,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW107" t="n">
         <v>10</v>
@@ -23828,10 +23828,10 @@
         <v>4</v>
       </c>
       <c r="AY107" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ107" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA107" t="n">
         <v>8</v>
@@ -24025,19 +24025,19 @@
         <v>0.89</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS108" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV108" t="n">
         <v>4</v>
-      </c>
-      <c r="AV108" t="n">
-        <v>5</v>
       </c>
       <c r="AW108" t="n">
         <v>11</v>
@@ -24046,10 +24046,10 @@
         <v>4</v>
       </c>
       <c r="AY108" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA108" t="n">
         <v>8</v>
@@ -24243,19 +24243,19 @@
         <v>2.57</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT109" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AU109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW109" t="n">
         <v>11</v>
@@ -24264,10 +24264,10 @@
         <v>13</v>
       </c>
       <c r="AY109" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ109" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA109" t="n">
         <v>5</v>
@@ -24461,19 +24461,19 @@
         <v>0.88</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT110" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AU110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW110" t="n">
         <v>11</v>
@@ -24482,10 +24482,10 @@
         <v>5</v>
       </c>
       <c r="AY110" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA110" t="n">
         <v>9</v>
@@ -24679,19 +24679,19 @@
         <v>1</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT111" t="n">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="AU111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW111" t="n">
         <v>7</v>
@@ -24700,10 +24700,10 @@
         <v>5</v>
       </c>
       <c r="AY111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA111" t="n">
         <v>6</v>
@@ -24894,22 +24894,22 @@
         <v>1.56</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW112" t="n">
         <v>7</v>
@@ -24918,10 +24918,10 @@
         <v>9</v>
       </c>
       <c r="AY112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ112" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA112" t="n">
         <v>4</v>
@@ -25115,19 +25115,19 @@
         <v>1.5</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AU113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW113" t="n">
         <v>8</v>
@@ -25136,10 +25136,10 @@
         <v>16</v>
       </c>
       <c r="AY113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ113" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA113" t="n">
         <v>9</v>
@@ -25333,19 +25333,19 @@
         <v>0.78</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AU114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW114" t="n">
         <v>25</v>
@@ -25354,10 +25354,10 @@
         <v>4</v>
       </c>
       <c r="AY114" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AZ114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA114" t="n">
         <v>15</v>
@@ -25551,19 +25551,19 @@
         <v>0.78</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.27</v>
+        <v>2.02</v>
       </c>
       <c r="AU115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW115" t="n">
         <v>13</v>
@@ -25572,10 +25572,10 @@
         <v>9</v>
       </c>
       <c r="AY115" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA115" t="n">
         <v>4</v>
@@ -25766,22 +25766,22 @@
         <v>1.67</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AU116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW116" t="n">
         <v>8</v>
@@ -25790,10 +25790,10 @@
         <v>5</v>
       </c>
       <c r="AY116" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA116" t="n">
         <v>4</v>
@@ -25987,19 +25987,19 @@
         <v>0.88</v>
       </c>
       <c r="AR117" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AT117" t="n">
-        <v>3.48</v>
+        <v>3.23</v>
       </c>
       <c r="AU117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW117" t="n">
         <v>10</v>
@@ -26008,10 +26008,10 @@
         <v>7</v>
       </c>
       <c r="AY117" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA117" t="n">
         <v>6</v>
@@ -26205,19 +26205,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR118" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.61</v>
+        <v>3.34</v>
       </c>
       <c r="AU118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV118" t="n">
         <v>4</v>
-      </c>
-      <c r="AV118" t="n">
-        <v>5</v>
       </c>
       <c r="AW118" t="n">
         <v>9</v>
@@ -26226,10 +26226,10 @@
         <v>4</v>
       </c>
       <c r="AY118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA118" t="n">
         <v>2</v>
@@ -26423,16 +26423,16 @@
         <v>0.88</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV119" t="n">
         <v>0</v>
@@ -26441,13 +26441,13 @@
         <v>4</v>
       </c>
       <c r="AX119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY119" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA119" t="n">
         <v>7</v>
@@ -26641,19 +26641,19 @@
         <v>1.38</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="AU120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV120" t="n">
         <v>6</v>
-      </c>
-      <c r="AV120" t="n">
-        <v>7</v>
       </c>
       <c r="AW120" t="n">
         <v>3</v>
@@ -26662,10 +26662,10 @@
         <v>10</v>
       </c>
       <c r="AY120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA120" t="n">
         <v>5</v>
@@ -26859,19 +26859,19 @@
         <v>0.89</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AU121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW121" t="n">
         <v>9</v>
@@ -26880,10 +26880,10 @@
         <v>4</v>
       </c>
       <c r="AY121" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA121" t="n">
         <v>4</v>
@@ -27077,19 +27077,19 @@
         <v>1.63</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT122" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW122" t="n">
         <v>3</v>
@@ -27098,10 +27098,10 @@
         <v>2</v>
       </c>
       <c r="AY122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ122" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA122" t="n">
         <v>10</v>
@@ -27292,22 +27292,22 @@
         <v>2.44</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="AU123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW123" t="n">
         <v>5</v>
@@ -27316,10 +27316,10 @@
         <v>7</v>
       </c>
       <c r="AY123" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA123" t="n">
         <v>6</v>
@@ -27513,31 +27513,31 @@
         <v>1</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU124" t="n">
         <v>0</v>
       </c>
       <c r="AV124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX124" t="n">
         <v>8</v>
       </c>
       <c r="AY124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA124" t="n">
         <v>3</v>
@@ -27731,19 +27731,19 @@
         <v>0.25</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AU125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW125" t="n">
         <v>2</v>
@@ -27752,10 +27752,10 @@
         <v>7</v>
       </c>
       <c r="AY125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ125" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA125" t="n">
         <v>1</v>
@@ -27949,19 +27949,19 @@
         <v>1.25</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AU126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW126" t="n">
         <v>8</v>
@@ -27970,10 +27970,10 @@
         <v>0</v>
       </c>
       <c r="AY126" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA126" t="n">
         <v>7</v>
@@ -28167,19 +28167,19 @@
         <v>0.78</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="AU127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW127" t="n">
         <v>8</v>
@@ -28188,10 +28188,10 @@
         <v>3</v>
       </c>
       <c r="AY127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA127" t="n">
         <v>7</v>
@@ -28385,19 +28385,19 @@
         <v>1.86</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AU128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV128" t="n">
         <v>5</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>6</v>
       </c>
       <c r="AW128" t="n">
         <v>2</v>
@@ -28406,10 +28406,10 @@
         <v>3</v>
       </c>
       <c r="AY128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ128" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA128" t="n">
         <v>3</v>
@@ -28603,19 +28603,19 @@
         <v>0.88</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="AU129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW129" t="n">
         <v>7</v>
@@ -28624,10 +28624,10 @@
         <v>7</v>
       </c>
       <c r="AY129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ129" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA129" t="n">
         <v>6</v>
@@ -28821,19 +28821,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT130" t="n">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="AU130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW130" t="n">
         <v>11</v>
@@ -28842,10 +28842,10 @@
         <v>4</v>
       </c>
       <c r="AY130" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA130" t="n">
         <v>6</v>
@@ -29033,25 +29033,25 @@
         <v>1.33</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.5</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT131" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW131" t="n">
         <v>16</v>
@@ -29060,10 +29060,10 @@
         <v>3</v>
       </c>
       <c r="AY131" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ131" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA131" t="n">
         <v>7</v>
@@ -29254,22 +29254,22 @@
         <v>1.22</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AU132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW132" t="n">
         <v>8</v>
@@ -29278,10 +29278,10 @@
         <v>9</v>
       </c>
       <c r="AY132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ132" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA132" t="n">
         <v>9</v>
@@ -29472,22 +29472,22 @@
         <v>1.38</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU133" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW133" t="n">
         <v>12</v>
@@ -29496,10 +29496,10 @@
         <v>4</v>
       </c>
       <c r="AY133" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA133" t="n">
         <v>12</v>
@@ -29687,22 +29687,22 @@
         <v>0.86</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.78</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV134" t="n">
         <v>0</v>
@@ -29711,13 +29711,13 @@
         <v>3</v>
       </c>
       <c r="AX134" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY134" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ134" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA134" t="n">
         <v>9</v>
@@ -29911,19 +29911,19 @@
         <v>0.78</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="AU135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW135" t="n">
         <v>7</v>
@@ -29932,10 +29932,10 @@
         <v>4</v>
       </c>
       <c r="AY135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA135" t="n">
         <v>6</v>
@@ -30129,19 +30129,19 @@
         <v>1</v>
       </c>
       <c r="AR136" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.35</v>
+        <v>3.09</v>
       </c>
       <c r="AU136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW136" t="n">
         <v>6</v>
@@ -30150,10 +30150,10 @@
         <v>7</v>
       </c>
       <c r="AY136" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ136" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA136" t="n">
         <v>7</v>
@@ -30347,19 +30347,19 @@
         <v>0</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS137" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AU137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW137" t="n">
         <v>9</v>
@@ -30368,10 +30368,10 @@
         <v>5</v>
       </c>
       <c r="AY137" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA137" t="n">
         <v>8</v>
@@ -30565,19 +30565,19 @@
         <v>1.63</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT138" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV138" t="n">
         <v>3</v>
-      </c>
-      <c r="AV138" t="n">
-        <v>4</v>
       </c>
       <c r="AW138" t="n">
         <v>7</v>
@@ -30586,10 +30586,10 @@
         <v>12</v>
       </c>
       <c r="AY138" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ138" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA138" t="n">
         <v>2</v>
@@ -30777,25 +30777,25 @@
         <v>1.14</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.38</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AU139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW139" t="n">
         <v>7</v>
@@ -30804,10 +30804,10 @@
         <v>8</v>
       </c>
       <c r="AY139" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ139" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ139" t="n">
-        <v>14</v>
       </c>
       <c r="BA139" t="n">
         <v>6</v>
@@ -31001,19 +31001,19 @@
         <v>0.89</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="AU140" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW140" t="n">
         <v>11</v>
@@ -31022,10 +31022,10 @@
         <v>3</v>
       </c>
       <c r="AY140" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA140" t="n">
         <v>9</v>
@@ -31219,19 +31219,19 @@
         <v>0.88</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT141" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="AU141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW141" t="n">
         <v>6</v>
@@ -31240,10 +31240,10 @@
         <v>4</v>
       </c>
       <c r="AY141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ141" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA141" t="n">
         <v>8</v>
@@ -31431,25 +31431,25 @@
         <v>2.5</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
         <v>2.57</v>
       </c>
       <c r="AR142" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW142" t="n">
         <v>16</v>
@@ -31458,10 +31458,10 @@
         <v>4</v>
       </c>
       <c r="AY142" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ142" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA142" t="n">
         <v>5</v>
@@ -31655,19 +31655,19 @@
         <v>1.25</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW143" t="n">
         <v>14</v>
@@ -31676,10 +31676,10 @@
         <v>1</v>
       </c>
       <c r="AY143" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ143" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA143" t="n">
         <v>14</v>
@@ -31873,19 +31873,19 @@
         <v>1.5</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AT144" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AU144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW144" t="n">
         <v>3</v>
@@ -31894,10 +31894,10 @@
         <v>9</v>
       </c>
       <c r="AY144" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ144" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA144" t="n">
         <v>4</v>
@@ -32091,19 +32091,19 @@
         <v>0.25</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU145" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV145" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW145" t="n">
         <v>15</v>
@@ -32112,10 +32112,10 @@
         <v>11</v>
       </c>
       <c r="AY145" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ145" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA145" t="n">
         <v>6</v>
@@ -32309,19 +32309,19 @@
         <v>0.88</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="AU146" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV146" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW146" t="n">
         <v>14</v>
@@ -32330,10 +32330,10 @@
         <v>7</v>
       </c>
       <c r="AY146" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ146" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA146" t="n">
         <v>8</v>
@@ -32527,19 +32527,19 @@
         <v>1.86</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT147" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW147" t="n">
         <v>8</v>
@@ -32548,10 +32548,10 @@
         <v>8</v>
       </c>
       <c r="AY147" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ147" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA147" t="n">
         <v>2</v>
@@ -32745,31 +32745,31 @@
         <v>0.88</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU148" t="n">
         <v>0</v>
       </c>
       <c r="AV148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW148" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX148" t="n">
         <v>13</v>
       </c>
       <c r="AY148" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ148" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA148" t="n">
         <v>4</v>
@@ -32963,19 +32963,19 @@
         <v>0.78</v>
       </c>
       <c r="AR149" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="AT149" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="AU149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV149" t="n">
         <v>4</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>5</v>
       </c>
       <c r="AW149" t="n">
         <v>8</v>
@@ -32984,10 +32984,10 @@
         <v>7</v>
       </c>
       <c r="AY149" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ149" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA149" t="n">
         <v>6</v>
@@ -33175,25 +33175,25 @@
         <v>0.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW150" t="n">
         <v>8</v>
@@ -33202,10 +33202,10 @@
         <v>9</v>
       </c>
       <c r="AY150" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ150" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>17</v>
       </c>
       <c r="BA150" t="n">
         <v>8</v>
@@ -33393,25 +33393,25 @@
         <v>0.75</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AQ151" t="n">
         <v>0.78</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.09</v>
+        <v>0.97</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AU151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV151" t="n">
         <v>5</v>
-      </c>
-      <c r="AV151" t="n">
-        <v>6</v>
       </c>
       <c r="AW151" t="n">
         <v>12</v>
@@ -33420,10 +33420,10 @@
         <v>4</v>
       </c>
       <c r="AY151" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ151" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA151" t="n">
         <v>4</v>
@@ -33617,19 +33617,19 @@
         <v>1.63</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT152" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AU152" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW152" t="n">
         <v>12</v>
@@ -33638,10 +33638,10 @@
         <v>6</v>
       </c>
       <c r="AY152" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA152" t="n">
         <v>9</v>
@@ -33832,22 +33832,22 @@
         <v>1.75</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AU153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW153" t="n">
         <v>7</v>
@@ -33856,10 +33856,10 @@
         <v>2</v>
       </c>
       <c r="AY153" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA153" t="n">
         <v>2</v>
@@ -34053,19 +34053,19 @@
         <v>1</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="AU154" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW154" t="n">
         <v>11</v>
@@ -34074,10 +34074,10 @@
         <v>6</v>
       </c>
       <c r="AY154" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA154" t="n">
         <v>10</v>
@@ -34271,19 +34271,19 @@
         <v>0.88</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="AU155" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW155" t="n">
         <v>6</v>
@@ -34292,10 +34292,10 @@
         <v>6</v>
       </c>
       <c r="AY155" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ155" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA155" t="n">
         <v>7</v>
@@ -34486,22 +34486,22 @@
         <v>1.75</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR156" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="AU156" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW156" t="n">
         <v>19</v>
@@ -34510,10 +34510,10 @@
         <v>10</v>
       </c>
       <c r="AY156" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ156" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA156" t="n">
         <v>10</v>
@@ -34707,16 +34707,16 @@
         <v>0</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS157" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AU157" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV157" t="n">
         <v>0</v>
@@ -34725,13 +34725,13 @@
         <v>9</v>
       </c>
       <c r="AX157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY157" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA157" t="n">
         <v>2</v>
@@ -34925,19 +34925,19 @@
         <v>0.89</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="AU158" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV158" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW158" t="n">
         <v>10</v>
@@ -34946,10 +34946,10 @@
         <v>8</v>
       </c>
       <c r="AY158" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA158" t="n">
         <v>5</v>
@@ -35143,19 +35143,19 @@
         <v>0.43</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AU159" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV159" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW159" t="n">
         <v>6</v>
@@ -35164,10 +35164,10 @@
         <v>8</v>
       </c>
       <c r="AY159" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ159" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ159" t="n">
-        <v>12</v>
       </c>
       <c r="BA159" t="n">
         <v>2</v>
@@ -35216,6 +35216,660 @@
       </c>
       <c r="BP159" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>7834490</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45871.66666666666</v>
+      </c>
+      <c r="F160" t="n">
+        <v>18</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V160" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X160" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>7834485</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45871.77083333334</v>
+      </c>
+      <c r="F161" t="n">
+        <v>18</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>3</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
+        <v>5</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['51', '58', '83']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['66', '70']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S161" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X161" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>7834481</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45871.875</v>
+      </c>
+      <c r="F162" t="n">
+        <v>18</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S162" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V162" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X162" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.5600000000000001</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.5</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR27" t="n">
         <v>1.44</v>
@@ -6582,7 +6582,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR28" t="n">
         <v>1.33</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.5600000000000001</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.5</v>
@@ -7669,10 +7669,10 @@
         <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR33" t="n">
         <v>1.76</v>
@@ -7890,7 +7890,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR34" t="n">
         <v>1.02</v>
@@ -8323,10 +8323,10 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AR36" t="n">
         <v>2.89</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.88</v>
@@ -8759,10 +8759,10 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR38" t="n">
         <v>0.66</v>
@@ -9631,7 +9631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.25</v>
@@ -9852,7 +9852,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR43" t="n">
         <v>1.42</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.38</v>
@@ -10942,7 +10942,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AR48" t="n">
         <v>0.86</v>
@@ -11378,7 +11378,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR50" t="n">
         <v>1.69</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ52" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR54" t="n">
         <v>1.22</v>
@@ -12468,7 +12468,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR55" t="n">
         <v>1.65</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.88</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.5600000000000001</v>
@@ -13776,7 +13776,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR61" t="n">
         <v>1.74</v>
@@ -13994,7 +13994,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR62" t="n">
         <v>1.14</v>
@@ -14427,7 +14427,7 @@
         <v>0.67</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.5600000000000001</v>
@@ -14645,7 +14645,7 @@
         <v>1</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.88</v>
@@ -15302,7 +15302,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -15520,7 +15520,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR69" t="n">
         <v>1.32</v>
@@ -16607,7 +16607,7 @@
         <v>0</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.5</v>
@@ -16828,7 +16828,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR75" t="n">
         <v>1.05</v>
@@ -17264,7 +17264,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR77" t="n">
         <v>1.76</v>
@@ -17482,7 +17482,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR78" t="n">
         <v>1.57</v>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.88</v>
@@ -17915,7 +17915,7 @@
         <v>0.75</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.88</v>
@@ -18351,7 +18351,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.25</v>
@@ -18572,7 +18572,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR83" t="n">
         <v>1.15</v>
@@ -19441,7 +19441,7 @@
         <v>0</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.78</v>
@@ -19880,7 +19880,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AR89" t="n">
         <v>1.76</v>
@@ -20313,7 +20313,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.25</v>
@@ -20967,7 +20967,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.78</v>
@@ -21624,7 +21624,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR97" t="n">
         <v>1.63</v>
@@ -21839,7 +21839,7 @@
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.78</v>
@@ -22060,7 +22060,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR99" t="n">
         <v>1.4</v>
@@ -22496,7 +22496,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR101" t="n">
         <v>1.23</v>
@@ -22714,7 +22714,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR102" t="n">
         <v>1.25</v>
@@ -23586,7 +23586,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR106" t="n">
         <v>1.74</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.5600000000000001</v>
@@ -24019,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.89</v>
@@ -24240,7 +24240,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AR109" t="n">
         <v>1.56</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.88</v>
@@ -24673,7 +24673,7 @@
         <v>0.5</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ111" t="n">
         <v>1</v>
@@ -25109,10 +25109,10 @@
         <v>1.4</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR113" t="n">
         <v>1.5</v>
@@ -25981,7 +25981,7 @@
         <v>0.67</v>
       </c>
       <c r="AP117" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.88</v>
@@ -26199,7 +26199,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.5600000000000001</v>
@@ -26420,7 +26420,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR119" t="n">
         <v>1.81</v>
@@ -27071,10 +27071,10 @@
         <v>2</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR122" t="n">
         <v>1.45</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.78</v>
@@ -28382,7 +28382,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR128" t="n">
         <v>1.65</v>
@@ -28600,7 +28600,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR129" t="n">
         <v>1.48</v>
@@ -28815,7 +28815,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.5600000000000001</v>
@@ -29036,7 +29036,7 @@
         <v>2</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR131" t="n">
         <v>1.76</v>
@@ -30123,7 +30123,7 @@
         <v>0.83</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ136" t="n">
         <v>1</v>
@@ -30559,10 +30559,10 @@
         <v>2.17</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR138" t="n">
         <v>1.44</v>
@@ -31434,7 +31434,7 @@
         <v>2</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AR142" t="n">
         <v>1.88</v>
@@ -31649,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.25</v>
@@ -31867,10 +31867,10 @@
         <v>1.57</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR144" t="n">
         <v>1.49</v>
@@ -32085,7 +32085,7 @@
         <v>0.14</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.25</v>
@@ -32524,7 +32524,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AR147" t="n">
         <v>1.45</v>
@@ -32742,7 +32742,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR148" t="n">
         <v>1.36</v>
@@ -32957,7 +32957,7 @@
         <v>0.75</v>
       </c>
       <c r="AP149" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.78</v>
@@ -33614,7 +33614,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR152" t="n">
         <v>1.47</v>
@@ -34483,7 +34483,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ156" t="n">
         <v>0.5</v>
@@ -35140,7 +35140,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR159" t="n">
         <v>1.22</v>
@@ -35870,6 +35870,1314 @@
       </c>
       <c r="BP162" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>7834482</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45872.66666666666</v>
+      </c>
+      <c r="F163" t="n">
+        <v>18</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>2</v>
+      </c>
+      <c r="K163" t="n">
+        <v>2</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>['23', '41']</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R163" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S163" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V163" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X163" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>7834483</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45872.66666666666</v>
+      </c>
+      <c r="F164" t="n">
+        <v>18</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R164" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S164" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V164" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X164" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>7834486</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45872.77083333334</v>
+      </c>
+      <c r="F165" t="n">
+        <v>18</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>3</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>['7', '81']</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S165" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U165" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V165" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X165" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>7834489</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45872.77083333334</v>
+      </c>
+      <c r="F166" t="n">
+        <v>18</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R166" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S166" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V166" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X166" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>7834488</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45872.8125</v>
+      </c>
+      <c r="F167" t="n">
+        <v>18</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>2</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>4</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>['34', '65']</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['70', '86']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>5</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S167" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V167" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X167" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>7834487</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45872.85416666666</v>
+      </c>
+      <c r="F168" t="n">
+        <v>18</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>3</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>['43', '76']</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S168" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V168" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X168" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP168"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.13</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.89</v>
@@ -13773,7 +13773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.44</v>
@@ -18133,7 +18133,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ81" t="n">
         <v>1</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.38</v>
@@ -28379,7 +28379,7 @@
         <v>2</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.75</v>
@@ -32303,7 +32303,7 @@
         <v>0.57</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.88</v>
@@ -37178,6 +37178,224 @@
       </c>
       <c r="BP168" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>7834484</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45873.83333333334</v>
+      </c>
+      <c r="F169" t="n">
+        <v>18</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>2</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" t="n">
+        <v>3</v>
+      </c>
+      <c r="L169" t="n">
+        <v>3</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>4</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>['37', '40', '80']</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S169" t="n">
+        <v>8</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U169" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V169" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X169" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -4049,7 +4049,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>7834327</v>
+        <v>7834325</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4069,197 +4069,197 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>['31', '37', '77']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S17" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="n">
         <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.77</v>
+        <v>3.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AD17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA17" t="n">
         <v>8</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="BB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK17" t="n">
         <v>1.6</v>
       </c>
-      <c r="AI17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BL17" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="18">
@@ -4267,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>7834328</v>
+        <v>7834327</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4287,50 +4287,50 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>3</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['31', '37', '77']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>['62', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
         <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="T18" t="n">
         <v>1.5</v>
@@ -4351,13 +4351,13 @@
         <v>1.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>4.7</v>
       </c>
       <c r="AC18" t="n">
         <v>1.07</v>
@@ -4372,25 +4372,25 @@
         <v>2.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AL18" t="n">
         <v>1.3</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.21</v>
+        <v>1.95</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4414,70 +4414,70 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY18" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="BL18" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="BO18" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BP18" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="19">
@@ -4485,7 +4485,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>7834330</v>
+        <v>7834328</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>['33', '90+1']</t>
+          <t>['62', '87']</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -4548,13 +4548,13 @@
         <v>2.05</v>
       </c>
       <c r="S19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.63</v>
       </c>
       <c r="V19" t="n">
         <v>3.4</v>
@@ -4569,13 +4569,13 @@
         <v>1.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>1.07</v>
@@ -4584,16 +4584,16 @@
         <v>8</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AI19" t="n">
         <v>2</v>
@@ -4602,13 +4602,13 @@
         <v>1.75</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AL19" t="n">
         <v>1.3</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4632,67 +4632,67 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX19" t="n">
         <v>7</v>
       </c>
-      <c r="AX19" t="n">
-        <v>3</v>
-      </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB19" t="n">
         <v>6</v>
       </c>
-      <c r="BB19" t="n">
-        <v>3</v>
-      </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="BE19" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BH19" t="n">
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BJ19" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="BL19" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BO19" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BP19" t="n">
         <v>1.48</v>
@@ -4703,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>7834325</v>
+        <v>7834330</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4723,197 +4723,197 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['33', '90+1']</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V20" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
         <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AD20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW20" t="n">
         <v>7</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV20" t="n">
+      <c r="AX20" t="n">
         <v>3</v>
       </c>
-      <c r="AW20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4</v>
-      </c>
       <c r="AY20" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
         <v>7</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC20" t="n">
         <v>9</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BJ20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BL20" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="BP20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="21">
@@ -5139,7 +5139,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>7834340</v>
+        <v>7834335</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5159,164 +5159,164 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>['45+1', '68']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="T22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U22" t="n">
-        <v>2.69</v>
+        <v>2.42</v>
       </c>
       <c r="V22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Y22" t="n">
         <v>1.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD22" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL22" t="n">
         <v>1.3</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA22" t="n">
         <v>3</v>
       </c>
-      <c r="AO22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4</v>
-      </c>
       <c r="BB22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BE22" t="n">
-        <v>8</v>
+        <v>6.65</v>
       </c>
       <c r="BF22" t="n">
         <v>2.05</v>
@@ -5325,31 +5325,31 @@
         <v>1.2</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BJ22" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="BL22" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="BM22" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BO22" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="BP22" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="23">
@@ -5357,7 +5357,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>7834335</v>
+        <v>7834340</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5377,164 +5377,164 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['45+1', '68']</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U23" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="V23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X23" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Y23" t="n">
         <v>1.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL23" t="n">
         <v>1.3</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.16</v>
+        <v>1.05</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.57</v>
+        <v>2.48</v>
       </c>
       <c r="AU23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA23" t="n">
         <v>4</v>
       </c>
-      <c r="AV23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA23" t="n">
+      <c r="BB23" t="n">
         <v>3</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BC23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE23" t="n">
         <v>8</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.65</v>
       </c>
       <c r="BF23" t="n">
         <v>2.05</v>
@@ -5543,31 +5543,31 @@
         <v>1.2</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="BI23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP23" t="n">
         <v>1.33</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1.41</v>
       </c>
     </row>
     <row r="24">
@@ -6229,7 +6229,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>7834334</v>
+        <v>7834337</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6249,197 +6249,197 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>2</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['4', '67']</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="S27" t="n">
-        <v>5.55</v>
+        <v>2.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="U27" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="V27" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X27" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.01</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.91</v>
+        <v>2.31</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD27" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="AG27" t="n">
         <v>2.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL27" t="n">
         <v>1.3</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.61</v>
+        <v>1.84</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.05</v>
+        <v>3.17</v>
       </c>
       <c r="AU27" t="n">
         <v>2</v>
       </c>
       <c r="AV27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB27" t="n">
         <v>4</v>
       </c>
-      <c r="BB27" t="n">
-        <v>6</v>
-      </c>
       <c r="BC27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.89</v>
+        <v>1.93</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="BJ27" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BL27" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="BN27" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="BO27" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="BP27" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="28">
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>7834337</v>
+        <v>7834334</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6467,197 +6467,197 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>['4', '67']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>4.1</v>
+        <v>2.69</v>
       </c>
       <c r="R28" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>5.55</v>
       </c>
       <c r="T28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.47</v>
       </c>
-      <c r="U28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V28" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="AG28" t="n">
         <v>2.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL28" t="n">
         <v>1.3</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK28" t="n">
         <v>1.75</v>
       </c>
-      <c r="AR28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BL28" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="BN28" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="BO28" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BP28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="29">
@@ -7755,7 +7755,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7834350</v>
+        <v>7834345</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7775,197 +7775,197 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '21', '78', '85']</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S34" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="U34" t="n">
-        <v>2.87</v>
+        <v>2.53</v>
       </c>
       <c r="V34" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="W34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL34" t="n">
         <v>1.35</v>
       </c>
-      <c r="X34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AM34" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.78</v>
+        <v>3.53</v>
       </c>
       <c r="AU34" t="n">
         <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AX34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY34" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AZ34" t="n">
         <v>16</v>
       </c>
       <c r="BA34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC34" t="n">
         <v>9</v>
       </c>
-      <c r="BB34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>12</v>
-      </c>
       <c r="BD34" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF34" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BH34" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="BJ34" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="BL34" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="BN34" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="BO34" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="BP34" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="35">
@@ -7973,7 +7973,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7834345</v>
+        <v>7834350</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7993,197 +7993,197 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>['3', '21', '78', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T35" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="U35" t="n">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="V35" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="W35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL35" t="n">
         <v>1.34</v>
       </c>
-      <c r="X35" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ35" t="n">
+      <c r="AM35" t="n">
         <v>1.73</v>
       </c>
-      <c r="AK35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.18</v>
+        <v>1.02</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.53</v>
+        <v>2.78</v>
       </c>
       <c r="AU35" t="n">
         <v>6</v>
       </c>
       <c r="AV35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW35" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AX35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY35" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AZ35" t="n">
         <v>16</v>
       </c>
       <c r="BA35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BB35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="BF35" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="BJ35" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="BL35" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="BM35" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="BN35" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="BO35" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="BP35" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="36">
@@ -8191,7 +8191,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>7834347</v>
+        <v>7834343</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -8211,12 +8211,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -8232,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -8244,98 +8244,98 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['63', '82']</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="R36" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S36" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="U36" t="n">
         <v>2.4</v>
       </c>
       <c r="V36" t="n">
-        <v>3.3</v>
+        <v>3.77</v>
       </c>
       <c r="W36" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X36" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AC36" t="n">
         <v>1.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AN36" t="n">
         <v>3</v>
       </c>
       <c r="AO36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2.38</v>
+        <v>0.88</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.89</v>
+        <v>0.86</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.92</v>
+        <v>1.44</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.81</v>
+        <v>2.3</v>
       </c>
       <c r="AU36" t="n">
         <v>2</v>
@@ -8344,64 +8344,64 @@
         <v>4</v>
       </c>
       <c r="AW36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>8</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="BA36" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC36" t="n">
         <v>11</v>
       </c>
-      <c r="AZ36" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>7</v>
-      </c>
       <c r="BD36" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="BE36" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BH36" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="BJ36" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="BL36" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="BM36" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="BN36" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="BO36" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="BP36" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="37">
@@ -8409,7 +8409,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>7834343</v>
+        <v>7834347</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -8450,10 +8450,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -8462,98 +8462,98 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>['63', '82']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="T37" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="U37" t="n">
         <v>2.4</v>
       </c>
       <c r="V37" t="n">
-        <v>3.77</v>
+        <v>3.3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AC37" t="n">
         <v>1.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM37" t="n">
         <v>1.46</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.75</v>
       </c>
       <c r="AN37" t="n">
         <v>3</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.88</v>
+        <v>2.38</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.86</v>
+        <v>2.89</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.44</v>
+        <v>0.92</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.3</v>
+        <v>3.81</v>
       </c>
       <c r="AU37" t="n">
         <v>2</v>
@@ -8562,64 +8562,64 @@
         <v>4</v>
       </c>
       <c r="AW37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX37" t="n">
         <v>8</v>
       </c>
-      <c r="AX37" t="n">
-        <v>4</v>
-      </c>
       <c r="AY37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC37" t="n">
         <v>7</v>
       </c>
-      <c r="BB37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>11</v>
-      </c>
       <c r="BD37" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="BJ37" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="BL37" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="BM37" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="BN37" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="BO37" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="BP37" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="38">
@@ -10807,7 +10807,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>7834359</v>
+        <v>7834351</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -10827,19 +10827,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -10848,149 +10848,149 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
+        <v>2</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V48" t="n">
         <v>3</v>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>['45+4', '58']</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R48" t="n">
-        <v>2</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="V48" t="n">
-        <v>3.3</v>
-      </c>
       <c r="W48" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
         <v>1.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.05</v>
+        <v>6.2</v>
       </c>
       <c r="AC48" t="n">
         <v>1.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR48" t="n">
         <v>1.53</v>
       </c>
-      <c r="AI48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AS48" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.94</v>
+        <v>2.79</v>
       </c>
       <c r="AU48" t="n">
         <v>5</v>
       </c>
       <c r="AV48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX48" t="n">
         <v>4</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AY48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>7</v>
       </c>
-      <c r="AX48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ48" t="n">
+      <c r="BA48" t="n">
         <v>6</v>
       </c>
-      <c r="BA48" t="n">
-        <v>8</v>
-      </c>
       <c r="BB48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC48" t="n">
         <v>10</v>
       </c>
       <c r="BD48" t="n">
-        <v>2.33</v>
+        <v>1.45</v>
       </c>
       <c r="BE48" t="n">
-        <v>6.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH48" t="n">
         <v>3.5</v>
@@ -10999,25 +10999,25 @@
         <v>1.46</v>
       </c>
       <c r="BJ48" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BL48" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="BM48" t="n">
         <v>2.37</v>
       </c>
       <c r="BN48" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="BO48" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP48" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="49">
@@ -11025,7 +11025,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>7834351</v>
+        <v>7834359</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -11045,19 +11045,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
@@ -11066,149 +11066,149 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['45+4', '58']</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="R49" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="U49" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="W49" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y49" t="n">
         <v>1.05</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>6.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC49" t="n">
         <v>1.1</v>
       </c>
       <c r="AD49" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="AN49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO49" t="n">
         <v>3</v>
       </c>
-      <c r="AO49" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.38</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.53</v>
+        <v>0.86</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.79</v>
+        <v>1.94</v>
       </c>
       <c r="AU49" t="n">
         <v>5</v>
       </c>
       <c r="AV49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW49" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>6</v>
       </c>
-      <c r="AX49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>7</v>
-      </c>
       <c r="BA49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC49" t="n">
         <v>10</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.45</v>
+        <v>2.33</v>
       </c>
       <c r="BE49" t="n">
-        <v>9.199999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="BF49" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH49" t="n">
         <v>3.5</v>
@@ -11217,25 +11217,25 @@
         <v>1.46</v>
       </c>
       <c r="BJ49" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BL49" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="BM49" t="n">
         <v>2.37</v>
       </c>
       <c r="BN49" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="BO49" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP49" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="50">
@@ -11897,7 +11897,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>7834365</v>
+        <v>7834369</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -11917,197 +11917,197 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>['12', '90+2']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>['70', '80']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R53" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="S53" t="n">
-        <v>3.2</v>
+        <v>4.88</v>
       </c>
       <c r="T53" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="U53" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="V53" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="W53" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X53" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.99</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AD53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AG53" t="n">
         <v>2.45</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL53" t="n">
         <v>1.28</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AN53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.02</v>
+        <v>1.19</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.74</v>
+        <v>2.41</v>
       </c>
       <c r="AU53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>14</v>
       </c>
-      <c r="AX53" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>17</v>
-      </c>
       <c r="BA53" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BC53" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="BD53" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="BE53" t="n">
-        <v>8.199999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BH53" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BJ53" t="n">
         <v>2.5</v>
       </c>
       <c r="BK53" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BL53" t="n">
         <v>1.95</v>
       </c>
       <c r="BM53" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BN53" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BO53" t="n">
         <v>2.8</v>
       </c>
       <c r="BP53" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="54">
@@ -12115,7 +12115,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>7834369</v>
+        <v>7834365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -12135,197 +12135,197 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['12', '90+2']</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['70', '80']</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R54" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="S54" t="n">
-        <v>4.88</v>
+        <v>3.2</v>
       </c>
       <c r="T54" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U54" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="V54" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="W54" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X54" t="n">
-        <v>9.75</v>
+        <v>8.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA54" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF54" t="n">
         <v>2.7</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2.28</v>
       </c>
       <c r="AG54" t="n">
         <v>2.45</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL54" t="n">
         <v>1.28</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AN54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.19</v>
+        <v>2.02</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.41</v>
+        <v>3.74</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW54" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB54" t="n">
         <v>7</v>
       </c>
-      <c r="AZ54" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>2</v>
-      </c>
       <c r="BC54" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="BE54" t="n">
-        <v>6.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF54" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BH54" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI54" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BJ54" t="n">
         <v>2.5</v>
       </c>
       <c r="BK54" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BL54" t="n">
         <v>1.95</v>
       </c>
       <c r="BM54" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BN54" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="BO54" t="n">
         <v>2.8</v>
       </c>
       <c r="BP54" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="55">
@@ -14077,7 +14077,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>7834371</v>
+        <v>7834373</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -14097,197 +14097,197 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>['60', '90+7']</t>
+          <t>['25', '64', '90+4', '90+13']</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['38', '42']</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="R63" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S63" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="T63" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U63" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V63" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="W63" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X63" t="n">
         <v>8</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="AB63" t="n">
-        <v>5</v>
+        <v>2.97</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AD63" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE63" t="n">
         <v>1.44</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AI63" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AL63" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AM63" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AN63" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO63" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.25</v>
+        <v>0.88</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.68</v>
+        <v>2.16</v>
       </c>
       <c r="AU63" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ63" t="n">
         <v>8</v>
       </c>
-      <c r="AV63" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>11</v>
-      </c>
       <c r="BA63" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC63" t="n">
         <v>10</v>
       </c>
-      <c r="BB63" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>16</v>
-      </c>
       <c r="BD63" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="BE63" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF63" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BH63" t="n">
         <v>3.55</v>
       </c>
       <c r="BI63" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="BJ63" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="BK63" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN63" t="n">
         <v>1.7</v>
       </c>
-      <c r="BL63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BO63" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="BP63" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="64">
@@ -14513,7 +14513,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>7834373</v>
+        <v>7834371</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -14533,197 +14533,197 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
         <v>3</v>
       </c>
-      <c r="L65" t="n">
-        <v>4</v>
-      </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>6</v>
-      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>['25', '64', '90+4', '90+13']</t>
+          <t>['60', '90+7']</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>['38', '42']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="R65" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S65" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="T65" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U65" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V65" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="W65" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X65" t="n">
         <v>8</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AD65" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE65" t="n">
         <v>1.44</v>
       </c>
       <c r="AF65" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AG65" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AL65" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AM65" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AN65" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO65" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="AR65" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG65" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>1.24</v>
       </c>
       <c r="BH65" t="n">
         <v>3.55</v>
       </c>
       <c r="BI65" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="BJ65" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="BK65" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="BL65" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BM65" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BN65" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="BO65" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="BP65" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="66">
@@ -16475,7 +16475,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>7834388</v>
+        <v>7834387</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -16495,197 +16495,197 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
         <v>1</v>
       </c>
       <c r="N74" t="n">
+        <v>2</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V74" t="n">
         <v>3</v>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>['60', '90']</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S74" t="n">
-        <v>4</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U74" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V74" t="n">
-        <v>3.35</v>
-      </c>
       <c r="W74" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X74" t="n">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AA74" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AD74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI74" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AJ74" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AK74" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AL74" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AM74" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AN74" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP74" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ74" t="n">
         <v>1.44</v>
       </c>
-      <c r="AQ74" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AR74" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AU74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW74" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX74" t="n">
         <v>8</v>
       </c>
-      <c r="AX74" t="n">
-        <v>12</v>
-      </c>
       <c r="AY74" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ74" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA74" t="n">
         <v>6</v>
       </c>
       <c r="BB74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD74" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="BE74" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF74" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="BG74" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="BH74" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="BI74" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="BJ74" t="n">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="BK74" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="BL74" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="BM74" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="BN74" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="BO74" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="BP74" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="75">
@@ -16693,7 +16693,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>7834387</v>
+        <v>7834388</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -16713,197 +16713,197 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
         <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['60', '90']</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>3.37</v>
+        <v>2.75</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S75" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U75" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V75" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="W75" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X75" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AA75" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.93</v>
+        <v>3.6</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AD75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW75" t="n">
         <v>8</v>
       </c>
-      <c r="AE75" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>13</v>
-      </c>
       <c r="AX75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ75" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA75" t="n">
         <v>6</v>
       </c>
       <c r="BB75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD75" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="BE75" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF75" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="BG75" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BH75" t="n">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="BI75" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="BJ75" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="BK75" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="BL75" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="BM75" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="BN75" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="BO75" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="BP75" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="76">
@@ -18873,7 +18873,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>7834400</v>
+        <v>7834393</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -18893,12 +18893,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -18914,41 +18914,41 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>4.56</v>
+        <v>2.49</v>
       </c>
       <c r="R85" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S85" t="n">
-        <v>2.75</v>
+        <v>5.06</v>
       </c>
       <c r="T85" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="U85" t="n">
         <v>2.58</v>
       </c>
       <c r="V85" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="W85" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="X85" t="n">
         <v>7.5</v>
@@ -18957,130 +18957,130 @@
         <v>1.05</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="AA85" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.24</v>
+        <v>3.47</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AD85" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AE85" t="n">
         <v>1.4</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH85" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP85" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI85" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AQ85" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AS85" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="AU85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ85" t="n">
         <v>6</v>
-      </c>
-      <c r="AW85" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX85" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>16</v>
       </c>
       <c r="BA85" t="n">
         <v>5</v>
       </c>
       <c r="BB85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD85" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="BE85" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BF85" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM85" t="n">
         <v>2.05</v>
       </c>
-      <c r="BG85" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH85" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="BI85" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BJ85" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BK85" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BL85" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BM85" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BN85" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BO85" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="BP85" t="n">
         <v>1.41</v>
@@ -19309,7 +19309,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>7834393</v>
+        <v>7834400</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -19329,12 +19329,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -19350,41 +19350,41 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>2.49</v>
+        <v>4.56</v>
       </c>
       <c r="R87" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="S87" t="n">
-        <v>5.06</v>
+        <v>2.75</v>
       </c>
       <c r="T87" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="U87" t="n">
         <v>2.58</v>
       </c>
       <c r="V87" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="W87" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X87" t="n">
         <v>7.5</v>
@@ -19393,130 +19393,130 @@
         <v>1.05</v>
       </c>
       <c r="Z87" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="AA87" t="n">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="AB87" t="n">
-        <v>3.47</v>
+        <v>2.24</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD87" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AE87" t="n">
         <v>1.4</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AJ87" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN87" t="n">
         <v>1.75</v>
       </c>
-      <c r="AK87" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL87" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM87" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN87" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AO87" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="AU87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV87" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY87" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ87" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BA87" t="n">
         <v>5</v>
       </c>
       <c r="BB87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC87" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE87" t="n">
         <v>8</v>
       </c>
-      <c r="BD87" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BE87" t="n">
-        <v>8.5</v>
-      </c>
       <c r="BF87" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="BG87" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BH87" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="BI87" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="BJ87" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BK87" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BL87" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="BM87" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="BN87" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO87" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BP87" t="n">
         <v>1.41</v>
@@ -19527,7 +19527,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>7834391</v>
+        <v>7834395</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -19547,197 +19547,197 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72', '78']</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>1.95</v>
+        <v>4.39</v>
       </c>
       <c r="R88" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S88" t="n">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="T88" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U88" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="V88" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="W88" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="X88" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD88" t="n">
         <v>7</v>
       </c>
-      <c r="Y88" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AE88" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM88" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI88" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ88" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK88" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AL88" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM88" t="n">
-        <v>2.3</v>
       </c>
       <c r="AN88" t="n">
         <v>2.5</v>
       </c>
       <c r="AO88" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.56</v>
+        <v>1.56</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.38</v>
+        <v>2.38</v>
       </c>
       <c r="AR88" t="n">
         <v>1.76</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW88" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY88" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ88" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB88" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BC88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BD88" t="n">
-        <v>1.3</v>
+        <v>2.38</v>
       </c>
       <c r="BE88" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF88" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="BG88" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BH88" t="n">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="BI88" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="BJ88" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="BK88" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="BL88" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="BM88" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="BN88" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="BO88" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="BP88" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="89">
@@ -19745,7 +19745,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>7834395</v>
+        <v>7834391</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -19765,197 +19765,197 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>['72', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>4.39</v>
+        <v>1.95</v>
       </c>
       <c r="R89" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S89" t="n">
-        <v>2.75</v>
+        <v>6.2</v>
       </c>
       <c r="T89" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U89" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V89" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="W89" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="X89" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z89" t="n">
-        <v>3.15</v>
+        <v>1.73</v>
       </c>
       <c r="AA89" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.28</v>
+        <v>5.1</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD89" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AJ89" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AK89" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AL89" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AM89" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AN89" t="n">
         <v>2.5</v>
       </c>
       <c r="AO89" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="AR89" t="n">
         <v>1.76</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="AU89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV89" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW89" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX89" t="n">
         <v>7</v>
       </c>
-      <c r="AX89" t="n">
+      <c r="AY89" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC89" t="n">
         <v>10</v>
       </c>
-      <c r="AY89" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA89" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB89" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC89" t="n">
-        <v>20</v>
-      </c>
       <c r="BD89" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="BE89" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF89" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG89" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BH89" t="n">
-        <v>4.05</v>
+        <v>3.42</v>
       </c>
       <c r="BI89" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="BJ89" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="BK89" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BL89" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="BM89" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="BN89" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="BO89" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="BP89" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="90">
@@ -20399,7 +20399,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>7834401</v>
+        <v>7834404</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -20419,98 +20419,98 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>['42', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['53', '89']</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>2.38</v>
       </c>
       <c r="R92" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S92" t="n">
-        <v>5.5</v>
+        <v>5.99</v>
       </c>
       <c r="T92" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U92" t="n">
         <v>2.5</v>
       </c>
       <c r="V92" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="W92" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X92" t="n">
         <v>8</v>
       </c>
       <c r="Y92" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC92" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z92" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AD92" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AG92" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AI92" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AJ92" t="n">
         <v>1.62</v>
@@ -20519,97 +20519,97 @@
         <v>1.3</v>
       </c>
       <c r="AL92" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ92" t="n">
         <v>1.25</v>
       </c>
-      <c r="AM92" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AN92" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP92" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ92" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AR92" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AT92" t="n">
-        <v>3.26</v>
+        <v>2.79</v>
       </c>
       <c r="AU92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW92" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY92" t="n">
         <v>12</v>
-      </c>
-      <c r="AX92" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY92" t="n">
-        <v>17</v>
       </c>
       <c r="AZ92" t="n">
         <v>7</v>
       </c>
       <c r="BA92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD92" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BE92" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF92" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BG92" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BH92" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BI92" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="BJ92" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="BK92" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="BL92" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="BM92" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BN92" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BO92" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="BP92" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="93">
@@ -20617,7 +20617,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>7834404</v>
+        <v>7834401</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -20637,98 +20637,98 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '87']</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>['53', '89']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>2.38</v>
       </c>
       <c r="R93" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S93" t="n">
-        <v>5.99</v>
+        <v>5.5</v>
       </c>
       <c r="T93" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U93" t="n">
         <v>2.5</v>
       </c>
       <c r="V93" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="W93" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X93" t="n">
         <v>8</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AA93" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB93" t="n">
-        <v>5.1</v>
+        <v>4.45</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AD93" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AG93" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI93" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AJ93" t="n">
         <v>1.62</v>
@@ -20737,97 +20737,97 @@
         <v>1.3</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM93" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AO93" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.79</v>
+        <v>3.26</v>
       </c>
       <c r="AU93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW93" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY93" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ93" t="n">
         <v>7</v>
       </c>
       <c r="BA93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD93" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BE93" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF93" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BG93" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BH93" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI93" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="BJ93" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BK93" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="BL93" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BM93" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BN93" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="BO93" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="BP93" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="94">
@@ -26067,7 +26067,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>7834437</v>
+        <v>7834431</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -26087,12 +26087,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -26105,17 +26105,17 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['61', '90+6']</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -26124,160 +26124,160 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="R118" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S118" t="n">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="T118" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U118" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V118" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X118" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z118" t="n">
         <v>1.45</v>
       </c>
-      <c r="U118" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V118" t="n">
-        <v>3</v>
-      </c>
-      <c r="W118" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X118" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y118" t="n">
+      <c r="AA118" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AC118" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z118" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AD118" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF118" t="n">
         <v>3</v>
       </c>
       <c r="AG118" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="AH118" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI118" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AJ118" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AK118" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL118" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AM118" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AN118" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="AO118" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="AR118" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AU118" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX118" t="n">
         <v>3</v>
       </c>
-      <c r="AV118" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW118" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX118" t="n">
-        <v>4</v>
-      </c>
       <c r="AY118" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC118" t="n">
         <v>8</v>
       </c>
-      <c r="BA118" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB118" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC118" t="n">
-        <v>7</v>
-      </c>
       <c r="BD118" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="BE118" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF118" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG118" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BH118" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="BI118" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN118" t="n">
         <v>1.5</v>
       </c>
-      <c r="BJ118" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BK118" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BL118" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BM118" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BN118" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BO118" t="n">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="BP118" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="119">
@@ -26285,7 +26285,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>7834431</v>
+        <v>7834437</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -26305,12 +26305,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -26323,17 +26323,17 @@
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>['61', '90+6']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -26342,160 +26342,160 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="R119" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S119" t="n">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="T119" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="U119" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="V119" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="W119" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X119" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AA119" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB119" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD119" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF119" t="n">
         <v>3</v>
       </c>
       <c r="AG119" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AH119" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AI119" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AJ119" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AK119" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AL119" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AM119" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AN119" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="AO119" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.56</v>
+        <v>1.56</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AT119" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU119" t="n">
         <v>3</v>
       </c>
-      <c r="AU119" t="n">
-        <v>10</v>
-      </c>
       <c r="AV119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW119" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX119" t="n">
         <v>4</v>
       </c>
-      <c r="AX119" t="n">
-        <v>3</v>
-      </c>
       <c r="AY119" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ119" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BA119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC119" t="n">
         <v>7</v>
       </c>
-      <c r="BB119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC119" t="n">
-        <v>8</v>
-      </c>
       <c r="BD119" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="BE119" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BF119" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="BG119" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BH119" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="BI119" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BJ119" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="BK119" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BL119" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="BM119" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="BN119" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO119" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="BP119" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="120">
@@ -28465,7 +28465,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>7834445</v>
+        <v>7834442</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -28485,197 +28485,197 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S129" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U129" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V129" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W129" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X129" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX129" t="n">
         <v>4</v>
       </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>['43', '48']</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>['9', '64']</t>
-        </is>
-      </c>
-      <c r="Q129" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R129" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S129" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T129" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U129" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V129" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="W129" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X129" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK129" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL129" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM129" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN129" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO129" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP129" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ129" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AR129" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AS129" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AT129" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AU129" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV129" t="n">
+      <c r="AY129" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ129" t="n">
         <v>5</v>
-      </c>
-      <c r="AW129" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX129" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY129" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ129" t="n">
-        <v>12</v>
       </c>
       <c r="BA129" t="n">
         <v>6</v>
       </c>
       <c r="BB129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD129" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="BE129" t="n">
-        <v>9.6</v>
+        <v>10.25</v>
       </c>
       <c r="BF129" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BG129" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="BH129" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI129" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="BJ129" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="BK129" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BL129" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BM129" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="BN129" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="BO129" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP129" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="130">
@@ -28683,7 +28683,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>7834442</v>
+        <v>7834445</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -28703,197 +28703,197 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '48']</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>2.03</v>
+        <v>2.84</v>
       </c>
       <c r="R130" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="S130" t="n">
-        <v>6.66</v>
+        <v>4.5</v>
       </c>
       <c r="T130" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="U130" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V130" t="n">
-        <v>2.8</v>
+        <v>3.72</v>
       </c>
       <c r="W130" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="X130" t="n">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.39</v>
+        <v>2.33</v>
       </c>
       <c r="AA130" t="n">
-        <v>4.46</v>
+        <v>3</v>
       </c>
       <c r="AB130" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC130" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS130" t="n">
         <v>1.06</v>
       </c>
-      <c r="AD130" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ130" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AK130" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL130" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM130" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AN130" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO130" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP130" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AQ130" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AR130" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS130" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AT130" t="n">
-        <v>3.07</v>
+        <v>2.54</v>
       </c>
       <c r="AU130" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW130" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX130" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY130" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AZ130" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BA130" t="n">
         <v>6</v>
       </c>
       <c r="BB130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD130" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="BE130" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="BF130" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BG130" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="BH130" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="BI130" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BJ130" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="BK130" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BL130" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="BM130" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="BN130" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="BO130" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="BP130" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="131">
@@ -31299,7 +31299,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>7834461</v>
+        <v>7834469</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -31319,197 +31319,197 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K142" t="n">
         <v>2</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>2</v>
       </c>
       <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>['16', '22']</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2</v>
+      </c>
+      <c r="S142" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U142" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V142" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X142" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV142" t="n">
         <v>3</v>
       </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>['45+4', '62']</t>
-        </is>
-      </c>
-      <c r="Q142" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R142" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S142" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T142" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U142" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V142" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W142" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X142" t="n">
+      <c r="AW142" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE142" t="n">
         <v>9</v>
       </c>
-      <c r="Y142" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ142" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK142" t="n">
+      <c r="BF142" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI142" t="n">
         <v>1.42</v>
       </c>
-      <c r="AL142" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AM142" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN142" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO142" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP142" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ142" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AR142" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS142" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT142" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AU142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV142" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW142" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX142" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY142" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ142" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA142" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB142" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC142" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD142" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BE142" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF142" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BG142" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH142" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI142" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BJ142" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BK142" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="BL142" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="BM142" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BN142" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BO142" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="BP142" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="143">
@@ -31517,7 +31517,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>7834469</v>
+        <v>7834461</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -31537,197 +31537,197 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K143" t="n">
         <v>2</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>['16', '22']</t>
+          <t>['45+4', '62']</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>2.65</v>
+        <v>3.53</v>
       </c>
       <c r="R143" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S143" t="n">
-        <v>4.86</v>
+        <v>3.35</v>
       </c>
       <c r="T143" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U143" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V143" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X143" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF143" t="n">
         <v>2.45</v>
       </c>
-      <c r="V143" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="W143" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X143" t="n">
+      <c r="AG143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC143" t="n">
         <v>8</v>
       </c>
-      <c r="Y143" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="AE143" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF143" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AJ143" t="n">
+      <c r="BD143" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN143" t="n">
         <v>1.7</v>
       </c>
-      <c r="AK143" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL143" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM143" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AN143" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP143" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ143" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR143" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AS143" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AT143" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU143" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV143" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW143" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY143" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ143" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA143" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB143" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC143" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD143" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BE143" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF143" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG143" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH143" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI143" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BJ143" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BK143" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BL143" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BM143" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BN143" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BO143" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BP143" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="144">
@@ -33915,7 +33915,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>7834476</v>
+        <v>7834474</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -33935,197 +33935,197 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I154" t="n">
         <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['24', '59', '90+1']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S154" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X154" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA154" t="n">
         <v>3</v>
       </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>['39', '60']</t>
-        </is>
-      </c>
-      <c r="Q154" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R154" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S154" t="n">
-        <v>7</v>
-      </c>
-      <c r="T154" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U154" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V154" t="n">
-        <v>3</v>
-      </c>
-      <c r="W154" t="n">
+      <c r="AB154" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL154" t="n">
         <v>1.33</v>
       </c>
-      <c r="X154" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB154" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH154" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI154" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ154" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AK154" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL154" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AM154" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="AN154" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO154" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.44</v>
+        <v>1.67</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.72</v>
+        <v>2.31</v>
       </c>
       <c r="AU154" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW154" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX154" t="n">
         <v>6</v>
       </c>
       <c r="AY154" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ154" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA154" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BB154" t="n">
         <v>3</v>
       </c>
       <c r="BC154" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD154" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BE154" t="n">
-        <v>10.25</v>
+        <v>6.5</v>
       </c>
       <c r="BF154" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="BG154" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH154" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="BI154" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="BJ154" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="BK154" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BL154" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="BM154" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="BN154" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="BO154" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="BP154" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="155">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>7834474</v>
+        <v>7834476</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,197 +34153,197 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>2</v>
+      </c>
+      <c r="N155" t="n">
         <v>3</v>
       </c>
-      <c r="M155" t="n">
-        <v>1</v>
-      </c>
-      <c r="N155" t="n">
-        <v>4</v>
-      </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>['24', '59', '90+1']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['39', '60']</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>3.14</v>
+        <v>1.93</v>
       </c>
       <c r="R155" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="S155" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="T155" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="U155" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="V155" t="n">
-        <v>3.68</v>
+        <v>3</v>
       </c>
       <c r="W155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X155" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL155" t="n">
         <v>1.23</v>
       </c>
-      <c r="X155" t="n">
+      <c r="AM155" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW155" t="n">
         <v>11</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB155" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC155" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD155" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AE155" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF155" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP155" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ155" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>6</v>
       </c>
       <c r="AX155" t="n">
         <v>6</v>
       </c>
       <c r="AY155" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ155" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA155" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB155" t="n">
         <v>3</v>
       </c>
       <c r="BC155" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD155" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK155" t="n">
         <v>1.67</v>
       </c>
-      <c r="BE155" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BI155" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BJ155" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="BK155" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BL155" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BO155" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="156">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -37338,16 +37338,16 @@
         <v>10</v>
       </c>
       <c r="AW169" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX169" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY169" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ169" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA169" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -37338,16 +37338,16 @@
         <v>10</v>
       </c>
       <c r="AW169" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX169" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY169" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ169" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA169" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.25</v>
@@ -1132,7 +1132,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.38</v>
@@ -6146,7 +6146,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR26" t="n">
         <v>1.59</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.67</v>
@@ -7018,7 +7018,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR30" t="n">
         <v>0.67</v>
@@ -7236,7 +7236,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR31" t="n">
         <v>2.41</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ39" t="n">
         <v>0</v>
@@ -10070,7 +10070,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR44" t="n">
         <v>1.21</v>
@@ -10288,7 +10288,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR45" t="n">
         <v>1.32</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.78</v>
@@ -10942,7 +10942,7 @@
         <v>2</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR48" t="n">
         <v>1.53</v>
@@ -11375,7 +11375,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.67</v>
@@ -12901,7 +12901,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.78</v>
@@ -13991,7 +13991,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.5</v>
@@ -14212,7 +14212,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR63" t="n">
         <v>1.23</v>
@@ -14430,7 +14430,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR64" t="n">
         <v>1.06</v>
@@ -15735,10 +15735,10 @@
         <v>0.67</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR70" t="n">
         <v>1.81</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.13</v>
@@ -17918,7 +17918,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR80" t="n">
         <v>1.99</v>
@@ -18787,7 +18787,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.5600000000000001</v>
@@ -19226,7 +19226,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR86" t="n">
         <v>1.33</v>
@@ -19659,7 +19659,7 @@
         <v>3</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.38</v>
@@ -19877,7 +19877,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.38</v>
@@ -20316,7 +20316,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR91" t="n">
         <v>1.91</v>
@@ -20531,10 +20531,10 @@
         <v>0.6</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR92" t="n">
         <v>1.36</v>
@@ -21406,7 +21406,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR96" t="n">
         <v>1.67</v>
@@ -22275,7 +22275,7 @@
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ100" t="n">
         <v>0</v>
@@ -23583,7 +23583,7 @@
         <v>0.6</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.5</v>
@@ -23804,7 +23804,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR107" t="n">
         <v>1.45</v>
@@ -24891,7 +24891,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.13</v>
@@ -25763,7 +25763,7 @@
         <v>0</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.5</v>
@@ -25984,7 +25984,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR117" t="n">
         <v>2</v>
@@ -26199,7 +26199,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.11</v>
@@ -26420,7 +26420,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR119" t="n">
         <v>2.07</v>
@@ -27946,7 +27946,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR126" t="n">
         <v>1.59</v>
@@ -28600,7 +28600,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR129" t="n">
         <v>1.84</v>
@@ -28815,7 +28815,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.11</v>
@@ -29905,7 +29905,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.78</v>
@@ -31213,7 +31213,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.88</v>
@@ -31434,7 +31434,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR142" t="n">
         <v>1.23</v>
@@ -32306,7 +32306,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR146" t="n">
         <v>1.51</v>
@@ -32521,7 +32521,7 @@
         <v>1.67</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.75</v>
@@ -33178,7 +33178,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR150" t="n">
         <v>1.66</v>
@@ -34047,7 +34047,7 @@
         <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.88</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.89</v>
@@ -37396,6 +37396,660 @@
       </c>
       <c r="BP169" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>7834495</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45878.77083333334</v>
+      </c>
+      <c r="F170" t="n">
+        <v>19</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>2</v>
+      </c>
+      <c r="K170" t="n">
+        <v>2</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>3</v>
+      </c>
+      <c r="N170" t="n">
+        <v>4</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>['7', '33', '46']</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S170" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V170" t="n">
+        <v>3</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X170" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>7834491</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45878.77083333334</v>
+      </c>
+      <c r="F171" t="n">
+        <v>19</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>3</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['19', '68']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S171" t="n">
+        <v>9</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U171" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X171" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>7834494</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45878.77083333334</v>
+      </c>
+      <c r="F172" t="n">
+        <v>19</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['20', '86']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2</v>
+      </c>
+      <c r="S172" t="n">
+        <v>6</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U172" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V172" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X172" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.78</v>
@@ -5274,7 +5274,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR22" t="n">
         <v>2.16</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.11</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.11</v>
@@ -8326,7 +8326,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR36" t="n">
         <v>0.86</v>
@@ -10724,7 +10724,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR47" t="n">
         <v>2.83</v>
@@ -11157,7 +11157,7 @@
         <v>3</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ49" t="n">
         <v>2.38</v>
@@ -11593,7 +11593,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ51" t="n">
         <v>1</v>
@@ -12686,7 +12686,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR56" t="n">
         <v>2.13</v>
@@ -14863,10 +14863,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR66" t="n">
         <v>1.44</v>
@@ -16171,7 +16171,7 @@
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ72" t="n">
         <v>0</v>
@@ -17700,7 +17700,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR79" t="n">
         <v>2.41</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.5</v>
@@ -19444,7 +19444,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR87" t="n">
         <v>1.62</v>
@@ -19880,7 +19880,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR89" t="n">
         <v>1.76</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.67</v>
@@ -22493,7 +22493,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.11</v>
@@ -23150,7 +23150,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR104" t="n">
         <v>1.65</v>
@@ -24458,7 +24458,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR110" t="n">
         <v>2.16</v>
@@ -25327,7 +25327,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.78</v>
@@ -26638,7 +26638,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR120" t="n">
         <v>1.41</v>
@@ -26853,7 +26853,7 @@
         <v>1.33</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.89</v>
@@ -27507,7 +27507,7 @@
         <v>0.4</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ124" t="n">
         <v>1</v>
@@ -29251,7 +29251,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.13</v>
@@ -30780,7 +30780,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR139" t="n">
         <v>1.62</v>
@@ -31216,7 +31216,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR141" t="n">
         <v>1.86</v>
@@ -33611,7 +33611,7 @@
         <v>1.86</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.44</v>
@@ -34050,7 +34050,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR154" t="n">
         <v>1.29</v>
@@ -34701,7 +34701,7 @@
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ157" t="n">
         <v>0</v>
@@ -37556,16 +37556,16 @@
         <v>6</v>
       </c>
       <c r="AW170" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX170" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY170" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ170" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA170" t="n">
         <v>8</v>
@@ -37774,16 +37774,16 @@
         <v>5</v>
       </c>
       <c r="AW171" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AX171" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY171" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AZ171" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA171" t="n">
         <v>11</v>
@@ -37992,16 +37992,16 @@
         <v>1</v>
       </c>
       <c r="AW172" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AX172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY172" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AZ172" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA172" t="n">
         <v>4</v>
@@ -38050,6 +38050,442 @@
       </c>
       <c r="BP172" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>7834499</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45878.85416666666</v>
+      </c>
+      <c r="F173" t="n">
+        <v>19</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" t="n">
+        <v>2</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>5</v>
+      </c>
+      <c r="N173" t="n">
+        <v>5</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>['14', '45+5', '48', '53', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2</v>
+      </c>
+      <c r="S173" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V173" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X173" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>7834498</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45878.875</v>
+      </c>
+      <c r="F174" t="n">
+        <v>19</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>2</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" t="n">
+        <v>3</v>
+      </c>
+      <c r="L174" t="n">
+        <v>3</v>
+      </c>
+      <c r="M174" t="n">
+        <v>3</v>
+      </c>
+      <c r="N174" t="n">
+        <v>6</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>['13', '19', '89']</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>['9', '49', '72']</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R174" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S174" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U174" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V174" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X174" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.11</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.56</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR23" t="n">
         <v>1.05</v>
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.78</v>
@@ -5925,10 +5925,10 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR25" t="n">
         <v>1.58</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.75</v>
@@ -6800,7 +6800,7 @@
         <v>2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>1.6</v>
@@ -9198,7 +9198,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR40" t="n">
         <v>2.26</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.13</v>
@@ -9634,7 +9634,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR42" t="n">
         <v>1.02</v>
@@ -9849,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.75</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.11</v>
@@ -10506,7 +10506,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR46" t="n">
         <v>1.27</v>
@@ -11596,7 +11596,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR51" t="n">
         <v>1.41</v>
@@ -12250,7 +12250,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR54" t="n">
         <v>1.72</v>
@@ -13119,7 +13119,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.13</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.5</v>
@@ -14648,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR65" t="n">
         <v>1.51</v>
@@ -15081,10 +15081,10 @@
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR67" t="n">
         <v>1.11</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.38</v>
@@ -15517,7 +15517,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.75</v>
@@ -15956,7 +15956,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR71" t="n">
         <v>1.66</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.44</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.11</v>
@@ -18136,7 +18136,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR81" t="n">
         <v>1.73</v>
@@ -18354,7 +18354,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR82" t="n">
         <v>1.3</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.5</v>
@@ -19008,7 +19008,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR85" t="n">
         <v>1.53</v>
@@ -20095,10 +20095,10 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR90" t="n">
         <v>1.52</v>
@@ -21185,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.13</v>
@@ -21621,7 +21621,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.75</v>
@@ -21842,7 +21842,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR98" t="n">
         <v>1.34</v>
@@ -22711,7 +22711,7 @@
         <v>1.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.44</v>
@@ -22932,7 +22932,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR103" t="n">
         <v>1.69</v>
@@ -24022,7 +24022,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR108" t="n">
         <v>1.21</v>
@@ -24237,7 +24237,7 @@
         <v>3</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ109" t="n">
         <v>2.38</v>
@@ -24676,7 +24676,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR111" t="n">
         <v>1.82</v>
@@ -25330,7 +25330,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR114" t="n">
         <v>1.34</v>
@@ -25545,7 +25545,7 @@
         <v>0.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.78</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.56</v>
@@ -26856,7 +26856,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR121" t="n">
         <v>1.3</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.5600000000000001</v>
@@ -27510,7 +27510,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR124" t="n">
         <v>1.68</v>
@@ -27728,7 +27728,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR125" t="n">
         <v>1.48</v>
@@ -27943,7 +27943,7 @@
         <v>1</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.11</v>
@@ -29469,7 +29469,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.5600000000000001</v>
@@ -29690,7 +29690,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR134" t="n">
         <v>1.62</v>
@@ -30126,7 +30126,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR136" t="n">
         <v>1.97</v>
@@ -30341,7 +30341,7 @@
         <v>0</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ137" t="n">
         <v>0</v>
@@ -30995,10 +30995,10 @@
         <v>1.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR140" t="n">
         <v>1.53</v>
@@ -32088,7 +32088,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR145" t="n">
         <v>1.36</v>
@@ -33396,7 +33396,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR151" t="n">
         <v>1.57</v>
@@ -33829,7 +33829,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.5600000000000001</v>
@@ -34265,10 +34265,10 @@
         <v>0.71</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR155" t="n">
         <v>1.6</v>
@@ -34922,7 +34922,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR158" t="n">
         <v>1.77</v>
@@ -35137,7 +35137,7 @@
         <v>0.5</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.5</v>
@@ -38486,6 +38486,878 @@
       </c>
       <c r="BP174" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>7834492</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45879.66666666666</v>
+      </c>
+      <c r="F175" t="n">
+        <v>19</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>2</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V175" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X175" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>7834493</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45879.66666666666</v>
+      </c>
+      <c r="F176" t="n">
+        <v>19</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2</v>
+      </c>
+      <c r="M176" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" t="n">
+        <v>3</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>['67', '69']</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S176" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U176" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V176" t="n">
+        <v>3</v>
+      </c>
+      <c r="W176" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X176" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>7834496</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45879.77083333334</v>
+      </c>
+      <c r="F177" t="n">
+        <v>19</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>2</v>
+      </c>
+      <c r="N177" t="n">
+        <v>3</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>['62', '89']</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R177" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S177" t="n">
+        <v>6</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U177" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V177" t="n">
+        <v>3</v>
+      </c>
+      <c r="W177" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X177" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>7834497</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45879.85416666666</v>
+      </c>
+      <c r="F178" t="n">
+        <v>19</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R178" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S178" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U178" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V178" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X178" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP178"/>
+  <dimension ref="A1:BP179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.5</v>
@@ -2658,7 +2658,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.89</v>
@@ -5710,7 +5710,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR24" t="n">
         <v>1.39</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.11</v>
@@ -12904,7 +12904,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR57" t="n">
         <v>1.95</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.9</v>
@@ -16392,7 +16392,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR73" t="n">
         <v>1.8</v>
@@ -19441,7 +19441,7 @@
         <v>0.75</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.89</v>
@@ -20970,7 +20970,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR94" t="n">
         <v>2.2</v>
@@ -23365,7 +23365,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.5600000000000001</v>
@@ -25548,7 +25548,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR115" t="n">
         <v>1.09</v>
@@ -27725,7 +27725,7 @@
         <v>0.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.5600000000000001</v>
@@ -28164,7 +28164,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR127" t="n">
         <v>1.24</v>
@@ -29908,7 +29908,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR135" t="n">
         <v>1.32</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.11</v>
@@ -32960,7 +32960,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR149" t="n">
         <v>1.94</v>
@@ -38646,16 +38646,16 @@
         <v>4</v>
       </c>
       <c r="AW175" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ175" t="n">
         <v>11</v>
-      </c>
-      <c r="AX175" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY175" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ175" t="n">
-        <v>17</v>
       </c>
       <c r="BA175" t="n">
         <v>6</v>
@@ -38867,13 +38867,13 @@
         <v>3</v>
       </c>
       <c r="AX176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY176" t="n">
         <v>8</v>
       </c>
       <c r="AZ176" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA176" t="n">
         <v>3</v>
@@ -39082,16 +39082,16 @@
         <v>2</v>
       </c>
       <c r="AW177" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AX177" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ177" t="n">
         <v>7</v>
-      </c>
-      <c r="AY177" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ177" t="n">
-        <v>9</v>
       </c>
       <c r="BA177" t="n">
         <v>15</v>
@@ -39358,6 +39358,224 @@
       </c>
       <c r="BP178" t="n">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>7834500</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45880.83333333334</v>
+      </c>
+      <c r="F179" t="n">
+        <v>19</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
+      <c r="L179" t="n">
+        <v>2</v>
+      </c>
+      <c r="M179" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" t="n">
+        <v>3</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>['27', '81']</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="R179" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S179" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V179" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X179" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -38035,16 +38035,16 @@
         <v>3</v>
       </c>
       <c r="AW179">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX179">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY179">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ179">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA179">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -39736,16 +39736,16 @@
         <v>5</v>
       </c>
       <c r="AW180" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX180" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY180" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ180" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA180" t="n">
         <v>2</v>
@@ -39954,16 +39954,16 @@
         <v>2</v>
       </c>
       <c r="AW181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX181" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY181" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA181" t="n">
         <v>3</v>
@@ -40172,16 +40172,16 @@
         <v>4</v>
       </c>
       <c r="AW182" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX182" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY182" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ182" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
@@ -40393,13 +40393,13 @@
         <v>3</v>
       </c>
       <c r="AX183" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY183" t="n">
         <v>8</v>
       </c>
       <c r="AZ183" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA183" t="n">
         <v>4</v>
@@ -40608,16 +40608,16 @@
         <v>5</v>
       </c>
       <c r="AW184" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AX184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY184" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA184" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -3127,10 +3127,10 @@
         <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD12" t="n">
         <v>1.68</v>
@@ -35173,10 +35173,10 @@
         <v>2</v>
       </c>
       <c r="BB159" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD159" t="n">
         <v>1.77</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -39736,16 +39736,16 @@
         <v>5</v>
       </c>
       <c r="AW180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY180" t="n">
         <v>7</v>
       </c>
-      <c r="AX180" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY180" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ180" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA180" t="n">
         <v>2</v>
@@ -39954,16 +39954,16 @@
         <v>2</v>
       </c>
       <c r="AW181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX181" t="n">
         <v>6</v>
       </c>
-      <c r="AX181" t="n">
-        <v>7</v>
-      </c>
       <c r="AY181" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ181" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA181" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.11</v>
@@ -4838,7 +4838,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.1</v>
@@ -8544,7 +8544,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR37" t="n">
         <v>2.89</v>
@@ -11160,7 +11160,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR49" t="n">
         <v>0.86</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.89</v>
@@ -15302,7 +15302,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -17915,7 +17915,7 @@
         <v>0.75</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.11</v>
@@ -19662,7 +19662,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ88" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR88" t="n">
         <v>1.76</v>
@@ -24240,7 +24240,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR109" t="n">
         <v>1.56</v>
@@ -24673,7 +24673,7 @@
         <v>0.5</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ111" t="n">
         <v>0.89</v>
@@ -28597,7 +28597,7 @@
         <v>0.43</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.5</v>
@@ -31652,7 +31652,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ143" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR143" t="n">
         <v>1.88</v>
@@ -32957,7 +32957,7 @@
         <v>0.75</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.7</v>
@@ -36009,7 +36009,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.67</v>
@@ -36884,7 +36884,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ167" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR167" t="n">
         <v>1.54</v>
@@ -39736,16 +39736,16 @@
         <v>5</v>
       </c>
       <c r="AW180" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX180" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY180" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ180" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA180" t="n">
         <v>2</v>
@@ -39954,16 +39954,16 @@
         <v>2</v>
       </c>
       <c r="AW181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX181" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY181" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA181" t="n">
         <v>3</v>
@@ -40175,13 +40175,13 @@
         <v>3</v>
       </c>
       <c r="AX182" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY182" t="n">
         <v>8</v>
       </c>
       <c r="AZ182" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
@@ -40390,16 +40390,16 @@
         <v>4</v>
       </c>
       <c r="AW183" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX183" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY183" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ183" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA183" t="n">
         <v>4</v>
@@ -40608,16 +40608,16 @@
         <v>5</v>
       </c>
       <c r="AW184" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AX184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY184" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA184" t="n">
         <v>9</v>
@@ -40826,16 +40826,16 @@
         <v>9</v>
       </c>
       <c r="AW185" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX185" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY185" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ185" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA185" t="n">
         <v>3</v>
@@ -41044,16 +41044,16 @@
         <v>4</v>
       </c>
       <c r="AW186" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY186" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ186" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ186" t="n">
-        <v>7</v>
       </c>
       <c r="BA186" t="n">
         <v>4</v>
@@ -41256,22 +41256,22 @@
         <v>3.39</v>
       </c>
       <c r="AU187" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV187" t="n">
         <v>3</v>
       </c>
       <c r="AW187" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX187" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AY187" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ187" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BA187" t="n">
         <v>10</v>
@@ -41320,6 +41320,224 @@
       </c>
       <c r="BP187" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>7834502</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45886.85416666666</v>
+      </c>
+      <c r="F188" t="n">
+        <v>20</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" t="n">
+        <v>1</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>4</v>
+      </c>
+      <c r="R188" t="n">
+        <v>2</v>
+      </c>
+      <c r="S188" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V188" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X188" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -40826,16 +40826,16 @@
         <v>9</v>
       </c>
       <c r="AW185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY185" t="n">
         <v>5</v>
       </c>
-      <c r="AX185" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY185" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ185" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA185" t="n">
         <v>3</v>
@@ -41044,16 +41044,16 @@
         <v>4</v>
       </c>
       <c r="AW186" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ186" t="n">
         <v>7</v>
-      </c>
-      <c r="AX186" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY186" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ186" t="n">
-        <v>8</v>
       </c>
       <c r="BA186" t="n">
         <v>4</v>
@@ -41256,22 +41256,22 @@
         <v>3.39</v>
       </c>
       <c r="AU187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV187" t="n">
         <v>3</v>
       </c>
       <c r="AW187" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX187" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AY187" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ187" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA187" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP188"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.44</v>
@@ -4402,7 +4402,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR28" t="n">
         <v>1.44</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.8</v>
@@ -11378,7 +11378,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR50" t="n">
         <v>1.69</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.9</v>
@@ -16389,7 +16389,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.7</v>
@@ -17264,7 +17264,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR77" t="n">
         <v>1.76</v>
@@ -22060,7 +22060,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR99" t="n">
         <v>1.4</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5600000000000001</v>
@@ -25112,7 +25112,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR113" t="n">
         <v>1.5</v>
@@ -29036,7 +29036,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR131" t="n">
         <v>1.76</v>
@@ -29687,7 +29687,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ134" t="n">
         <v>1</v>
@@ -31870,7 +31870,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR144" t="n">
         <v>1.49</v>
@@ -33175,7 +33175,7 @@
         <v>0.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.5</v>
@@ -35573,7 +35573,7 @@
         <v>0.57</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.78</v>
@@ -36012,7 +36012,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR163" t="n">
         <v>1.84</v>
@@ -41480,16 +41480,16 @@
         <v>2</v>
       </c>
       <c r="AW188" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX188" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ188" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA188" t="n">
         <v>4</v>
@@ -41538,6 +41538,224 @@
       </c>
       <c r="BP188" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>7834505</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>45887.83333333334</v>
+      </c>
+      <c r="F189" t="n">
+        <v>20</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" t="n">
+        <v>2</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R189" t="n">
+        <v>2</v>
+      </c>
+      <c r="S189" t="n">
+        <v>3</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V189" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W189" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X189" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -40826,16 +40826,16 @@
         <v>9</v>
       </c>
       <c r="AW185" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX185" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY185" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ185" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA185" t="n">
         <v>3</v>
@@ -41044,16 +41044,16 @@
         <v>4</v>
       </c>
       <c r="AW186" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY186" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ186" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ186" t="n">
-        <v>7</v>
       </c>
       <c r="BA186" t="n">
         <v>4</v>
@@ -41256,22 +41256,22 @@
         <v>3.39</v>
       </c>
       <c r="AU187" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV187" t="n">
         <v>3</v>
       </c>
       <c r="AW187" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX187" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AY187" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ187" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BA187" t="n">
         <v>10</v>
@@ -41480,16 +41480,16 @@
         <v>2</v>
       </c>
       <c r="AW188" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY188" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ188" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA188" t="n">
         <v>4</v>
@@ -41698,16 +41698,16 @@
         <v>3</v>
       </c>
       <c r="AW189" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AX189" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY189" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ189" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA189" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.5</v>
@@ -3312,7 +3312,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.89</v>
@@ -7454,7 +7454,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR32" t="n">
         <v>1.38</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.11</v>
@@ -13340,7 +13340,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR59" t="n">
         <v>1.28</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.9</v>
@@ -16828,7 +16828,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR75" t="n">
         <v>1.34</v>
@@ -19441,7 +19441,7 @@
         <v>0.75</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.89</v>
@@ -20752,7 +20752,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR93" t="n">
         <v>1.74</v>
@@ -23365,7 +23365,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.8</v>
@@ -25766,7 +25766,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR116" t="n">
         <v>1.34</v>
@@ -27725,7 +27725,7 @@
         <v>0.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.5600000000000001</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.1</v>
@@ -34486,7 +34486,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR156" t="n">
         <v>1.87</v>
@@ -35576,7 +35576,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR161" t="n">
         <v>1.68</v>
@@ -39497,7 +39497,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ179" t="n">
         <v>0.7</v>
@@ -40808,7 +40808,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR185" t="n">
         <v>1.68</v>
@@ -41756,6 +41756,224 @@
       </c>
       <c r="BP189" t="n">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>7834450</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45889.79166666666</v>
+      </c>
+      <c r="F190" t="n">
+        <v>14</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>2</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>2</v>
+      </c>
+      <c r="L190" t="n">
+        <v>2</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>['3', '16']</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R190" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S190" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V190" t="n">
+        <v>3</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X190" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.11</v>
@@ -1568,7 +1568,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.89</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.56</v>
@@ -7018,7 +7018,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
         <v>0.67</v>
@@ -8326,7 +8326,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR36" t="n">
         <v>0.86</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.33</v>
@@ -10070,7 +10070,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR44" t="n">
         <v>1.21</v>
@@ -11375,7 +11375,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.6</v>
@@ -12686,7 +12686,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR56" t="n">
         <v>2.13</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.7</v>
@@ -14212,7 +14212,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR63" t="n">
         <v>1.23</v>
@@ -15517,7 +15517,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.89</v>
@@ -15735,7 +15735,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.11</v>
@@ -17700,7 +17700,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR79" t="n">
         <v>2.41</v>
@@ -17918,7 +17918,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR80" t="n">
         <v>1.99</v>
@@ -19444,7 +19444,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR87" t="n">
         <v>1.62</v>
@@ -19659,7 +19659,7 @@
         <v>3</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ88" t="n">
         <v>2.44</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.9</v>
@@ -21406,7 +21406,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR96" t="n">
         <v>1.67</v>
@@ -22275,7 +22275,7 @@
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.11</v>
@@ -24237,7 +24237,7 @@
         <v>3</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ109" t="n">
         <v>2.44</v>
@@ -24458,7 +24458,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR110" t="n">
         <v>2.16</v>
@@ -24891,7 +24891,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.33</v>
@@ -25984,7 +25984,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR117" t="n">
         <v>2</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.8</v>
@@ -28815,7 +28815,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.1</v>
@@ -30341,7 +30341,7 @@
         <v>0</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.11</v>
@@ -31216,7 +31216,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR141" t="n">
         <v>1.86</v>
@@ -32306,7 +32306,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR146" t="n">
         <v>1.51</v>
@@ -32521,7 +32521,7 @@
         <v>1.67</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.89</v>
@@ -34050,7 +34050,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR154" t="n">
         <v>1.29</v>
@@ -34265,7 +34265,7 @@
         <v>0.71</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.89</v>
@@ -37535,10 +37535,10 @@
         <v>0.88</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR170" t="n">
         <v>1.39</v>
@@ -38410,7 +38410,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR174" t="n">
         <v>1.44</v>
@@ -39061,7 +39061,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ177" t="n">
         <v>1</v>
@@ -41974,6 +41974,442 @@
       </c>
       <c r="BP190" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>7834515</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45892.66666666666</v>
+      </c>
+      <c r="F191" t="n">
+        <v>21</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>2</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>3</v>
+      </c>
+      <c r="L191" t="n">
+        <v>4</v>
+      </c>
+      <c r="M191" t="n">
+        <v>2</v>
+      </c>
+      <c r="N191" t="n">
+        <v>6</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>['2', '4', '48', '81']</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>['45+2', '63']</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S191" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V191" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X191" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>7834516</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>45892.77083333334</v>
+      </c>
+      <c r="F192" t="n">
+        <v>21</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="n">
+        <v>2</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="n">
+        <v>1</v>
+      </c>
+      <c r="N192" t="n">
+        <v>3</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>['19', '58']</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R192" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S192" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V192" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X192" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.9</v>
@@ -2876,7 +2876,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR23" t="n">
         <v>1.05</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.89</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR51" t="n">
         <v>1.41</v>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ67" t="n">
         <v>1</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.3</v>
@@ -18136,7 +18136,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR81" t="n">
         <v>1.73</v>
@@ -21185,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.33</v>
@@ -24676,7 +24676,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR111" t="n">
         <v>1.82</v>
@@ -25545,7 +25545,7 @@
         <v>0.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.7</v>
@@ -27510,7 +27510,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR124" t="n">
         <v>1.68</v>
@@ -30126,7 +30126,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR136" t="n">
         <v>1.97</v>
@@ -34268,7 +34268,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR155" t="n">
         <v>1.6</v>
@@ -35137,7 +35137,7 @@
         <v>0.5</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.44</v>
@@ -38846,7 +38846,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR176" t="n">
         <v>1.53</v>
@@ -39279,7 +39279,7 @@
         <v>0.25</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.5600000000000001</v>
@@ -42410,6 +42410,224 @@
       </c>
       <c r="BP192" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>7834517</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>45892.875</v>
+      </c>
+      <c r="F193" t="n">
+        <v>21</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R193" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S193" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V193" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W193" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X193" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -19459,19 +19459,19 @@
         <v>1</v>
       </c>
       <c r="AV87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX87" t="n">
         <v>10</v>
       </c>
       <c r="AY87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA87" t="n">
         <v>5</v>
@@ -19898,16 +19898,16 @@
         <v>2</v>
       </c>
       <c r="AW89" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY89" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA89" t="n">
         <v>7</v>
@@ -20110,19 +20110,19 @@
         <v>3.7</v>
       </c>
       <c r="AU90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV90" t="n">
         <v>3</v>
       </c>
       <c r="AW90" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX90" t="n">
         <v>4</v>
       </c>
       <c r="AY90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ90" t="n">
         <v>7</v>
@@ -20328,13 +20328,13 @@
         <v>3.44</v>
       </c>
       <c r="AU91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV91" t="n">
         <v>2</v>
       </c>
       <c r="AW91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX91" t="n">
         <v>6</v>
@@ -20540,28 +20540,28 @@
         <v>1.36</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AU92" t="n">
         <v>3</v>
       </c>
       <c r="AV92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX92" t="n">
         <v>4</v>
       </c>
       <c r="AY92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA92" t="n">
         <v>5</v>
@@ -21424,13 +21424,13 @@
         <v>4</v>
       </c>
       <c r="AW96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX96" t="n">
         <v>13</v>
       </c>
       <c r="AY96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ96" t="n">
         <v>17</v>
@@ -21760,7 +21760,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -22726,7 +22726,7 @@
         <v>2.87</v>
       </c>
       <c r="AU102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV102" t="n">
         <v>3</v>
@@ -22738,7 +22738,7 @@
         <v>1</v>
       </c>
       <c r="AY102" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ102" t="n">
         <v>4</v>
@@ -22938,10 +22938,10 @@
         <v>1.69</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AU103" t="n">
         <v>4</v>
@@ -23156,10 +23156,10 @@
         <v>1.65</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AU104" t="n">
         <v>4</v>
@@ -23371,13 +23371,13 @@
         <v>0.8</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AS105" t="n">
         <v>1.31</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="AU105" t="n">
         <v>5</v>
@@ -23389,13 +23389,13 @@
         <v>9</v>
       </c>
       <c r="AX105" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY105" t="n">
         <v>14</v>
       </c>
       <c r="AZ105" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA105" t="n">
         <v>5</v>
@@ -23589,13 +23589,13 @@
         <v>0.44</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS106" t="n">
         <v>1.13</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AU106" t="n">
         <v>13</v>
@@ -23822,13 +23822,13 @@
         <v>2</v>
       </c>
       <c r="AW107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX107" t="n">
         <v>4</v>
       </c>
       <c r="AY107" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ107" t="n">
         <v>6</v>
@@ -24028,10 +24028,10 @@
         <v>1.21</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AU108" t="n">
         <v>3</v>
@@ -24461,13 +24461,13 @@
         <v>0.8</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AT110" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AU110" t="n">
         <v>4</v>
@@ -24688,22 +24688,22 @@
         <v>3.01</v>
       </c>
       <c r="AU111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV111" t="n">
         <v>3</v>
       </c>
       <c r="AW111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY111" t="n">
         <v>16</v>
       </c>
       <c r="AZ111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA111" t="n">
         <v>6</v>
@@ -24897,13 +24897,13 @@
         <v>1.33</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AS112" t="n">
         <v>1.13</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU112" t="n">
         <v>2</v>
@@ -25118,10 +25118,10 @@
         <v>1.5</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AU113" t="n">
         <v>2</v>
@@ -25130,13 +25130,13 @@
         <v>2</v>
       </c>
       <c r="AW113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX113" t="n">
         <v>16</v>
       </c>
       <c r="AY113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ113" t="n">
         <v>18</v>
@@ -25333,28 +25333,28 @@
         <v>1</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AS114" t="n">
         <v>1.02</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AU114" t="n">
         <v>10</v>
       </c>
       <c r="AV114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW114" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY114" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="AZ114" t="n">
         <v>8</v>
@@ -25560,19 +25560,19 @@
         <v>2.02</v>
       </c>
       <c r="AU115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV115" t="n">
         <v>3</v>
       </c>
       <c r="AW115" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX115" t="n">
         <v>9</v>
       </c>
       <c r="AY115" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ115" t="n">
         <v>12</v>
@@ -25769,13 +25769,13 @@
         <v>0.7</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AS116" t="n">
         <v>1.36</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AU116" t="n">
         <v>3</v>
@@ -25996,22 +25996,22 @@
         <v>3.23</v>
       </c>
       <c r="AU117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV117" t="n">
         <v>2</v>
       </c>
       <c r="AW117" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ117" t="n">
         <v>10</v>
-      </c>
-      <c r="AX117" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY117" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ117" t="n">
-        <v>9</v>
       </c>
       <c r="BA117" t="n">
         <v>6</v>
@@ -26205,13 +26205,13 @@
         <v>1.1</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AS118" t="n">
         <v>1.19</v>
       </c>
       <c r="AT118" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AU118" t="n">
         <v>10</v>
@@ -26220,16 +26220,16 @@
         <v>0</v>
       </c>
       <c r="AW118" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY118" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AZ118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BA118" t="n">
         <v>7</v>
@@ -26423,13 +26423,13 @@
         <v>0.5</v>
       </c>
       <c r="AR119" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AS119" t="n">
         <v>1.27</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="AU119" t="n">
         <v>3</v>
@@ -26438,16 +26438,16 @@
         <v>4</v>
       </c>
       <c r="AW119" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AX119" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY119" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AZ119" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA119" t="n">
         <v>2</v>
@@ -26641,13 +26641,13 @@
         <v>1.56</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AU120" t="n">
         <v>5</v>
@@ -26656,16 +26656,16 @@
         <v>6</v>
       </c>
       <c r="AW120" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AY120" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ120" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA120" t="n">
         <v>5</v>
@@ -26862,10 +26862,10 @@
         <v>1.3</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AU121" t="n">
         <v>5</v>
@@ -26874,16 +26874,16 @@
         <v>2</v>
       </c>
       <c r="AW121" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX121" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY121" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA121" t="n">
         <v>4</v>
@@ -27077,13 +27077,13 @@
         <v>1.3</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AS122" t="n">
         <v>1.42</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AU122" t="n">
         <v>8</v>
@@ -27092,16 +27092,16 @@
         <v>5</v>
       </c>
       <c r="AW122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY122" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ122" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA122" t="n">
         <v>10</v>
@@ -27295,13 +27295,13 @@
         <v>0.8</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="AU123" t="n">
         <v>9</v>
@@ -27310,16 +27310,16 @@
         <v>2</v>
       </c>
       <c r="AW123" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX123" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY123" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ123" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA123" t="n">
         <v>6</v>
@@ -27513,13 +27513,13 @@
         <v>0.9</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="AU124" t="n">
         <v>0</v>
@@ -27528,16 +27528,16 @@
         <v>3</v>
       </c>
       <c r="AW124" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AX124" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY124" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AZ124" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA124" t="n">
         <v>3</v>
@@ -27731,13 +27731,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AS125" t="n">
         <v>1.22</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AU125" t="n">
         <v>3</v>
@@ -27749,13 +27749,13 @@
         <v>2</v>
       </c>
       <c r="AX125" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AY125" t="n">
         <v>5</v>
       </c>
       <c r="AZ125" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BA125" t="n">
         <v>1</v>
@@ -27952,10 +27952,10 @@
         <v>1.59</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AU126" t="n">
         <v>3</v>
@@ -27964,16 +27964,16 @@
         <v>1</v>
       </c>
       <c r="AW126" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY126" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA126" t="n">
         <v>7</v>
@@ -28170,10 +28170,10 @@
         <v>1.24</v>
       </c>
       <c r="AS127" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AU127" t="n">
         <v>2</v>
@@ -28182,13 +28182,13 @@
         <v>2</v>
       </c>
       <c r="AW127" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX127" t="n">
         <v>3</v>
       </c>
       <c r="AY127" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AZ127" t="n">
         <v>5</v>
@@ -28400,16 +28400,16 @@
         <v>5</v>
       </c>
       <c r="AW128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY128" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ128" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA128" t="n">
         <v>3</v>
@@ -28603,13 +28603,13 @@
         <v>0.5</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AT129" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="AU129" t="n">
         <v>8</v>
@@ -28618,16 +28618,16 @@
         <v>1</v>
       </c>
       <c r="AW129" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AX129" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY129" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AZ129" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA129" t="n">
         <v>6</v>
@@ -28821,13 +28821,13 @@
         <v>1.1</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AU130" t="n">
         <v>3</v>
@@ -28836,16 +28836,16 @@
         <v>5</v>
       </c>
       <c r="AW130" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX130" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY130" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AZ130" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA130" t="n">
         <v>6</v>
@@ -29042,10 +29042,10 @@
         <v>1.76</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT131" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AU131" t="n">
         <v>6</v>
@@ -29054,13 +29054,13 @@
         <v>5</v>
       </c>
       <c r="AW131" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AX131" t="n">
         <v>3</v>
       </c>
       <c r="AY131" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AZ131" t="n">
         <v>8</v>
@@ -29257,13 +29257,13 @@
         <v>1.33</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AS132" t="n">
         <v>1.24</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="AU132" t="n">
         <v>2</v>
@@ -29272,16 +29272,16 @@
         <v>4</v>
       </c>
       <c r="AW132" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX132" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ132" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA132" t="n">
         <v>9</v>
@@ -29475,10 +29475,10 @@
         <v>0.8</v>
       </c>
       <c r="AR133" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS133" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>1.39</v>
       </c>
       <c r="AT133" t="n">
         <v>2.77</v>
@@ -29490,16 +29490,16 @@
         <v>4</v>
       </c>
       <c r="AW133" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AX133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY133" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AZ133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA133" t="n">
         <v>12</v>
@@ -29696,10 +29696,10 @@
         <v>1.62</v>
       </c>
       <c r="AS134" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AU134" t="n">
         <v>11</v>
@@ -29708,16 +29708,16 @@
         <v>0</v>
       </c>
       <c r="AW134" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX134" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY134" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AZ134" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA134" t="n">
         <v>9</v>
@@ -29914,10 +29914,10 @@
         <v>1.32</v>
       </c>
       <c r="AS135" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AU135" t="n">
         <v>3</v>
@@ -29926,16 +29926,16 @@
         <v>3</v>
       </c>
       <c r="AW135" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX135" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY135" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AZ135" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA135" t="n">
         <v>6</v>
@@ -30129,19 +30129,19 @@
         <v>0.9</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AU136" t="n">
         <v>4</v>
       </c>
       <c r="AV136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW136" t="n">
         <v>6</v>
@@ -30153,7 +30153,7 @@
         <v>10</v>
       </c>
       <c r="AZ136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA136" t="n">
         <v>7</v>
@@ -30347,13 +30347,13 @@
         <v>0.11</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AS137" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AU137" t="n">
         <v>7</v>
@@ -30565,13 +30565,13 @@
         <v>1.3</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AU138" t="n">
         <v>2</v>
@@ -30783,13 +30783,13 @@
         <v>1.56</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AU139" t="n">
         <v>5</v>
@@ -31001,13 +31001,13 @@
         <v>0.9</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="AU140" t="n">
         <v>7</v>
@@ -31219,13 +31219,13 @@
         <v>0.8</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="AU141" t="n">
         <v>3</v>
@@ -31437,13 +31437,13 @@
         <v>1.11</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AU142" t="n">
         <v>8</v>
@@ -31655,13 +31655,13 @@
         <v>2.44</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT143" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="AU143" t="n">
         <v>1</v>
@@ -31873,13 +31873,13 @@
         <v>1.6</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AU144" t="n">
         <v>4</v>
@@ -31891,13 +31891,13 @@
         <v>3</v>
       </c>
       <c r="AX144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY144" t="n">
         <v>7</v>
       </c>
       <c r="AZ144" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA144" t="n">
         <v>4</v>
@@ -32091,13 +32091,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AU145" t="n">
         <v>11</v>
@@ -32309,13 +32309,13 @@
         <v>1</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AS146" t="n">
         <v>1.2</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AU146" t="n">
         <v>7</v>
@@ -32527,13 +32527,13 @@
         <v>1.89</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AU147" t="n">
         <v>2</v>
@@ -32745,13 +32745,13 @@
         <v>1.1</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AU148" t="n">
         <v>0</v>
@@ -32963,19 +32963,19 @@
         <v>0.7</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AS149" t="n">
         <v>0.93</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AU149" t="n">
         <v>3</v>
       </c>
       <c r="AV149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW149" t="n">
         <v>8</v>
@@ -32987,7 +32987,7 @@
         <v>11</v>
       </c>
       <c r="AZ149" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA149" t="n">
         <v>6</v>
@@ -33181,13 +33181,13 @@
         <v>0.5</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="AU150" t="n">
         <v>7</v>
@@ -33199,13 +33199,13 @@
         <v>8</v>
       </c>
       <c r="AX150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY150" t="n">
         <v>15</v>
       </c>
       <c r="AZ150" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA150" t="n">
         <v>8</v>
@@ -33399,13 +33399,13 @@
         <v>1</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AS151" t="n">
         <v>0.97</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AU151" t="n">
         <v>4</v>
@@ -33617,13 +33617,13 @@
         <v>1.3</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AU152" t="n">
         <v>9</v>
@@ -33835,13 +33835,13 @@
         <v>0.8</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AS153" t="n">
         <v>1.31</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AU153" t="n">
         <v>3</v>
@@ -34053,13 +34053,13 @@
         <v>0.8</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="AU154" t="n">
         <v>9</v>
@@ -34271,22 +34271,22 @@
         <v>0.9</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AS155" t="n">
         <v>1.12</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AU155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV155" t="n">
         <v>3</v>
       </c>
       <c r="AW155" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX155" t="n">
         <v>6</v>
@@ -34489,13 +34489,13 @@
         <v>0.7</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AS156" t="n">
         <v>1.42</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="AU156" t="n">
         <v>8</v>
@@ -34707,13 +34707,13 @@
         <v>0.11</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AS157" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AU157" t="n">
         <v>8</v>
@@ -34925,13 +34925,13 @@
         <v>0.9</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AU158" t="n">
         <v>6</v>
@@ -35143,13 +35143,13 @@
         <v>0.44</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AS159" t="n">
         <v>1.14</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AU159" t="n">
         <v>4</v>
@@ -35161,22 +35161,22 @@
         <v>6</v>
       </c>
       <c r="AX159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY159" t="n">
         <v>10</v>
       </c>
       <c r="AZ159" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA159" t="n">
         <v>2</v>
       </c>
       <c r="BB159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC159" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD159" t="n">
         <v>1.77</v>
@@ -35361,13 +35361,13 @@
         <v>1.33</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AU160" t="n">
         <v>1</v>
@@ -35579,13 +35579,13 @@
         <v>0.7</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AS161" t="n">
         <v>1.44</v>
       </c>
       <c r="AT161" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="AU161" t="n">
         <v>4</v>
@@ -35797,13 +35797,13 @@
         <v>0.8</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AS162" t="n">
         <v>1.23</v>
       </c>
       <c r="AT162" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="AU162" t="n">
         <v>1</v>
@@ -36015,13 +36015,13 @@
         <v>1.6</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT163" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="AU163" t="n">
         <v>2</v>
@@ -36236,10 +36236,10 @@
         <v>1.44</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AU164" t="n">
         <v>5</v>
@@ -36451,13 +36451,13 @@
         <v>1.3</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AT165" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="AU165" t="n">
         <v>9</v>
@@ -36466,13 +36466,13 @@
         <v>3</v>
       </c>
       <c r="AW165" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX165" t="n">
         <v>1</v>
       </c>
       <c r="AY165" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ165" t="n">
         <v>4</v>
@@ -36669,13 +36669,13 @@
         <v>1.89</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="AU166" t="n">
         <v>4</v>
@@ -36887,13 +36887,13 @@
         <v>2.44</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AU167" t="n">
         <v>6</v>
@@ -36905,13 +36905,13 @@
         <v>9</v>
       </c>
       <c r="AX167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY167" t="n">
         <v>15</v>
       </c>
       <c r="AZ167" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA167" t="n">
         <v>6</v>
@@ -37105,13 +37105,13 @@
         <v>1.1</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="AU168" t="n">
         <v>4</v>
@@ -37323,10 +37323,10 @@
         <v>0.11</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AS169" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="AT169" t="n">
         <v>2.27</v>
@@ -37541,13 +37541,13 @@
         <v>1</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="AU170" t="n">
         <v>8</v>
@@ -37759,13 +37759,13 @@
         <v>1.11</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AU171" t="n">
         <v>8</v>
@@ -37777,13 +37777,13 @@
         <v>16</v>
       </c>
       <c r="AX171" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY171" t="n">
         <v>24</v>
       </c>
       <c r="AZ171" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA171" t="n">
         <v>11</v>
@@ -37977,13 +37977,13 @@
         <v>0.5</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AT172" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AU172" t="n">
         <v>3</v>
@@ -38195,13 +38195,13 @@
         <v>1.56</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="AU173" t="n">
         <v>1</v>
@@ -38413,13 +38413,13 @@
         <v>0.8</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AS174" t="n">
         <v>1</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AU174" t="n">
         <v>6</v>
@@ -38631,13 +38631,13 @@
         <v>0.9</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="AU175" t="n">
         <v>4</v>
@@ -38849,13 +38849,13 @@
         <v>0.9</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS176" t="n">
         <v>1.1</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AU176" t="n">
         <v>5</v>
@@ -38867,13 +38867,13 @@
         <v>3</v>
       </c>
       <c r="AX176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY176" t="n">
         <v>8</v>
       </c>
       <c r="AZ176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA176" t="n">
         <v>3</v>
@@ -39067,13 +39067,13 @@
         <v>1</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AS177" t="n">
         <v>0.99</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AU177" t="n">
         <v>4</v>
@@ -39285,13 +39285,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AT178" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AU178" t="n">
         <v>6</v>
@@ -39303,13 +39303,13 @@
         <v>8</v>
       </c>
       <c r="AX178" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY178" t="n">
         <v>14</v>
       </c>
       <c r="AZ178" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA178" t="n">
         <v>3</v>
@@ -39503,13 +39503,13 @@
         <v>0.7</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AS179" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AU179" t="n">
         <v>4</v>
@@ -39721,13 +39721,13 @@
         <v>0.44</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AU180" t="n">
         <v>3</v>
@@ -39939,13 +39939,13 @@
         <v>1.3</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AU181" t="n">
         <v>4</v>
@@ -40157,13 +40157,13 @@
         <v>1.1</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="AU182" t="n">
         <v>5</v>
@@ -40375,13 +40375,13 @@
         <v>0.11</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AS183" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AU183" t="n">
         <v>4</v>
@@ -40596,28 +40596,28 @@
         <v>1.51</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AT184" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AU184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV184" t="n">
         <v>5</v>
       </c>
       <c r="AW184" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY184" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ184" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA184" t="n">
         <v>9</v>
@@ -40811,13 +40811,13 @@
         <v>0.7</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AS185" t="n">
         <v>1.44</v>
       </c>
       <c r="AT185" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="AU185" t="n">
         <v>2</v>
@@ -41029,13 +41029,13 @@
         <v>0.8</v>
       </c>
       <c r="AR186" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AS186" t="n">
         <v>1.2</v>
       </c>
       <c r="AT186" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="AU186" t="n">
         <v>3</v>
@@ -41247,16 +41247,16 @@
         <v>1.89</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AT187" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="AU187" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV187" t="n">
         <v>3</v>
@@ -41268,7 +41268,7 @@
         <v>13</v>
       </c>
       <c r="AY187" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ187" t="n">
         <v>16</v>
@@ -41465,13 +41465,13 @@
         <v>2.44</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AS188" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT188" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AU188" t="n">
         <v>6</v>
@@ -41483,13 +41483,13 @@
         <v>9</v>
       </c>
       <c r="AX188" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY188" t="n">
         <v>15</v>
       </c>
       <c r="AZ188" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA188" t="n">
         <v>4</v>
@@ -41683,13 +41683,13 @@
         <v>1.6</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AT189" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="AU189" t="n">
         <v>3</v>
@@ -41901,13 +41901,13 @@
         <v>0.7</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AS190" t="n">
         <v>1.47</v>
       </c>
       <c r="AT190" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AU190" t="n">
         <v>5</v>
@@ -41916,16 +41916,16 @@
         <v>2</v>
       </c>
       <c r="AW190" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX190" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY190" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ190" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA190" t="n">
         <v>1</v>
@@ -42119,13 +42119,13 @@
         <v>0.8</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS191" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AU191" t="n">
         <v>5</v>
@@ -42337,13 +42337,13 @@
         <v>1</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AU192" t="n">
         <v>7</v>
@@ -42555,13 +42555,13 @@
         <v>0.9</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AU193" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.5600000000000001</v>
@@ -1132,7 +1132,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.8</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.5</v>
@@ -2222,7 +2222,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR22" t="n">
         <v>2.16</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.9</v>
@@ -5710,7 +5710,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR24" t="n">
         <v>1.39</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.5600000000000001</v>
@@ -6143,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR26" t="n">
         <v>1.59</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.6</v>
@@ -6800,7 +6800,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR29" t="n">
         <v>1.6</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -9198,7 +9198,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR40" t="n">
         <v>2.26</v>
@@ -9849,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.89</v>
@@ -10285,10 +10285,10 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR45" t="n">
         <v>1.32</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR46" t="n">
         <v>1.27</v>
@@ -10724,7 +10724,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR47" t="n">
         <v>2.83</v>
@@ -11157,7 +11157,7 @@
         <v>3</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ49" t="n">
         <v>2.44</v>
@@ -11593,7 +11593,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.9</v>
@@ -12250,7 +12250,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR54" t="n">
         <v>1.72</v>
@@ -12904,7 +12904,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR57" t="n">
         <v>1.95</v>
@@ -13991,7 +13991,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.44</v>
@@ -14863,10 +14863,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR66" t="n">
         <v>1.44</v>
@@ -15084,7 +15084,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR67" t="n">
         <v>1.11</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.44</v>
@@ -15738,7 +15738,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR70" t="n">
         <v>1.81</v>
@@ -15953,10 +15953,10 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR71" t="n">
         <v>1.66</v>
@@ -16171,7 +16171,7 @@
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.11</v>
@@ -16392,7 +16392,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR73" t="n">
         <v>1.8</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.44</v>
@@ -18787,7 +18787,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.8</v>
@@ -19008,7 +19008,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR85" t="n">
         <v>1.53</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.5</v>
@@ -19441,7 +19441,7 @@
         <v>0.75</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.8</v>
@@ -19880,7 +19880,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR89" t="n">
         <v>1.76</v>
@@ -20098,7 +20098,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR90" t="n">
         <v>1.52</v>
@@ -20316,7 +20316,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR91" t="n">
         <v>1.91</v>
@@ -20531,10 +20531,10 @@
         <v>0.6</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR92" t="n">
         <v>1.36</v>
@@ -20970,7 +20970,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR94" t="n">
         <v>2.2</v>
@@ -21842,7 +21842,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR98" t="n">
         <v>1.34</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.6</v>
@@ -22493,7 +22493,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.1</v>
@@ -22711,7 +22711,7 @@
         <v>1.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.3</v>
@@ -23150,7 +23150,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR104" t="n">
         <v>1.65</v>
@@ -23365,7 +23365,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.8</v>
@@ -24022,7 +24022,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR108" t="n">
         <v>1.21</v>
@@ -25327,10 +25327,10 @@
         <v>0.5</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR114" t="n">
         <v>1.27</v>
@@ -25548,7 +25548,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR115" t="n">
         <v>1.09</v>
@@ -25763,7 +25763,7 @@
         <v>0</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.7</v>
@@ -26635,10 +26635,10 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR120" t="n">
         <v>1.39</v>
@@ -26853,10 +26853,10 @@
         <v>1.33</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR121" t="n">
         <v>1.3</v>
@@ -27507,7 +27507,7 @@
         <v>0.4</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.9</v>
@@ -27725,7 +27725,7 @@
         <v>0.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.5600000000000001</v>
@@ -27946,7 +27946,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR126" t="n">
         <v>1.59</v>
@@ -28164,7 +28164,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR127" t="n">
         <v>1.24</v>
@@ -29251,7 +29251,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.33</v>
@@ -29469,7 +29469,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.8</v>
@@ -29690,7 +29690,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR134" t="n">
         <v>1.62</v>
@@ -29905,10 +29905,10 @@
         <v>0.86</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR135" t="n">
         <v>1.32</v>
@@ -30780,7 +30780,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR139" t="n">
         <v>1.63</v>
@@ -30998,7 +30998,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR140" t="n">
         <v>1.59</v>
@@ -31434,7 +31434,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR142" t="n">
         <v>1.28</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.1</v>
@@ -32960,7 +32960,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR149" t="n">
         <v>1.97</v>
@@ -33396,7 +33396,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -33611,7 +33611,7 @@
         <v>1.86</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.3</v>
@@ -34047,7 +34047,7 @@
         <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.8</v>
@@ -34701,7 +34701,7 @@
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.11</v>
@@ -34922,7 +34922,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR158" t="n">
         <v>1.82</v>
@@ -37756,7 +37756,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR171" t="n">
         <v>1.81</v>
@@ -37971,7 +37971,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.5</v>
@@ -38189,10 +38189,10 @@
         <v>1.38</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR173" t="n">
         <v>1.58</v>
@@ -38407,7 +38407,7 @@
         <v>0.88</v>
       </c>
       <c r="AP174" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.8</v>
@@ -38625,10 +38625,10 @@
         <v>0.89</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR175" t="n">
         <v>1.58</v>
@@ -39064,7 +39064,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR177" t="n">
         <v>1.63</v>
@@ -39497,10 +39497,10 @@
         <v>0.78</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR179" t="n">
         <v>1.29</v>
@@ -41895,7 +41895,7 @@
         <v>0.78</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.7</v>
@@ -42628,6 +42628,1096 @@
       </c>
       <c r="BP193" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>7834512</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>45893.66666666666</v>
+      </c>
+      <c r="F194" t="n">
+        <v>21</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
+      <c r="L194" t="n">
+        <v>2</v>
+      </c>
+      <c r="M194" t="n">
+        <v>3</v>
+      </c>
+      <c r="N194" t="n">
+        <v>5</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>['59', '90+6']</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>['21', '69', '85']</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>3</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S194" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X194" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>7834518</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>45893.66666666666</v>
+      </c>
+      <c r="F195" t="n">
+        <v>21</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>['12', '60']</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S195" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V195" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X195" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>7834519</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45893.77083333334</v>
+      </c>
+      <c r="F196" t="n">
+        <v>21</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V196" t="n">
+        <v>3</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>7834520</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45893.77083333334</v>
+      </c>
+      <c r="F197" t="n">
+        <v>21</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="n">
+        <v>2</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>3</v>
+      </c>
+      <c r="N197" t="n">
+        <v>4</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['39', '83', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S197" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V197" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X197" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>7834514</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45893.85416666666</v>
+      </c>
+      <c r="F198" t="n">
+        <v>21</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>2</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>['23', '81']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S198" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V198" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X198" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.7</v>
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.91</v>
@@ -5928,7 +5928,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR25" t="n">
         <v>1.58</v>
@@ -7236,7 +7236,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR31" t="n">
         <v>2.41</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.11</v>
@@ -9634,7 +9634,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR42" t="n">
         <v>1.02</v>
@@ -10942,7 +10942,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR48" t="n">
         <v>1.53</v>
@@ -12901,7 +12901,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.91</v>
@@ -13119,7 +13119,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.33</v>
@@ -14430,7 +14430,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR64" t="n">
         <v>1.06</v>
@@ -14648,7 +14648,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR65" t="n">
         <v>1.51</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.33</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.1</v>
@@ -18354,7 +18354,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR82" t="n">
         <v>1.3</v>
@@ -19226,7 +19226,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR86" t="n">
         <v>1.33</v>
@@ -19877,7 +19877,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.7</v>
@@ -21621,7 +21621,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.89</v>
@@ -22932,7 +22932,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR103" t="n">
         <v>1.69</v>
@@ -23583,7 +23583,7 @@
         <v>0.6</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.44</v>
@@ -23804,7 +23804,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR107" t="n">
         <v>1.45</v>
@@ -26199,7 +26199,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.1</v>
@@ -26420,7 +26420,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR119" t="n">
         <v>1.92</v>
@@ -27728,7 +27728,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR125" t="n">
         <v>1.49</v>
@@ -27943,7 +27943,7 @@
         <v>1</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.3</v>
@@ -28600,7 +28600,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR129" t="n">
         <v>1.83</v>
@@ -30995,7 +30995,7 @@
         <v>1.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.82</v>
@@ -31213,7 +31213,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.8</v>
@@ -32088,7 +32088,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR145" t="n">
         <v>1.35</v>
@@ -33178,7 +33178,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR150" t="n">
         <v>1.71</v>
@@ -33829,7 +33829,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.8</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.82</v>
@@ -37753,7 +37753,7 @@
         <v>1.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.3</v>
@@ -37974,7 +37974,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR172" t="n">
         <v>1.39</v>
@@ -38843,7 +38843,7 @@
         <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.9</v>
@@ -39282,7 +39282,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR178" t="n">
         <v>1.15</v>
@@ -42573,13 +42573,13 @@
         <v>8</v>
       </c>
       <c r="AX193" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY193" t="n">
         <v>13</v>
       </c>
       <c r="AZ193" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA193" t="n">
         <v>4</v>
@@ -43718,6 +43718,442 @@
       </c>
       <c r="BP198" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>7834513</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45894.79166666666</v>
+      </c>
+      <c r="F199" t="n">
+        <v>21</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>3</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>['14', '56', '59']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R199" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S199" t="n">
+        <v>8</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U199" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V199" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X199" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>7834511</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45894.875</v>
+      </c>
+      <c r="F200" t="n">
+        <v>21</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>3</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>3</v>
+      </c>
+      <c r="L200" t="n">
+        <v>8</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>8</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>['2', '3', '34', '47', '50', '54', '59', '81']</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S200" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U200" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V200" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X200" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -39583,7 +39583,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>7834509</v>
+        <v>7834501</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -39603,12 +39603,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -39621,122 +39621,122 @@
         <v>1</v>
       </c>
       <c r="L180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="R180" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S180" t="n">
+        <v>5</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V180" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X180" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB180" t="n">
         <v>4.5</v>
       </c>
-      <c r="T180" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U180" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V180" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="W180" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X180" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z180" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA180" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>3.11</v>
-      </c>
       <c r="AC180" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD180" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW180" t="n">
         <v>7</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AK180" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL180" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM180" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN180" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO180" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AP180" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AQ180" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR180" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS180" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AT180" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU180" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV180" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW180" t="n">
-        <v>6</v>
       </c>
       <c r="AX180" t="n">
         <v>7</v>
@@ -39745,55 +39745,55 @@
         <v>10</v>
       </c>
       <c r="AZ180" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB180" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH180" t="n">
         <v>4</v>
       </c>
-      <c r="BC180" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD180" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE180" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF180" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG180" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH180" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BI180" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BJ180" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="BK180" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="BL180" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BM180" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BN180" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BO180" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BP180" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="181">
@@ -39801,7 +39801,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7834501</v>
+        <v>7834509</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -39821,12 +39821,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -39839,122 +39839,122 @@
         <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R181" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S181" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X181" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z181" t="n">
         <v>2.19</v>
       </c>
-      <c r="S181" t="n">
-        <v>5</v>
-      </c>
-      <c r="T181" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U181" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V181" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W181" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X181" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z181" t="n">
+      <c r="AA181" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM181" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA181" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>2</v>
-      </c>
       <c r="AN181" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AO181" t="n">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP181" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AU181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV181" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX181" t="n">
         <v>7</v>
@@ -39963,55 +39963,55 @@
         <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC181" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD181" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BE181" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF181" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG181" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BH181" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BI181" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BJ181" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="BK181" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="BL181" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BM181" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BN181" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="BO181" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="BP181" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="182">
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>7834518</v>
+        <v>7834512</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,19 +42655,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -42676,176 +42676,176 @@
         <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>['12', '60']</t>
+          <t>['59', '90+6']</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '69', '85']</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R194" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S194" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="T194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X194" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK194" t="n">
         <v>1.36</v>
       </c>
-      <c r="U194" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V194" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W194" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X194" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL194" t="n">
         <v>0</v>
       </c>
       <c r="AM194" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AN194" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO194" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.91</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS194" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AU194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV194" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX194" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY194" t="n">
         <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA194" t="n">
         <v>3</v>
       </c>
       <c r="BB194" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC194" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD194" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE194" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF194" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH194" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BK194" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL194" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BO194" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="195">
@@ -42853,7 +42853,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7834512</v>
+        <v>7834518</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -42873,19 +42873,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -42894,176 +42894,176 @@
         <v>2</v>
       </c>
       <c r="M195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>['59', '90+6']</t>
+          <t>['12', '60']</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>['21', '69', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R195" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S195" t="n">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="T195" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U195" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V195" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X195" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP195" t="n">
         <v>2.4</v>
-      </c>
-      <c r="V195" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W195" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X195" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM195" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN195" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO195" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP195" t="n">
-        <v>1.2</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.91</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AS195" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
         <v>3</v>
       </c>
-      <c r="AV195" t="n">
-        <v>7</v>
-      </c>
       <c r="AW195" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX195" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY195" t="n">
         <v>12</v>
       </c>
       <c r="AZ195" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA195" t="n">
         <v>3</v>
       </c>
       <c r="BB195" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC195" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD195" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BE195" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF195" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG195" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH195" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI195" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ195" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BK195" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BL195" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BM195" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BN195" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BO195" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP195" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="196">
@@ -43071,7 +43071,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>7834520</v>
+        <v>7834519</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -43091,197 +43091,197 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
       </c>
       <c r="K196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V196" t="n">
         <v>3</v>
       </c>
-      <c r="N196" t="n">
-        <v>4</v>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>['39', '83', '90+2']</t>
-        </is>
-      </c>
-      <c r="Q196" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R196" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S196" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T196" t="n">
+      <c r="W196" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR196" t="n">
         <v>1.5</v>
       </c>
-      <c r="U196" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V196" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W196" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X196" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Y196" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z196" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA196" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB196" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC196" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD196" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE196" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF196" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG196" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH196" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI196" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ196" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK196" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM196" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN196" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO196" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP196" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ196" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR196" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AS196" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU196" t="n">
         <v>6</v>
       </c>
       <c r="AV196" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW196" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ196" t="n">
         <v>7</v>
       </c>
-      <c r="AY196" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ196" t="n">
-        <v>13</v>
-      </c>
       <c r="BA196" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BB196" t="n">
         <v>3</v>
       </c>
       <c r="BC196" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD196" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="BE196" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BF196" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="BG196" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BH196" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="BI196" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="BJ196" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="BK196" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="BL196" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="BM196" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="BN196" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="BO196" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="BP196" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="197">
@@ -43289,7 +43289,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>7834519</v>
+        <v>7834520</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -43309,197 +43309,197 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['39', '83', '90+2']</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="R197" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S197" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="T197" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U197" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V197" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W197" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X197" t="n">
-        <v>7.2</v>
+        <v>8.25</v>
       </c>
       <c r="Y197" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z197" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA197" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB197" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC197" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AD197" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AE197" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF197" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AG197" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH197" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI197" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AJ197" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AK197" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL197" t="n">
         <v>0</v>
       </c>
       <c r="AM197" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AN197" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO197" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AP197" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU197" t="n">
         <v>6</v>
       </c>
       <c r="AV197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW197" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX197" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY197" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ197" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA197" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BB197" t="n">
         <v>3</v>
       </c>
       <c r="BC197" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD197" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="BE197" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF197" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="BG197" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BH197" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="BI197" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BJ197" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="BK197" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="BL197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM197" t="n">
         <v>2.38</v>
       </c>
-      <c r="BM197" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BN197" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="BO197" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP197" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="198">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.3</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.8</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.7</v>
@@ -7669,10 +7669,10 @@
         <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
         <v>1.76</v>
@@ -8108,7 +8108,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR35" t="n">
         <v>1.02</v>
@@ -9198,7 +9198,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR40" t="n">
         <v>1.72</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.33</v>
@@ -11814,7 +11814,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR52" t="n">
         <v>2.07</v>
@@ -12247,10 +12247,10 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR54" t="n">
         <v>1.22</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.8</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.7</v>
@@ -13776,7 +13776,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR61" t="n">
         <v>1.74</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.45</v>
@@ -15517,7 +15517,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.89</v>
@@ -16174,7 +16174,7 @@
         <v>1</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR72" t="n">
         <v>1.11</v>
@@ -16828,7 +16828,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR75" t="n">
         <v>1.05</v>
@@ -17482,7 +17482,7 @@
         <v>2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
         <v>1.57</v>
@@ -17915,7 +17915,7 @@
         <v>0.75</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ80" t="n">
         <v>1</v>
@@ -18351,7 +18351,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.5</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.82</v>
@@ -22278,7 +22278,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR100" t="n">
         <v>1.61</v>
@@ -22496,7 +22496,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR101" t="n">
         <v>1.23</v>
@@ -22714,7 +22714,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR102" t="n">
         <v>1.25</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.82</v>
@@ -24237,7 +24237,7 @@
         <v>3</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ109" t="n">
         <v>2.44</v>
@@ -24673,7 +24673,7 @@
         <v>0.5</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ111" t="n">
         <v>0.9</v>
@@ -26420,7 +26420,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR119" t="n">
         <v>1.8</v>
@@ -27074,7 +27074,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR122" t="n">
         <v>1.44</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.8</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.91</v>
@@ -28600,7 +28600,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -28815,7 +28815,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.45</v>
@@ -30344,7 +30344,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR137" t="n">
         <v>1.43</v>
@@ -30559,10 +30559,10 @@
         <v>0</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR138" t="n">
         <v>1.59</v>
@@ -31649,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.3</v>
@@ -32742,7 +32742,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR148" t="n">
         <v>1.37</v>
@@ -32957,7 +32957,7 @@
         <v>0.75</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.91</v>
@@ -33178,7 +33178,7 @@
         <v>1</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR150" t="n">
         <v>1.5</v>
@@ -34265,7 +34265,7 @@
         <v>0.71</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.9</v>
@@ -34486,7 +34486,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR156" t="n">
         <v>1.39</v>
@@ -36009,7 +36009,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.6</v>
@@ -36445,7 +36445,7 @@
         <v>1.86</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.89</v>
@@ -36666,7 +36666,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR166" t="n">
         <v>1.9</v>
@@ -37102,7 +37102,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR168" t="n">
         <v>1.94</v>
@@ -37320,7 +37320,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR169" t="n">
         <v>1.64</v>
@@ -39061,7 +39061,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ177" t="n">
         <v>0.91</v>
@@ -39933,10 +39933,10 @@
         <v>1.44</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR181" t="n">
         <v>1.39</v>
@@ -40154,7 +40154,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR182" t="n">
         <v>1.48</v>
@@ -40372,7 +40372,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR183" t="n">
         <v>1.55</v>
@@ -41459,7 +41459,7 @@
         <v>2.38</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ188" t="n">
         <v>2.44</v>
@@ -42331,7 +42331,7 @@
         <v>1.11</v>
       </c>
       <c r="AP192" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ192" t="n">
         <v>1</v>
@@ -44154,6 +44154,660 @@
       </c>
       <c r="BP200" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>7834529</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45899.66666666666</v>
+      </c>
+      <c r="F201" t="n">
+        <v>22</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>1</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S201" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U201" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V201" t="n">
+        <v>3</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X201" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>7834522</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>45899.77083333334</v>
+      </c>
+      <c r="F202" t="n">
+        <v>22</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>3</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="n">
+        <v>4</v>
+      </c>
+      <c r="L202" t="n">
+        <v>4</v>
+      </c>
+      <c r="M202" t="n">
+        <v>1</v>
+      </c>
+      <c r="N202" t="n">
+        <v>5</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>['6', '33', '45+2', '90+2']</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S202" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U202" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V202" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X202" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>7834526</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45899.875</v>
+      </c>
+      <c r="F203" t="n">
+        <v>22</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R203" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S203" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V203" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X203" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -39583,7 +39583,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>7834501</v>
+        <v>7834509</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -39603,12 +39603,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -39621,122 +39621,122 @@
         <v>1</v>
       </c>
       <c r="L180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R180" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S180" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V180" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X180" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z180" t="n">
         <v>2.19</v>
       </c>
-      <c r="S180" t="n">
-        <v>5</v>
-      </c>
-      <c r="T180" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U180" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V180" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W180" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X180" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z180" t="n">
+      <c r="AA180" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM180" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA180" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC180" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD180" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK180" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL180" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM180" t="n">
-        <v>2</v>
-      </c>
       <c r="AN180" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AO180" t="n">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP180" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.44</v>
+        <v>1.18</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AU180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV180" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX180" t="n">
         <v>7</v>
@@ -39745,55 +39745,55 @@
         <v>10</v>
       </c>
       <c r="AZ180" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB180" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC180" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD180" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BE180" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF180" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG180" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BH180" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BI180" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BJ180" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="BK180" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="BL180" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BM180" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BN180" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="BO180" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="BP180" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="181">
@@ -39801,7 +39801,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7834509</v>
+        <v>7834501</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -39821,12 +39821,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -39839,122 +39839,122 @@
         <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="R181" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S181" t="n">
+        <v>5</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V181" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X181" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB181" t="n">
         <v>4.5</v>
       </c>
-      <c r="T181" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U181" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V181" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="W181" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X181" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z181" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA181" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>3.11</v>
-      </c>
       <c r="AC181" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW181" t="n">
         <v>7</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN181" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO181" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AP181" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ181" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR181" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS181" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AT181" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU181" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV181" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW181" t="n">
-        <v>6</v>
       </c>
       <c r="AX181" t="n">
         <v>7</v>
@@ -39963,55 +39963,55 @@
         <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB181" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH181" t="n">
         <v>4</v>
       </c>
-      <c r="BC181" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD181" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE181" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF181" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG181" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH181" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BI181" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BJ181" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="BK181" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="BL181" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BM181" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BN181" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BO181" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BP181" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="182">
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>7834512</v>
+        <v>7834518</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,19 +42655,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -42676,176 +42676,176 @@
         <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>['59', '90+6']</t>
+          <t>['12', '60']</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>['21', '69', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R194" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S194" t="n">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="T194" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V194" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X194" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP194" t="n">
         <v>2.4</v>
-      </c>
-      <c r="V194" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W194" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X194" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM194" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN194" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO194" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP194" t="n">
-        <v>1.2</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.91</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AS194" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AU194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV194" t="n">
         <v>3</v>
       </c>
-      <c r="AV194" t="n">
-        <v>7</v>
-      </c>
       <c r="AW194" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX194" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY194" t="n">
         <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA194" t="n">
         <v>3</v>
       </c>
       <c r="BB194" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC194" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD194" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BE194" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF194" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH194" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BK194" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BL194" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BO194" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="195">
@@ -42853,7 +42853,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7834518</v>
+        <v>7834512</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -42873,19 +42873,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -42894,176 +42894,176 @@
         <v>2</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>['12', '60']</t>
+          <t>['59', '90+6']</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '69', '85']</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R195" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S195" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="T195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X195" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK195" t="n">
         <v>1.36</v>
       </c>
-      <c r="U195" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V195" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W195" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X195" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL195" t="n">
         <v>0</v>
       </c>
       <c r="AM195" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AN195" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO195" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.91</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS195" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AU195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV195" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW195" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX195" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY195" t="n">
         <v>12</v>
       </c>
       <c r="AZ195" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA195" t="n">
         <v>3</v>
       </c>
       <c r="BB195" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC195" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD195" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE195" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF195" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG195" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH195" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI195" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="BJ195" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BK195" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL195" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="BM195" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="BN195" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BO195" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP195" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="196">
@@ -43071,7 +43071,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>7834519</v>
+        <v>7834520</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -43091,197 +43091,197 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
       </c>
       <c r="K196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['39', '83', '90+2']</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="R196" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S196" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="T196" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U196" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V196" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W196" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X196" t="n">
-        <v>7.2</v>
+        <v>8.25</v>
       </c>
       <c r="Y196" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z196" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA196" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AD196" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF196" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AG196" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH196" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI196" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AJ196" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AK196" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL196" t="n">
         <v>0</v>
       </c>
       <c r="AM196" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AN196" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO196" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AP196" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU196" t="n">
         <v>6</v>
       </c>
       <c r="AV196" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW196" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX196" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY196" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ196" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA196" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BB196" t="n">
         <v>3</v>
       </c>
       <c r="BC196" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD196" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="BE196" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF196" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="BG196" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BH196" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="BI196" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BJ196" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="BK196" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="BL196" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM196" t="n">
         <v>2.38</v>
       </c>
-      <c r="BM196" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BN196" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="BO196" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP196" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="197">
@@ -43289,7 +43289,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>7834520</v>
+        <v>7834519</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -43309,197 +43309,197 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R197" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S197" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V197" t="n">
         <v>3</v>
       </c>
-      <c r="N197" t="n">
-        <v>4</v>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>['39', '83', '90+2']</t>
-        </is>
-      </c>
-      <c r="Q197" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R197" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S197" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T197" t="n">
+      <c r="W197" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X197" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR197" t="n">
         <v>1.5</v>
       </c>
-      <c r="U197" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V197" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W197" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X197" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Y197" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z197" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA197" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB197" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC197" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD197" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE197" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG197" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH197" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI197" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ197" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK197" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM197" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN197" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO197" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP197" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ197" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR197" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AS197" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU197" t="n">
         <v>6</v>
       </c>
       <c r="AV197" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW197" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ197" t="n">
         <v>7</v>
       </c>
-      <c r="AY197" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ197" t="n">
-        <v>13</v>
-      </c>
       <c r="BA197" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BB197" t="n">
         <v>3</v>
       </c>
       <c r="BC197" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD197" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="BE197" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BF197" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="BG197" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BH197" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="BI197" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="BJ197" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="BK197" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="BL197" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="BM197" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="BN197" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="BO197" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="BP197" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="198">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP203"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -3094,7 +3094,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.33</v>
@@ -7890,7 +7890,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR34" t="n">
         <v>2.18</v>
@@ -8326,7 +8326,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR36" t="n">
         <v>0.86</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.82</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.4</v>
@@ -12686,7 +12686,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR56" t="n">
         <v>2.13</v>
@@ -12901,7 +12901,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.91</v>
@@ -13558,7 +13558,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR60" t="n">
         <v>1.24</v>
@@ -13773,7 +13773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.18</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.33</v>
@@ -17700,7 +17700,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR79" t="n">
         <v>2.41</v>
@@ -18133,7 +18133,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.9</v>
@@ -18790,7 +18790,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR84" t="n">
         <v>1.22</v>
@@ -19008,7 +19008,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR85" t="n">
         <v>1.62</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.7</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.7</v>
@@ -23368,7 +23368,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR105" t="n">
         <v>1.47</v>
@@ -23801,7 +23801,7 @@
         <v>0.6</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.44</v>
@@ -24458,7 +24458,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR110" t="n">
         <v>2.08</v>
@@ -26417,7 +26417,7 @@
         <v>0.6</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ119" t="n">
         <v>1</v>
@@ -27292,7 +27292,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR123" t="n">
         <v>1.51</v>
@@ -28379,7 +28379,7 @@
         <v>2</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.89</v>
@@ -29472,7 +29472,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR133" t="n">
         <v>1.39</v>
@@ -31213,10 +31213,10 @@
         <v>1.17</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR141" t="n">
         <v>1.92</v>
@@ -32085,7 +32085,7 @@
         <v>0.57</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ145" t="n">
         <v>1</v>
@@ -33832,7 +33832,7 @@
         <v>2</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR153" t="n">
         <v>1.64</v>
@@ -34050,7 +34050,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR154" t="n">
         <v>1.34</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.82</v>
@@ -35794,7 +35794,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR162" t="n">
         <v>1.88</v>
@@ -37317,7 +37317,7 @@
         <v>0</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ169" t="n">
         <v>0.4</v>
@@ -37535,7 +37535,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.3</v>
@@ -38410,7 +38410,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR174" t="n">
         <v>1.47</v>
@@ -40805,7 +40805,7 @@
         <v>0.5</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.7</v>
@@ -41026,7 +41026,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR186" t="n">
         <v>2.03</v>
@@ -42116,7 +42116,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR191" t="n">
         <v>1.49</v>
@@ -44075,7 +44075,7 @@
         <v>0.5</v>
       </c>
       <c r="AP200" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.45</v>
@@ -44808,6 +44808,442 @@
       </c>
       <c r="BP203" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>7834521</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45900.66666666666</v>
+      </c>
+      <c r="F204" t="n">
+        <v>22</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>1</v>
+      </c>
+      <c r="N204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S204" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X204" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>7834524</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45900.66666666666</v>
+      </c>
+      <c r="F205" t="n">
+        <v>22</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S205" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X205" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.6</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.89</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR32" t="n">
         <v>1.38</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.82</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.18</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.82</v>
@@ -8541,10 +8541,10 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR37" t="n">
         <v>2.89</v>
@@ -8762,7 +8762,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR38" t="n">
         <v>2.26</v>
@@ -8977,10 +8977,10 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR39" t="n">
         <v>0.66</v>
@@ -9416,7 +9416,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR41" t="n">
         <v>0.83</v>
@@ -9631,7 +9631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.5</v>
@@ -11160,7 +11160,7 @@
         <v>1</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR49" t="n">
         <v>0.86</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.4</v>
@@ -12029,10 +12029,10 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR53" t="n">
         <v>1.72</v>
@@ -12465,10 +12465,10 @@
         <v>0.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR55" t="n">
         <v>1.65</v>
@@ -13122,7 +13122,7 @@
         <v>2</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR58" t="n">
         <v>1.41</v>
@@ -13340,7 +13340,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR59" t="n">
         <v>1.28</v>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.82</v>
@@ -13994,7 +13994,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR62" t="n">
         <v>1.14</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -15084,7 +15084,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ67" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR67" t="n">
         <v>1.15</v>
@@ -15956,7 +15956,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR71" t="n">
         <v>1.66</v>
@@ -16389,10 +16389,10 @@
         <v>0</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR73" t="n">
         <v>1.34</v>
@@ -16607,7 +16607,7 @@
         <v>0.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.91</v>
@@ -17046,7 +17046,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR76" t="n">
         <v>1.9</v>
@@ -17261,7 +17261,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.6</v>
@@ -18572,7 +18572,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR83" t="n">
         <v>1.15</v>
@@ -19223,7 +19223,7 @@
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.91</v>
@@ -19880,7 +19880,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR89" t="n">
         <v>1.76</v>
@@ -20098,7 +20098,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR90" t="n">
         <v>1.52</v>
@@ -20313,7 +20313,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.3</v>
@@ -20752,7 +20752,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR93" t="n">
         <v>1.74</v>
@@ -21188,7 +21188,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR95" t="n">
         <v>1.12</v>
@@ -21403,7 +21403,7 @@
         <v>0.6</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ96" t="n">
         <v>1</v>
@@ -21839,7 +21839,7 @@
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.91</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5</v>
@@ -23586,7 +23586,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR106" t="n">
         <v>1.21</v>
@@ -23804,7 +23804,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR107" t="n">
         <v>1.73</v>
@@ -24019,7 +24019,7 @@
         <v>0.4</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.45</v>
@@ -24240,7 +24240,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR109" t="n">
         <v>1.56</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.82</v>
@@ -24891,7 +24891,7 @@
         <v>1.4</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.6</v>
@@ -25112,7 +25112,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR113" t="n">
         <v>1.55</v>
@@ -25984,7 +25984,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR117" t="n">
         <v>1.35</v>
@@ -26199,7 +26199,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.45</v>
@@ -26856,7 +26856,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR121" t="n">
         <v>1.3</v>
@@ -27071,7 +27071,7 @@
         <v>2</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.18</v>
@@ -29254,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR132" t="n">
         <v>1.52</v>
@@ -29687,7 +29687,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.91</v>
@@ -30123,7 +30123,7 @@
         <v>0.83</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.9</v>
@@ -30341,7 +30341,7 @@
         <v>2.17</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.18</v>
@@ -30777,7 +30777,7 @@
         <v>1.14</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.7</v>
@@ -30998,7 +30998,7 @@
         <v>2</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR140" t="n">
         <v>1.59</v>
@@ -31434,7 +31434,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR142" t="n">
         <v>1.94</v>
@@ -31867,7 +31867,7 @@
         <v>1.57</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.6</v>
@@ -32521,7 +32521,7 @@
         <v>0.14</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.5</v>
@@ -33393,7 +33393,7 @@
         <v>0.75</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ151" t="n">
         <v>0.91</v>
@@ -33611,7 +33611,7 @@
         <v>0.5</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.45</v>
@@ -34701,10 +34701,10 @@
         <v>0.5</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR157" t="n">
         <v>1.84</v>
@@ -34922,7 +34922,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR158" t="n">
         <v>1.82</v>
@@ -35140,7 +35140,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR159" t="n">
         <v>1.15</v>
@@ -35355,10 +35355,10 @@
         <v>1.14</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR160" t="n">
         <v>1.6</v>
@@ -35573,10 +35573,10 @@
         <v>0.57</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR161" t="n">
         <v>1.72</v>
@@ -36227,10 +36227,10 @@
         <v>0.43</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR164" t="n">
         <v>1.44</v>
@@ -36881,10 +36881,10 @@
         <v>2.57</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ167" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR167" t="n">
         <v>1.53</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ168" t="n">
         <v>1</v>
@@ -38628,7 +38628,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR175" t="n">
         <v>1.58</v>
@@ -39936,7 +39936,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR181" t="n">
         <v>1.77</v>
@@ -40151,7 +40151,7 @@
         <v>1.11</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ182" t="n">
         <v>1</v>
@@ -40369,7 +40369,7 @@
         <v>0</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ183" t="n">
         <v>0.4</v>
@@ -40587,10 +40587,10 @@
         <v>1.13</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR184" t="n">
         <v>1.51</v>
@@ -40808,7 +40808,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR185" t="n">
         <v>1.69</v>
@@ -41241,7 +41241,7 @@
         <v>1.75</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.89</v>
@@ -41462,7 +41462,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ188" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AR188" t="n">
         <v>1.78</v>
@@ -41677,7 +41677,7 @@
         <v>1.67</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.6</v>
@@ -41898,7 +41898,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR190" t="n">
         <v>1.29</v>
@@ -43642,7 +43642,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR198" t="n">
         <v>1.44</v>
@@ -45244,6 +45244,1096 @@
       </c>
       <c r="BP205" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>7834525</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45900.77083333334</v>
+      </c>
+      <c r="F206" t="n">
+        <v>22</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>3</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>3</v>
+      </c>
+      <c r="L206" t="n">
+        <v>5</v>
+      </c>
+      <c r="M206" t="n">
+        <v>1</v>
+      </c>
+      <c r="N206" t="n">
+        <v>6</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['2', '22', '30', '59', '75']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S206" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V206" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X206" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>7834528</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45900.77083333334</v>
+      </c>
+      <c r="F207" t="n">
+        <v>22</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>1</v>
+      </c>
+      <c r="L207" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>1</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R207" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S207" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V207" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X207" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>7834523</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45900.77083333334</v>
+      </c>
+      <c r="F208" t="n">
+        <v>22</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="n">
+        <v>2</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" t="n">
+        <v>2</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S208" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U208" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V208" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X208" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>7834527</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45900.85416666666</v>
+      </c>
+      <c r="F209" t="n">
+        <v>22</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="n">
+        <v>2</v>
+      </c>
+      <c r="L209" t="n">
+        <v>2</v>
+      </c>
+      <c r="M209" t="n">
+        <v>1</v>
+      </c>
+      <c r="N209" t="n">
+        <v>3</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>['24', '51']</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R209" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S209" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U209" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V209" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W209" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X209" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>7834530</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45900.85416666666</v>
+      </c>
+      <c r="F210" t="n">
+        <v>22</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>2</v>
+      </c>
+      <c r="K210" t="n">
+        <v>3</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="n">
+        <v>3</v>
+      </c>
+      <c r="N210" t="n">
+        <v>5</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>['25', '74']</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>['8', '43', '49']</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R210" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S210" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V210" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X210" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -39583,7 +39583,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>7834509</v>
+        <v>7834501</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -39603,12 +39603,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -39621,122 +39621,122 @@
         <v>1</v>
       </c>
       <c r="L180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="R180" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S180" t="n">
+        <v>5</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V180" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X180" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB180" t="n">
         <v>4.5</v>
       </c>
-      <c r="T180" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U180" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V180" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="W180" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X180" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z180" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA180" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>3.11</v>
-      </c>
       <c r="AC180" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD180" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW180" t="n">
         <v>7</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AK180" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL180" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM180" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN180" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO180" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AP180" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ180" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR180" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS180" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AT180" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU180" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV180" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW180" t="n">
-        <v>6</v>
       </c>
       <c r="AX180" t="n">
         <v>7</v>
@@ -39745,55 +39745,55 @@
         <v>10</v>
       </c>
       <c r="AZ180" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB180" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH180" t="n">
         <v>4</v>
       </c>
-      <c r="BC180" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD180" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE180" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF180" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG180" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH180" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BI180" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BJ180" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="BK180" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="BL180" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BM180" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BN180" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BO180" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BP180" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="181">
@@ -39801,7 +39801,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7834501</v>
+        <v>7834509</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -39821,12 +39821,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -39839,122 +39839,122 @@
         <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R181" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S181" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X181" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z181" t="n">
         <v>2.19</v>
       </c>
-      <c r="S181" t="n">
-        <v>5</v>
-      </c>
-      <c r="T181" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U181" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V181" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W181" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X181" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z181" t="n">
+      <c r="AA181" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM181" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA181" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>2</v>
-      </c>
       <c r="AN181" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AO181" t="n">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP181" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.4</v>
+        <v>1.18</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AU181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV181" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX181" t="n">
         <v>7</v>
@@ -39963,55 +39963,55 @@
         <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC181" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD181" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BE181" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF181" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG181" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BH181" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BI181" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BJ181" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="BK181" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="BL181" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BM181" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BN181" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="BO181" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="BP181" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="182">
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>7834518</v>
+        <v>7834512</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,19 +42655,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -42676,176 +42676,176 @@
         <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>['12', '60']</t>
+          <t>['59', '90+6']</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '69', '85']</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R194" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S194" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="T194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X194" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK194" t="n">
         <v>1.36</v>
       </c>
-      <c r="U194" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V194" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W194" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X194" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL194" t="n">
         <v>0</v>
       </c>
       <c r="AM194" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AN194" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO194" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.91</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS194" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AU194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV194" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX194" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY194" t="n">
         <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA194" t="n">
         <v>3</v>
       </c>
       <c r="BB194" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC194" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD194" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE194" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF194" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH194" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BK194" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL194" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BO194" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="195">
@@ -42853,7 +42853,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7834512</v>
+        <v>7834518</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -42873,19 +42873,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -42894,176 +42894,176 @@
         <v>2</v>
       </c>
       <c r="M195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>['59', '90+6']</t>
+          <t>['12', '60']</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>['21', '69', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R195" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S195" t="n">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="T195" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U195" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V195" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X195" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP195" t="n">
         <v>2.4</v>
-      </c>
-      <c r="V195" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W195" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X195" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM195" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN195" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO195" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP195" t="n">
-        <v>1.2</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.91</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AS195" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
         <v>3</v>
       </c>
-      <c r="AV195" t="n">
-        <v>7</v>
-      </c>
       <c r="AW195" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX195" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY195" t="n">
         <v>12</v>
       </c>
       <c r="AZ195" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA195" t="n">
         <v>3</v>
       </c>
       <c r="BB195" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC195" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD195" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BE195" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF195" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG195" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH195" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI195" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ195" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BK195" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BL195" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BM195" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BN195" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BO195" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP195" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="196">
@@ -43071,7 +43071,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>7834520</v>
+        <v>7834519</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -43091,197 +43091,197 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
       </c>
       <c r="K196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V196" t="n">
         <v>3</v>
       </c>
-      <c r="N196" t="n">
-        <v>4</v>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>['39', '83', '90+2']</t>
-        </is>
-      </c>
-      <c r="Q196" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R196" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S196" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T196" t="n">
+      <c r="W196" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR196" t="n">
         <v>1.5</v>
       </c>
-      <c r="U196" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V196" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W196" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X196" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Y196" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z196" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA196" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB196" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC196" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD196" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE196" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF196" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG196" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH196" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI196" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ196" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK196" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM196" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN196" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO196" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP196" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ196" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR196" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AS196" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU196" t="n">
         <v>6</v>
       </c>
       <c r="AV196" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW196" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ196" t="n">
         <v>7</v>
       </c>
-      <c r="AY196" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ196" t="n">
-        <v>13</v>
-      </c>
       <c r="BA196" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BB196" t="n">
         <v>3</v>
       </c>
       <c r="BC196" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD196" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="BE196" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BF196" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="BG196" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BH196" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="BI196" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="BJ196" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="BK196" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="BL196" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="BM196" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="BN196" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="BO196" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="BP196" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="197">
@@ -43289,7 +43289,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>7834519</v>
+        <v>7834520</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -43309,197 +43309,197 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['39', '83', '90+2']</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="R197" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S197" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="T197" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U197" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V197" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W197" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X197" t="n">
-        <v>7.2</v>
+        <v>8.25</v>
       </c>
       <c r="Y197" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z197" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA197" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB197" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC197" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AD197" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AE197" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF197" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AG197" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH197" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI197" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AJ197" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AK197" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL197" t="n">
         <v>0</v>
       </c>
       <c r="AM197" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AN197" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO197" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AP197" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU197" t="n">
         <v>6</v>
       </c>
       <c r="AV197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW197" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX197" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY197" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ197" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA197" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BB197" t="n">
         <v>3</v>
       </c>
       <c r="BC197" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD197" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="BE197" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF197" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="BG197" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BH197" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="BI197" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BJ197" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="BK197" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="BL197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM197" t="n">
         <v>2.38</v>
       </c>
-      <c r="BM197" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BN197" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="BO197" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP197" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="198">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -46058,13 +46058,13 @@
         <v>3</v>
       </c>
       <c r="AW209" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX209" t="n">
         <v>7</v>
       </c>
       <c r="AY209" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ209" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -45404,16 +45404,16 @@
         <v>6</v>
       </c>
       <c r="AW206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX206" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY206" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ206" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA206" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -45625,13 +45625,13 @@
         <v>10</v>
       </c>
       <c r="AX207" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY207" t="n">
         <v>14</v>
       </c>
       <c r="AZ207" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA207" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.08</v>
@@ -4402,7 +4402,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.45</v>
@@ -6582,7 +6582,7 @@
         <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR28" t="n">
         <v>1.44</v>
@@ -11378,7 +11378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR50" t="n">
         <v>1.69</v>
@@ -11593,7 +11593,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.91</v>
@@ -14863,7 +14863,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.55</v>
@@ -17264,7 +17264,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR77" t="n">
         <v>1.76</v>
@@ -19005,7 +19005,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.42</v>
@@ -22060,7 +22060,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR99" t="n">
         <v>1.4</v>
@@ -22493,7 +22493,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ101" t="n">
         <v>1</v>
@@ -25112,7 +25112,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR113" t="n">
         <v>1.5</v>
@@ -26853,7 +26853,7 @@
         <v>1.33</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.75</v>
@@ -29036,7 +29036,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR131" t="n">
         <v>1.76</v>
@@ -31870,7 +31870,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR144" t="n">
         <v>1.5</v>
@@ -34701,7 +34701,7 @@
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.4</v>
@@ -36230,7 +36230,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR164" t="n">
         <v>1.87</v>
@@ -38407,7 +38407,7 @@
         <v>0.88</v>
       </c>
       <c r="AP174" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.82</v>
@@ -41680,7 +41680,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR189" t="n">
         <v>1.69</v>
@@ -42985,7 +42985,7 @@
         <v>1</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.92</v>
@@ -46341,7 +46341,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>7834539</v>
+        <v>7834537</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -46361,197 +46361,197 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K211" t="n">
         <v>1</v>
       </c>
       <c r="L211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>['31', '47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R211" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S211" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="T211" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="U211" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V211" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="W211" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X211" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK211" t="n">
         <v>1.32</v>
       </c>
-      <c r="X211" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y211" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z211" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA211" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB211" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC211" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD211" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE211" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF211" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG211" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH211" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI211" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ211" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK211" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL211" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AM211" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AN211" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AO211" t="n">
-        <v>0.45</v>
+        <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0.42</v>
+        <v>1.45</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="AU211" t="n">
         <v>5</v>
       </c>
       <c r="AV211" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB211" t="n">
         <v>3</v>
       </c>
-      <c r="AW211" t="n">
+      <c r="BC211" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE211" t="n">
         <v>8</v>
       </c>
-      <c r="AX211" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY211" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ211" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA211" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB211" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC211" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD211" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BE211" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF211" t="n">
-        <v>4.65</v>
+        <v>2.65</v>
       </c>
       <c r="BG211" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BH211" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="BI211" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BJ211" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="BK211" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BL211" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BM211" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="BN211" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="BO211" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="BP211" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="212">
@@ -46559,7 +46559,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>7834537</v>
+        <v>7834539</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -46579,197 +46579,197 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K212" t="n">
         <v>1</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
+          <t>['31', '47']</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
       <c r="Q212" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="R212" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S212" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="T212" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U212" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V212" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="W212" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X212" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Y212" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z212" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG212" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA212" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB212" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AC212" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD212" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE212" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF212" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG212" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH212" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI212" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AJ212" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AK212" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AL212" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AM212" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AN212" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AO212" t="n">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="AU212" t="n">
         <v>5</v>
       </c>
       <c r="AV212" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC212" t="n">
         <v>6</v>
       </c>
-      <c r="AW212" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX212" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY212" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ212" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA212" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB212" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC212" t="n">
-        <v>9</v>
-      </c>
       <c r="BD212" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="BE212" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF212" t="n">
-        <v>2.65</v>
+        <v>4.65</v>
       </c>
       <c r="BG212" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BH212" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="BI212" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BJ212" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="BK212" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="BL212" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BM212" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="BN212" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="BO212" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="BP212" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="213">
@@ -48232,7 +48232,7 @@
         <v>2.64</v>
       </c>
       <c r="AU219" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV219" t="n">
         <v>7</v>
@@ -48244,7 +48244,7 @@
         <v>5</v>
       </c>
       <c r="AY219" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ219" t="n">
         <v>12</v>
@@ -48296,6 +48296,224 @@
       </c>
       <c r="BP219" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>7834538</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>45915.83333333334</v>
+      </c>
+      <c r="F220" t="n">
+        <v>23</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>2</v>
+      </c>
+      <c r="N220" t="n">
+        <v>3</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['77', '86']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S220" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X220" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -28465,7 +28465,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>7834445</v>
+        <v>7834442</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -28485,197 +28485,197 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>['43', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>2.84</v>
+        <v>2.03</v>
       </c>
       <c r="R129" t="n">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="S129" t="n">
-        <v>4.5</v>
+        <v>6.66</v>
       </c>
       <c r="T129" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="U129" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V129" t="n">
-        <v>3.72</v>
+        <v>2.8</v>
       </c>
       <c r="W129" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="X129" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y129" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.33</v>
+        <v>1.39</v>
       </c>
       <c r="AA129" t="n">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="AB129" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AD129" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AF129" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AG129" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AI129" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AJ129" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK129" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL129" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AM129" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AN129" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="AO129" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.56</v>
+        <v>3.09</v>
       </c>
       <c r="AU129" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV129" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AW129" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX129" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY129" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AZ129" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA129" t="n">
         <v>6</v>
       </c>
       <c r="BB129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD129" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="BE129" t="n">
-        <v>9.6</v>
+        <v>10.25</v>
       </c>
       <c r="BF129" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BG129" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="BH129" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI129" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="BJ129" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="BK129" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BL129" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BM129" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="BN129" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="BO129" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP129" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="130">
@@ -28683,7 +28683,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>7834442</v>
+        <v>7834445</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -28703,197 +28703,197 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '48']</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>2.03</v>
+        <v>2.84</v>
       </c>
       <c r="R130" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="S130" t="n">
-        <v>6.66</v>
+        <v>4.5</v>
       </c>
       <c r="T130" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="U130" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V130" t="n">
-        <v>2.8</v>
+        <v>3.72</v>
       </c>
       <c r="W130" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="X130" t="n">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.39</v>
+        <v>2.33</v>
       </c>
       <c r="AA130" t="n">
-        <v>4.46</v>
+        <v>3</v>
       </c>
       <c r="AB130" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AD130" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AF130" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG130" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AH130" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI130" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AJ130" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AK130" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL130" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AM130" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AN130" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="AO130" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AT130" t="n">
-        <v>3.09</v>
+        <v>2.56</v>
       </c>
       <c r="AU130" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW130" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX130" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY130" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ130" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA130" t="n">
         <v>6</v>
       </c>
       <c r="BB130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD130" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="BE130" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="BF130" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BG130" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="BH130" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="BI130" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BJ130" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="BK130" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BL130" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="BM130" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="BN130" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="BO130" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="BP130" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="131">
@@ -31299,7 +31299,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>7834469</v>
+        <v>7834461</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -31319,197 +31319,197 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K142" t="n">
         <v>2</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" t="n">
         <v>2</v>
       </c>
       <c r="N142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>['16', '22']</t>
+          <t>['45+4', '62']</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>2.65</v>
+        <v>3.53</v>
       </c>
       <c r="R142" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S142" t="n">
-        <v>4.86</v>
+        <v>3.35</v>
       </c>
       <c r="T142" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U142" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V142" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X142" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF142" t="n">
         <v>2.45</v>
       </c>
-      <c r="V142" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="W142" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X142" t="n">
+      <c r="AG142" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC142" t="n">
         <v>8</v>
       </c>
-      <c r="Y142" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AJ142" t="n">
+      <c r="BD142" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN142" t="n">
         <v>1.7</v>
       </c>
-      <c r="AK142" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL142" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM142" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AN142" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP142" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ142" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR142" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS142" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT142" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU142" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV142" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW142" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY142" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ142" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA142" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB142" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC142" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD142" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BE142" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF142" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG142" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH142" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI142" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BJ142" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BK142" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BL142" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BM142" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BN142" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BO142" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BP142" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="143">
@@ -31517,7 +31517,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>7834461</v>
+        <v>7834469</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -31537,197 +31537,197 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K143" t="n">
         <v>2</v>
       </c>
       <c r="L143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
         <v>2</v>
       </c>
       <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>['16', '22']</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R143" t="n">
+        <v>2</v>
+      </c>
+      <c r="S143" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U143" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V143" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X143" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV143" t="n">
         <v>3</v>
       </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>['45+4', '62']</t>
-        </is>
-      </c>
-      <c r="Q143" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R143" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S143" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T143" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U143" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V143" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W143" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X143" t="n">
+      <c r="AW143" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE143" t="n">
         <v>9</v>
       </c>
-      <c r="Y143" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE143" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF143" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ143" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK143" t="n">
+      <c r="BF143" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI143" t="n">
         <v>1.42</v>
       </c>
-      <c r="AL143" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AM143" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN143" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO143" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP143" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ143" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR143" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS143" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AT143" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV143" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW143" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX143" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY143" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ143" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA143" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB143" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC143" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD143" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BE143" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF143" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BG143" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH143" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI143" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BJ143" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BK143" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="BL143" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="BM143" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BN143" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BO143" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="BP143" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="144">
@@ -31953,7 +31953,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>7834468</v>
+        <v>7834465</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -31973,12 +31973,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -31991,179 +31991,179 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
         <v>2</v>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>['54', '90+4']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>['89', '90+9']</t>
+          <t>['66', '85']</t>
         </is>
       </c>
       <c r="Q145" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R145" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S145" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U145" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V145" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X145" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB145" t="n">
         <v>3</v>
       </c>
-      <c r="R145" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S145" t="n">
-        <v>4</v>
-      </c>
-      <c r="T145" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U145" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V145" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W145" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X145" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA145" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AC145" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD145" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE145" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH145" t="n">
+      <c r="BC145" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI145" t="n">
         <v>1.41</v>
       </c>
-      <c r="AI145" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK145" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AL145" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM145" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN145" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO145" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AP145" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ145" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR145" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS145" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AT145" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AU145" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV145" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW145" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX145" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY145" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ145" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA145" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB145" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC145" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD145" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BE145" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BF145" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BG145" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BH145" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="BI145" t="n">
-        <v>1.37</v>
-      </c>
       <c r="BJ145" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="BK145" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="BL145" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BM145" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="BN145" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO145" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="BP145" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="146">
@@ -32171,7 +32171,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>7834464</v>
+        <v>7834468</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -32191,197 +32191,197 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M146" t="n">
         <v>2</v>
       </c>
       <c r="N146" t="n">
+        <v>4</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>['54', '90+4']</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>['89', '90+9']</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
         <v>3</v>
       </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>['9', '75']</t>
-        </is>
-      </c>
-      <c r="Q146" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R146" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="S146" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="T146" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U146" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V146" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="W146" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X146" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Y146" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Z146" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AA146" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AB146" t="n">
-        <v>3.32</v>
+        <v>3.96</v>
       </c>
       <c r="AC146" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AD146" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE146" t="n">
         <v>1.5</v>
       </c>
       <c r="AF146" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AG146" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AH146" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AI146" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AJ146" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AK146" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AL146" t="n">
         <v>1.32</v>
       </c>
       <c r="AM146" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AN146" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO146" t="n">
-        <v>0.57</v>
+        <v>0.14</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.91</v>
+        <v>0.55</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AU146" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV146" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW146" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX146" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY146" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ146" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BA146" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB146" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BC146" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BD146" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="BE146" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="BF146" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="BG146" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BH146" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="BI146" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="BJ146" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="BK146" t="n">
         <v>1.73</v>
       </c>
       <c r="BL146" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BM146" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="BN146" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="BO146" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="BP146" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="147">
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>7834465</v>
+        <v>7834464</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,22 +32409,22 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
         <v>1</v>
@@ -32437,169 +32437,169 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>['66', '85']</t>
+          <t>['9', '75']</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="R147" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="S147" t="n">
-        <v>2.6</v>
+        <v>3.88</v>
       </c>
       <c r="T147" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U147" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V147" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="W147" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X147" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Y147" t="n">
         <v>1.05</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.93</v>
+        <v>2.02</v>
       </c>
       <c r="AA147" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO147" t="n">
         <v>3.02</v>
       </c>
-      <c r="AB147" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE147" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AK147" t="n">
+      <c r="BP147" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS147" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AT147" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV147" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX147" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY147" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB147" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC147" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD147" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE147" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF147" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BG147" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH147" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI147" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BJ147" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BK147" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BL147" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BM147" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BN147" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO147" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BP147" t="n">
-        <v>1.42</v>
       </c>
     </row>
     <row r="148">
@@ -32825,7 +32825,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>7834475</v>
+        <v>7834480</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -32845,197 +32845,197 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I149" t="n">
         <v>1</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['4', '70']</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['79', '88']</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>2.3</v>
+        <v>3.48</v>
       </c>
       <c r="R149" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S149" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="T149" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U149" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V149" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="W149" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X149" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Y149" t="n">
         <v>1.05</v>
       </c>
       <c r="Z149" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="AA149" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AB149" t="n">
-        <v>5.73</v>
+        <v>2.8</v>
       </c>
       <c r="AC149" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD149" t="n">
-        <v>7.5</v>
+        <v>7.74</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AG149" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH149" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AI149" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AJ149" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AK149" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL149" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AM149" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AN149" t="n">
-        <v>2.33</v>
+        <v>0.33</v>
       </c>
       <c r="AO149" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP149" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP149" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AQ149" t="n">
-        <v>0.42</v>
+        <v>0.92</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.2</v>
+        <v>0.97</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="AU149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC149" t="n">
         <v>7</v>
       </c>
-      <c r="AV149" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW149" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB149" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC149" t="n">
-        <v>13</v>
-      </c>
       <c r="BD149" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="BE149" t="n">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="BF149" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="BG149" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BH149" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="BI149" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="BJ149" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="BK149" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="BL149" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="BM149" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="BN149" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="BO149" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BP149" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="150">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>7834480</v>
+        <v>7834479</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,197 +33063,197 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N150" t="n">
         <v>4</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['4', '70']</t>
+          <t>['4', '19', '48']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>['79', '88']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="R150" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S150" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T150" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U150" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V150" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X150" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA150" t="n">
         <v>3.2</v>
       </c>
-      <c r="W150" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X150" t="n">
+      <c r="AB150" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU150" t="n">
         <v>9</v>
       </c>
-      <c r="Y150" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>7.74</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI150" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ150" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK150" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL150" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AM150" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN150" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AO150" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP150" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ150" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR150" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AS150" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AT150" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU150" t="n">
+      <c r="AV150" t="n">
         <v>4</v>
-      </c>
-      <c r="AV150" t="n">
-        <v>5</v>
       </c>
       <c r="AW150" t="n">
         <v>12</v>
       </c>
       <c r="AX150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY150" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AZ150" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA150" t="n">
         <v>9</v>
       </c>
-      <c r="BA150" t="n">
-        <v>4</v>
-      </c>
       <c r="BB150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC150" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BD150" t="n">
         <v>1.6</v>
       </c>
       <c r="BE150" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BH150" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BJ150" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BK150" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BL150" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BM150" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="BN150" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BO150" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>7834479</v>
+        <v>7834475</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>['4', '19', '48']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="R151" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S151" t="n">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="T151" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U151" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="V151" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="W151" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X151" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z151" t="n">
-        <v>2.31</v>
+        <v>1.72</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AB151" t="n">
-        <v>3.25</v>
+        <v>5.73</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AD151" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AE151" t="n">
         <v>1.33</v>
       </c>
       <c r="AF151" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="AG151" t="n">
         <v>2.22</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AJ151" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AN151" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO151" t="n">
-        <v>1.86</v>
+        <v>0.5</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.18</v>
+        <v>0.42</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AU151" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV151" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW151" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX151" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY151" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA151" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB151" t="n">
         <v>5</v>
       </c>
       <c r="BC151" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD151" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="BE151" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="BF151" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BH151" t="n">
         <v>4.33</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BJ151" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BL151" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="BM151" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="152">
@@ -33915,7 +33915,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>7834474</v>
+        <v>7834476</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -33935,197 +33935,197 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="I154" t="n">
         <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>2</v>
+      </c>
+      <c r="N154" t="n">
         <v>3</v>
       </c>
-      <c r="M154" t="n">
-        <v>1</v>
-      </c>
-      <c r="N154" t="n">
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>['39', '60']</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R154" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S154" t="n">
+        <v>7</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X154" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU154" t="n">
         <v>4</v>
       </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>['24', '59', '90+1']</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="Q154" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R154" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S154" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T154" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U154" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V154" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="W154" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X154" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA154" t="n">
+      <c r="AV154" t="n">
         <v>3</v>
       </c>
-      <c r="AB154" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH154" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI154" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AJ154" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK154" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL154" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM154" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN154" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO154" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP154" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ154" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AR154" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AS154" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT154" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AU154" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV154" t="n">
-        <v>1</v>
-      </c>
       <c r="AW154" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX154" t="n">
         <v>6</v>
       </c>
       <c r="AY154" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ154" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA154" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB154" t="n">
         <v>3</v>
       </c>
       <c r="BC154" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD154" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK154" t="n">
         <v>1.67</v>
       </c>
-      <c r="BE154" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BF154" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG154" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH154" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BI154" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BJ154" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="BK154" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BL154" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="BM154" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="BN154" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BO154" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="BP154" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="155">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>7834476</v>
+        <v>7834474</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,197 +34153,197 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N155" t="n">
+        <v>4</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['24', '59', '90+1']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S155" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V155" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X155" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA155" t="n">
         <v>3</v>
       </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>['39', '60']</t>
-        </is>
-      </c>
-      <c r="Q155" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R155" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S155" t="n">
-        <v>7</v>
-      </c>
-      <c r="T155" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U155" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V155" t="n">
-        <v>3</v>
-      </c>
-      <c r="W155" t="n">
+      <c r="AB155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL155" t="n">
         <v>1.33</v>
       </c>
-      <c r="X155" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y155" t="n">
+      <c r="AM155" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS155" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z155" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB155" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AC155" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD155" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AE155" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF155" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP155" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ155" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AT155" t="n">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="AU155" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW155" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AX155" t="n">
         <v>6</v>
       </c>
       <c r="AY155" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ155" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA155" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BB155" t="n">
         <v>3</v>
       </c>
       <c r="BC155" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD155" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BE155" t="n">
-        <v>10.25</v>
+        <v>6.5</v>
       </c>
       <c r="BF155" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="BG155" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH155" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="BI155" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="BJ155" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="BK155" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BL155" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="BO155" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="156">
@@ -34351,7 +34351,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>7834477</v>
+        <v>7834478</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -34371,197 +34371,197 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
         <v>1</v>
       </c>
       <c r="L156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['27', '58', '90+3']</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="R156" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S156" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U156" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X156" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI156" t="n">
         <v>2.23</v>
       </c>
-      <c r="S156" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="T156" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U156" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V156" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W156" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X156" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y156" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z156" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA156" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB156" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AC156" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD156" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE156" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF156" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG156" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH156" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI156" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ156" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AK156" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AL156" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AM156" t="n">
-        <v>2.3</v>
+        <v>3.53</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="AO156" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.91</v>
+        <v>0.4</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.42</v>
+        <v>0.68</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.26</v>
+        <v>2.07</v>
       </c>
       <c r="AU156" t="n">
         <v>8</v>
       </c>
       <c r="AV156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW156" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AX156" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AY156" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AZ156" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="BA156" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BB156" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC156" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="BD156" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP156" t="n">
         <v>1.44</v>
-      </c>
-      <c r="BE156" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="BF156" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG156" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH156" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI156" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BJ156" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BK156" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BL156" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM156" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BN156" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BO156" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BP156" t="n">
-        <v>1.41</v>
       </c>
     </row>
     <row r="157">
@@ -34569,7 +34569,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>7834478</v>
+        <v>7834477</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -34589,197 +34589,197 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" t="n">
         <v>1</v>
       </c>
       <c r="L157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>['27', '58', '90+3']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="R157" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="S157" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="T157" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="U157" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V157" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="W157" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="X157" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z157" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AA157" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB157" t="n">
         <v>5.75</v>
       </c>
-      <c r="AB157" t="n">
-        <v>9.75</v>
-      </c>
       <c r="AC157" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AD157" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AF157" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="AG157" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AH157" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AI157" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL157" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AM157" t="n">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="AN157" t="n">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="AO157" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.4</v>
+        <v>0.91</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="AS157" t="n">
-        <v>0.68</v>
+        <v>1.42</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.07</v>
+        <v>3.26</v>
       </c>
       <c r="AU157" t="n">
         <v>8</v>
       </c>
       <c r="AV157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW157" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AX157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AY157" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AZ157" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA157" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BB157" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC157" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BD157" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="BE157" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="BF157" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="BG157" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH157" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BI157" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BJ157" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="BK157" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="BL157" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="BM157" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="BN157" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BO157" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="BP157" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="158">
@@ -35877,7 +35877,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>7834482</v>
+        <v>7834483</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -35897,197 +35897,197 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N163" t="n">
         <v>2</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>['23', '41']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R163" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S163" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T163" t="n">
         <v>1.5</v>
       </c>
       <c r="U163" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V163" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W163" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X163" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z163" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AA163" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AB163" t="n">
-        <v>3.4</v>
+        <v>4.04</v>
       </c>
       <c r="AC163" t="n">
         <v>1.05</v>
       </c>
       <c r="AD163" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF163" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AG163" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI163" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AJ163" t="n">
         <v>1.7</v>
       </c>
       <c r="AK163" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL163" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AM163" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AN163" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AO163" t="n">
-        <v>1.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.73</v>
+        <v>0.4</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AT163" t="n">
-        <v>3.23</v>
+        <v>2.6</v>
       </c>
       <c r="AU163" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW163" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX163" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY163" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ163" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC163" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD163" t="n">
         <v>1.6</v>
       </c>
       <c r="BE163" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="BF163" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BG163" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BH163" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI163" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BJ163" t="n">
         <v>2.5</v>
       </c>
       <c r="BK163" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="BL163" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BM163" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="BN163" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BO163" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BP163" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="164">
@@ -36095,7 +36095,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>7834483</v>
+        <v>7834482</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -36115,197 +36115,197 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I164" t="n">
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N164" t="n">
         <v>2</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['23', '41']</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R164" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S164" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T164" t="n">
         <v>1.5</v>
       </c>
       <c r="U164" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V164" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W164" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X164" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z164" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AA164" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB164" t="n">
-        <v>4.04</v>
+        <v>3.4</v>
       </c>
       <c r="AC164" t="n">
         <v>1.05</v>
       </c>
       <c r="AD164" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF164" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AG164" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AH164" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI164" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AJ164" t="n">
         <v>1.7</v>
       </c>
       <c r="AK164" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS164" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL164" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AM164" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AN164" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO164" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP164" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ164" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AR164" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS164" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AT164" t="n">
-        <v>2.6</v>
+        <v>3.23</v>
       </c>
       <c r="AU164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB164" t="n">
         <v>5</v>
       </c>
-      <c r="AV164" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW164" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX164" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY164" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ164" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA164" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB164" t="n">
-        <v>3</v>
-      </c>
       <c r="BC164" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD164" t="n">
         <v>1.6</v>
       </c>
       <c r="BE164" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="BF164" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="BG164" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BH164" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI164" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BJ164" t="n">
         <v>2.5</v>
       </c>
       <c r="BK164" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="BL164" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BM164" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="BN164" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="BO164" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BP164" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="165">
@@ -37403,7 +37403,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>7834491</v>
+        <v>7834494</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -37423,12 +37423,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -37444,176 +37444,176 @@
         <v>2</v>
       </c>
       <c r="M170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>['20', '86']</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2</v>
+      </c>
+      <c r="S170" t="n">
+        <v>6</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V170" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X170" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU170" t="n">
         <v>3</v>
       </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>['19', '68']</t>
-        </is>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="Q170" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R170" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S170" t="n">
-        <v>9</v>
-      </c>
-      <c r="T170" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U170" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V170" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W170" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X170" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y170" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z170" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA170" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB170" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC170" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD170" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE170" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF170" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AG170" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH170" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI170" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ170" t="n">
+      <c r="AV170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN170" t="n">
         <v>1.62</v>
       </c>
-      <c r="AK170" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AL170" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AM170" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AN170" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AO170" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP170" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ170" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR170" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS170" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT170" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AU170" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV170" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW170" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX170" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY170" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ170" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA170" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB170" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC170" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD170" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BE170" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF170" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG170" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BH170" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="BI170" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BJ170" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BK170" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BL170" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BM170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN170" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BO170" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="BP170" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="171">
@@ -37621,7 +37621,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>7834495</v>
+        <v>7834491</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -37641,197 +37641,197 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
         <v>3</v>
       </c>
-      <c r="N171" t="n">
-        <v>4</v>
-      </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['19', '68']</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>['7', '33', '46']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="R171" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="S171" t="n">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="T171" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="U171" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="V171" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="W171" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="X171" t="n">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="Y171" t="n">
         <v>1.06</v>
       </c>
       <c r="Z171" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="AA171" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AB171" t="n">
-        <v>2.92</v>
+        <v>10</v>
       </c>
       <c r="AC171" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AD171" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AE171" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AF171" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="AG171" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH171" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ171" t="n">
         <v>1.62</v>
       </c>
-      <c r="AI171" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ171" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AK171" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AL171" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AM171" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="AN171" t="n">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="AO171" t="n">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.64</v>
+        <v>2.91</v>
       </c>
       <c r="AU171" t="n">
         <v>8</v>
       </c>
       <c r="AV171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW171" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX171" t="n">
         <v>8</v>
       </c>
       <c r="AY171" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AZ171" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA171" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BB171" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BC171" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BD171" t="n">
-        <v>2.03</v>
+        <v>1.06</v>
       </c>
       <c r="BE171" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="BF171" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BG171" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH171" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="BI171" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="BJ171" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="BK171" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="BL171" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BM171" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BN171" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="BO171" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="BP171" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="172">
@@ -37839,7 +37839,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>7834494</v>
+        <v>7834495</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -37859,197 +37859,197 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>['20', '86']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '33', '46']</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="R172" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S172" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="T172" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="U172" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="V172" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="W172" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="X172" t="n">
-        <v>8.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="Y172" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z172" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="AA172" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AB172" t="n">
-        <v>5.9</v>
+        <v>2.92</v>
       </c>
       <c r="AC172" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AD172" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE172" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AF172" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AG172" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH172" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AI172" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AJ172" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="AK172" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL172" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AM172" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AN172" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AO172" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.42</v>
+        <v>0.91</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AT172" t="n">
         <v>2.64</v>
       </c>
       <c r="AU172" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV172" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW172" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AX172" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY172" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ172" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BA172" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB172" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC172" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BD172" t="n">
-        <v>1.45</v>
+        <v>2.03</v>
       </c>
       <c r="BE172" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF172" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="BG172" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BH172" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BI172" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="BJ172" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="BK172" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="BL172" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BM172" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BN172" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="BO172" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="BP172" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="173">
@@ -38493,7 +38493,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>7834492</v>
+        <v>7834493</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -38513,197 +38513,197 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M175" t="n">
         <v>1</v>
       </c>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['67', '69']</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="R175" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S175" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="T175" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="U175" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V175" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="W175" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X175" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Y175" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AC175" t="n">
         <v>1.05</v>
       </c>
-      <c r="Z175" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA175" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB175" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AC175" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AD175" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AE175" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF175" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AG175" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH175" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AJ175" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI175" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ175" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AK175" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AL175" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AM175" t="n">
-        <v>1.45</v>
+        <v>3.04</v>
       </c>
       <c r="AN175" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AO175" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.18</v>
+        <v>2.09</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="AT175" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="AU175" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV175" t="n">
         <v>4</v>
       </c>
       <c r="AW175" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AX175" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AY175" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ175" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="BA175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC175" t="n">
         <v>6</v>
       </c>
-      <c r="BB175" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC175" t="n">
-        <v>16</v>
-      </c>
       <c r="BD175" t="n">
-        <v>2.05</v>
+        <v>1.19</v>
       </c>
       <c r="BE175" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF175" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG175" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BH175" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BI175" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="BJ175" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="BK175" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="BL175" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="BM175" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="BN175" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="BO175" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="BP175" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="176">
@@ -38711,7 +38711,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>7834493</v>
+        <v>7834492</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -38731,197 +38731,197 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M176" t="n">
         <v>1</v>
       </c>
       <c r="N176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>['67', '69']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="R176" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S176" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="T176" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="U176" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V176" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="W176" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X176" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y176" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z176" t="n">
-        <v>1.46</v>
+        <v>2.36</v>
       </c>
       <c r="AA176" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="AB176" t="n">
-        <v>8.84</v>
+        <v>2.98</v>
       </c>
       <c r="AC176" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD176" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AE176" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK176" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF176" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG176" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH176" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI176" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AJ176" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK176" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AL176" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AM176" t="n">
-        <v>3.04</v>
+        <v>1.45</v>
       </c>
       <c r="AN176" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AO176" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.09</v>
+        <v>1.18</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="AU176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV176" t="n">
         <v>4</v>
       </c>
       <c r="AW176" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AX176" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AY176" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AZ176" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BA176" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BB176" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BC176" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BD176" t="n">
-        <v>1.19</v>
+        <v>2.05</v>
       </c>
       <c r="BE176" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF176" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="BG176" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BH176" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BI176" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="BJ176" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="BK176" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BL176" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="BM176" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="BN176" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="BO176" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BP176" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="177">
@@ -39583,7 +39583,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>7834501</v>
+        <v>7834509</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -39603,12 +39603,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -39621,122 +39621,122 @@
         <v>1</v>
       </c>
       <c r="L180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R180" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S180" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V180" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X180" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z180" t="n">
         <v>2.19</v>
       </c>
-      <c r="S180" t="n">
-        <v>5</v>
-      </c>
-      <c r="T180" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U180" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V180" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W180" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X180" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z180" t="n">
+      <c r="AA180" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM180" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA180" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC180" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD180" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK180" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL180" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM180" t="n">
-        <v>2</v>
-      </c>
       <c r="AN180" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AO180" t="n">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.4</v>
+        <v>1.18</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AU180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV180" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX180" t="n">
         <v>7</v>
@@ -39745,55 +39745,55 @@
         <v>10</v>
       </c>
       <c r="AZ180" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB180" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC180" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD180" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BE180" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF180" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG180" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BH180" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BI180" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BJ180" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="BK180" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="BL180" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BM180" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BN180" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="BO180" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="BP180" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="181">
@@ -39801,7 +39801,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7834509</v>
+        <v>7834501</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -39821,12 +39821,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -39839,122 +39839,122 @@
         <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="R181" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S181" t="n">
+        <v>5</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V181" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X181" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB181" t="n">
         <v>4.5</v>
       </c>
-      <c r="T181" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U181" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V181" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="W181" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X181" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z181" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA181" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>3.11</v>
-      </c>
       <c r="AC181" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW181" t="n">
         <v>7</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN181" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO181" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AP181" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ181" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR181" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS181" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AT181" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU181" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV181" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW181" t="n">
-        <v>6</v>
       </c>
       <c r="AX181" t="n">
         <v>7</v>
@@ -39963,55 +39963,55 @@
         <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB181" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH181" t="n">
         <v>4</v>
       </c>
-      <c r="BC181" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD181" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE181" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF181" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG181" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH181" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BI181" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BJ181" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="BK181" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="BL181" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BM181" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BN181" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BO181" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BP181" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="182">
@@ -40673,7 +40673,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>7834504</v>
+        <v>7834506</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -40693,197 +40693,197 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>1</v>
       </c>
       <c r="K185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>['18', '52', '54', '60', '62', '68']</t>
+          <t>['45', '58', '90']</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R185" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S185" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="T185" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="U185" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V185" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="W185" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X185" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Y185" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z185" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AA185" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="AB185" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AC185" t="n">
         <v>1.06</v>
       </c>
       <c r="AD185" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE185" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF185" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AG185" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI185" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH185" t="n">
+      <c r="AJ185" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI185" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ185" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AK185" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL185" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM185" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AN185" t="n">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="AO185" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP185" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS185" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ185" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AR185" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS185" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AT185" t="n">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="AU185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV185" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AW185" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX185" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY185" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ185" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC185" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD185" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="BE185" t="n">
-        <v>9.1</v>
+        <v>10.25</v>
       </c>
       <c r="BF185" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="BG185" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BH185" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="BI185" t="n">
         <v>1.33</v>
       </c>
       <c r="BJ185" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BK185" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="BL185" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO185" t="n">
         <v>2.3</v>
       </c>
-      <c r="BM185" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BN185" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BO185" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BP185" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="186">
@@ -40891,7 +40891,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>7834506</v>
+        <v>7834504</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -40911,197 +40911,197 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J186" t="n">
         <v>1</v>
       </c>
       <c r="K186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N186" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>['45', '58', '90']</t>
+          <t>['18', '52', '54', '60', '62', '68']</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R186" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="T186" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U186" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V186" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W186" t="n">
         <v>1.4</v>
       </c>
-      <c r="U186" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V186" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="W186" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X186" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Y186" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z186" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AA186" t="n">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="AB186" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AC186" t="n">
         <v>1.06</v>
       </c>
       <c r="AD186" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE186" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK186" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF186" t="n">
+      <c r="AL186" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA186" t="n">
         <v>3</v>
       </c>
-      <c r="AG186" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH186" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI186" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ186" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK186" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL186" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM186" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN186" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AO186" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AP186" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ186" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AR186" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS186" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT186" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AU186" t="n">
+      <c r="BB186" t="n">
         <v>3</v>
       </c>
-      <c r="AV186" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW186" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX186" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY186" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ186" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA186" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB186" t="n">
-        <v>4</v>
-      </c>
       <c r="BC186" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD186" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="BE186" t="n">
-        <v>10.25</v>
+        <v>9.1</v>
       </c>
       <c r="BF186" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="BG186" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BH186" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BI186" t="n">
         <v>1.33</v>
       </c>
       <c r="BJ186" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BK186" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BL186" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BM186" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="BN186" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO186" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BP186" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="187">
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>7834518</v>
+        <v>7834512</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,19 +42655,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -42676,176 +42676,176 @@
         <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>['12', '60']</t>
+          <t>['59', '90+6']</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '69', '85']</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R194" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S194" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="T194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X194" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK194" t="n">
         <v>1.36</v>
       </c>
-      <c r="U194" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V194" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W194" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X194" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL194" t="n">
         <v>0</v>
       </c>
       <c r="AM194" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AN194" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO194" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS194" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AU194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV194" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX194" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY194" t="n">
         <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA194" t="n">
         <v>3</v>
       </c>
       <c r="BB194" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC194" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD194" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE194" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF194" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH194" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BK194" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL194" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BO194" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="195">
@@ -42853,7 +42853,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7834512</v>
+        <v>7834518</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -42873,19 +42873,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -42894,176 +42894,176 @@
         <v>2</v>
       </c>
       <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>['12', '60']</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S195" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V195" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X195" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
         <v>3</v>
       </c>
-      <c r="N195" t="n">
+      <c r="AW195" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX195" t="n">
         <v>5</v>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>['59', '90+6']</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>['21', '69', '85']</t>
-        </is>
-      </c>
-      <c r="Q195" t="n">
-        <v>3</v>
-      </c>
-      <c r="R195" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S195" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T195" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U195" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V195" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W195" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X195" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM195" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN195" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO195" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP195" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ195" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AR195" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS195" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT195" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU195" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV195" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW195" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX195" t="n">
-        <v>7</v>
       </c>
       <c r="AY195" t="n">
         <v>12</v>
       </c>
       <c r="AZ195" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA195" t="n">
         <v>3</v>
       </c>
       <c r="BB195" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC195" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD195" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BE195" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF195" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG195" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH195" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI195" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ195" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BK195" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BL195" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BM195" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BN195" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BO195" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP195" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="196">
@@ -43071,7 +43071,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>7834520</v>
+        <v>7834519</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -43091,197 +43091,197 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
       </c>
       <c r="K196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V196" t="n">
         <v>3</v>
       </c>
-      <c r="N196" t="n">
-        <v>4</v>
-      </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>['39', '83', '90+2']</t>
-        </is>
-      </c>
-      <c r="Q196" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R196" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S196" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T196" t="n">
+      <c r="W196" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR196" t="n">
         <v>1.5</v>
       </c>
-      <c r="U196" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V196" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W196" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X196" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Y196" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z196" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA196" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB196" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC196" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD196" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE196" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF196" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG196" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH196" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI196" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ196" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK196" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM196" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN196" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO196" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP196" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ196" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR196" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AS196" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU196" t="n">
         <v>6</v>
       </c>
       <c r="AV196" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW196" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ196" t="n">
         <v>7</v>
       </c>
-      <c r="AY196" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ196" t="n">
-        <v>13</v>
-      </c>
       <c r="BA196" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BB196" t="n">
         <v>3</v>
       </c>
       <c r="BC196" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD196" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="BE196" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BF196" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="BG196" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BH196" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="BI196" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="BJ196" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="BK196" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="BL196" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="BM196" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="BN196" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="BO196" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="BP196" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="197">
@@ -43289,7 +43289,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>7834519</v>
+        <v>7834520</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -43309,197 +43309,197 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['39', '83', '90+2']</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="R197" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S197" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="T197" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U197" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V197" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W197" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X197" t="n">
-        <v>7.2</v>
+        <v>8.25</v>
       </c>
       <c r="Y197" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z197" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA197" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB197" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC197" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AD197" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AE197" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF197" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AG197" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH197" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI197" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AJ197" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AK197" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL197" t="n">
         <v>0</v>
       </c>
       <c r="AM197" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AN197" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO197" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU197" t="n">
         <v>6</v>
       </c>
       <c r="AV197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW197" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX197" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY197" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ197" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA197" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BB197" t="n">
         <v>3</v>
       </c>
       <c r="BC197" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD197" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="BE197" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF197" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="BG197" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BH197" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="BI197" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BJ197" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="BK197" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="BL197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM197" t="n">
         <v>2.38</v>
       </c>
-      <c r="BM197" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BN197" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="BO197" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP197" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="198">
@@ -44815,7 +44815,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>7834524</v>
+        <v>7834521</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -44835,12 +44835,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -44853,179 +44853,179 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>2.94</v>
+        <v>1.71</v>
       </c>
       <c r="R204" t="n">
-        <v>2.04</v>
+        <v>2.69</v>
       </c>
       <c r="S204" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X204" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF204" t="n">
         <v>3.75</v>
       </c>
-      <c r="T204" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U204" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V204" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W204" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X204" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y204" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z204" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA204" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB204" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC204" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD204" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AE204" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF204" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AG204" t="n">
-        <v>2.49</v>
+        <v>1.78</v>
       </c>
       <c r="AH204" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AI204" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AJ204" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK204" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AL204" t="n">
         <v>0</v>
       </c>
       <c r="AM204" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="AN204" t="n">
-        <v>1.22</v>
+        <v>2.64</v>
       </c>
       <c r="AO204" t="n">
         <v>0.8</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ204" t="n">
         <v>0.82</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="AU204" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW204" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AX204" t="n">
         <v>5</v>
       </c>
       <c r="AY204" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AZ204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA204" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BB204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF204" t="n">
         <v>7</v>
       </c>
-      <c r="BD204" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BE204" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF204" t="n">
-        <v>2.65</v>
-      </c>
       <c r="BG204" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BH204" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="BI204" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BJ204" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="BK204" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="BL204" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="BM204" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="BN204" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="BO204" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="BP204" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="205">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>7834521</v>
+        <v>7834524</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,12 +45053,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -45071,179 +45071,179 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="R205" t="n">
-        <v>2.69</v>
+        <v>2.04</v>
       </c>
       <c r="S205" t="n">
-        <v>8.1</v>
+        <v>3.75</v>
       </c>
       <c r="T205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W205" t="n">
         <v>1.3</v>
       </c>
-      <c r="U205" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V205" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W205" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X205" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="AA205" t="n">
-        <v>5.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB205" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD205" t="n">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF205" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="AG205" t="n">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="AH205" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AI205" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AJ205" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AK205" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AL205" t="n">
         <v>0</v>
       </c>
       <c r="AM205" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="AN205" t="n">
-        <v>2.64</v>
+        <v>1.22</v>
       </c>
       <c r="AO205" t="n">
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.82</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT205" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="AU205" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW205" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AX205" t="n">
         <v>5</v>
       </c>
       <c r="AY205" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AZ205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA205" t="n">
         <v>6</v>
       </c>
-      <c r="BA205" t="n">
-        <v>13</v>
-      </c>
       <c r="BB205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC205" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD205" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="BE205" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BF205" t="n">
-        <v>7</v>
+        <v>2.65</v>
       </c>
       <c r="BG205" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BH205" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="BI205" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BJ205" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="BK205" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="BL205" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="BM205" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BN205" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BO205" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="BP205" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>7834528</v>
+        <v>7834523</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I206" t="n">
         <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R206" t="n">
         <v>1.95</v>
       </c>
       <c r="S206" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="T206" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V206" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X206" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH206" t="n">
         <v>1.44</v>
       </c>
-      <c r="U206" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V206" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W206" t="n">
+      <c r="AI206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM206" t="n">
         <v>1.3</v>
       </c>
-      <c r="X206" t="n">
+      <c r="AN206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY206" t="n">
         <v>9</v>
-      </c>
-      <c r="Y206" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z206" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA206" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD206" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE206" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH206" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI206" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN206" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO206" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AP206" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ206" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AR206" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS206" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT206" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AU206" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV206" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW206" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX206" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>14</v>
       </c>
       <c r="AZ206" t="n">
         <v>19</v>
       </c>
       <c r="BA206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BC206" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD206" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BE206" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF206" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="BG206" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BH206" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BI206" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BJ206" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="BL206" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="BM206" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="BO206" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="207">
@@ -45469,7 +45469,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>7834523</v>
+        <v>7834528</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -45489,197 +45489,197 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I207" t="n">
         <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L207" t="n">
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R207" t="n">
         <v>1.95</v>
       </c>
       <c r="S207" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T207" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="U207" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V207" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="W207" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X207" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z207" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA207" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AB207" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AD207" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF207" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG207" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS207" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI207" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ207" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK207" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM207" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN207" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO207" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AP207" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ207" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR207" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS207" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AT207" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU207" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV207" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW207" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX207" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY207" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ207" t="n">
         <v>19</v>
       </c>
       <c r="BA207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB207" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BC207" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD207" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="BE207" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF207" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="BG207" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BH207" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BI207" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BJ207" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="BK207" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="BL207" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="BM207" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BN207" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BO207" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="BP207" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="208">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -28465,7 +28465,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>7834442</v>
+        <v>7834445</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -28485,197 +28485,197 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '48']</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>2.03</v>
+        <v>2.84</v>
       </c>
       <c r="R129" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="S129" t="n">
-        <v>6.66</v>
+        <v>4.5</v>
       </c>
       <c r="T129" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="U129" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V129" t="n">
-        <v>2.8</v>
+        <v>3.72</v>
       </c>
       <c r="W129" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="X129" t="n">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.39</v>
+        <v>2.33</v>
       </c>
       <c r="AA129" t="n">
-        <v>4.46</v>
+        <v>3</v>
       </c>
       <c r="AB129" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AD129" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AF129" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG129" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI129" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AJ129" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AK129" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL129" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AM129" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AN129" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="AO129" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AT129" t="n">
-        <v>3.09</v>
+        <v>2.56</v>
       </c>
       <c r="AU129" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW129" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY129" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ129" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA129" t="n">
         <v>6</v>
       </c>
       <c r="BB129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD129" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="BE129" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="BF129" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BG129" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="BH129" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="BI129" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BJ129" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="BK129" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BL129" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="BM129" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="BN129" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="BO129" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="BP129" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="130">
@@ -28683,7 +28683,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>7834445</v>
+        <v>7834442</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -28703,197 +28703,197 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>['43', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>2.84</v>
+        <v>2.03</v>
       </c>
       <c r="R130" t="n">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="S130" t="n">
-        <v>4.5</v>
+        <v>6.66</v>
       </c>
       <c r="T130" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="U130" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V130" t="n">
-        <v>3.72</v>
+        <v>2.8</v>
       </c>
       <c r="W130" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="X130" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y130" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.33</v>
+        <v>1.39</v>
       </c>
       <c r="AA130" t="n">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="AB130" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AD130" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AF130" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AG130" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AH130" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AI130" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AJ130" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK130" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL130" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AM130" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AN130" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="AO130" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.56</v>
+        <v>3.09</v>
       </c>
       <c r="AU130" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV130" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AW130" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX130" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY130" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AZ130" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA130" t="n">
         <v>6</v>
       </c>
       <c r="BB130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD130" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="BE130" t="n">
-        <v>9.6</v>
+        <v>10.25</v>
       </c>
       <c r="BF130" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BG130" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="BH130" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI130" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="BJ130" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="BK130" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BL130" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="BM130" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="BN130" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="BO130" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP130" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="131">
@@ -31299,7 +31299,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>7834461</v>
+        <v>7834469</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -31319,197 +31319,197 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K142" t="n">
         <v>2</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>2</v>
       </c>
       <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>['16', '22']</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2</v>
+      </c>
+      <c r="S142" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U142" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V142" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X142" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV142" t="n">
         <v>3</v>
       </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>['45+4', '62']</t>
-        </is>
-      </c>
-      <c r="Q142" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R142" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S142" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T142" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U142" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V142" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W142" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X142" t="n">
+      <c r="AW142" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE142" t="n">
         <v>9</v>
       </c>
-      <c r="Y142" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ142" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK142" t="n">
+      <c r="BF142" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI142" t="n">
         <v>1.42</v>
       </c>
-      <c r="AL142" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AM142" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN142" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO142" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP142" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ142" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR142" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS142" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AT142" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV142" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW142" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX142" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY142" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ142" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA142" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB142" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC142" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD142" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BE142" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BF142" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BG142" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH142" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI142" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BJ142" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BK142" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="BL142" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="BM142" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BN142" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BO142" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="BP142" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="143">
@@ -31517,7 +31517,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>7834469</v>
+        <v>7834461</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -31537,197 +31537,197 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K143" t="n">
         <v>2</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
         <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>['16', '22']</t>
+          <t>['45+4', '62']</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>2.65</v>
+        <v>3.53</v>
       </c>
       <c r="R143" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S143" t="n">
-        <v>4.86</v>
+        <v>3.35</v>
       </c>
       <c r="T143" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U143" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V143" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X143" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF143" t="n">
         <v>2.45</v>
       </c>
-      <c r="V143" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="W143" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X143" t="n">
+      <c r="AG143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC143" t="n">
         <v>8</v>
       </c>
-      <c r="Y143" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="AE143" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF143" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AJ143" t="n">
+      <c r="BD143" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN143" t="n">
         <v>1.7</v>
       </c>
-      <c r="AK143" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL143" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM143" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AN143" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP143" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ143" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR143" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS143" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT143" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU143" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV143" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW143" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY143" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ143" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA143" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB143" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC143" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD143" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BE143" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF143" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG143" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH143" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI143" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BJ143" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BK143" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BL143" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BM143" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BN143" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BO143" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BP143" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="144">
@@ -31953,7 +31953,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>7834465</v>
+        <v>7834468</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -31973,12 +31973,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -31991,179 +31991,179 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M145" t="n">
         <v>2</v>
       </c>
       <c r="N145" t="n">
+        <v>4</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>['54', '90+4']</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>['89', '90+9']</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
         <v>3</v>
       </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>['66', '85']</t>
-        </is>
-      </c>
-      <c r="Q145" t="n">
-        <v>4.8</v>
-      </c>
       <c r="R145" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="S145" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="T145" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="U145" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V145" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="W145" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X145" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y145" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Z145" t="n">
-        <v>2.93</v>
+        <v>1.84</v>
       </c>
       <c r="AA145" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="AB145" t="n">
-        <v>2.24</v>
+        <v>3.96</v>
       </c>
       <c r="AC145" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AD145" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF145" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG145" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="AH145" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AP145" t="n">
         <v>1.55</v>
       </c>
-      <c r="AI145" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AK145" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL145" t="n">
+      <c r="AQ145" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS145" t="n">
         <v>1.34</v>
       </c>
-      <c r="AM145" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN145" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO145" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP145" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ145" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR145" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS145" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AT145" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU145" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AV145" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA145" t="n">
         <v>6</v>
       </c>
-      <c r="AW145" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX145" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY145" t="n">
+      <c r="BB145" t="n">
         <v>10</v>
       </c>
-      <c r="AZ145" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB145" t="n">
+      <c r="BC145" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO145" t="n">
         <v>3</v>
       </c>
-      <c r="BC145" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD145" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE145" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF145" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BG145" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH145" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BI145" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BJ145" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BK145" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BL145" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BM145" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BN145" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO145" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BP145" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="146">
@@ -32171,7 +32171,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>7834468</v>
+        <v>7834464</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -32191,197 +32191,197 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M146" t="n">
         <v>2</v>
       </c>
       <c r="N146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>['54', '90+4']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>['89', '90+9']</t>
+          <t>['9', '75']</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R146" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="S146" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="T146" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U146" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V146" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="W146" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X146" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Y146" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Z146" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AA146" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AB146" t="n">
-        <v>3.96</v>
+        <v>3.32</v>
       </c>
       <c r="AC146" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AD146" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AE146" t="n">
         <v>1.5</v>
       </c>
       <c r="AF146" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AG146" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AH146" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AI146" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AJ146" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AK146" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AL146" t="n">
         <v>1.32</v>
       </c>
       <c r="AM146" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR146" t="n">
         <v>1.53</v>
       </c>
-      <c r="AN146" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO146" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AP146" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ146" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR146" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AS146" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="AU146" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ146" t="n">
         <v>11</v>
       </c>
-      <c r="AV146" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW146" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX146" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY146" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ146" t="n">
-        <v>20</v>
-      </c>
       <c r="BA146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC146" t="n">
         <v>10</v>
       </c>
-      <c r="BC146" t="n">
-        <v>16</v>
-      </c>
       <c r="BD146" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="BE146" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="BF146" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="BG146" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="BH146" t="n">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="BI146" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="BJ146" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="BK146" t="n">
         <v>1.73</v>
       </c>
       <c r="BL146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM146" t="n">
         <v>2.1</v>
       </c>
-      <c r="BM146" t="n">
-        <v>1.97</v>
-      </c>
       <c r="BN146" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BO146" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="BP146" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="147">
@@ -32389,7 +32389,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>7834464</v>
+        <v>7834465</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -32409,22 +32409,22 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>1</v>
@@ -32437,169 +32437,169 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>['9', '75']</t>
+          <t>['66', '85']</t>
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S147" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V147" t="n">
         <v>3.2</v>
       </c>
-      <c r="R147" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S147" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U147" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V147" t="n">
-        <v>3.28</v>
-      </c>
       <c r="W147" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X147" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Y147" t="n">
         <v>1.05</v>
       </c>
       <c r="Z147" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL147" t="n">
         <v>2.02</v>
       </c>
-      <c r="AA147" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE147" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AK147" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AL147" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM147" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN147" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO147" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP147" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ147" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AR147" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS147" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT147" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AU147" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV147" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW147" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX147" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY147" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB147" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC147" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD147" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BE147" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BF147" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG147" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BH147" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI147" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BJ147" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BK147" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL147" t="n">
-        <v>2</v>
-      </c>
       <c r="BM147" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="BN147" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO147" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="BP147" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="148">
@@ -32825,7 +32825,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>7834480</v>
+        <v>7834475</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -32845,197 +32845,197 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I149" t="n">
         <v>1</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>['4', '70']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>['79', '88']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="R149" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S149" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="T149" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U149" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V149" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="W149" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X149" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Y149" t="n">
         <v>1.05</v>
       </c>
       <c r="Z149" t="n">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="AA149" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AB149" t="n">
-        <v>2.8</v>
+        <v>5.73</v>
       </c>
       <c r="AC149" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AD149" t="n">
-        <v>7.74</v>
+        <v>7.5</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AG149" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH149" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AI149" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AJ149" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AK149" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL149" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AM149" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.33</v>
+        <v>2.33</v>
       </c>
       <c r="AO149" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP149" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.92</v>
+        <v>0.42</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="AS149" t="n">
-        <v>0.97</v>
+        <v>1.2</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.56</v>
+        <v>2.91</v>
       </c>
       <c r="AU149" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV149" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB149" t="n">
         <v>5</v>
       </c>
-      <c r="AW149" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB149" t="n">
-        <v>3</v>
-      </c>
       <c r="BC149" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD149" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="BE149" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="BF149" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="BG149" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BH149" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="BI149" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BJ149" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="BK149" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="BL149" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="BM149" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="BN149" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="BO149" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BP149" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="150">
@@ -33043,7 +33043,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>7834479</v>
+        <v>7834480</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -33063,197 +33063,197 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N150" t="n">
         <v>4</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>['4', '19', '48']</t>
+          <t>['4', '70']</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['79', '88']</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="R150" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S150" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T150" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U150" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V150" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X150" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA150" t="n">
         <v>3.1</v>
       </c>
-      <c r="W150" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X150" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AB150" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AD150" t="n">
-        <v>8</v>
+        <v>7.74</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AF150" t="n">
-        <v>3.13</v>
+        <v>2.65</v>
       </c>
       <c r="AG150" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL150" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AN150" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO150" t="n">
-        <v>1.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.18</v>
+        <v>0.92</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.42</v>
+        <v>0.97</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="AU150" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AV150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW150" t="n">
         <v>12</v>
       </c>
       <c r="AX150" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY150" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AZ150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA150" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BB150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC150" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BD150" t="n">
         <v>1.6</v>
       </c>
       <c r="BE150" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF150" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="BG150" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BH150" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="BI150" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BJ150" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BK150" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BL150" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BM150" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN150" t="n">
         <v>1.8</v>
       </c>
-      <c r="BN150" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BO150" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="BP150" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="151">
@@ -33261,7 +33261,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>7834475</v>
+        <v>7834479</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -33281,197 +33281,197 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['4', '19', '48']</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="R151" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S151" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="T151" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U151" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="V151" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="W151" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X151" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z151" t="n">
-        <v>1.72</v>
+        <v>2.31</v>
       </c>
       <c r="AA151" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AB151" t="n">
-        <v>5.73</v>
+        <v>3.25</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AD151" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AE151" t="n">
         <v>1.33</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="AG151" t="n">
         <v>2.22</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AI151" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AJ151" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AK151" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL151" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AM151" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AN151" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO151" t="n">
-        <v>0.5</v>
+        <v>1.86</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0.42</v>
+        <v>1.18</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AU151" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV151" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AW151" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX151" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY151" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB151" t="n">
         <v>5</v>
       </c>
       <c r="BC151" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD151" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="BE151" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="BF151" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="BG151" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BH151" t="n">
         <v>4.33</v>
       </c>
       <c r="BI151" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="BJ151" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="BK151" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="BL151" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="BM151" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="BN151" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="BO151" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="BP151" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="152">
@@ -33915,7 +33915,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>7834476</v>
+        <v>7834474</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -33935,197 +33935,197 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I154" t="n">
         <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['24', '59', '90+1']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S154" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X154" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA154" t="n">
         <v>3</v>
       </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>['39', '60']</t>
-        </is>
-      </c>
-      <c r="Q154" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R154" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S154" t="n">
-        <v>7</v>
-      </c>
-      <c r="T154" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U154" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V154" t="n">
-        <v>3</v>
-      </c>
-      <c r="W154" t="n">
+      <c r="AB154" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL154" t="n">
         <v>1.33</v>
       </c>
-      <c r="X154" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y154" t="n">
+      <c r="AM154" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS154" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z154" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB154" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH154" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI154" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ154" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AK154" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL154" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AM154" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AN154" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO154" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP154" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ154" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AR154" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS154" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AT154" t="n">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="AU154" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AV154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW154" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AX154" t="n">
         <v>6</v>
       </c>
       <c r="AY154" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ154" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA154" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BB154" t="n">
         <v>3</v>
       </c>
       <c r="BC154" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD154" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BE154" t="n">
-        <v>10.25</v>
+        <v>6.5</v>
       </c>
       <c r="BF154" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="BG154" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH154" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="BI154" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="BJ154" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="BK154" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BL154" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="BM154" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="BN154" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="BO154" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="BP154" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="155">
@@ -34133,7 +34133,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>7834474</v>
+        <v>7834476</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -34153,197 +34153,197 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>2</v>
+      </c>
+      <c r="N155" t="n">
         <v>3</v>
       </c>
-      <c r="M155" t="n">
-        <v>1</v>
-      </c>
-      <c r="N155" t="n">
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['39', '60']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R155" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S155" t="n">
+        <v>7</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V155" t="n">
+        <v>3</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X155" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU155" t="n">
         <v>4</v>
       </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>['24', '59', '90+1']</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="Q155" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R155" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S155" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T155" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U155" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V155" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="W155" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X155" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA155" t="n">
+      <c r="AV155" t="n">
         <v>3</v>
       </c>
-      <c r="AB155" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC155" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD155" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AE155" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF155" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP155" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ155" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>1</v>
-      </c>
       <c r="AW155" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX155" t="n">
         <v>6</v>
       </c>
       <c r="AY155" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ155" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA155" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB155" t="n">
         <v>3</v>
       </c>
       <c r="BC155" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD155" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK155" t="n">
         <v>1.67</v>
       </c>
-      <c r="BE155" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BI155" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BJ155" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="BK155" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BL155" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="BM155" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="BN155" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BO155" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="BP155" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="156">
@@ -34351,7 +34351,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>7834478</v>
+        <v>7834477</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -34371,197 +34371,197 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" t="n">
         <v>1</v>
       </c>
       <c r="L156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>['27', '58', '90+3']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="R156" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="S156" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="T156" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="U156" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V156" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="W156" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="X156" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AA156" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB156" t="n">
         <v>5.75</v>
       </c>
-      <c r="AB156" t="n">
-        <v>9.75</v>
-      </c>
       <c r="AC156" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AD156" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AF156" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="AG156" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AH156" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AI156" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AJ156" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AK156" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL156" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AM156" t="n">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="AN156" t="n">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="AO156" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.4</v>
+        <v>0.91</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="AS156" t="n">
-        <v>0.68</v>
+        <v>1.42</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.07</v>
+        <v>3.26</v>
       </c>
       <c r="AU156" t="n">
         <v>8</v>
       </c>
       <c r="AV156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW156" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AX156" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AY156" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AZ156" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BA156" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BB156" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC156" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BD156" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="BE156" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="BF156" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="BG156" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH156" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BI156" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BJ156" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="BK156" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="BL156" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="BM156" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="BN156" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BO156" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="BP156" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="157">
@@ -34569,7 +34569,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>7834477</v>
+        <v>7834478</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -34589,197 +34589,197 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
         <v>1</v>
       </c>
       <c r="L157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['27', '58', '90+3']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="R157" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S157" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U157" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X157" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI157" t="n">
         <v>2.23</v>
       </c>
-      <c r="S157" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="T157" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U157" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V157" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W157" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X157" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA157" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB157" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AC157" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE157" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF157" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH157" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI157" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ157" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AL157" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AM157" t="n">
-        <v>2.3</v>
+        <v>3.53</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="AO157" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.91</v>
+        <v>0.4</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.42</v>
+        <v>0.68</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.26</v>
+        <v>2.07</v>
       </c>
       <c r="AU157" t="n">
         <v>8</v>
       </c>
       <c r="AV157" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW157" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AX157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AY157" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AZ157" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="BA157" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BB157" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC157" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="BD157" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP157" t="n">
         <v>1.44</v>
-      </c>
-      <c r="BE157" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="BF157" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG157" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH157" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI157" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BJ157" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BK157" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BL157" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM157" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BN157" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BO157" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BP157" t="n">
-        <v>1.41</v>
       </c>
     </row>
     <row r="158">
@@ -35877,7 +35877,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>7834483</v>
+        <v>7834482</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -35897,197 +35897,197 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N163" t="n">
         <v>2</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['23', '41']</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R163" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S163" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T163" t="n">
         <v>1.5</v>
       </c>
       <c r="U163" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V163" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W163" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X163" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z163" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AA163" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB163" t="n">
-        <v>4.04</v>
+        <v>3.4</v>
       </c>
       <c r="AC163" t="n">
         <v>1.05</v>
       </c>
       <c r="AD163" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF163" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AG163" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AH163" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI163" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AJ163" t="n">
         <v>1.7</v>
       </c>
       <c r="AK163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS163" t="n">
         <v>1.36</v>
       </c>
-      <c r="AL163" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AM163" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AN163" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO163" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP163" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ163" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AR163" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS163" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AT163" t="n">
-        <v>2.6</v>
+        <v>3.23</v>
       </c>
       <c r="AU163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB163" t="n">
         <v>5</v>
       </c>
-      <c r="AV163" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW163" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX163" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY163" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ163" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB163" t="n">
-        <v>3</v>
-      </c>
       <c r="BC163" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD163" t="n">
         <v>1.6</v>
       </c>
       <c r="BE163" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="BF163" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="BG163" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BH163" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI163" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BJ163" t="n">
         <v>2.5</v>
       </c>
       <c r="BK163" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="BL163" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BM163" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="BN163" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="BO163" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BP163" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="164">
@@ -36095,7 +36095,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>7834482</v>
+        <v>7834483</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -36115,197 +36115,197 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I164" t="n">
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N164" t="n">
         <v>2</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>['23', '41']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R164" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S164" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T164" t="n">
         <v>1.5</v>
       </c>
       <c r="U164" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V164" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W164" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X164" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z164" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AA164" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AB164" t="n">
-        <v>3.4</v>
+        <v>4.04</v>
       </c>
       <c r="AC164" t="n">
         <v>1.05</v>
       </c>
       <c r="AD164" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AE164" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF164" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AG164" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AH164" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI164" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AJ164" t="n">
         <v>1.7</v>
       </c>
       <c r="AK164" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL164" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AM164" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AN164" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AO164" t="n">
-        <v>1.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.73</v>
+        <v>0.4</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AT164" t="n">
-        <v>3.23</v>
+        <v>2.6</v>
       </c>
       <c r="AU164" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW164" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX164" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY164" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ164" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB164" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC164" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD164" t="n">
         <v>1.6</v>
       </c>
       <c r="BE164" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="BF164" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BG164" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BH164" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI164" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BJ164" t="n">
         <v>2.5</v>
       </c>
       <c r="BK164" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="BL164" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BM164" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="BN164" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BO164" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BP164" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="165">
@@ -37403,7 +37403,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>7834494</v>
+        <v>7834491</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -37423,12 +37423,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -37444,176 +37444,176 @@
         <v>2</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>['20', '86']</t>
+          <t>['19', '68']</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="R170" t="n">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="S170" t="n">
+        <v>9</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U170" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V170" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X170" t="n">
         <v>6</v>
       </c>
-      <c r="T170" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U170" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="V170" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W170" t="n">
+      <c r="Y170" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE170" t="n">
         <v>1.26</v>
       </c>
-      <c r="X170" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Y170" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z170" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA170" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB170" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AC170" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD170" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE170" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF170" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO170" t="n">
         <v>2.4</v>
       </c>
-      <c r="AG170" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH170" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI170" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ170" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AK170" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL170" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM170" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN170" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO170" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AP170" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ170" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AR170" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS170" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AT170" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AU170" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV170" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW170" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX170" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY170" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ170" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA170" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB170" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC170" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD170" t="n">
+      <c r="BP170" t="n">
         <v>1.45</v>
-      </c>
-      <c r="BE170" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF170" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG170" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BH170" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI170" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BJ170" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BK170" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL170" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM170" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BN170" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BO170" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BP170" t="n">
-        <v>1.38</v>
       </c>
     </row>
     <row r="171">
@@ -37621,7 +37621,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>7834491</v>
+        <v>7834495</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -37641,197 +37641,197 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N171" t="n">
+        <v>4</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['7', '33', '46']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S171" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V171" t="n">
         <v>3</v>
       </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>['19', '68']</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="Q171" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R171" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S171" t="n">
-        <v>9</v>
-      </c>
-      <c r="T171" t="n">
+      <c r="W171" t="n">
         <v>1.33</v>
       </c>
-      <c r="U171" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V171" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W171" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X171" t="n">
-        <v>6</v>
+        <v>8.25</v>
       </c>
       <c r="Y171" t="n">
         <v>1.06</v>
       </c>
       <c r="Z171" t="n">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="AA171" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AB171" t="n">
-        <v>10</v>
+        <v>2.92</v>
       </c>
       <c r="AC171" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AD171" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AE171" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AF171" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="AG171" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH171" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AI171" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AJ171" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AK171" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AL171" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AM171" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="AN171" t="n">
-        <v>2.56</v>
+        <v>1.56</v>
       </c>
       <c r="AO171" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.42</v>
+        <v>0.91</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="AU171" t="n">
         <v>8</v>
       </c>
       <c r="AV171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW171" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AX171" t="n">
         <v>8</v>
       </c>
       <c r="AY171" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ171" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA171" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BB171" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BC171" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BD171" t="n">
-        <v>1.06</v>
+        <v>2.03</v>
       </c>
       <c r="BE171" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF171" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BG171" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH171" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="BI171" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="BJ171" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="BK171" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="BL171" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BM171" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BN171" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BO171" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="BP171" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="172">
@@ -37839,7 +37839,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>7834495</v>
+        <v>7834494</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -37859,197 +37859,197 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['20', '86']</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>['7', '33', '46']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="R172" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S172" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="T172" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U172" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V172" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X172" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE172" t="n">
         <v>1.48</v>
       </c>
-      <c r="U172" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V172" t="n">
-        <v>3</v>
-      </c>
-      <c r="W172" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X172" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Y172" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z172" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA172" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB172" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC172" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD172" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE172" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF172" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AG172" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH172" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AI172" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AJ172" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AK172" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL172" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AM172" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AN172" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AO172" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AT172" t="n">
         <v>2.64</v>
       </c>
       <c r="AU172" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV172" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AW172" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AX172" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY172" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AZ172" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="BA172" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BB172" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BC172" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BD172" t="n">
-        <v>2.03</v>
+        <v>1.45</v>
       </c>
       <c r="BE172" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF172" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="BG172" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BH172" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BI172" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="BJ172" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="BK172" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="BL172" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BM172" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BN172" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="BO172" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="BP172" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="173">
@@ -38493,7 +38493,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>7834493</v>
+        <v>7834492</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -38513,197 +38513,197 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M175" t="n">
         <v>1</v>
       </c>
       <c r="N175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>['67', '69']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="R175" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S175" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="T175" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="U175" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V175" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="W175" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X175" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y175" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z175" t="n">
-        <v>1.46</v>
+        <v>2.36</v>
       </c>
       <c r="AA175" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="AB175" t="n">
-        <v>8.84</v>
+        <v>2.98</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD175" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AE175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK175" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF175" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG175" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH175" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI175" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AJ175" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK175" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AL175" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AM175" t="n">
-        <v>3.04</v>
+        <v>1.45</v>
       </c>
       <c r="AN175" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AO175" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.09</v>
+        <v>1.18</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="AU175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV175" t="n">
         <v>4</v>
       </c>
       <c r="AW175" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AX175" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AY175" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AZ175" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BA175" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BB175" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BC175" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BD175" t="n">
-        <v>1.19</v>
+        <v>2.05</v>
       </c>
       <c r="BE175" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF175" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="BG175" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BH175" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BI175" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="BJ175" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="BK175" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BL175" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="BM175" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="BN175" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="BO175" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BP175" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="176">
@@ -38711,7 +38711,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>7834492</v>
+        <v>7834493</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -38731,197 +38731,197 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M176" t="n">
         <v>1</v>
       </c>
       <c r="N176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['67', '69']</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="R176" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S176" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="T176" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="U176" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V176" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="W176" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X176" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Y176" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AC176" t="n">
         <v>1.05</v>
       </c>
-      <c r="Z176" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA176" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB176" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AC176" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AD176" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AE176" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF176" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AG176" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH176" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AJ176" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI176" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ176" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AK176" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AL176" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AM176" t="n">
-        <v>1.45</v>
+        <v>3.04</v>
       </c>
       <c r="AN176" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AO176" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.18</v>
+        <v>2.09</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="AT176" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="AU176" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV176" t="n">
         <v>4</v>
       </c>
       <c r="AW176" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AX176" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AY176" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AZ176" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="BA176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC176" t="n">
         <v>6</v>
       </c>
-      <c r="BB176" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC176" t="n">
-        <v>16</v>
-      </c>
       <c r="BD176" t="n">
-        <v>2.05</v>
+        <v>1.19</v>
       </c>
       <c r="BE176" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF176" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG176" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BH176" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BI176" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="BJ176" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="BK176" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="BL176" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="BM176" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="BN176" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="BO176" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="BP176" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="177">
@@ -39583,7 +39583,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>7834509</v>
+        <v>7834501</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -39603,12 +39603,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -39621,122 +39621,122 @@
         <v>1</v>
       </c>
       <c r="L180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['9', '64']</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="R180" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S180" t="n">
+        <v>5</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V180" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X180" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB180" t="n">
         <v>4.5</v>
       </c>
-      <c r="T180" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U180" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V180" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="W180" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X180" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z180" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA180" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>3.11</v>
-      </c>
       <c r="AC180" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD180" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW180" t="n">
         <v>7</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AK180" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL180" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM180" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN180" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO180" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AP180" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ180" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR180" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS180" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AT180" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU180" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV180" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW180" t="n">
-        <v>6</v>
       </c>
       <c r="AX180" t="n">
         <v>7</v>
@@ -39745,55 +39745,55 @@
         <v>10</v>
       </c>
       <c r="AZ180" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB180" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH180" t="n">
         <v>4</v>
       </c>
-      <c r="BC180" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD180" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE180" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF180" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG180" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH180" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BI180" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="BJ180" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="BK180" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="BL180" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BM180" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BN180" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BO180" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BP180" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="181">
@@ -39801,7 +39801,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7834501</v>
+        <v>7834509</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -39821,12 +39821,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -39839,122 +39839,122 @@
         <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>['9', '64']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R181" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S181" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X181" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z181" t="n">
         <v>2.19</v>
       </c>
-      <c r="S181" t="n">
-        <v>5</v>
-      </c>
-      <c r="T181" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U181" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V181" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="W181" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X181" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z181" t="n">
+      <c r="AA181" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM181" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA181" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>2</v>
-      </c>
       <c r="AN181" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AO181" t="n">
-        <v>0.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.4</v>
+        <v>1.18</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AU181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV181" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX181" t="n">
         <v>7</v>
@@ -39963,55 +39963,55 @@
         <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC181" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD181" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BE181" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF181" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG181" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BH181" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BI181" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BJ181" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="BK181" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="BL181" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BM181" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BN181" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="BO181" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="BP181" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="182">
@@ -40673,7 +40673,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>7834506</v>
+        <v>7834504</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -40693,197 +40693,197 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J185" t="n">
         <v>1</v>
       </c>
       <c r="K185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N185" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>['45', '58', '90']</t>
+          <t>['18', '52', '54', '60', '62', '68']</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R185" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="T185" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U185" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V185" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W185" t="n">
         <v>1.4</v>
       </c>
-      <c r="U185" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V185" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="W185" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X185" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Y185" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z185" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AA185" t="n">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="AB185" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AC185" t="n">
         <v>1.06</v>
       </c>
       <c r="AD185" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE185" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK185" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF185" t="n">
+      <c r="AL185" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA185" t="n">
         <v>3</v>
       </c>
-      <c r="AG185" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH185" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI185" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ185" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK185" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL185" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AM185" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN185" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AO185" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AP185" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ185" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AR185" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS185" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT185" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AU185" t="n">
+      <c r="BB185" t="n">
         <v>3</v>
       </c>
-      <c r="AV185" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW185" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX185" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY185" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ185" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA185" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB185" t="n">
-        <v>4</v>
-      </c>
       <c r="BC185" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD185" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="BE185" t="n">
-        <v>10.25</v>
+        <v>9.1</v>
       </c>
       <c r="BF185" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="BG185" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BH185" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BI185" t="n">
         <v>1.33</v>
       </c>
       <c r="BJ185" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BK185" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BL185" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BM185" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="BN185" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BO185" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BP185" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="186">
@@ -40891,7 +40891,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>7834504</v>
+        <v>7834506</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -40911,197 +40911,197 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>1</v>
       </c>
       <c r="K186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N186" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>['18', '52', '54', '60', '62', '68']</t>
+          <t>['45', '58', '90']</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R186" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S186" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="T186" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="U186" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V186" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="W186" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X186" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Y186" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z186" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AA186" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="AB186" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AC186" t="n">
         <v>1.06</v>
       </c>
       <c r="AD186" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE186" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF186" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AG186" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI186" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH186" t="n">
+      <c r="AJ186" t="n">
         <v>1.75</v>
       </c>
-      <c r="AI186" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ186" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AK186" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL186" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM186" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AN186" t="n">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="AO186" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP186" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS186" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ186" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AR186" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS186" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AT186" t="n">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="AU186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV186" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AW186" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY186" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ186" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC186" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD186" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="BE186" t="n">
-        <v>9.1</v>
+        <v>10.25</v>
       </c>
       <c r="BF186" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="BG186" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BH186" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="BI186" t="n">
         <v>1.33</v>
       </c>
       <c r="BJ186" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BK186" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="BL186" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO186" t="n">
         <v>2.3</v>
       </c>
-      <c r="BM186" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BN186" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BO186" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BP186" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="187">
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>7834512</v>
+        <v>7834518</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,19 +42655,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -42676,176 +42676,176 @@
         <v>2</v>
       </c>
       <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>2</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>['12', '60']</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S194" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V194" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X194" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV194" t="n">
         <v>3</v>
       </c>
-      <c r="N194" t="n">
+      <c r="AW194" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX194" t="n">
         <v>5</v>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>['59', '90+6']</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>['21', '69', '85']</t>
-        </is>
-      </c>
-      <c r="Q194" t="n">
-        <v>3</v>
-      </c>
-      <c r="R194" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S194" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T194" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U194" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V194" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W194" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X194" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM194" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN194" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO194" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP194" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ194" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AR194" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT194" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU194" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV194" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW194" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX194" t="n">
-        <v>7</v>
       </c>
       <c r="AY194" t="n">
         <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA194" t="n">
         <v>3</v>
       </c>
       <c r="BB194" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC194" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD194" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BE194" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF194" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH194" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BK194" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BL194" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BO194" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="195">
@@ -42853,7 +42853,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7834518</v>
+        <v>7834512</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -42873,19 +42873,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -42894,176 +42894,176 @@
         <v>2</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>['12', '60']</t>
+          <t>['59', '90+6']</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '69', '85']</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R195" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S195" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="T195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X195" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK195" t="n">
         <v>1.36</v>
       </c>
-      <c r="U195" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V195" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W195" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X195" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL195" t="n">
         <v>0</v>
       </c>
       <c r="AM195" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AN195" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO195" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS195" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AU195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV195" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW195" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX195" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY195" t="n">
         <v>12</v>
       </c>
       <c r="AZ195" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA195" t="n">
         <v>3</v>
       </c>
       <c r="BB195" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC195" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD195" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE195" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF195" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG195" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH195" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI195" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="BJ195" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BK195" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL195" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="BM195" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="BN195" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BO195" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP195" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="196">
@@ -43071,7 +43071,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>7834519</v>
+        <v>7834520</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -43091,197 +43091,197 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
       </c>
       <c r="K196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['39', '83', '90+2']</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="R196" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S196" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="T196" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U196" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V196" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W196" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X196" t="n">
-        <v>7.2</v>
+        <v>8.25</v>
       </c>
       <c r="Y196" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z196" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA196" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AD196" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AF196" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AG196" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH196" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI196" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AJ196" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AK196" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL196" t="n">
         <v>0</v>
       </c>
       <c r="AM196" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AN196" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO196" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AU196" t="n">
         <v>6</v>
       </c>
       <c r="AV196" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW196" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX196" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY196" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ196" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA196" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BB196" t="n">
         <v>3</v>
       </c>
       <c r="BC196" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD196" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="BE196" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF196" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="BG196" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="BH196" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="BI196" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BJ196" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="BK196" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="BL196" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM196" t="n">
         <v>2.38</v>
       </c>
-      <c r="BM196" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BN196" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="BO196" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP196" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="197">
@@ -43289,7 +43289,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>7834520</v>
+        <v>7834519</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -43309,197 +43309,197 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R197" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S197" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V197" t="n">
         <v>3</v>
       </c>
-      <c r="N197" t="n">
-        <v>4</v>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>['39', '83', '90+2']</t>
-        </is>
-      </c>
-      <c r="Q197" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R197" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S197" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T197" t="n">
+      <c r="W197" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X197" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR197" t="n">
         <v>1.5</v>
       </c>
-      <c r="U197" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V197" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W197" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X197" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="Y197" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z197" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA197" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB197" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC197" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD197" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE197" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG197" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH197" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI197" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AJ197" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK197" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM197" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN197" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO197" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP197" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ197" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR197" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AS197" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU197" t="n">
         <v>6</v>
       </c>
       <c r="AV197" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW197" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ197" t="n">
         <v>7</v>
       </c>
-      <c r="AY197" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ197" t="n">
-        <v>13</v>
-      </c>
       <c r="BA197" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BB197" t="n">
         <v>3</v>
       </c>
       <c r="BC197" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD197" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="BE197" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BF197" t="n">
-        <v>1.62</v>
+        <v>2.7</v>
       </c>
       <c r="BG197" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BH197" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="BI197" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="BJ197" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="BK197" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="BL197" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="BM197" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="BN197" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="BO197" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="BP197" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="198">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>7834523</v>
+        <v>7834528</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I206" t="n">
         <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R206" t="n">
         <v>1.95</v>
       </c>
       <c r="S206" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T206" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="U206" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V206" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="W206" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X206" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y206" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z206" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA206" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AB206" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC206" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AD206" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE206" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF206" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG206" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH206" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS206" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI206" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN206" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO206" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AP206" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ206" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR206" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS206" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AT206" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU206" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV206" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW206" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX206" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY206" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ206" t="n">
         <v>19</v>
       </c>
       <c r="BA206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BC206" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD206" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="BE206" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF206" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="BG206" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BH206" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BI206" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BJ206" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="BL206" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="BM206" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BO206" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="207">
@@ -45469,7 +45469,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>7834528</v>
+        <v>7834523</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -45489,197 +45489,197 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I207" t="n">
         <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L207" t="n">
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R207" t="n">
         <v>1.95</v>
       </c>
       <c r="S207" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="T207" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V207" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X207" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH207" t="n">
         <v>1.44</v>
       </c>
-      <c r="U207" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V207" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W207" t="n">
+      <c r="AI207" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM207" t="n">
         <v>1.3</v>
       </c>
-      <c r="X207" t="n">
+      <c r="AN207" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY207" t="n">
         <v>9</v>
-      </c>
-      <c r="Y207" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z207" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA207" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB207" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC207" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD207" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE207" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF207" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG207" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH207" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI207" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ207" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK207" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM207" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN207" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO207" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AP207" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ207" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AR207" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS207" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT207" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AU207" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV207" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW207" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX207" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY207" t="n">
-        <v>14</v>
       </c>
       <c r="AZ207" t="n">
         <v>19</v>
       </c>
       <c r="BA207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB207" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BC207" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD207" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BE207" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF207" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="BG207" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BH207" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BI207" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BJ207" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="BK207" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="BL207" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="BM207" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BN207" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="BO207" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="BP207" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -44815,7 +44815,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>7834524</v>
+        <v>7834521</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -44835,12 +44835,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -44853,179 +44853,179 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>2.94</v>
+        <v>1.71</v>
       </c>
       <c r="R204" t="n">
-        <v>2.04</v>
+        <v>2.69</v>
       </c>
       <c r="S204" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X204" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF204" t="n">
         <v>3.75</v>
       </c>
-      <c r="T204" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U204" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V204" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W204" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X204" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y204" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z204" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA204" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB204" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC204" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD204" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AE204" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF204" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AG204" t="n">
-        <v>2.49</v>
+        <v>1.78</v>
       </c>
       <c r="AH204" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AI204" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AJ204" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK204" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AL204" t="n">
         <v>0</v>
       </c>
       <c r="AM204" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="AN204" t="n">
-        <v>1.22</v>
+        <v>2.64</v>
       </c>
       <c r="AO204" t="n">
         <v>0.8</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="AU204" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW204" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AX204" t="n">
         <v>5</v>
       </c>
       <c r="AY204" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AZ204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA204" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BB204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF204" t="n">
         <v>7</v>
       </c>
-      <c r="BD204" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BE204" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF204" t="n">
-        <v>2.65</v>
-      </c>
       <c r="BG204" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BH204" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="BI204" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BJ204" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="BK204" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="BL204" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="BM204" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="BN204" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="BO204" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="BP204" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="205">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>7834521</v>
+        <v>7834524</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,12 +45053,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -45071,179 +45071,179 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="R205" t="n">
-        <v>2.69</v>
+        <v>2.04</v>
       </c>
       <c r="S205" t="n">
-        <v>8.1</v>
+        <v>3.75</v>
       </c>
       <c r="T205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W205" t="n">
         <v>1.3</v>
       </c>
-      <c r="U205" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V205" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W205" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X205" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="AA205" t="n">
-        <v>5.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB205" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD205" t="n">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF205" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="AG205" t="n">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="AH205" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AI205" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AJ205" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AK205" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AL205" t="n">
         <v>0</v>
       </c>
       <c r="AM205" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="AN205" t="n">
-        <v>2.64</v>
+        <v>1.22</v>
       </c>
       <c r="AO205" t="n">
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT205" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="AU205" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW205" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AX205" t="n">
         <v>5</v>
       </c>
       <c r="AY205" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AZ205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA205" t="n">
         <v>6</v>
       </c>
-      <c r="BA205" t="n">
-        <v>13</v>
-      </c>
       <c r="BB205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC205" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD205" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="BE205" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BF205" t="n">
-        <v>7</v>
+        <v>2.65</v>
       </c>
       <c r="BG205" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BH205" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="BI205" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BJ205" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="BK205" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="BL205" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="BM205" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BN205" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BO205" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="BP205" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="206">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.91</v>
@@ -2658,7 +2658,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.36</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.73</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ20" t="n">
         <v>2.3</v>
@@ -5710,7 +5710,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>1.39</v>
@@ -7454,7 +7454,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR32" t="n">
         <v>1.38</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
         <v>2.18</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.18</v>
@@ -8541,7 +8541,7 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ37" t="n">
         <v>2.3</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR39" t="n">
         <v>1.72</v>
@@ -11811,10 +11811,10 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR52" t="n">
         <v>2.07</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.6899999999999999</v>
@@ -12465,7 +12465,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.36</v>
@@ -12901,10 +12901,10 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR57" t="n">
         <v>1.95</v>
@@ -13122,7 +13122,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR58" t="n">
         <v>1.28</v>
@@ -13340,7 +13340,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR59" t="n">
         <v>1.24</v>
@@ -16174,7 +16174,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR72" t="n">
         <v>1.11</v>
@@ -16389,10 +16389,10 @@
         <v>0.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR73" t="n">
         <v>1.8</v>
@@ -16828,7 +16828,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR75" t="n">
         <v>1.34</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.18</v>
@@ -17261,7 +17261,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.73</v>
@@ -18790,7 +18790,7 @@
         <v>2</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR84" t="n">
         <v>1.22</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.55</v>
@@ -20313,7 +20313,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.42</v>
@@ -20752,7 +20752,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR93" t="n">
         <v>1.74</v>
@@ -20970,7 +20970,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR94" t="n">
         <v>2.2</v>
@@ -21621,7 +21621,7 @@
         <v>0.6</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.91</v>
@@ -22278,7 +22278,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR100" t="n">
         <v>1.61</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.55</v>
@@ -23150,7 +23150,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR104" t="n">
         <v>1.47</v>
@@ -23583,7 +23583,7 @@
         <v>0.6</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.36</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110" t="n">
         <v>1</v>
@@ -25548,7 +25548,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR115" t="n">
         <v>1.09</v>
@@ -25766,7 +25766,7 @@
         <v>2</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR116" t="n">
         <v>1.35</v>
@@ -26199,7 +26199,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ118" t="n">
         <v>1</v>
@@ -26417,7 +26417,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.42</v>
@@ -27292,7 +27292,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR123" t="n">
         <v>1.51</v>
@@ -28164,7 +28164,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR127" t="n">
         <v>1.24</v>
@@ -29472,7 +29472,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR133" t="n">
         <v>1.39</v>
@@ -29687,7 +29687,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.92</v>
@@ -29908,7 +29908,7 @@
         <v>2</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR135" t="n">
         <v>1.32</v>
@@ -30123,7 +30123,7 @@
         <v>0.83</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.91</v>
@@ -30562,7 +30562,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR138" t="n">
         <v>1.59</v>
@@ -30777,7 +30777,7 @@
         <v>1.14</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.55</v>
@@ -31213,7 +31213,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ141" t="n">
         <v>1</v>
@@ -32957,7 +32957,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.42</v>
@@ -33175,7 +33175,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.92</v>
@@ -33614,7 +33614,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR152" t="n">
         <v>1.97</v>
@@ -33832,7 +33832,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR153" t="n">
         <v>1.64</v>
@@ -34483,10 +34483,10 @@
         <v>0.5</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR156" t="n">
         <v>1.84</v>
@@ -34704,7 +34704,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR157" t="n">
         <v>1.39</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.6899999999999999</v>
@@ -35355,7 +35355,7 @@
         <v>1.14</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.18</v>
@@ -35573,10 +35573,10 @@
         <v>0.57</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR161" t="n">
         <v>1.72</v>
@@ -35794,7 +35794,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR162" t="n">
         <v>1.88</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ168" t="n">
         <v>1</v>
@@ -37320,7 +37320,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR169" t="n">
         <v>1.64</v>
@@ -37535,7 +37535,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.42</v>
@@ -39500,7 +39500,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR179" t="n">
         <v>1.29</v>
@@ -40151,7 +40151,7 @@
         <v>1.11</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ182" t="n">
         <v>1</v>
@@ -40372,7 +40372,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR183" t="n">
         <v>1.55</v>
@@ -40808,7 +40808,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR185" t="n">
         <v>1.69</v>
@@ -41026,7 +41026,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR186" t="n">
         <v>2.03</v>
@@ -41241,7 +41241,7 @@
         <v>1.75</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ187" t="n">
         <v>2</v>
@@ -41677,7 +41677,7 @@
         <v>1.67</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.73</v>
@@ -41898,7 +41898,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR190" t="n">
         <v>1.29</v>
@@ -42988,7 +42988,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR195" t="n">
         <v>1.57</v>
@@ -44075,7 +44075,7 @@
         <v>0.5</v>
       </c>
       <c r="AP200" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.42</v>
@@ -44296,7 +44296,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR201" t="n">
         <v>1.36</v>
@@ -44947,10 +44947,10 @@
         <v>0.8</v>
       </c>
       <c r="AP204" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR204" t="n">
         <v>1.96</v>
@@ -45819,7 +45819,7 @@
         <v>1.33</v>
       </c>
       <c r="AP208" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ208" t="n">
         <v>1.18</v>
@@ -46037,10 +46037,10 @@
         <v>0.7</v>
       </c>
       <c r="AP209" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR209" t="n">
         <v>1.45</v>
@@ -46255,7 +46255,7 @@
         <v>0.44</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.36</v>
@@ -47130,7 +47130,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ214" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR214" t="n">
         <v>1.7</v>
@@ -49604,6 +49604,878 @@
       </c>
       <c r="BP225" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>7834545</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>45921.66666666666</v>
+      </c>
+      <c r="F226" t="n">
+        <v>24</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>2</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>2</v>
+      </c>
+      <c r="L226" t="n">
+        <v>2</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>2</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>['34', '45+2']</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S226" t="n">
+        <v>6</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U226" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X226" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>7834547</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>45921.72916666666</v>
+      </c>
+      <c r="F227" t="n">
+        <v>24</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>2</v>
+      </c>
+      <c r="J227" t="n">
+        <v>2</v>
+      </c>
+      <c r="K227" t="n">
+        <v>4</v>
+      </c>
+      <c r="L227" t="n">
+        <v>2</v>
+      </c>
+      <c r="M227" t="n">
+        <v>3</v>
+      </c>
+      <c r="N227" t="n">
+        <v>5</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>['21', '45+6']</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>['29', '45+8', '62']</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R227" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S227" t="n">
+        <v>5</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V227" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X227" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>7834541</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>45921.72916666666</v>
+      </c>
+      <c r="F228" t="n">
+        <v>24</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>1</v>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" t="n">
+        <v>2</v>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="n">
+        <v>1</v>
+      </c>
+      <c r="N228" t="n">
+        <v>2</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R228" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S228" t="n">
+        <v>8</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U228" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V228" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X228" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>7834550</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>45921.72916666666</v>
+      </c>
+      <c r="F229" t="n">
+        <v>24</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R229" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U229" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V229" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X229" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.42</v>
@@ -3748,7 +3748,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.18</v>
@@ -7672,7 +7672,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR33" t="n">
         <v>1.76</v>
@@ -8108,7 +8108,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR35" t="n">
         <v>1.02</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.6899999999999999</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.18</v>
@@ -12032,7 +12032,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR53" t="n">
         <v>1.22</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.92</v>
@@ -13773,10 +13773,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR61" t="n">
         <v>1.74</v>
@@ -15517,7 +15517,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ69" t="n">
         <v>2</v>
@@ -16610,7 +16610,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR74" t="n">
         <v>1.05</v>
@@ -17482,7 +17482,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR78" t="n">
         <v>1.57</v>
@@ -18133,7 +18133,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.91</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.6899999999999999</v>
@@ -22496,7 +22496,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR101" t="n">
         <v>1.23</v>
@@ -22714,7 +22714,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR102" t="n">
         <v>1.25</v>
@@ -23365,7 +23365,7 @@
         <v>0.4</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.55</v>
@@ -24237,7 +24237,7 @@
         <v>3</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ109" t="n">
         <v>2.3</v>
@@ -26202,7 +26202,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR118" t="n">
         <v>1.8</v>
@@ -27074,7 +27074,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR122" t="n">
         <v>1.44</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ123" t="n">
         <v>1</v>
@@ -28379,7 +28379,7 @@
         <v>2</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ128" t="n">
         <v>2</v>
@@ -28600,7 +28600,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -30344,7 +30344,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR137" t="n">
         <v>1.43</v>
@@ -30559,7 +30559,7 @@
         <v>0</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.36</v>
@@ -32303,7 +32303,7 @@
         <v>0.57</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.91</v>
@@ -32742,7 +32742,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR148" t="n">
         <v>1.37</v>
@@ -33396,7 +33396,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR151" t="n">
         <v>1.5</v>
@@ -34265,7 +34265,7 @@
         <v>0.71</v>
       </c>
       <c r="AP155" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.91</v>
@@ -36666,7 +36666,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR166" t="n">
         <v>1.9</v>
@@ -37102,7 +37102,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR168" t="n">
         <v>1.94</v>
@@ -37317,7 +37317,7 @@
         <v>0</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ169" t="n">
         <v>0.36</v>
@@ -39061,7 +39061,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ177" t="n">
         <v>0.92</v>
@@ -39936,7 +39936,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR181" t="n">
         <v>1.39</v>
@@ -40019,7 +40019,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>7834510</v>
+        <v>7834508</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -40039,12 +40039,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -40067,169 +40067,169 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>['5', '50']</t>
+          <t>['32', '46']</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>['66', '90+1']</t>
+          <t>['81', '90+10']</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="R182" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="S182" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="T182" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U182" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V182" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W182" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X182" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR182" t="n">
         <v>1.55</v>
       </c>
-      <c r="U182" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V182" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W182" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X182" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y182" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z182" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA182" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB182" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC182" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD182" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE182" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF182" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG182" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AH182" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI182" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ182" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK182" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL182" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM182" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN182" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO182" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AP182" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AQ182" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR182" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AS182" t="n">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="AU182" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV182" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW182" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AX182" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY182" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AZ182" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
       </c>
       <c r="BB182" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC182" t="n">
         <v>10</v>
       </c>
-      <c r="BC182" t="n">
-        <v>14</v>
-      </c>
       <c r="BD182" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="BE182" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF182" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG182" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BH182" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="BI182" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BJ182" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="BK182" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="BL182" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BM182" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="BN182" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BO182" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="BP182" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="183">
@@ -40237,7 +40237,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>7834508</v>
+        <v>7834510</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -40257,12 +40257,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -40285,169 +40285,169 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>['32', '46']</t>
+          <t>['5', '50']</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>['81', '90+10']</t>
+          <t>['66', '90+1']</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>2.48</v>
+        <v>3.24</v>
       </c>
       <c r="R183" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="S183" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="T183" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="U183" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="V183" t="n">
-        <v>3.04</v>
+        <v>3.9</v>
       </c>
       <c r="W183" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="X183" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Y183" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z183" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AA183" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="AB183" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AC183" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AD183" t="n">
-        <v>7.7</v>
+        <v>6.25</v>
       </c>
       <c r="AE183" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK183" t="n">
         <v>1.4</v>
       </c>
-      <c r="AF183" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AG183" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH183" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI183" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ183" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK183" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AL183" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AM183" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AN183" t="n">
-        <v>1.44</v>
+        <v>0.5</v>
       </c>
       <c r="AO183" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.42</v>
+        <v>0.73</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.36</v>
+        <v>0.92</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AS183" t="n">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="AU183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV183" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW183" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AX183" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY183" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ183" t="n">
         <v>18</v>
-      </c>
-      <c r="AZ183" t="n">
-        <v>13</v>
       </c>
       <c r="BA183" t="n">
         <v>4</v>
       </c>
       <c r="BB183" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BC183" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BD183" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="BE183" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF183" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="BG183" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="BH183" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="BI183" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BJ183" t="n">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="BK183" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="BL183" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="BM183" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BN183" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO183" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="BP183" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="184">
@@ -40805,7 +40805,7 @@
         <v>0.5</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.92</v>
@@ -42331,7 +42331,7 @@
         <v>1.11</v>
       </c>
       <c r="AP192" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ192" t="n">
         <v>0.91</v>
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>7834518</v>
+        <v>7834512</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,19 +42655,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -42676,176 +42676,176 @@
         <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>['12', '60']</t>
+          <t>['59', '90+6']</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '69', '85']</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R194" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S194" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="T194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X194" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK194" t="n">
         <v>1.36</v>
       </c>
-      <c r="U194" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V194" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W194" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X194" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL194" t="n">
         <v>0</v>
       </c>
       <c r="AM194" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AN194" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO194" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS194" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AU194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV194" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX194" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY194" t="n">
         <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA194" t="n">
         <v>3</v>
       </c>
       <c r="BB194" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC194" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD194" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE194" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF194" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH194" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BK194" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL194" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BO194" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="195">
@@ -42853,7 +42853,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7834512</v>
+        <v>7834518</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -42873,19 +42873,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -42894,176 +42894,176 @@
         <v>2</v>
       </c>
       <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>['12', '60']</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S195" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V195" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X195" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
         <v>3</v>
       </c>
-      <c r="N195" t="n">
+      <c r="AW195" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX195" t="n">
         <v>5</v>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>['59', '90+6']</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>['21', '69', '85']</t>
-        </is>
-      </c>
-      <c r="Q195" t="n">
-        <v>3</v>
-      </c>
-      <c r="R195" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S195" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T195" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U195" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V195" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W195" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X195" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL195" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM195" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN195" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO195" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP195" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ195" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR195" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS195" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT195" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU195" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV195" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW195" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX195" t="n">
-        <v>7</v>
       </c>
       <c r="AY195" t="n">
         <v>12</v>
       </c>
       <c r="AZ195" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA195" t="n">
         <v>3</v>
       </c>
       <c r="BB195" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC195" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD195" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BE195" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF195" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG195" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH195" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI195" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ195" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BK195" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BL195" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BM195" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BN195" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BO195" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP195" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="196">
@@ -44514,7 +44514,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR202" t="n">
         <v>1.78</v>
@@ -44729,10 +44729,10 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR203" t="n">
         <v>1.68</v>
@@ -44815,7 +44815,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>7834521</v>
+        <v>7834524</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -44835,12 +44835,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -44853,179 +44853,179 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="R204" t="n">
-        <v>2.69</v>
+        <v>2.04</v>
       </c>
       <c r="S204" t="n">
-        <v>8.1</v>
+        <v>3.75</v>
       </c>
       <c r="T204" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V204" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W204" t="n">
         <v>1.3</v>
       </c>
-      <c r="U204" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V204" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W204" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X204" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="Y204" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z204" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="AA204" t="n">
-        <v>5.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB204" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC204" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD204" t="n">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="AE204" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF204" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="AG204" t="n">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="AH204" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AI204" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AJ204" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AK204" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AL204" t="n">
         <v>0</v>
       </c>
       <c r="AM204" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="AN204" t="n">
-        <v>2.64</v>
+        <v>1.22</v>
       </c>
       <c r="AO204" t="n">
         <v>0.8</v>
       </c>
       <c r="AP204" t="n">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ204" t="n">
         <v>1</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT204" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="AU204" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW204" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AX204" t="n">
         <v>5</v>
       </c>
       <c r="AY204" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AZ204" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA204" t="n">
         <v>6</v>
       </c>
-      <c r="BA204" t="n">
-        <v>13</v>
-      </c>
       <c r="BB204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC204" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD204" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="BE204" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BF204" t="n">
-        <v>7</v>
+        <v>2.65</v>
       </c>
       <c r="BG204" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BH204" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="BI204" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BJ204" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="BK204" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="BL204" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="BM204" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BN204" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BO204" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="BP204" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="205">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>7834524</v>
+        <v>7834521</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,12 +45053,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -45071,179 +45071,179 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>2.94</v>
+        <v>1.71</v>
       </c>
       <c r="R205" t="n">
-        <v>2.04</v>
+        <v>2.69</v>
       </c>
       <c r="S205" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X205" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF205" t="n">
         <v>3.75</v>
       </c>
-      <c r="T205" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U205" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V205" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W205" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X205" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y205" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z205" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD205" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AE205" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF205" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AG205" t="n">
-        <v>2.49</v>
+        <v>1.78</v>
       </c>
       <c r="AH205" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AI205" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AJ205" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK205" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AL205" t="n">
         <v>0</v>
       </c>
       <c r="AM205" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="AN205" t="n">
-        <v>1.22</v>
+        <v>2.64</v>
       </c>
       <c r="AO205" t="n">
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.2</v>
+        <v>2.38</v>
       </c>
       <c r="AQ205" t="n">
         <v>1</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="AU205" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW205" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AX205" t="n">
         <v>5</v>
       </c>
       <c r="AY205" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AZ205" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA205" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BB205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC205" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF205" t="n">
         <v>7</v>
       </c>
-      <c r="BD205" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF205" t="n">
-        <v>2.65</v>
-      </c>
       <c r="BG205" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BH205" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="BI205" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BJ205" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="BK205" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="BL205" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="BM205" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="BN205" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="BO205" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="BP205" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>7834528</v>
+        <v>7834523</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I206" t="n">
         <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R206" t="n">
         <v>1.95</v>
       </c>
       <c r="S206" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="T206" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V206" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X206" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH206" t="n">
         <v>1.44</v>
       </c>
-      <c r="U206" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V206" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W206" t="n">
+      <c r="AI206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM206" t="n">
         <v>1.3</v>
       </c>
-      <c r="X206" t="n">
+      <c r="AN206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY206" t="n">
         <v>9</v>
-      </c>
-      <c r="Y206" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z206" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA206" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD206" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE206" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH206" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI206" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN206" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO206" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AP206" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ206" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR206" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS206" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT206" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AU206" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV206" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW206" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX206" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>14</v>
       </c>
       <c r="AZ206" t="n">
         <v>19</v>
       </c>
       <c r="BA206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BC206" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD206" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BE206" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF206" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="BG206" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BH206" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BI206" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BJ206" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="BL206" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="BM206" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="BO206" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="207">
@@ -45469,7 +45469,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>7834523</v>
+        <v>7834528</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -45489,197 +45489,197 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I207" t="n">
         <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L207" t="n">
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R207" t="n">
         <v>1.95</v>
       </c>
       <c r="S207" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T207" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="U207" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V207" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="W207" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X207" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z207" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA207" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AB207" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AD207" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF207" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG207" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS207" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI207" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ207" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK207" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM207" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN207" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO207" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AP207" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ207" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR207" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS207" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AT207" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU207" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV207" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW207" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX207" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY207" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ207" t="n">
         <v>19</v>
       </c>
       <c r="BA207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB207" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BC207" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD207" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="BE207" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF207" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="BG207" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BH207" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BI207" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BJ207" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="BK207" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="BL207" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="BM207" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BN207" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BO207" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="BP207" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="208">
@@ -48957,7 +48957,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>7834549</v>
+        <v>7834542</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -48977,197 +48977,197 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223" t="n">
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="R223" t="n">
         <v>2</v>
       </c>
       <c r="S223" t="n">
-        <v>3.71</v>
+        <v>5.03</v>
       </c>
       <c r="T223" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U223" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="V223" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="W223" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X223" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y223" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z223" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA223" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB223" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="AC223" t="n">
         <v>1.08</v>
       </c>
       <c r="AD223" t="n">
-        <v>7.23</v>
+        <v>7</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO223" t="n">
         <v>2.7</v>
       </c>
-      <c r="AG223" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH223" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI223" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AJ223" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK223" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL223" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AM223" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN223" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO223" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AP223" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ223" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR223" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS223" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT223" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AU223" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV223" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW223" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX223" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY223" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ223" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA223" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB223" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC223" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD223" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BE223" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF223" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BG223" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BH223" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BI223" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BJ223" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BK223" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BL223" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM223" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BN223" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO223" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BP223" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="224">
@@ -49175,7 +49175,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>7834542</v>
+        <v>7834549</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -49195,197 +49195,197 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L224" t="n">
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="R224" t="n">
         <v>2</v>
       </c>
       <c r="S224" t="n">
-        <v>5.03</v>
+        <v>3.71</v>
       </c>
       <c r="T224" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U224" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="V224" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X224" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA224" t="n">
         <v>3.1</v>
       </c>
-      <c r="W224" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X224" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y224" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z224" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA224" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB224" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="AC224" t="n">
         <v>1.08</v>
       </c>
       <c r="AD224" t="n">
-        <v>7</v>
+        <v>7.23</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AF224" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AG224" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AH224" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI224" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AJ224" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK224" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AL224" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AM224" t="n">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="AN224" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AO224" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AQ224" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AT224" t="n">
-        <v>3.24</v>
+        <v>2.71</v>
       </c>
       <c r="AU224" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV224" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW224" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB224" t="n">
         <v>6</v>
       </c>
-      <c r="AX224" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY224" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ224" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA224" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB224" t="n">
-        <v>4</v>
-      </c>
       <c r="BC224" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD224" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="BE224" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF224" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="BG224" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BH224" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO224" t="n">
         <v>3.5</v>
       </c>
-      <c r="BI224" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BJ224" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BK224" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BL224" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM224" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BN224" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BO224" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BP224" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="225">
@@ -49540,13 +49540,13 @@
         <v>2.81</v>
       </c>
       <c r="AU225" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV225" t="n">
         <v>5</v>
       </c>
       <c r="AW225" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX225" t="n">
         <v>3</v>
@@ -49767,13 +49767,13 @@
         <v>12</v>
       </c>
       <c r="AX226" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY226" t="n">
         <v>16</v>
       </c>
       <c r="AZ226" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA226" t="n">
         <v>4</v>
@@ -50047,7 +50047,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>7834541</v>
+        <v>7834550</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -50067,197 +50067,197 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L228" t="n">
         <v>1</v>
       </c>
       <c r="M228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>1.84</v>
+        <v>3.55</v>
       </c>
       <c r="R228" t="n">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="S228" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U228" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V228" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X228" t="n">
         <v>8</v>
       </c>
-      <c r="T228" t="n">
+      <c r="Y228" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL228" t="n">
         <v>1.33</v>
       </c>
-      <c r="U228" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V228" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W228" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X228" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y228" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z228" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA228" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB228" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC228" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD228" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE228" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF228" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AG228" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH228" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI228" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ228" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AK228" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL228" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AM228" t="n">
-        <v>3.11</v>
+        <v>1.42</v>
       </c>
       <c r="AN228" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="AO228" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AP228" t="n">
-        <v>2.38</v>
+        <v>0.73</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="AS228" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AT228" t="n">
-        <v>3.43</v>
+        <v>2.47</v>
       </c>
       <c r="AU228" t="n">
         <v>3</v>
       </c>
       <c r="AV228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW228" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX228" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AY228" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ228" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BA228" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BB228" t="n">
         <v>7</v>
       </c>
       <c r="BC228" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BD228" t="n">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="BE228" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="BF228" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="BG228" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BH228" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="BI228" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="BJ228" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="BK228" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BL228" t="n">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="BM228" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="BN228" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="BO228" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="BP228" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="229">
@@ -50265,7 +50265,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>7834550</v>
+        <v>7834541</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -50285,197 +50285,633 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L229" t="n">
         <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>3.55</v>
+        <v>1.84</v>
       </c>
       <c r="R229" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="S229" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="T229" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="U229" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="V229" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="W229" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="X229" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y229" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z229" t="n">
-        <v>2.48</v>
+        <v>1.31</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="AB229" t="n">
-        <v>2.73</v>
+        <v>7.6</v>
       </c>
       <c r="AC229" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AD229" t="n">
-        <v>7.42</v>
+        <v>9.1</v>
       </c>
       <c r="AE229" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AF229" t="n">
-        <v>2.29</v>
+        <v>3.64</v>
       </c>
       <c r="AG229" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AH229" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AI229" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AJ229" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AK229" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AL229" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AM229" t="n">
-        <v>1.42</v>
+        <v>3.11</v>
       </c>
       <c r="AN229" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AO229" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="AP229" t="n">
-        <v>0.73</v>
+        <v>2.38</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AS229" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.47</v>
+        <v>3.43</v>
       </c>
       <c r="AU229" t="n">
         <v>3</v>
       </c>
       <c r="AV229" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA229" t="n">
         <v>3</v>
-      </c>
-      <c r="AW229" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX229" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY229" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ229" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA229" t="n">
-        <v>8</v>
       </c>
       <c r="BB229" t="n">
         <v>7</v>
       </c>
       <c r="BC229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>7834546</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>45921.85416666666</v>
+      </c>
+      <c r="F230" t="n">
+        <v>24</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
+        <v>2</v>
+      </c>
+      <c r="L230" t="n">
+        <v>2</v>
+      </c>
+      <c r="M230" t="n">
+        <v>1</v>
+      </c>
+      <c r="N230" t="n">
+        <v>3</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>['45+2', '77']</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R230" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S230" t="n">
+        <v>6</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X230" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>7834544</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>45921.85416666666</v>
+      </c>
+      <c r="F231" t="n">
+        <v>24</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>3</v>
+      </c>
+      <c r="R231" t="n">
+        <v>2</v>
+      </c>
+      <c r="S231" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U231" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V231" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X231" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW231" t="n">
         <v>15</v>
       </c>
-      <c r="BD229" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BE229" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BF229" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BG229" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BH229" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="BI229" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ229" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BK229" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BL229" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BM229" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BN229" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BO229" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BP229" t="n">
-        <v>1.34</v>
+      <c r="AX231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.6899999999999999</v>
@@ -2222,7 +2222,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.92</v>
@@ -5056,7 +5056,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
         <v>2.16</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.55</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ27" t="n">
         <v>2</v>
@@ -9416,7 +9416,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR41" t="n">
         <v>0.83</v>
@@ -9849,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43" t="n">
         <v>2</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.91</v>
@@ -10506,7 +10506,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR46" t="n">
         <v>2.83</v>
@@ -13558,7 +13558,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR60" t="n">
         <v>1.41</v>
@@ -14866,7 +14866,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR66" t="n">
         <v>1.44</v>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.92</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.3</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.08</v>
@@ -17046,7 +17046,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR76" t="n">
         <v>1.9</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.36</v>
@@ -19662,7 +19662,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR88" t="n">
         <v>1.76</v>
@@ -21185,10 +21185,10 @@
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR95" t="n">
         <v>1.12</v>
@@ -22711,7 +22711,7 @@
         <v>1.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.08</v>
@@ -23368,7 +23368,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR105" t="n">
         <v>1.65</v>
@@ -24894,7 +24894,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR112" t="n">
         <v>1.55</v>
@@ -25545,7 +25545,7 @@
         <v>0.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ115" t="n">
         <v>1</v>
@@ -26635,10 +26635,10 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR120" t="n">
         <v>1.39</v>
@@ -29254,7 +29254,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR132" t="n">
         <v>1.52</v>
@@ -29469,7 +29469,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -30780,7 +30780,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR139" t="n">
         <v>1.63</v>
@@ -35137,7 +35137,7 @@
         <v>0.5</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.36</v>
@@ -35358,7 +35358,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR160" t="n">
         <v>1.6</v>
@@ -38192,7 +38192,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR173" t="n">
         <v>1.58</v>
@@ -38625,7 +38625,7 @@
         <v>0.89</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.6899999999999999</v>
@@ -39279,7 +39279,7 @@
         <v>0.25</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.55</v>
@@ -40019,7 +40019,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>7834508</v>
+        <v>7834510</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -40039,12 +40039,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -40067,169 +40067,169 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>['32', '46']</t>
+          <t>['5', '50']</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>['81', '90+10']</t>
+          <t>['66', '90+1']</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>2.48</v>
+        <v>3.24</v>
       </c>
       <c r="R182" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="S182" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="T182" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="U182" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="V182" t="n">
-        <v>3.04</v>
+        <v>3.9</v>
       </c>
       <c r="W182" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="X182" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Y182" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z182" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AA182" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="AB182" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AC182" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AD182" t="n">
-        <v>7.7</v>
+        <v>6.25</v>
       </c>
       <c r="AE182" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK182" t="n">
         <v>1.4</v>
       </c>
-      <c r="AF182" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AG182" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH182" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI182" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ182" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK182" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AL182" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AM182" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AN182" t="n">
-        <v>1.44</v>
+        <v>0.5</v>
       </c>
       <c r="AO182" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.42</v>
+        <v>0.73</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.36</v>
+        <v>0.92</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AS182" t="n">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="AU182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV182" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW182" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AX182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY182" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ182" t="n">
         <v>18</v>
-      </c>
-      <c r="AZ182" t="n">
-        <v>13</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
       </c>
       <c r="BB182" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BC182" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BD182" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="BE182" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF182" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="BG182" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="BH182" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="BI182" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BJ182" t="n">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="BK182" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="BL182" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="BM182" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BN182" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BO182" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="BP182" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="183">
@@ -40237,7 +40237,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>7834510</v>
+        <v>7834508</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -40257,12 +40257,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -40285,169 +40285,169 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>['5', '50']</t>
+          <t>['32', '46']</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>['66', '90+1']</t>
+          <t>['81', '90+10']</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="R183" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="S183" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="T183" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U183" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V183" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W183" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X183" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR183" t="n">
         <v>1.55</v>
       </c>
-      <c r="U183" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V183" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W183" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X183" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y183" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z183" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA183" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB183" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC183" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD183" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE183" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF183" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG183" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AH183" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI183" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ183" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK183" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL183" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM183" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO183" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AP183" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AQ183" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR183" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AS183" t="n">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="AU183" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV183" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW183" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AX183" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY183" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AZ183" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA183" t="n">
         <v>4</v>
       </c>
       <c r="BB183" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC183" t="n">
         <v>10</v>
       </c>
-      <c r="BC183" t="n">
-        <v>14</v>
-      </c>
       <c r="BD183" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="BE183" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF183" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG183" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BH183" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="BI183" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BJ183" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="BK183" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="BL183" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BM183" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="BN183" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BO183" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="BP183" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="184">
@@ -40590,7 +40590,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR184" t="n">
         <v>1.51</v>
@@ -42549,7 +42549,7 @@
         <v>0.89</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.91</v>
@@ -42635,7 +42635,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>7834512</v>
+        <v>7834518</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -42655,19 +42655,19 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -42676,176 +42676,176 @@
         <v>2</v>
       </c>
       <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>2</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>['12', '60']</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S194" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V194" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X194" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV194" t="n">
         <v>3</v>
       </c>
-      <c r="N194" t="n">
+      <c r="AW194" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX194" t="n">
         <v>5</v>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>['59', '90+6']</t>
-        </is>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>['21', '69', '85']</t>
-        </is>
-      </c>
-      <c r="Q194" t="n">
-        <v>3</v>
-      </c>
-      <c r="R194" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S194" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T194" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U194" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V194" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W194" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X194" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF194" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG194" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH194" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ194" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK194" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL194" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM194" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN194" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO194" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP194" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR194" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT194" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU194" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV194" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW194" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX194" t="n">
-        <v>7</v>
       </c>
       <c r="AY194" t="n">
         <v>12</v>
       </c>
       <c r="AZ194" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA194" t="n">
         <v>3</v>
       </c>
       <c r="BB194" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC194" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD194" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BE194" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BF194" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="BG194" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH194" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI194" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ194" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BK194" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BL194" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="BM194" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="BN194" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BO194" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP194" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="195">
@@ -42853,7 +42853,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7834518</v>
+        <v>7834512</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -42873,19 +42873,19 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -42894,176 +42894,176 @@
         <v>2</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>['12', '60']</t>
+          <t>['59', '90+6']</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '69', '85']</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R195" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S195" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="T195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X195" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK195" t="n">
         <v>1.36</v>
       </c>
-      <c r="U195" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V195" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="W195" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X195" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y195" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z195" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA195" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB195" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AC195" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD195" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE195" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF195" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG195" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH195" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI195" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ195" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AK195" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL195" t="n">
         <v>0</v>
       </c>
       <c r="AM195" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AN195" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="AO195" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AS195" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AU195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV195" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW195" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX195" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY195" t="n">
         <v>12</v>
       </c>
       <c r="AZ195" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA195" t="n">
         <v>3</v>
       </c>
       <c r="BB195" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC195" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BD195" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="BE195" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BF195" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG195" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH195" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI195" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="BJ195" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="BK195" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL195" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="BM195" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="BN195" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BO195" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP195" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="196">
@@ -43206,7 +43206,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR196" t="n">
         <v>1.27</v>
@@ -44815,7 +44815,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>7834524</v>
+        <v>7834521</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -44835,12 +44835,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -44853,179 +44853,179 @@
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>2.94</v>
+        <v>1.71</v>
       </c>
       <c r="R204" t="n">
-        <v>2.04</v>
+        <v>2.69</v>
       </c>
       <c r="S204" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X204" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF204" t="n">
         <v>3.75</v>
       </c>
-      <c r="T204" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U204" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V204" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W204" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X204" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y204" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z204" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA204" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB204" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC204" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD204" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AE204" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF204" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AG204" t="n">
-        <v>2.49</v>
+        <v>1.78</v>
       </c>
       <c r="AH204" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AI204" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AJ204" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK204" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AL204" t="n">
         <v>0</v>
       </c>
       <c r="AM204" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="AN204" t="n">
-        <v>1.22</v>
+        <v>2.64</v>
       </c>
       <c r="AO204" t="n">
         <v>0.8</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="AQ204" t="n">
         <v>1</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="AU204" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW204" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AX204" t="n">
         <v>5</v>
       </c>
       <c r="AY204" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AZ204" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA204" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BB204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF204" t="n">
         <v>7</v>
       </c>
-      <c r="BD204" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BE204" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF204" t="n">
-        <v>2.65</v>
-      </c>
       <c r="BG204" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BH204" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="BI204" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BJ204" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="BK204" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="BL204" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="BM204" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="BN204" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="BO204" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="BP204" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="205">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>7834521</v>
+        <v>7834524</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,12 +45053,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -45071,179 +45071,179 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="R205" t="n">
-        <v>2.69</v>
+        <v>2.04</v>
       </c>
       <c r="S205" t="n">
-        <v>8.1</v>
+        <v>3.75</v>
       </c>
       <c r="T205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W205" t="n">
         <v>1.3</v>
       </c>
-      <c r="U205" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V205" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W205" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X205" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="AA205" t="n">
-        <v>5.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB205" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD205" t="n">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="AE205" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF205" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="AG205" t="n">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="AH205" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AI205" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="AJ205" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AK205" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AL205" t="n">
         <v>0</v>
       </c>
       <c r="AM205" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="AN205" t="n">
-        <v>2.64</v>
+        <v>1.22</v>
       </c>
       <c r="AO205" t="n">
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ205" t="n">
         <v>1</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT205" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="AU205" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW205" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AX205" t="n">
         <v>5</v>
       </c>
       <c r="AY205" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AZ205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA205" t="n">
         <v>6</v>
       </c>
-      <c r="BA205" t="n">
-        <v>13</v>
-      </c>
       <c r="BB205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC205" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD205" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="BE205" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BF205" t="n">
-        <v>7</v>
+        <v>2.65</v>
       </c>
       <c r="BG205" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BH205" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="BI205" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BJ205" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="BK205" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="BL205" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="BM205" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="BN205" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="BO205" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="BP205" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>7834523</v>
+        <v>7834528</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I206" t="n">
         <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R206" t="n">
         <v>1.95</v>
       </c>
       <c r="S206" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T206" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="U206" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V206" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="W206" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X206" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y206" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z206" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA206" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AB206" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AC206" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AD206" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE206" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF206" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG206" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH206" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS206" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI206" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN206" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO206" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AP206" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ206" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR206" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS206" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AT206" t="n">
-        <v>2.94</v>
+        <v>3.01</v>
       </c>
       <c r="AU206" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV206" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW206" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX206" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY206" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ206" t="n">
         <v>19</v>
       </c>
       <c r="BA206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BC206" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD206" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="BE206" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF206" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="BG206" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BH206" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BI206" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BJ206" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="BL206" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="BM206" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BO206" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="207">
@@ -45469,7 +45469,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>7834528</v>
+        <v>7834523</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -45489,197 +45489,197 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I207" t="n">
         <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L207" t="n">
         <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="R207" t="n">
         <v>1.95</v>
       </c>
       <c r="S207" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="T207" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V207" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X207" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH207" t="n">
         <v>1.44</v>
       </c>
-      <c r="U207" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V207" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W207" t="n">
+      <c r="AI207" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM207" t="n">
         <v>1.3</v>
       </c>
-      <c r="X207" t="n">
+      <c r="AN207" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY207" t="n">
         <v>9</v>
-      </c>
-      <c r="Y207" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z207" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA207" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB207" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC207" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD207" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE207" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF207" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG207" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH207" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI207" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ207" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK207" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM207" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN207" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO207" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AP207" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ207" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR207" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS207" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT207" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AU207" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV207" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW207" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX207" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY207" t="n">
-        <v>14</v>
       </c>
       <c r="AZ207" t="n">
         <v>19</v>
       </c>
       <c r="BA207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB207" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BC207" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD207" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="BE207" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF207" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="BG207" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BH207" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="BI207" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BJ207" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="BK207" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="BL207" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="BM207" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BN207" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="BO207" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="BP207" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">
@@ -45822,7 +45822,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR208" t="n">
         <v>1.72</v>
@@ -46473,7 +46473,7 @@
         <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.42</v>
@@ -48002,7 +48002,7 @@
         <v>2</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR218" t="n">
         <v>1.43</v>
@@ -48217,7 +48217,7 @@
         <v>0.9</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ219" t="n">
         <v>0.91</v>
@@ -48957,7 +48957,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>7834542</v>
+        <v>7834549</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -48977,197 +48977,197 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L223" t="n">
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="R223" t="n">
         <v>2</v>
       </c>
       <c r="S223" t="n">
-        <v>5.03</v>
+        <v>3.71</v>
       </c>
       <c r="T223" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U223" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="V223" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X223" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA223" t="n">
         <v>3.1</v>
       </c>
-      <c r="W223" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X223" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y223" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z223" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA223" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB223" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="AC223" t="n">
         <v>1.08</v>
       </c>
       <c r="AD223" t="n">
-        <v>7</v>
+        <v>7.23</v>
       </c>
       <c r="AE223" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AF223" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AG223" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AH223" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI223" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AJ223" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK223" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AL223" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AM223" t="n">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="AN223" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AO223" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AQ223" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AT223" t="n">
-        <v>3.24</v>
+        <v>2.71</v>
       </c>
       <c r="AU223" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV223" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW223" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB223" t="n">
         <v>6</v>
       </c>
-      <c r="AX223" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY223" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ223" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA223" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB223" t="n">
-        <v>4</v>
-      </c>
       <c r="BC223" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD223" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="BE223" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF223" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="BG223" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BH223" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO223" t="n">
         <v>3.5</v>
       </c>
-      <c r="BI223" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BJ223" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BK223" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BL223" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM223" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BN223" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BO223" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BP223" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="224">
@@ -49175,7 +49175,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>7834549</v>
+        <v>7834542</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -49195,197 +49195,197 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L224" t="n">
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="R224" t="n">
         <v>2</v>
       </c>
       <c r="S224" t="n">
-        <v>3.71</v>
+        <v>5.03</v>
       </c>
       <c r="T224" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U224" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="V224" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="W224" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X224" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y224" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z224" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA224" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB224" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="AC224" t="n">
         <v>1.08</v>
       </c>
       <c r="AD224" t="n">
-        <v>7.23</v>
+        <v>7</v>
       </c>
       <c r="AE224" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AF224" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO224" t="n">
         <v>2.7</v>
       </c>
-      <c r="AG224" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH224" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI224" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AJ224" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK224" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL224" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AM224" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN224" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO224" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AP224" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ224" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR224" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS224" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT224" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AU224" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV224" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW224" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX224" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY224" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ224" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA224" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB224" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC224" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD224" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BE224" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF224" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BG224" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BH224" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BI224" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BJ224" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BK224" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BL224" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM224" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BN224" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO224" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BP224" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="225">
@@ -50047,7 +50047,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>7834550</v>
+        <v>7834541</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -50067,197 +50067,197 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L228" t="n">
         <v>1</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>3.55</v>
+        <v>1.84</v>
       </c>
       <c r="R228" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="S228" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="T228" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="U228" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="V228" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="W228" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="X228" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y228" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z228" t="n">
-        <v>2.48</v>
+        <v>1.31</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="AB228" t="n">
-        <v>2.73</v>
+        <v>7.6</v>
       </c>
       <c r="AC228" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AD228" t="n">
-        <v>7.42</v>
+        <v>9.1</v>
       </c>
       <c r="AE228" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AF228" t="n">
-        <v>2.29</v>
+        <v>3.64</v>
       </c>
       <c r="AG228" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AH228" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AI228" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AJ228" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AK228" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AL228" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AM228" t="n">
-        <v>1.42</v>
+        <v>3.11</v>
       </c>
       <c r="AN228" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="AO228" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="AP228" t="n">
-        <v>0.73</v>
+        <v>2.38</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AS228" t="n">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AT228" t="n">
-        <v>2.47</v>
+        <v>3.43</v>
       </c>
       <c r="AU228" t="n">
         <v>3</v>
       </c>
       <c r="AV228" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA228" t="n">
         <v>3</v>
-      </c>
-      <c r="AW228" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX228" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY228" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ228" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA228" t="n">
-        <v>8</v>
       </c>
       <c r="BB228" t="n">
         <v>7</v>
       </c>
       <c r="BC228" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BD228" t="n">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="BE228" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="BF228" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="BG228" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BH228" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="BI228" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BJ228" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="BK228" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="BL228" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="BM228" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="BN228" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="BO228" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BP228" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="229">
@@ -50265,7 +50265,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>7834541</v>
+        <v>7834550</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -50285,197 +50285,197 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L229" t="n">
         <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>1.84</v>
+        <v>3.55</v>
       </c>
       <c r="R229" t="n">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="S229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U229" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V229" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X229" t="n">
         <v>8</v>
       </c>
-      <c r="T229" t="n">
+      <c r="Y229" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL229" t="n">
         <v>1.33</v>
       </c>
-      <c r="U229" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V229" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W229" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X229" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y229" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z229" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA229" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB229" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC229" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD229" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE229" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF229" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AG229" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH229" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI229" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ229" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AK229" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL229" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AM229" t="n">
-        <v>3.11</v>
+        <v>1.42</v>
       </c>
       <c r="AN229" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="AO229" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.38</v>
+        <v>0.73</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AT229" t="n">
-        <v>3.43</v>
+        <v>2.47</v>
       </c>
       <c r="AU229" t="n">
         <v>3</v>
       </c>
       <c r="AV229" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW229" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX229" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AY229" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ229" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BA229" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BB229" t="n">
         <v>7</v>
       </c>
       <c r="BC229" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BD229" t="n">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="BE229" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="BF229" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="BG229" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BH229" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="BI229" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="BJ229" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="BK229" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="BL229" t="n">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="BM229" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="BN229" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="BO229" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="BP229" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="230">
@@ -50912,6 +50912,442 @@
       </c>
       <c r="BP231" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>7834467</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>45924.8125</v>
+      </c>
+      <c r="F232" t="n">
+        <v>16</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" t="n">
+        <v>1</v>
+      </c>
+      <c r="N232" t="n">
+        <v>2</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R232" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S232" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U232" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V232" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X232" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC232" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BE232" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH232" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI232" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ232" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO232" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BP232" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>7834462</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>45924.8125</v>
+      </c>
+      <c r="F233" t="n">
+        <v>16</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>1</v>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="n">
+        <v>2</v>
+      </c>
+      <c r="L233" t="n">
+        <v>3</v>
+      </c>
+      <c r="M233" t="n">
+        <v>1</v>
+      </c>
+      <c r="N233" t="n">
+        <v>4</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>['45+1', '60', '77']</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R233" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T233" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U233" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V233" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="W233" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X233" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE233" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI233" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO233" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP233" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.6899999999999999</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.92</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.92</v>
@@ -4402,7 +4402,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.91</v>
@@ -5925,10 +5925,10 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR25" t="n">
         <v>1.58</v>
@@ -6146,7 +6146,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR26" t="n">
         <v>1.59</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ27" t="n">
         <v>2</v>
@@ -6582,7 +6582,7 @@
         <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR28" t="n">
         <v>1.44</v>
@@ -7015,10 +7015,10 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR30" t="n">
         <v>0.67</v>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR31" t="n">
         <v>2.41</v>
@@ -9634,7 +9634,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR42" t="n">
         <v>1.02</v>
@@ -9849,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ43" t="n">
         <v>2</v>
@@ -10067,10 +10067,10 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR44" t="n">
         <v>1.21</v>
@@ -10285,10 +10285,10 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR45" t="n">
         <v>1.32</v>
@@ -10503,7 +10503,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.5</v>
@@ -10939,7 +10939,7 @@
         <v>3</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ48" t="n">
         <v>2.3</v>
@@ -11160,7 +11160,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR49" t="n">
         <v>1.53</v>
@@ -11378,7 +11378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR50" t="n">
         <v>1.69</v>
@@ -14212,7 +14212,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR63" t="n">
         <v>1.51</v>
@@ -14430,7 +14430,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -14648,7 +14648,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR65" t="n">
         <v>1.06</v>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.92</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.3</v>
@@ -15738,7 +15738,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR70" t="n">
         <v>1.81</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.6899999999999999</v>
@@ -16171,7 +16171,7 @@
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.36</v>
@@ -16607,7 +16607,7 @@
         <v>2</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.08</v>
@@ -17264,7 +17264,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR77" t="n">
         <v>1.76</v>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ79" t="n">
         <v>1</v>
@@ -17918,7 +17918,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR80" t="n">
         <v>1.99</v>
@@ -18354,7 +18354,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR82" t="n">
         <v>1.3</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.36</v>
@@ -19008,7 +19008,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR85" t="n">
         <v>1.33</v>
@@ -19223,7 +19223,7 @@
         <v>0.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ86" t="n">
         <v>1</v>
@@ -20316,7 +20316,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR91" t="n">
         <v>1.91</v>
@@ -20534,7 +20534,7 @@
         <v>2</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR92" t="n">
         <v>1.36</v>
@@ -20967,7 +20967,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ94" t="n">
         <v>1</v>
@@ -21185,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.08</v>
@@ -21624,7 +21624,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR97" t="n">
         <v>1.67</v>
@@ -22057,10 +22057,10 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR99" t="n">
         <v>1.4</v>
@@ -22711,7 +22711,7 @@
         <v>1.75</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.08</v>
@@ -22932,7 +22932,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR103" t="n">
         <v>1.69</v>
@@ -23147,7 +23147,7 @@
         <v>0.25</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ104" t="n">
         <v>1</v>
@@ -23804,7 +23804,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR107" t="n">
         <v>1.45</v>
@@ -25112,7 +25112,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR113" t="n">
         <v>1.5</v>
@@ -25327,7 +25327,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.92</v>
@@ -25545,7 +25545,7 @@
         <v>0.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ115" t="n">
         <v>1</v>
@@ -25981,10 +25981,10 @@
         <v>0.67</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR117" t="n">
         <v>2</v>
@@ -26420,7 +26420,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR119" t="n">
         <v>1.92</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.5</v>
@@ -27507,7 +27507,7 @@
         <v>0.4</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.91</v>
@@ -27725,10 +27725,10 @@
         <v>0.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR125" t="n">
         <v>1.49</v>
@@ -27946,7 +27946,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR126" t="n">
         <v>1.59</v>
@@ -28818,7 +28818,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR130" t="n">
         <v>1.83</v>
@@ -29036,7 +29036,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR131" t="n">
         <v>1.76</v>
@@ -29251,7 +29251,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.08</v>
@@ -29469,7 +29469,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -31434,7 +31434,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR142" t="n">
         <v>1.28</v>
@@ -31870,7 +31870,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR144" t="n">
         <v>1.5</v>
@@ -32088,7 +32088,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR145" t="n">
         <v>1.35</v>
@@ -32306,7 +32306,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR146" t="n">
         <v>1.53</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.92</v>
@@ -32960,7 +32960,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR149" t="n">
         <v>1.71</v>
@@ -33393,7 +33393,7 @@
         <v>1.86</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.08</v>
@@ -35137,7 +35137,7 @@
         <v>0.5</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.36</v>
@@ -36012,7 +36012,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR163" t="n">
         <v>1.87</v>
@@ -36663,7 +36663,7 @@
         <v>1.63</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.08</v>
@@ -37538,7 +37538,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR170" t="n">
         <v>1.81</v>
@@ -37756,7 +37756,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR171" t="n">
         <v>1.43</v>
@@ -37974,7 +37974,7 @@
         <v>2</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR172" t="n">
         <v>1.39</v>
@@ -38189,7 +38189,7 @@
         <v>1.38</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.5</v>
@@ -38625,7 +38625,7 @@
         <v>0.89</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.6899999999999999</v>
@@ -39279,10 +39279,10 @@
         <v>0.25</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR178" t="n">
         <v>1.15</v>
@@ -39497,7 +39497,7 @@
         <v>0.78</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ179" t="n">
         <v>1</v>
@@ -41023,7 +41023,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ186" t="n">
         <v>1</v>
@@ -41680,7 +41680,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR189" t="n">
         <v>1.69</v>
@@ -41895,7 +41895,7 @@
         <v>0.78</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.92</v>
@@ -42334,7 +42334,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR192" t="n">
         <v>1.67</v>
@@ -42549,7 +42549,7 @@
         <v>0.89</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.91</v>
@@ -42985,7 +42985,7 @@
         <v>0.7</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ195" t="n">
         <v>1</v>
@@ -43203,7 +43203,7 @@
         <v>1.56</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.5</v>
@@ -43421,10 +43421,10 @@
         <v>1.11</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR197" t="n">
         <v>1.5</v>
@@ -43860,7 +43860,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR199" t="n">
         <v>1.53</v>
@@ -44078,7 +44078,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR200" t="n">
         <v>1.89</v>
@@ -46473,10 +46473,10 @@
         <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR211" t="n">
         <v>1.24</v>
@@ -46691,10 +46691,10 @@
         <v>0.45</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR212" t="n">
         <v>1.53</v>
@@ -46912,7 +46912,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR213" t="n">
         <v>1.6</v>
@@ -47348,7 +47348,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ215" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR215" t="n">
         <v>1.45</v>
@@ -47563,7 +47563,7 @@
         <v>0.91</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.92</v>
@@ -47781,7 +47781,7 @@
         <v>1.89</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ217" t="n">
         <v>2</v>
@@ -48217,7 +48217,7 @@
         <v>0.9</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ219" t="n">
         <v>0.91</v>
@@ -48438,7 +48438,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR220" t="n">
         <v>1.52</v>
@@ -48656,7 +48656,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR221" t="n">
         <v>1.78</v>
@@ -51051,7 +51051,7 @@
         <v>1.55</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ232" t="n">
         <v>1.5</v>
@@ -51269,7 +51269,7 @@
         <v>1.18</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ233" t="n">
         <v>1.08</v>
@@ -51348,6 +51348,1096 @@
       </c>
       <c r="BP233" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>7834559</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>45927.66666666666</v>
+      </c>
+      <c r="F234" t="n">
+        <v>25</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>1</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>1</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R234" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S234" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T234" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U234" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V234" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X234" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY234" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB234" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC234" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE234" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH234" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI234" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ234" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK234" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN234" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO234" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP234" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>7834560</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>45927.77083333334</v>
+      </c>
+      <c r="F235" t="n">
+        <v>25</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" t="n">
+        <v>1</v>
+      </c>
+      <c r="L235" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" t="n">
+        <v>1</v>
+      </c>
+      <c r="N235" t="n">
+        <v>2</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>4</v>
+      </c>
+      <c r="R235" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S235" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U235" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V235" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="W235" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X235" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC235" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BE235" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI235" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL235" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM235" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN235" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO235" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP235" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>7834552</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>45927.77083333334</v>
+      </c>
+      <c r="F236" t="n">
+        <v>25</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>1</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>1</v>
+      </c>
+      <c r="L236" t="n">
+        <v>2</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>['8', '61']</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R236" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S236" t="n">
+        <v>3</v>
+      </c>
+      <c r="T236" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U236" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V236" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W236" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X236" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI236" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ236" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK236" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL236" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM236" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN236" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO236" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP236" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>7834556</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>45927.875</v>
+      </c>
+      <c r="F237" t="n">
+        <v>25</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>1</v>
+      </c>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R237" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S237" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T237" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U237" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V237" t="n">
+        <v>3</v>
+      </c>
+      <c r="W237" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X237" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT237" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU237" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV237" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX237" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY237" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA237" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB237" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC237" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE237" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF237" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH237" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI237" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ237" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BK237" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM237" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN237" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO237" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP237" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>7834557</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>45928.45833333334</v>
+      </c>
+      <c r="F238" t="n">
+        <v>25</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>1</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>1</v>
+      </c>
+      <c r="L238" t="n">
+        <v>3</v>
+      </c>
+      <c r="M238" t="n">
+        <v>1</v>
+      </c>
+      <c r="N238" t="n">
+        <v>4</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>['45+2', '67', '89']</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R238" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S238" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="T238" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U238" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V238" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W238" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X238" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA238" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB238" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC238" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE238" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF238" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG238" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH238" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI238" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ238" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK238" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL238" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM238" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN238" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO238" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP238" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10" t="n">
         <v>1</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.08</v>
@@ -4838,7 +4838,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR23" t="n">
         <v>2.16</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.31</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.92</v>
@@ -8544,7 +8544,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR37" t="n">
         <v>2.89</v>
@@ -10506,7 +10506,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR46" t="n">
         <v>2.83</v>
@@ -10942,7 +10942,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR48" t="n">
         <v>0.86</v>
@@ -11157,7 +11157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.38</v>
@@ -11593,7 +11593,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.91</v>
@@ -14209,7 +14209,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.5</v>
@@ -14863,10 +14863,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR66" t="n">
         <v>1.44</v>
@@ -15302,7 +15302,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -19005,7 +19005,7 @@
         <v>0.5</v>
       </c>
       <c r="AP85" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.38</v>
@@ -19662,7 +19662,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR88" t="n">
         <v>1.76</v>
@@ -19880,7 +19880,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR89" t="n">
         <v>1.76</v>
@@ -20749,7 +20749,7 @@
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.92</v>
@@ -22493,7 +22493,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.92</v>
@@ -23368,7 +23368,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR105" t="n">
         <v>1.65</v>
@@ -24240,7 +24240,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR109" t="n">
         <v>1.56</v>
@@ -26638,7 +26638,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR120" t="n">
         <v>1.39</v>
@@ -26853,7 +26853,7 @@
         <v>1.33</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.6899999999999999</v>
@@ -29033,7 +29033,7 @@
         <v>1.33</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.58</v>
@@ -30780,7 +30780,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR139" t="n">
         <v>1.63</v>
@@ -31649,10 +31649,10 @@
         <v>2.5</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ143" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR143" t="n">
         <v>1.94</v>
@@ -34701,7 +34701,7 @@
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.36</v>
@@ -35791,7 +35791,7 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
         <v>1</v>
@@ -36884,7 +36884,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ167" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR167" t="n">
         <v>1.53</v>
@@ -38192,7 +38192,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR173" t="n">
         <v>1.58</v>
@@ -38407,7 +38407,7 @@
         <v>0.88</v>
       </c>
       <c r="AP174" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ174" t="n">
         <v>1</v>
@@ -39715,7 +39715,7 @@
         <v>0.5</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ180" t="n">
         <v>0.36</v>
@@ -41462,7 +41462,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ188" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR188" t="n">
         <v>1.78</v>
@@ -42767,7 +42767,7 @@
         <v>1</v>
       </c>
       <c r="AP194" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ194" t="n">
         <v>0.92</v>
@@ -43206,7 +43206,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR196" t="n">
         <v>1.27</v>
@@ -45604,7 +45604,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ207" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AR207" t="n">
         <v>1.63</v>
@@ -47127,7 +47127,7 @@
         <v>0.91</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ214" t="n">
         <v>1</v>
@@ -48002,7 +48002,7 @@
         <v>2</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR218" t="n">
         <v>1.43</v>
@@ -48435,7 +48435,7 @@
         <v>1.6</v>
       </c>
       <c r="AP220" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.58</v>
@@ -51054,7 +51054,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR232" t="n">
         <v>1.28</v>
@@ -52438,6 +52438,442 @@
       </c>
       <c r="BP238" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>7834558</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>45928.66666666666</v>
+      </c>
+      <c r="F239" t="n">
+        <v>25</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>4</v>
+      </c>
+      <c r="R239" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S239" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T239" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U239" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V239" t="n">
+        <v>3</v>
+      </c>
+      <c r="W239" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X239" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA239" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB239" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ239" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK239" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM239" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN239" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO239" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP239" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>7834551</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>45928.66666666666</v>
+      </c>
+      <c r="F240" t="n">
+        <v>25</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>1</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" t="n">
+        <v>2</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="n">
+        <v>2</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>['33', '89']</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R240" t="n">
+        <v>2</v>
+      </c>
+      <c r="S240" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T240" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U240" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V240" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W240" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X240" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY240" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA240" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB240" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO240" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP240" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.91</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.92</v>
@@ -4620,7 +4620,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.38</v>
@@ -6364,7 +6364,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR27" t="n">
         <v>1.33</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ36" t="n">
         <v>1</v>
@@ -9631,7 +9631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.5</v>
@@ -9852,7 +9852,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR43" t="n">
         <v>1.42</v>
@@ -11375,7 +11375,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.58</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.92</v>
@@ -15520,7 +15520,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ69" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR69" t="n">
         <v>1.32</v>
@@ -15735,7 +15735,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.31</v>
@@ -19441,7 +19441,7 @@
         <v>0</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.92</v>
@@ -19877,7 +19877,7 @@
         <v>3</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ89" t="n">
         <v>2.09</v>
@@ -21406,7 +21406,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ96" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR96" t="n">
         <v>1.63</v>
@@ -22275,7 +22275,7 @@
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.36</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.38</v>
@@ -24891,7 +24891,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.08</v>
@@ -27071,7 +27071,7 @@
         <v>2</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.08</v>
@@ -28382,7 +28382,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ128" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR128" t="n">
         <v>1.65</v>
@@ -28597,7 +28597,7 @@
         <v>0.5</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.92</v>
@@ -31867,7 +31867,7 @@
         <v>1.57</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.58</v>
@@ -32521,10 +32521,10 @@
         <v>1.67</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ147" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR147" t="n">
         <v>1.49</v>
@@ -36227,7 +36227,7 @@
         <v>0.43</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.36</v>
@@ -36448,7 +36448,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ165" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR165" t="n">
         <v>1.44</v>
@@ -37753,7 +37753,7 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.92</v>
@@ -40587,7 +40587,7 @@
         <v>1.13</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.08</v>
@@ -41244,7 +41244,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ187" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR187" t="n">
         <v>1.86</v>
@@ -42113,7 +42113,7 @@
         <v>0.89</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ191" t="n">
         <v>1</v>
@@ -45601,7 +45601,7 @@
         <v>2.44</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ207" t="n">
         <v>2.09</v>
@@ -47345,7 +47345,7 @@
         <v>0.5</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ215" t="n">
         <v>0.5</v>
@@ -47784,7 +47784,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ217" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AR217" t="n">
         <v>1.32</v>
@@ -50483,7 +50483,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>7834546</v>
+        <v>7834544</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -50503,197 +50503,197 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
         <v>3</v>
       </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>['45+2', '77']</t>
-        </is>
-      </c>
-      <c r="P230" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="Q230" t="n">
-        <v>2.12</v>
-      </c>
       <c r="R230" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S230" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="T230" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="U230" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="V230" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="W230" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="X230" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z230" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA230" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AB230" t="n">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="AC230" t="n">
         <v>1.05</v>
       </c>
       <c r="AD230" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AE230" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AF230" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AG230" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AH230" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AI230" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ230" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK230" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AL230" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AM230" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AN230" t="n">
-        <v>2.33</v>
+        <v>1.2</v>
       </c>
       <c r="AO230" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>2.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AR230" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS230" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AU230" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX230" t="n">
         <v>3</v>
       </c>
-      <c r="AV230" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW230" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX230" t="n">
-        <v>2</v>
-      </c>
       <c r="AY230" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ230" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA230" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC230" t="n">
         <v>7</v>
       </c>
-      <c r="BB230" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC230" t="n">
-        <v>11</v>
-      </c>
       <c r="BD230" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="BE230" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF230" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="BG230" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="BH230" t="n">
-        <v>5.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI230" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="BJ230" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="BK230" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="BL230" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="BM230" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="BN230" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="BO230" t="n">
-        <v>2.05</v>
+        <v>2.97</v>
       </c>
       <c r="BP230" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="231">
@@ -50701,7 +50701,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>7834544</v>
+        <v>7834546</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -50721,197 +50721,197 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['45+2', '77']</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="R231" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S231" t="n">
+        <v>6</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U231" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V231" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X231" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA231" t="n">
         <v>3.85</v>
       </c>
-      <c r="T231" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U231" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V231" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W231" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X231" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y231" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z231" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA231" t="n">
-        <v>3</v>
-      </c>
       <c r="AB231" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="AC231" t="n">
         <v>1.05</v>
       </c>
       <c r="AD231" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AE231" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AF231" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM231" t="n">
         <v>2.4</v>
       </c>
-      <c r="AG231" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH231" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI231" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ231" t="n">
+      <c r="AN231" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR231" t="n">
         <v>1.67</v>
       </c>
-      <c r="AK231" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AL231" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM231" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN231" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO231" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP231" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ231" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR231" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AS231" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD231" t="n">
         <v>1.32</v>
       </c>
-      <c r="AT231" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU231" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV231" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW231" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX231" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY231" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ231" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA231" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB231" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC231" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD231" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BE231" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF231" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="BG231" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="BH231" t="n">
-        <v>3.5</v>
+        <v>5.45</v>
       </c>
       <c r="BI231" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="BJ231" t="n">
-        <v>2.55</v>
+        <v>3.58</v>
       </c>
       <c r="BK231" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="BL231" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="BM231" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="BN231" t="n">
-        <v>1.54</v>
+        <v>2.07</v>
       </c>
       <c r="BO231" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="BP231" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="232">
@@ -51573,7 +51573,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>7834560</v>
+        <v>7834552</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -51593,197 +51593,197 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" t="n">
         <v>1</v>
       </c>
       <c r="L235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
         <v>2</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['8', '61']</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R235" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S235" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T235" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U235" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V235" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="W235" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X235" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Y235" t="n">
         <v>1.01</v>
       </c>
       <c r="Z235" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA235" t="n">
         <v>3.1</v>
       </c>
       <c r="AB235" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="AC235" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD235" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AE235" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AF235" t="n">
-        <v>3.06</v>
+        <v>2.67</v>
       </c>
       <c r="AG235" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AH235" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI235" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ235" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AK235" t="n">
         <v>1.38</v>
       </c>
       <c r="AL235" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM235" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AN235" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AO235" t="n">
-        <v>0.91</v>
+        <v>1.73</v>
       </c>
       <c r="AP235" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.92</v>
+        <v>1.58</v>
       </c>
       <c r="AR235" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC235" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE235" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG235" t="n">
         <v>1.26</v>
       </c>
-      <c r="AS235" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT235" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU235" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV235" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW235" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX235" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY235" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ235" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA235" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB235" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC235" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD235" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BE235" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF235" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BG235" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BH235" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="BI235" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="BJ235" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="BK235" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BL235" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BM235" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BN235" t="n">
         <v>1.64</v>
       </c>
       <c r="BO235" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="BP235" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="236">
@@ -51791,7 +51791,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>7834552</v>
+        <v>7834560</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -51811,197 +51811,197 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" t="n">
         <v>1</v>
       </c>
       <c r="L236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N236" t="n">
         <v>2</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>['8', '61']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="R236" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S236" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T236" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U236" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V236" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="W236" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X236" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Y236" t="n">
         <v>1.01</v>
       </c>
       <c r="Z236" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA236" t="n">
         <v>3.1</v>
       </c>
       <c r="AB236" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD236" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AE236" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF236" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="AG236" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AH236" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI236" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ236" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AK236" t="n">
         <v>1.38</v>
       </c>
       <c r="AL236" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AM236" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AN236" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AO236" t="n">
-        <v>1.73</v>
+        <v>0.91</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.58</v>
+        <v>0.92</v>
       </c>
       <c r="AR236" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AS236" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT236" t="n">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="AU236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX236" t="n">
         <v>3</v>
       </c>
-      <c r="AW236" t="n">
+      <c r="AY236" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC236" t="n">
         <v>8</v>
       </c>
-      <c r="AX236" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY236" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ236" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA236" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB236" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC236" t="n">
-        <v>12</v>
-      </c>
       <c r="BD236" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="BE236" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF236" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI236" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ236" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK236" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL236" t="n">
         <v>1.85</v>
       </c>
-      <c r="BG236" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BH236" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI236" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ236" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BK236" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BL236" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BM236" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BN236" t="n">
         <v>1.64</v>
       </c>
       <c r="BO236" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="BP236" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="237">
@@ -52445,7 +52445,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>7834558</v>
+        <v>7834551</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -52465,35 +52465,35 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M239" t="n">
         <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['33', '89']</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -52502,160 +52502,160 @@
         </is>
       </c>
       <c r="Q239" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R239" t="n">
+        <v>2</v>
+      </c>
+      <c r="S239" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T239" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U239" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V239" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W239" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X239" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA239" t="n">
         <v>4</v>
       </c>
-      <c r="R239" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S239" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T239" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U239" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V239" t="n">
-        <v>3</v>
-      </c>
-      <c r="W239" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X239" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Y239" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z239" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA239" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AB239" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC239" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD239" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE239" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF239" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG239" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH239" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI239" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ239" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK239" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL239" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM239" t="n">
+      <c r="BB239" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ239" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK239" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM239" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN239" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO239" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP239" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AN239" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AO239" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AP239" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ239" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AR239" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS239" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT239" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AU239" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV239" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW239" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX239" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY239" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ239" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA239" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB239" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC239" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD239" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BE239" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF239" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BG239" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BH239" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BI239" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BJ239" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BK239" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BL239" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BM239" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BN239" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO239" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP239" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="240">
@@ -52663,7 +52663,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>7834551</v>
+        <v>7834558</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -52683,35 +52683,35 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M240" t="n">
         <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>['33', '89']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -52720,160 +52720,596 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R240" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S240" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="T240" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="U240" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="V240" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="W240" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X240" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY240" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA240" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB240" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO240" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP240" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>7834555</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>45928.77083333334</v>
+      </c>
+      <c r="F241" t="n">
+        <v>25</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" t="n">
+        <v>2</v>
+      </c>
+      <c r="M241" t="n">
+        <v>2</v>
+      </c>
+      <c r="N241" t="n">
+        <v>4</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>['30', '77']</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>['56', '60']</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R241" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S241" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T241" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U241" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V241" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="W241" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X241" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL241" t="n">
         <v>1.28</v>
       </c>
-      <c r="X240" t="n">
+      <c r="AM241" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ241" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR241" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS241" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT241" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV241" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW241" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX241" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ241" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA241" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB241" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC241" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD241" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE241" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF241" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG241" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH241" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI241" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ241" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK241" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL241" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM241" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN241" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO241" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP241" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>7834553</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>45928.85416666666</v>
+      </c>
+      <c r="F242" t="n">
+        <v>25</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="n">
+        <v>2</v>
+      </c>
+      <c r="N242" t="n">
+        <v>3</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>['55', '87']</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R242" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S242" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T242" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U242" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V242" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W242" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X242" t="n">
         <v>10</v>
       </c>
-      <c r="Y240" t="n">
+      <c r="Y242" t="n">
         <v>1.05</v>
       </c>
-      <c r="Z240" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AA240" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB240" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC240" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD240" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE240" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF240" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG240" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH240" t="n">
+      <c r="Z242" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AE242" t="n">
         <v>1.52</v>
       </c>
-      <c r="AI240" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AJ240" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AK240" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AL240" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM240" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AN240" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AO240" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP240" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ240" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR240" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS240" t="n">
+      <c r="AF242" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN242" t="n">
         <v>1.45</v>
       </c>
-      <c r="AT240" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU240" t="n">
+      <c r="AO242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ242" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AR242" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS242" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT242" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU242" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW242" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX242" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY242" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ242" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA242" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB242" t="n">
         <v>3</v>
       </c>
-      <c r="AV240" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW240" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX240" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY240" t="n">
+      <c r="BC242" t="n">
         <v>8</v>
       </c>
-      <c r="AZ240" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA240" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB240" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC240" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD240" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BE240" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF240" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG240" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BH240" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BI240" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BJ240" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BK240" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BL240" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM240" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BN240" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BO240" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BP240" t="n">
-        <v>1.26</v>
+      <c r="BD242" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE242" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF242" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG242" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH242" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI242" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ242" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK242" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL242" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM242" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN242" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO242" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BP242" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.5</v>
@@ -2876,7 +2876,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.92</v>
@@ -5274,7 +5274,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR22" t="n">
         <v>1.05</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.58</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.38</v>
@@ -8980,7 +8980,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR39" t="n">
         <v>1.72</v>
@@ -10503,7 +10503,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.38</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.92</v>
@@ -11596,7 +11596,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR51" t="n">
         <v>1.41</v>
@@ -11814,7 +11814,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR52" t="n">
         <v>2.07</v>
@@ -13991,7 +13991,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.36</v>
@@ -16174,7 +16174,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR72" t="n">
         <v>1.11</v>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ79" t="n">
         <v>1</v>
@@ -18136,7 +18136,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR81" t="n">
         <v>1.73</v>
@@ -18787,7 +18787,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ84" t="n">
         <v>1</v>
@@ -20531,7 +20531,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.31</v>
@@ -20967,7 +20967,7 @@
         <v>0.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ94" t="n">
         <v>1</v>
@@ -22278,7 +22278,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR100" t="n">
         <v>1.61</v>
@@ -24676,7 +24676,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR111" t="n">
         <v>1.82</v>
@@ -25763,7 +25763,7 @@
         <v>0</v>
       </c>
       <c r="AP116" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.92</v>
@@ -25981,7 +25981,7 @@
         <v>0.67</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.92</v>
@@ -27510,7 +27510,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR124" t="n">
         <v>1.58</v>
@@ -29905,7 +29905,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ135" t="n">
         <v>1</v>
@@ -30126,7 +30126,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR136" t="n">
         <v>1.93</v>
@@ -30562,7 +30562,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR138" t="n">
         <v>1.59</v>
@@ -34047,7 +34047,7 @@
         <v>1</v>
       </c>
       <c r="AP154" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ154" t="n">
         <v>1</v>
@@ -34268,7 +34268,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR155" t="n">
         <v>1.61</v>
@@ -34704,7 +34704,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR157" t="n">
         <v>1.39</v>
@@ -36663,7 +36663,7 @@
         <v>1.63</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.08</v>
@@ -37320,7 +37320,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR169" t="n">
         <v>1.64</v>
@@ -37971,7 +37971,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP172" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.38</v>
@@ -38846,7 +38846,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR176" t="n">
         <v>1.57</v>
@@ -40372,7 +40372,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR183" t="n">
         <v>1.55</v>
@@ -41023,7 +41023,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ186" t="n">
         <v>1</v>
@@ -42552,7 +42552,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR193" t="n">
         <v>1.19</v>
@@ -43639,7 +43639,7 @@
         <v>0.9</v>
       </c>
       <c r="AP198" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.6899999999999999</v>
@@ -44296,7 +44296,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR201" t="n">
         <v>1.36</v>
@@ -47563,7 +47563,7 @@
         <v>0.91</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.92</v>
@@ -47999,7 +47999,7 @@
         <v>1.7</v>
       </c>
       <c r="AP218" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.38</v>
@@ -48220,7 +48220,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR219" t="n">
         <v>1.53</v>
@@ -49746,7 +49746,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ226" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR226" t="n">
         <v>1.74</v>
@@ -52141,7 +52141,7 @@
         <v>1.42</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ237" t="n">
         <v>1.31</v>
@@ -52165,13 +52165,13 @@
         <v>6</v>
       </c>
       <c r="AX237" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY237" t="n">
         <v>11</v>
       </c>
       <c r="AZ237" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA237" t="n">
         <v>4</v>
@@ -52929,7 +52929,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>['30', '77']</t>
+          <t>['30', '78']</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -53310,6 +53310,442 @@
       </c>
       <c r="BP242" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>7834554</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>45929.83333333334</v>
+      </c>
+      <c r="F243" t="n">
+        <v>25</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="n">
+        <v>1</v>
+      </c>
+      <c r="N243" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R243" t="n">
+        <v>2</v>
+      </c>
+      <c r="S243" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="T243" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U243" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V243" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W243" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X243" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ243" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR243" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS243" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT243" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV243" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW243" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY243" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ243" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA243" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB243" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC243" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE243" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF243" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG243" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH243" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI243" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ243" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK243" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL243" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM243" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN243" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO243" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP243" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>7834566</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>45930.89583333334</v>
+      </c>
+      <c r="F244" t="n">
+        <v>26</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R244" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S244" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="T244" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U244" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V244" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="W244" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X244" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO244" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ244" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AR244" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS244" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT244" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW244" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY244" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ244" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA244" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB244" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC244" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD244" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE244" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF244" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BG244" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH244" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI244" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ244" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK244" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL244" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM244" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN244" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO244" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BP244" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.38</v>
@@ -3312,7 +3312,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.42</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.36</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.58</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ20" t="n">
         <v>2.09</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
@@ -7454,7 +7454,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR32" t="n">
         <v>1.38</v>
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.92</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ34" t="n">
         <v>1</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.08</v>
@@ -8541,7 +8541,7 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37" t="n">
         <v>2.09</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.6899999999999999</v>
@@ -9416,7 +9416,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR41" t="n">
         <v>0.83</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.42</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.6899999999999999</v>
@@ -12465,7 +12465,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.36</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ56" t="n">
         <v>1</v>
@@ -13122,7 +13122,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR58" t="n">
         <v>1.28</v>
@@ -13555,10 +13555,10 @@
         <v>0.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR60" t="n">
         <v>1.41</v>
@@ -13773,7 +13773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.08</v>
@@ -16389,7 +16389,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ73" t="n">
         <v>1</v>
@@ -16828,7 +16828,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR75" t="n">
         <v>1.34</v>
@@ -17046,7 +17046,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR76" t="n">
         <v>1.9</v>
@@ -17261,7 +17261,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.58</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.92</v>
@@ -17915,7 +17915,7 @@
         <v>0.75</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.92</v>
@@ -18133,7 +18133,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.08</v>
@@ -20313,7 +20313,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.31</v>
@@ -20752,7 +20752,7 @@
         <v>2</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR93" t="n">
         <v>1.74</v>
@@ -21188,7 +21188,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR95" t="n">
         <v>1.12</v>
@@ -21403,7 +21403,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ96" t="n">
         <v>2.09</v>
@@ -21621,7 +21621,7 @@
         <v>0.6</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.92</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5</v>
@@ -23365,7 +23365,7 @@
         <v>0.4</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.38</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ110" t="n">
         <v>1</v>
@@ -24673,7 +24673,7 @@
         <v>0.5</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.08</v>
@@ -24894,7 +24894,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR112" t="n">
         <v>1.55</v>
@@ -25766,7 +25766,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR116" t="n">
         <v>1.35</v>
@@ -26417,7 +26417,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.38</v>
@@ -27943,7 +27943,7 @@
         <v>1</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.31</v>
@@ -28379,7 +28379,7 @@
         <v>2</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ128" t="n">
         <v>2.09</v>
@@ -28815,7 +28815,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.38</v>
@@ -29254,7 +29254,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR132" t="n">
         <v>1.52</v>
@@ -29687,7 +29687,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.92</v>
@@ -30123,7 +30123,7 @@
         <v>0.83</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.08</v>
@@ -30777,7 +30777,7 @@
         <v>1.14</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.38</v>
@@ -30995,7 +30995,7 @@
         <v>1.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.6899999999999999</v>
@@ -32303,7 +32303,7 @@
         <v>0.57</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.92</v>
@@ -32957,7 +32957,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.38</v>
@@ -33175,7 +33175,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.92</v>
@@ -33611,7 +33611,7 @@
         <v>0.75</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ152" t="n">
         <v>1</v>
@@ -33829,7 +33829,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ153" t="n">
         <v>1</v>
@@ -34483,10 +34483,10 @@
         <v>0.5</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR156" t="n">
         <v>1.84</v>
@@ -35355,10 +35355,10 @@
         <v>1.14</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR160" t="n">
         <v>1.6</v>
@@ -35573,10 +35573,10 @@
         <v>0.57</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR161" t="n">
         <v>1.72</v>
@@ -36009,7 +36009,7 @@
         <v>1.5</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.58</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.92</v>
@@ -37317,7 +37317,7 @@
         <v>0</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ169" t="n">
         <v>0.42</v>
@@ -38843,7 +38843,7 @@
         <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.08</v>
@@ -40151,7 +40151,7 @@
         <v>1.11</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.92</v>
@@ -40590,7 +40590,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR184" t="n">
         <v>1.51</v>
@@ -40805,10 +40805,10 @@
         <v>0.5</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR185" t="n">
         <v>1.69</v>
@@ -41241,7 +41241,7 @@
         <v>1.75</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ187" t="n">
         <v>2.09</v>
@@ -41459,7 +41459,7 @@
         <v>2.38</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ188" t="n">
         <v>2.09</v>
@@ -41677,7 +41677,7 @@
         <v>1.67</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.58</v>
@@ -41898,7 +41898,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR190" t="n">
         <v>1.29</v>
@@ -43857,7 +43857,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP199" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.5</v>
@@ -44511,7 +44511,7 @@
         <v>1.3</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.08</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ205" t="n">
         <v>1</v>
@@ -45819,10 +45819,10 @@
         <v>1.33</v>
       </c>
       <c r="AP208" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR208" t="n">
         <v>1.72</v>
@@ -46037,10 +46037,10 @@
         <v>0.7</v>
       </c>
       <c r="AP209" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR209" t="n">
         <v>1.45</v>
@@ -46255,7 +46255,7 @@
         <v>0.44</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.36</v>
@@ -46909,7 +46909,7 @@
         <v>1</v>
       </c>
       <c r="AP213" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.92</v>
@@ -48653,7 +48653,7 @@
         <v>1.45</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ221" t="n">
         <v>1.31</v>
@@ -49092,7 +49092,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR223" t="n">
         <v>1.39</v>
@@ -49307,7 +49307,7 @@
         <v>0.75</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ224" t="n">
         <v>0.6899999999999999</v>
@@ -49525,7 +49525,7 @@
         <v>0.4</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.36</v>
@@ -49743,7 +49743,7 @@
         <v>0.4</v>
       </c>
       <c r="AP226" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.42</v>
@@ -49961,7 +49961,7 @@
         <v>0.82</v>
       </c>
       <c r="AP227" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ227" t="n">
         <v>1</v>
@@ -50182,7 +50182,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR228" t="n">
         <v>1.98</v>
@@ -50397,7 +50397,7 @@
         <v>1.08</v>
       </c>
       <c r="AP229" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ229" t="n">
         <v>1</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.92</v>
@@ -51272,7 +51272,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR233" t="n">
         <v>1.56</v>
@@ -53746,6 +53746,1314 @@
       </c>
       <c r="BP244" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>7834565</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>45931.79166666666</v>
+      </c>
+      <c r="F245" t="n">
+        <v>26</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" t="n">
+        <v>1</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="n">
+        <v>1</v>
+      </c>
+      <c r="N245" t="n">
+        <v>2</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R245" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S245" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T245" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V245" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W245" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X245" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT245" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY245" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB245" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC245" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE245" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF245" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI245" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ245" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK245" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM245" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN245" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO245" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP245" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>7834563</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>45931.79166666666</v>
+      </c>
+      <c r="F246" t="n">
+        <v>26</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>3</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>3</v>
+      </c>
+      <c r="L246" t="n">
+        <v>3</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="n">
+        <v>3</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>['6', '18', '24']</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R246" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S246" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="T246" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U246" t="n">
+        <v>3</v>
+      </c>
+      <c r="V246" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W246" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X246" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT246" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU246" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY246" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA246" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB246" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC246" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BE246" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF246" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG246" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH246" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI246" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ246" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK246" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM246" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN246" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO246" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP246" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>7834570</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>45931.79166666666</v>
+      </c>
+      <c r="F247" t="n">
+        <v>26</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>2</v>
+      </c>
+      <c r="M247" t="n">
+        <v>2</v>
+      </c>
+      <c r="N247" t="n">
+        <v>4</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>['73', '90+7']</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>['64', '83']</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>4</v>
+      </c>
+      <c r="R247" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S247" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="T247" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U247" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V247" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W247" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X247" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT247" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX247" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY247" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ247" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA247" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB247" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC247" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD247" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE247" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF247" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG247" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH247" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI247" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ247" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK247" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL247" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM247" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN247" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO247" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP247" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>7834567</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>45931.8125</v>
+      </c>
+      <c r="F248" t="n">
+        <v>26</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>1</v>
+      </c>
+      <c r="K248" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" t="n">
+        <v>1</v>
+      </c>
+      <c r="N248" t="n">
+        <v>2</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>['90+12']</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R248" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S248" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T248" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U248" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V248" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W248" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X248" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP248" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR248" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS248" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT248" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU248" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX248" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY248" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ248" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA248" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB248" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC248" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD248" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE248" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF248" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG248" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH248" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BI248" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ248" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK248" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL248" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM248" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BN248" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO248" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP248" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>7834562</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>45931.89583333334</v>
+      </c>
+      <c r="F249" t="n">
+        <v>26</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>1</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" t="n">
+        <v>2</v>
+      </c>
+      <c r="M249" t="n">
+        <v>1</v>
+      </c>
+      <c r="N249" t="n">
+        <v>3</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>['27', '46']</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R249" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S249" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T249" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U249" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V249" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W249" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X249" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO249" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP249" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR249" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS249" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT249" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU249" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW249" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX249" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY249" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA249" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB249" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC249" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD249" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE249" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF249" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG249" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH249" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI249" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ249" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK249" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BL249" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM249" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN249" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO249" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP249" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>7834564</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>45931.89583333334</v>
+      </c>
+      <c r="F250" t="n">
+        <v>26</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="n">
+        <v>1</v>
+      </c>
+      <c r="N250" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R250" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S250" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T250" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U250" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V250" t="n">
+        <v>3</v>
+      </c>
+      <c r="W250" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X250" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR250" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS250" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT250" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU250" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY250" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ250" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA250" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB250" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC250" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD250" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE250" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF250" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG250" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH250" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI250" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ250" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK250" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL250" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM250" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN250" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO250" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP250" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -53909,13 +53909,13 @@
         <v>9</v>
       </c>
       <c r="AX245" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY245" t="n">
         <v>14</v>
       </c>
       <c r="AZ245" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA245" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP250"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.92</v>
@@ -2876,7 +2876,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ19" t="n">
         <v>2.09</v>
@@ -5274,7 +5274,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>1.05</v>
@@ -6582,7 +6582,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR28" t="n">
         <v>1.44</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.92</v>
@@ -7672,7 +7672,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR33" t="n">
         <v>1.76</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.42</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.36</v>
@@ -10939,7 +10939,7 @@
         <v>3</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ48" t="n">
         <v>2.09</v>
@@ -11378,7 +11378,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR50" t="n">
         <v>1.69</v>
@@ -11596,7 +11596,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR51" t="n">
         <v>1.41</v>
@@ -12032,7 +12032,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR53" t="n">
         <v>1.22</v>
@@ -12901,7 +12901,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ57" t="n">
         <v>1</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ59" t="n">
         <v>1</v>
@@ -16171,7 +16171,7 @@
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.42</v>
@@ -16825,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.85</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ76" t="n">
         <v>1</v>
@@ -17264,7 +17264,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR77" t="n">
         <v>1.76</v>
@@ -17482,7 +17482,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR78" t="n">
         <v>1.57</v>
@@ -18136,7 +18136,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR81" t="n">
         <v>1.73</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.38</v>
@@ -21839,7 +21839,7 @@
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.92</v>
@@ -22057,10 +22057,10 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR99" t="n">
         <v>1.4</v>
@@ -22496,7 +22496,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR101" t="n">
         <v>1.23</v>
@@ -23583,7 +23583,7 @@
         <v>0.6</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.36</v>
@@ -24676,7 +24676,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR111" t="n">
         <v>1.82</v>
@@ -25109,10 +25109,10 @@
         <v>1.4</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR113" t="n">
         <v>1.5</v>
@@ -25327,7 +25327,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.92</v>
@@ -26199,10 +26199,10 @@
         <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR118" t="n">
         <v>1.8</v>
@@ -27507,10 +27507,10 @@
         <v>0.4</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR124" t="n">
         <v>1.58</v>
@@ -28600,7 +28600,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -29036,7 +29036,7 @@
         <v>2</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR131" t="n">
         <v>1.76</v>
@@ -29251,7 +29251,7 @@
         <v>1.17</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ132" t="n">
         <v>1</v>
@@ -30126,7 +30126,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR136" t="n">
         <v>1.93</v>
@@ -30341,7 +30341,7 @@
         <v>2.17</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.08</v>
@@ -31213,7 +31213,7 @@
         <v>1.17</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ141" t="n">
         <v>1</v>
@@ -31870,7 +31870,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR144" t="n">
         <v>1.5</v>
@@ -32085,7 +32085,7 @@
         <v>0.14</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.5</v>
@@ -32742,7 +32742,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR148" t="n">
         <v>1.37</v>
@@ -33393,7 +33393,7 @@
         <v>1.86</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.08</v>
@@ -34268,7 +34268,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR155" t="n">
         <v>1.61</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.6899999999999999</v>
@@ -36012,7 +36012,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR163" t="n">
         <v>1.87</v>
@@ -36881,7 +36881,7 @@
         <v>2.57</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ167" t="n">
         <v>2.09</v>
@@ -37102,7 +37102,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR168" t="n">
         <v>1.94</v>
@@ -37535,7 +37535,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.31</v>
@@ -38189,7 +38189,7 @@
         <v>1.38</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.38</v>
@@ -38846,7 +38846,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR176" t="n">
         <v>1.57</v>
@@ -40154,7 +40154,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR182" t="n">
         <v>1.48</v>
@@ -40369,7 +40369,7 @@
         <v>0</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ183" t="n">
         <v>0.42</v>
@@ -41680,7 +41680,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR189" t="n">
         <v>1.69</v>
@@ -42552,7 +42552,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR193" t="n">
         <v>1.19</v>
@@ -43421,7 +43421,7 @@
         <v>1.11</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.31</v>
@@ -44075,7 +44075,7 @@
         <v>0.5</v>
       </c>
       <c r="AP200" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.38</v>
@@ -44732,7 +44732,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ203" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR203" t="n">
         <v>1.68</v>
@@ -44947,7 +44947,7 @@
         <v>0.8</v>
       </c>
       <c r="AP204" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ204" t="n">
         <v>1</v>
@@ -45383,7 +45383,7 @@
         <v>0.82</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.6899999999999999</v>
@@ -46691,7 +46691,7 @@
         <v>0.45</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ212" t="n">
         <v>0.38</v>
@@ -48220,7 +48220,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR219" t="n">
         <v>1.53</v>
@@ -48438,7 +48438,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR220" t="n">
         <v>1.52</v>
@@ -48871,7 +48871,7 @@
         <v>0.82</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ222" t="n">
         <v>1</v>
@@ -50179,7 +50179,7 @@
         <v>0.91</v>
       </c>
       <c r="AP228" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.85</v>
@@ -50483,7 +50483,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>7834544</v>
+        <v>7834546</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -50503,197 +50503,197 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['45+2', '77']</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="R230" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S230" t="n">
+        <v>6</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X230" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA230" t="n">
         <v>3.85</v>
       </c>
-      <c r="T230" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U230" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V230" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W230" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X230" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y230" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z230" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA230" t="n">
-        <v>3</v>
-      </c>
       <c r="AB230" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="AC230" t="n">
         <v>1.05</v>
       </c>
       <c r="AD230" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AE230" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AF230" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM230" t="n">
         <v>2.4</v>
       </c>
-      <c r="AG230" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH230" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI230" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ230" t="n">
+      <c r="AN230" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR230" t="n">
         <v>1.67</v>
       </c>
-      <c r="AK230" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AL230" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM230" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN230" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO230" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP230" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ230" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AR230" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AS230" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD230" t="n">
         <v>1.32</v>
       </c>
-      <c r="AT230" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU230" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV230" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW230" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX230" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY230" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ230" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA230" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB230" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC230" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD230" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BE230" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF230" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="BG230" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="BH230" t="n">
-        <v>3.5</v>
+        <v>5.45</v>
       </c>
       <c r="BI230" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="BJ230" t="n">
-        <v>2.55</v>
+        <v>3.58</v>
       </c>
       <c r="BK230" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="BL230" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="BM230" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="BN230" t="n">
-        <v>1.54</v>
+        <v>2.07</v>
       </c>
       <c r="BO230" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="BP230" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="231">
@@ -50701,7 +50701,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>7834546</v>
+        <v>7834544</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -50721,197 +50721,197 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
         <v>3</v>
       </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>['45+2', '77']</t>
-        </is>
-      </c>
-      <c r="P231" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="Q231" t="n">
-        <v>2.12</v>
-      </c>
       <c r="R231" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S231" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="T231" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="U231" t="n">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="V231" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="W231" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="X231" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Y231" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z231" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AA231" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AB231" t="n">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="AC231" t="n">
         <v>1.05</v>
       </c>
       <c r="AD231" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AE231" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AF231" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AG231" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AH231" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AI231" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ231" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK231" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AL231" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AM231" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AN231" t="n">
-        <v>2.33</v>
+        <v>1.2</v>
       </c>
       <c r="AO231" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AP231" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ231" t="n">
         <v>1.08</v>
       </c>
       <c r="AR231" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AT231" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AU231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX231" t="n">
         <v>3</v>
       </c>
-      <c r="AV231" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW231" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX231" t="n">
-        <v>2</v>
-      </c>
       <c r="AY231" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ231" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC231" t="n">
         <v>7</v>
       </c>
-      <c r="BB231" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC231" t="n">
-        <v>11</v>
-      </c>
       <c r="BD231" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="BE231" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF231" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="BG231" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="BH231" t="n">
-        <v>5.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI231" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="BJ231" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="BK231" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="BL231" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="BM231" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="BN231" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="BO231" t="n">
-        <v>2.05</v>
+        <v>2.97</v>
       </c>
       <c r="BP231" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="232">
@@ -51487,7 +51487,7 @@
         <v>0.55</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ234" t="n">
         <v>0.5</v>
@@ -51573,7 +51573,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>7834552</v>
+        <v>7834560</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -51593,197 +51593,197 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="n">
         <v>1</v>
       </c>
       <c r="L235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N235" t="n">
         <v>2</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>['8', '61']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="R235" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S235" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T235" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U235" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V235" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="W235" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X235" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Y235" t="n">
         <v>1.01</v>
       </c>
       <c r="Z235" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA235" t="n">
         <v>3.1</v>
       </c>
       <c r="AB235" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="AC235" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD235" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AE235" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF235" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="AG235" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AH235" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI235" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ235" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AK235" t="n">
         <v>1.38</v>
       </c>
       <c r="AL235" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AM235" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AN235" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AO235" t="n">
-        <v>1.73</v>
+        <v>0.91</v>
       </c>
       <c r="AP235" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AQ235" t="n">
-        <v>1.58</v>
+        <v>0.92</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AS235" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="AU235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX235" t="n">
         <v>3</v>
       </c>
-      <c r="AW235" t="n">
+      <c r="AY235" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC235" t="n">
         <v>8</v>
       </c>
-      <c r="AX235" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY235" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ235" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA235" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB235" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC235" t="n">
-        <v>12</v>
-      </c>
       <c r="BD235" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="BE235" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF235" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI235" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL235" t="n">
         <v>1.85</v>
       </c>
-      <c r="BG235" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BH235" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI235" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ235" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BK235" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BL235" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BM235" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BN235" t="n">
         <v>1.64</v>
       </c>
       <c r="BO235" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="BP235" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="236">
@@ -51791,7 +51791,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>7834560</v>
+        <v>7834552</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -51811,197 +51811,197 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236" t="n">
         <v>1</v>
       </c>
       <c r="L236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
         <v>2</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['8', '61']</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R236" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S236" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T236" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U236" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V236" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="W236" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X236" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Y236" t="n">
         <v>1.01</v>
       </c>
       <c r="Z236" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA236" t="n">
         <v>3.1</v>
       </c>
       <c r="AB236" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD236" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AE236" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AF236" t="n">
-        <v>3.06</v>
+        <v>2.67</v>
       </c>
       <c r="AG236" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AH236" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI236" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ236" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AK236" t="n">
         <v>1.38</v>
       </c>
       <c r="AL236" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM236" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AN236" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AO236" t="n">
-        <v>0.91</v>
+        <v>1.73</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AQ236" t="n">
-        <v>0.92</v>
+        <v>1.54</v>
       </c>
       <c r="AR236" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG236" t="n">
         <v>1.26</v>
       </c>
-      <c r="AS236" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT236" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU236" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV236" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW236" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX236" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY236" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ236" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA236" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB236" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC236" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD236" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BE236" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF236" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BG236" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BH236" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="BI236" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="BJ236" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="BK236" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BL236" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BM236" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BN236" t="n">
         <v>1.64</v>
       </c>
       <c r="BO236" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="BP236" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="237">
@@ -52445,7 +52445,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>7834551</v>
+        <v>7834558</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -52465,35 +52465,35 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
         <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>['33', '89']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -52502,160 +52502,160 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R239" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S239" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="T239" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="U239" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="V239" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="W239" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X239" t="n">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="Y239" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z239" t="n">
-        <v>2.47</v>
+        <v>3.8</v>
       </c>
       <c r="AA239" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="AB239" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC239" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AD239" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE239" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA239" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB239" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ239" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK239" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM239" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN239" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF239" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG239" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH239" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI239" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AJ239" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AK239" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AL239" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM239" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AN239" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AO239" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP239" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ239" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR239" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS239" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AT239" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU239" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV239" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW239" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX239" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY239" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ239" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA239" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB239" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC239" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD239" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BE239" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF239" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG239" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BH239" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BI239" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BJ239" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BK239" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BL239" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM239" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BN239" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BO239" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="BP239" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="240">
@@ -52663,7 +52663,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>7834558</v>
+        <v>7834551</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -52683,35 +52683,35 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M240" t="n">
         <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['33', '89']</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -52720,160 +52720,160 @@
         </is>
       </c>
       <c r="Q240" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R240" t="n">
+        <v>2</v>
+      </c>
+      <c r="S240" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T240" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U240" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V240" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W240" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X240" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY240" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA240" t="n">
         <v>4</v>
       </c>
-      <c r="R240" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S240" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T240" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U240" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V240" t="n">
-        <v>3</v>
-      </c>
-      <c r="W240" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X240" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Y240" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z240" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA240" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AB240" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC240" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD240" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE240" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF240" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG240" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH240" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI240" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ240" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK240" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL240" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM240" t="n">
+      <c r="BB240" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO240" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP240" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AN240" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AO240" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AP240" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ240" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AR240" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS240" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT240" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AU240" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV240" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW240" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX240" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY240" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ240" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA240" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB240" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC240" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD240" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BE240" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF240" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BG240" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BH240" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BI240" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BJ240" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BK240" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BL240" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BM240" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BN240" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO240" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP240" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="241">
@@ -53452,7 +53452,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ243" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR243" t="n">
         <v>1.41</v>
@@ -53753,7 +53753,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>7834565</v>
+        <v>7834570</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -53773,197 +53773,197 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I245" t="n">
         <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['73', '90+7']</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['64', '83']</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="R245" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S245" t="n">
-        <v>4.75</v>
+        <v>3.21</v>
       </c>
       <c r="T245" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U245" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="V245" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="W245" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="X245" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y245" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z245" t="n">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="AA245" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AB245" t="n">
-        <v>4.5</v>
+        <v>2.44</v>
       </c>
       <c r="AC245" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AD245" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE245" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF245" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AG245" t="n">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="AH245" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AI245" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AJ245" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AK245" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AL245" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AM245" t="n">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="AN245" t="n">
-        <v>2.27</v>
+        <v>0.73</v>
       </c>
       <c r="AO245" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP245" t="n">
-        <v>2.17</v>
+        <v>0.75</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR245" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AS245" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AT245" t="n">
-        <v>2.96</v>
+        <v>2.54</v>
       </c>
       <c r="AU245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV245" t="n">
         <v>5</v>
       </c>
-      <c r="AV245" t="n">
+      <c r="AW245" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY245" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB245" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC245" t="n">
         <v>4</v>
       </c>
-      <c r="AW245" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX245" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY245" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ245" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA245" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB245" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC245" t="n">
-        <v>17</v>
-      </c>
       <c r="BD245" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="BE245" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF245" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="BG245" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BH245" t="n">
-        <v>4.6</v>
+        <v>3.78</v>
       </c>
       <c r="BI245" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BJ245" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BK245" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BL245" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="BM245" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="BN245" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BO245" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="BP245" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="246">
@@ -53971,7 +53971,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>7834563</v>
+        <v>7834565</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -53991,197 +53991,197 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I246" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L246" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>['6', '18', '24']</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="Q246" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R246" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S246" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T246" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U246" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V246" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W246" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X246" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT246" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU246" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY246" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA246" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB246" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC246" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE246" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF246" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG246" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH246" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI246" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ246" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK246" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM246" t="n">
         <v>1.9</v>
       </c>
-      <c r="R246" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S246" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="T246" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="U246" t="n">
-        <v>3</v>
-      </c>
-      <c r="V246" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="W246" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X246" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y246" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z246" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA246" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB246" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AC246" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD246" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AE246" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF246" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AG246" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH246" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI246" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AJ246" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK246" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AL246" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AM246" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN246" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO246" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP246" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AQ246" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AR246" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS246" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AT246" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AU246" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV246" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW246" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX246" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY246" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ246" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA246" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB246" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC246" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD246" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BE246" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF246" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG246" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BH246" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BI246" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BJ246" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BK246" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BL246" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BM246" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BN246" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="BO246" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BP246" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="247">
@@ -54189,7 +54189,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>7834570</v>
+        <v>7834563</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -54209,197 +54209,197 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>['73', '90+7']</t>
+          <t>['6', '18', '24']</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>['64', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="R247" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S247" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="T247" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U247" t="n">
+        <v>3</v>
+      </c>
+      <c r="V247" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W247" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X247" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH247" t="n">
         <v>1.95</v>
       </c>
-      <c r="S247" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="T247" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U247" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="V247" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W247" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X247" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y247" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z247" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA247" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB247" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AC247" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD247" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE247" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF247" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG247" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AH247" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AI247" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AJ247" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AK247" t="n">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="AL247" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AM247" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="AN247" t="n">
-        <v>0.73</v>
+        <v>2.17</v>
       </c>
       <c r="AO247" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP247" t="n">
-        <v>0.75</v>
+        <v>2.23</v>
       </c>
       <c r="AQ247" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AR247" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AS247" t="n">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AT247" t="n">
-        <v>2.54</v>
+        <v>3.16</v>
       </c>
       <c r="AU247" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW247" t="n">
         <v>5</v>
-      </c>
-      <c r="AW247" t="n">
-        <v>8</v>
       </c>
       <c r="AX247" t="n">
         <v>6</v>
       </c>
       <c r="AY247" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ247" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA247" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB247" t="n">
         <v>3</v>
-      </c>
-      <c r="BB247" t="n">
-        <v>1</v>
       </c>
       <c r="BC247" t="n">
         <v>4</v>
       </c>
       <c r="BD247" t="n">
-        <v>2.35</v>
+        <v>1.16</v>
       </c>
       <c r="BE247" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF247" t="n">
-        <v>1.82</v>
+        <v>5.1</v>
       </c>
       <c r="BG247" t="n">
         <v>1.21</v>
       </c>
       <c r="BH247" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="BI247" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BJ247" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="BK247" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BL247" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="BM247" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BN247" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BO247" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="BP247" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="248">
@@ -55054,6 +55054,660 @@
       </c>
       <c r="BP250" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>7834568</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>45932.79166666666</v>
+      </c>
+      <c r="F251" t="n">
+        <v>26</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>1</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R251" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S251" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T251" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U251" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V251" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W251" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X251" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO251" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR251" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS251" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT251" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU251" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV251" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX251" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY251" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA251" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB251" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC251" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD251" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE251" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF251" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG251" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH251" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI251" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ251" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK251" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL251" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM251" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN251" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO251" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP251" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>7834569</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>45932.8125</v>
+      </c>
+      <c r="F252" t="n">
+        <v>26</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>1</v>
+      </c>
+      <c r="K252" t="n">
+        <v>1</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" t="n">
+        <v>2</v>
+      </c>
+      <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>['11', '85']</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R252" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S252" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T252" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U252" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V252" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W252" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X252" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO252" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ252" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR252" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS252" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT252" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU252" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX252" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY252" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA252" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB252" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC252" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD252" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE252" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF252" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG252" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH252" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI252" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ252" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK252" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM252" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN252" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO252" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP252" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>7834561</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>45932.85416666666</v>
+      </c>
+      <c r="F253" t="n">
+        <v>26</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R253" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S253" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T253" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U253" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V253" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W253" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X253" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ253" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR253" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS253" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT253" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AU253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV253" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX253" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY253" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA253" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB253" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC253" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE253" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF253" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG253" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI253" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ253" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK253" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL253" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM253" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN253" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO253" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP253" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -41901,13 +41901,13 @@
         <v>0.85</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AS190" t="n">
         <v>1.47</v>
       </c>
       <c r="AT190" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="AU190" t="n">
         <v>5</v>
@@ -42555,13 +42555,13 @@
         <v>1</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AS193" t="n">
         <v>1.08</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AU193" t="n">
         <v>5</v>
@@ -42994,10 +42994,10 @@
         <v>1.57</v>
       </c>
       <c r="AS195" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AU195" t="n">
         <v>3</v>
@@ -43209,13 +43209,13 @@
         <v>1.29</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AS196" t="n">
         <v>1.48</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AU196" t="n">
         <v>6</v>
@@ -43866,10 +43866,10 @@
         <v>1.53</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AU199" t="n">
         <v>8</v>
@@ -44517,13 +44517,13 @@
         <v>1.08</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AS202" t="n">
         <v>1.28</v>
       </c>
       <c r="AT202" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="AU202" t="n">
         <v>6</v>
@@ -45392,10 +45392,10 @@
         <v>1.57</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AT206" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AU206" t="n">
         <v>4</v>
@@ -45469,7 +45469,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>7834523</v>
+        <v>7834525</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -45489,197 +45489,197 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M207" t="n">
         <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['2', '22', '30', '59', '75']</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="R207" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S207" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V207" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X207" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ207" t="n">
         <v>1.95</v>
       </c>
-      <c r="S207" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T207" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U207" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V207" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W207" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X207" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y207" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z207" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA207" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB207" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC207" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD207" t="n">
+      <c r="AK207" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV207" t="n">
         <v>6</v>
       </c>
-      <c r="AE207" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF207" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG207" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH207" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI207" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ207" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK207" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL207" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM207" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN207" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO207" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AP207" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ207" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AR207" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS207" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AT207" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AU207" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV207" t="n">
-        <v>7</v>
-      </c>
       <c r="AW207" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX207" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY207" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ207" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB207" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BC207" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BD207" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="BE207" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF207" t="n">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="BG207" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BH207" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="BI207" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="BJ207" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="BK207" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BL207" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="BM207" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="BN207" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="BO207" t="n">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="BP207" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="208">
@@ -45687,7 +45687,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>7834525</v>
+        <v>7834523</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -45707,197 +45707,197 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="n">
+        <v>2</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" t="n">
+        <v>2</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S208" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U208" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V208" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X208" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA208" t="n">
         <v>3</v>
       </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
+      <c r="AB208" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA208" t="n">
         <v>3</v>
       </c>
-      <c r="L208" t="n">
-        <v>5</v>
-      </c>
-      <c r="M208" t="n">
-        <v>1</v>
-      </c>
-      <c r="N208" t="n">
-        <v>6</v>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>['2', '22', '30', '59', '75']</t>
-        </is>
-      </c>
-      <c r="P208" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="Q208" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R208" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S208" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T208" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U208" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V208" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="W208" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X208" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="Y208" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z208" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA208" t="n">
+      <c r="BB208" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH208" t="n">
         <v>3.15</v>
       </c>
-      <c r="AB208" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AC208" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD208" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE208" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF208" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AG208" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH208" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI208" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ208" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK208" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM208" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN208" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AO208" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AP208" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AQ208" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR208" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS208" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AT208" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AU208" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV208" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW208" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX208" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY208" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ208" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA208" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB208" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC208" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD208" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BE208" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF208" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BG208" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH208" t="n">
-        <v>3.92</v>
-      </c>
       <c r="BI208" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="BJ208" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="BK208" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="BL208" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="BM208" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="BN208" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="BO208" t="n">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="BP208" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="209">
@@ -45905,7 +45905,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>7834530</v>
+        <v>7834527</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -45925,143 +45925,143 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I209" t="n">
         <v>1</v>
       </c>
       <c r="J209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K209" t="n">
+        <v>2</v>
+      </c>
+      <c r="L209" t="n">
+        <v>2</v>
+      </c>
+      <c r="M209" t="n">
+        <v>1</v>
+      </c>
+      <c r="N209" t="n">
         <v>3</v>
       </c>
-      <c r="L209" t="n">
-        <v>2</v>
-      </c>
-      <c r="M209" t="n">
-        <v>3</v>
-      </c>
-      <c r="N209" t="n">
-        <v>5</v>
-      </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>['25', '74']</t>
+          <t>['24', '51']</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>['8', '43', '49']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="R209" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="S209" t="n">
-        <v>3.66</v>
+        <v>5.5</v>
       </c>
       <c r="T209" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="U209" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V209" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="W209" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X209" t="n">
         <v>7.5</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z209" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AA209" t="n">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="AB209" t="n">
-        <v>3.08</v>
+        <v>5.05</v>
       </c>
       <c r="AC209" t="n">
         <v>1.06</v>
       </c>
       <c r="AD209" t="n">
-        <v>7.4</v>
+        <v>9.5</v>
       </c>
       <c r="AE209" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AF209" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="AG209" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH209" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AI209" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ209" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AK209" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AL209" t="n">
         <v>0</v>
       </c>
       <c r="AM209" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AN209" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="AO209" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="AP209" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.85</v>
+        <v>0.58</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="AU209" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX209" t="n">
         <v>7</v>
-      </c>
-      <c r="AW209" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX209" t="n">
-        <v>3</v>
       </c>
       <c r="AY209" t="n">
         <v>14</v>
@@ -46070,52 +46070,52 @@
         <v>10</v>
       </c>
       <c r="BA209" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BB209" t="n">
         <v>5</v>
       </c>
       <c r="BC209" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BD209" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="BE209" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="BF209" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="BG209" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BH209" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BI209" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="BJ209" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BK209" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="BL209" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="BM209" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="BN209" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="BO209" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="BP209" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="210">
@@ -46123,7 +46123,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>7834527</v>
+        <v>7834530</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -46143,143 +46143,143 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I210" t="n">
         <v>1</v>
       </c>
       <c r="J210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N210" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>['24', '51']</t>
+          <t>['25', '74']</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['8', '43', '49']</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="R210" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="S210" t="n">
-        <v>5.5</v>
+        <v>3.66</v>
       </c>
       <c r="T210" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U210" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V210" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="W210" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X210" t="n">
         <v>7.5</v>
       </c>
       <c r="Y210" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z210" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AA210" t="n">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="AB210" t="n">
-        <v>5.05</v>
+        <v>3.08</v>
       </c>
       <c r="AC210" t="n">
         <v>1.06</v>
       </c>
       <c r="AD210" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="AE210" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AF210" t="n">
-        <v>3.12</v>
+        <v>2.83</v>
       </c>
       <c r="AG210" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH210" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI210" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AJ210" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AK210" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AL210" t="n">
         <v>0</v>
       </c>
       <c r="AM210" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="AN210" t="n">
-        <v>1.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO210" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="AU210" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV210" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX210" t="n">
         <v>3</v>
-      </c>
-      <c r="AW210" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX210" t="n">
-        <v>7</v>
       </c>
       <c r="AY210" t="n">
         <v>14</v>
@@ -46288,52 +46288,52 @@
         <v>10</v>
       </c>
       <c r="BA210" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BB210" t="n">
         <v>5</v>
       </c>
       <c r="BC210" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BD210" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="BE210" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="BF210" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="BG210" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BH210" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BI210" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="BJ210" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BK210" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="BL210" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="BM210" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="BN210" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="BO210" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BP210" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="211">
@@ -46341,7 +46341,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>7834537</v>
+        <v>7834539</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -46361,197 +46361,197 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K211" t="n">
         <v>1</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
+          <t>['31', '47']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
       <c r="Q211" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="R211" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="S211" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="T211" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="U211" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V211" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="W211" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X211" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z211" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG211" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA211" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB211" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AC211" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD211" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE211" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF211" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG211" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH211" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI211" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AJ211" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AK211" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AL211" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AM211" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AN211" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AO211" t="n">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.21</v>
+        <v>0.36</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="AU211" t="n">
         <v>5</v>
       </c>
       <c r="AV211" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC211" t="n">
         <v>6</v>
       </c>
-      <c r="AW211" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX211" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY211" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ211" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA211" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB211" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC211" t="n">
-        <v>9</v>
-      </c>
       <c r="BD211" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="BE211" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF211" t="n">
-        <v>2.65</v>
+        <v>4.65</v>
       </c>
       <c r="BG211" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BH211" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="BI211" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BJ211" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="BK211" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="BL211" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BM211" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="BN211" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="BO211" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="BP211" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="212">
@@ -46559,7 +46559,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>7834539</v>
+        <v>7834537</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -46579,197 +46579,197 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K212" t="n">
         <v>1</v>
       </c>
       <c r="L212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>['31', '47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R212" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S212" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="T212" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="U212" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V212" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="W212" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X212" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK212" t="n">
         <v>1.32</v>
       </c>
-      <c r="X212" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y212" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z212" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA212" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB212" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC212" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD212" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE212" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF212" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG212" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH212" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI212" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ212" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AK212" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AL212" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AM212" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AN212" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AO212" t="n">
-        <v>0.45</v>
+        <v>1.3</v>
       </c>
       <c r="AP212" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ212" t="n">
         <v>1.21</v>
       </c>
-      <c r="AQ212" t="n">
-        <v>0.36</v>
-      </c>
       <c r="AR212" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="AU212" t="n">
         <v>5</v>
       </c>
       <c r="AV212" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB212" t="n">
         <v>3</v>
       </c>
-      <c r="AW212" t="n">
+      <c r="BC212" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE212" t="n">
         <v>8</v>
       </c>
-      <c r="AX212" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY212" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ212" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA212" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB212" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC212" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD212" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BE212" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF212" t="n">
-        <v>4.65</v>
+        <v>2.65</v>
       </c>
       <c r="BG212" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BH212" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="BI212" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="BJ212" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="BK212" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="BL212" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BM212" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="BN212" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="BO212" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="BP212" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="213">
@@ -47136,10 +47136,10 @@
         <v>1.7</v>
       </c>
       <c r="AS214" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AT214" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="AU214" t="n">
         <v>4</v>
@@ -47351,13 +47351,13 @@
         <v>0.5</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="AU215" t="n">
         <v>9</v>
@@ -47431,7 +47431,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>7834540</v>
+        <v>7834536</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -47451,197 +47451,197 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I216" t="n">
         <v>0</v>
       </c>
       <c r="J216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N216" t="n">
         <v>2</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>['32', '87']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="Q216" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S216" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V216" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X216" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX216" t="n">
         <v>7</v>
       </c>
-      <c r="R216" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S216" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T216" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U216" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V216" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="W216" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X216" t="n">
+      <c r="AY216" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA216" t="n">
         <v>7</v>
       </c>
-      <c r="Y216" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z216" t="n">
+      <c r="BB216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE216" t="n">
         <v>8</v>
       </c>
-      <c r="AA216" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB216" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC216" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD216" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE216" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF216" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AG216" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH216" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI216" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ216" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK216" t="n">
+      <c r="BF216" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG216" t="n">
         <v>1.19</v>
       </c>
-      <c r="AL216" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AM216" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN216" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO216" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AP216" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ216" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AR216" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AS216" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AT216" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AU216" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV216" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW216" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX216" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY216" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ216" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA216" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB216" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC216" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD216" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE216" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF216" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BG216" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BH216" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BI216" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BJ216" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="BK216" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BL216" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="BM216" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="BN216" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BO216" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BP216" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="217">
@@ -47649,7 +47649,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>7834536</v>
+        <v>7834540</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -47669,197 +47669,197 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I217" t="n">
         <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N217" t="n">
         <v>2</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['32', '87']</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>2.38</v>
+        <v>7</v>
       </c>
       <c r="R217" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S217" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="T217" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="U217" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V217" t="n">
-        <v>3.32</v>
+        <v>2.67</v>
       </c>
       <c r="W217" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X217" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Y217" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z217" t="n">
-        <v>1.82</v>
+        <v>8</v>
       </c>
       <c r="AA217" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB217" t="n">
-        <v>4.6</v>
+        <v>1.43</v>
       </c>
       <c r="AC217" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AD217" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AE217" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF217" t="n">
-        <v>2.9</v>
+        <v>3.66</v>
       </c>
       <c r="AG217" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH217" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI217" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AJ217" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AK217" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AL217" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AM217" t="n">
-        <v>1.87</v>
+        <v>1.08</v>
       </c>
       <c r="AN217" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AO217" t="n">
-        <v>0.91</v>
+        <v>1.89</v>
       </c>
       <c r="AP217" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ217" t="n">
         <v>1.92</v>
       </c>
-      <c r="AQ217" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AR217" t="n">
-        <v>1.95</v>
+        <v>1.31</v>
       </c>
       <c r="AS217" t="n">
-        <v>0.99</v>
+        <v>1.52</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="AU217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW217" t="n">
         <v>5</v>
       </c>
-      <c r="AV217" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW217" t="n">
-        <v>12</v>
-      </c>
       <c r="AX217" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB217" t="n">
         <v>7</v>
       </c>
-      <c r="AY217" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ217" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA217" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB217" t="n">
-        <v>3</v>
-      </c>
       <c r="BC217" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE217" t="n">
         <v>10</v>
       </c>
-      <c r="BD217" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BE217" t="n">
-        <v>8</v>
-      </c>
       <c r="BF217" t="n">
-        <v>3.25</v>
+        <v>1.29</v>
       </c>
       <c r="BG217" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BH217" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BI217" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BJ217" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="BK217" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BL217" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="BM217" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="BN217" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO217" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BP217" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="218">
@@ -48005,13 +48005,13 @@
         <v>1.29</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AS218" t="n">
         <v>1.48</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="AU218" t="n">
         <v>3</v>
@@ -48138,7 +48138,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>['16', '90+5']</t>
+          <t>['16', '90+4']</t>
         </is>
       </c>
       <c r="Q219" t="n">
@@ -48444,10 +48444,10 @@
         <v>1.52</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AU220" t="n">
         <v>5</v>
@@ -48659,13 +48659,13 @@
         <v>1.21</v>
       </c>
       <c r="AR221" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AS221" t="n">
         <v>1.2</v>
       </c>
       <c r="AT221" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="AU221" t="n">
         <v>4</v>
@@ -49095,13 +49095,13 @@
         <v>0.64</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AT223" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="AU223" t="n">
         <v>2</v>
@@ -49441,7 +49441,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>['10', '57', '82', '90']</t>
+          <t>['10', '57', '82', '89']</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -49534,10 +49534,10 @@
         <v>1.66</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="AU225" t="n">
         <v>10</v>
@@ -49749,13 +49749,13 @@
         <v>0.42</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AS226" t="n">
         <v>0.91</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AU226" t="n">
         <v>4</v>
@@ -49829,7 +49829,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>7834541</v>
+        <v>7834547</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -49849,197 +49849,197 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K227" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N227" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['21', '45+6']</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['29', '45+8', '62']</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="R227" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="S227" t="n">
+        <v>5</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V227" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X227" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD227" t="n">
         <v>8</v>
       </c>
-      <c r="T227" t="n">
+      <c r="AE227" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK227" t="n">
         <v>1.33</v>
       </c>
-      <c r="U227" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V227" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W227" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X227" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y227" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z227" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA227" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB227" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC227" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD227" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE227" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF227" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AG227" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH227" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI227" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ227" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AK227" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AL227" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AM227" t="n">
-        <v>3.11</v>
+        <v>1.85</v>
       </c>
       <c r="AN227" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="AO227" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AP227" t="n">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AR227" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AS227" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="AT227" t="n">
-        <v>3.43</v>
+        <v>2.92</v>
       </c>
       <c r="AU227" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV227" t="n">
         <v>3</v>
       </c>
-      <c r="AV227" t="n">
-        <v>4</v>
-      </c>
       <c r="AW227" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX227" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY227" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AZ227" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA227" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BB227" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BC227" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD227" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BE227" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BF227" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BG227" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BH227" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BI227" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BJ227" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BK227" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BL227" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BM227" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BN227" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BO227" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BP227" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -50047,7 +50047,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>7834547</v>
+        <v>7834550</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -50067,197 +50067,197 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R228" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S228" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U228" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V228" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X228" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU228" t="n">
         <v>3</v>
-      </c>
-      <c r="N228" t="n">
-        <v>5</v>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>['21', '45+6']</t>
-        </is>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>['29', '45+8', '62']</t>
-        </is>
-      </c>
-      <c r="Q228" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R228" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S228" t="n">
-        <v>5</v>
-      </c>
-      <c r="T228" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U228" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V228" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="W228" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X228" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y228" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z228" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA228" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB228" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AC228" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD228" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE228" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF228" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG228" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH228" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI228" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ228" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK228" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL228" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AM228" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN228" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO228" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AP228" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ228" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AR228" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS228" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AT228" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AU228" t="n">
-        <v>6</v>
       </c>
       <c r="AV228" t="n">
         <v>3</v>
       </c>
       <c r="AW228" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX228" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AY228" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ228" t="n">
         <v>19</v>
-      </c>
-      <c r="AZ228" t="n">
-        <v>6</v>
       </c>
       <c r="BA228" t="n">
         <v>8</v>
       </c>
       <c r="BB228" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BC228" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BD228" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BE228" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="BF228" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BG228" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BH228" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BI228" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BJ228" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BK228" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BL228" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BM228" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BN228" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BO228" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BP228" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="229">
@@ -50265,7 +50265,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>7834550</v>
+        <v>7834541</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -50285,197 +50285,197 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L229" t="n">
         <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>3.55</v>
+        <v>1.84</v>
       </c>
       <c r="R229" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="S229" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="T229" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="U229" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="V229" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="W229" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="X229" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y229" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z229" t="n">
-        <v>2.48</v>
+        <v>1.31</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="AB229" t="n">
-        <v>2.73</v>
+        <v>7.6</v>
       </c>
       <c r="AC229" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AD229" t="n">
-        <v>7.42</v>
+        <v>9.1</v>
       </c>
       <c r="AE229" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AF229" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP229" t="n">
         <v>2.29</v>
       </c>
-      <c r="AG229" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH229" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI229" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AJ229" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AK229" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL229" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM229" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN229" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO229" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AP229" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AQ229" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AS229" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.47</v>
+        <v>3.42</v>
       </c>
       <c r="AU229" t="n">
         <v>3</v>
       </c>
       <c r="AV229" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA229" t="n">
         <v>3</v>
-      </c>
-      <c r="AW229" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX229" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY229" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ229" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA229" t="n">
-        <v>8</v>
       </c>
       <c r="BB229" t="n">
         <v>7</v>
       </c>
       <c r="BC229" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BD229" t="n">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="BE229" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="BF229" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="BG229" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BH229" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="BI229" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BJ229" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="BK229" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="BL229" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="BM229" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="BN229" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="BO229" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BP229" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="230">
@@ -51057,13 +51057,13 @@
         <v>1</v>
       </c>
       <c r="AR232" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AS232" t="n">
         <v>1.34</v>
       </c>
       <c r="AT232" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU232" t="n">
         <v>6</v>
@@ -51275,13 +51275,13 @@
         <v>1.29</v>
       </c>
       <c r="AR233" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AS233" t="n">
         <v>1.45</v>
       </c>
       <c r="AT233" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AU233" t="n">
         <v>4</v>
@@ -51496,10 +51496,10 @@
         <v>1.53</v>
       </c>
       <c r="AS234" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AU234" t="n">
         <v>5</v>
@@ -51573,7 +51573,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>7834552</v>
+        <v>7834560</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -51593,197 +51593,197 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="n">
         <v>1</v>
       </c>
       <c r="L235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N235" t="n">
         <v>2</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>['8', '61']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="R235" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S235" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T235" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U235" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V235" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="W235" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X235" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Y235" t="n">
         <v>1.01</v>
       </c>
       <c r="Z235" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA235" t="n">
         <v>3.1</v>
       </c>
       <c r="AB235" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="AC235" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD235" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AE235" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF235" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="AG235" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AH235" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI235" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ235" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AK235" t="n">
         <v>1.38</v>
       </c>
       <c r="AL235" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AM235" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AN235" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AO235" t="n">
-        <v>1.73</v>
+        <v>0.91</v>
       </c>
       <c r="AP235" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AQ235" t="n">
-        <v>1.54</v>
+        <v>0.92</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AS235" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.89</v>
+        <v>2.42</v>
       </c>
       <c r="AU235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX235" t="n">
         <v>3</v>
       </c>
-      <c r="AW235" t="n">
+      <c r="AY235" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC235" t="n">
         <v>8</v>
       </c>
-      <c r="AX235" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY235" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ235" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA235" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB235" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC235" t="n">
-        <v>12</v>
-      </c>
       <c r="BD235" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="BE235" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF235" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI235" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL235" t="n">
         <v>1.85</v>
       </c>
-      <c r="BG235" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BH235" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI235" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ235" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BK235" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BL235" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BM235" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BN235" t="n">
         <v>1.64</v>
       </c>
       <c r="BO235" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="BP235" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="236">
@@ -51791,7 +51791,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>7834560</v>
+        <v>7834552</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -51811,197 +51811,197 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236" t="n">
         <v>1</v>
       </c>
       <c r="L236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
         <v>2</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['8', '61']</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R236" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S236" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T236" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U236" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V236" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="W236" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X236" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Y236" t="n">
         <v>1.01</v>
       </c>
       <c r="Z236" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA236" t="n">
         <v>3.1</v>
       </c>
       <c r="AB236" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="AC236" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD236" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AE236" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AF236" t="n">
-        <v>3.06</v>
+        <v>2.67</v>
       </c>
       <c r="AG236" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AH236" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI236" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ236" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AK236" t="n">
         <v>1.38</v>
       </c>
       <c r="AL236" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM236" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AN236" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AO236" t="n">
-        <v>0.91</v>
+        <v>1.73</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AQ236" t="n">
-        <v>0.92</v>
+        <v>1.54</v>
       </c>
       <c r="AR236" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG236" t="n">
         <v>1.26</v>
       </c>
-      <c r="AS236" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT236" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU236" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV236" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW236" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX236" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY236" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ236" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA236" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB236" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC236" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD236" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BE236" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF236" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BG236" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BH236" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="BI236" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="BJ236" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="BK236" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BL236" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BM236" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BN236" t="n">
         <v>1.64</v>
       </c>
       <c r="BO236" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="BP236" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="237">
@@ -52365,13 +52365,13 @@
         <v>0.36</v>
       </c>
       <c r="AR238" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AS238" t="n">
         <v>1.12</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AU238" t="n">
         <v>6</v>
@@ -52445,7 +52445,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>7834551</v>
+        <v>7834558</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -52465,35 +52465,35 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
         <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>['33', '89']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -52502,160 +52502,160 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R239" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S239" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="T239" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="U239" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="V239" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="W239" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X239" t="n">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="Y239" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z239" t="n">
-        <v>2.47</v>
+        <v>3.8</v>
       </c>
       <c r="AA239" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="AB239" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC239" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AD239" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE239" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA239" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB239" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ239" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK239" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BM239" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN239" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF239" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG239" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH239" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI239" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AJ239" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AK239" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AL239" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AM239" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AN239" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AO239" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP239" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ239" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR239" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS239" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AT239" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU239" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV239" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW239" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX239" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY239" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ239" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA239" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB239" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC239" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD239" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BE239" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF239" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG239" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BH239" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BI239" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BJ239" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BK239" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BL239" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BM239" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BN239" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BO239" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="BP239" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="240">
@@ -52663,7 +52663,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>7834558</v>
+        <v>7834551</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -52683,35 +52683,35 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M240" t="n">
         <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['33', '89']</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -52720,160 +52720,160 @@
         </is>
       </c>
       <c r="Q240" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R240" t="n">
+        <v>2</v>
+      </c>
+      <c r="S240" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T240" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U240" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V240" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W240" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X240" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY240" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA240" t="n">
         <v>4</v>
       </c>
-      <c r="R240" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S240" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T240" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U240" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V240" t="n">
-        <v>3</v>
-      </c>
-      <c r="W240" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X240" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Y240" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z240" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA240" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AB240" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC240" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD240" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE240" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF240" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG240" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH240" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI240" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ240" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AK240" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL240" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM240" t="n">
+      <c r="BB240" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO240" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP240" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AN240" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AO240" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AP240" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AQ240" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AR240" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS240" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT240" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AU240" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV240" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW240" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX240" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY240" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ240" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA240" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB240" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC240" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD240" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BE240" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF240" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BG240" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BH240" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BI240" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BJ240" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BK240" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BL240" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BM240" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BN240" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO240" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP240" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="241">
@@ -53455,13 +53455,13 @@
         <v>1</v>
       </c>
       <c r="AR243" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AU243" t="n">
         <v>2</v>
@@ -53753,7 +53753,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>7834570</v>
+        <v>7834565</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -53773,197 +53773,197 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="I245" t="n">
         <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N245" t="n">
+        <v>2</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R245" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S245" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T245" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V245" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W245" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X245" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT245" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU245" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV245" t="n">
         <v>4</v>
       </c>
-      <c r="O245" t="inlineStr">
-        <is>
-          <t>['73', '90+7']</t>
-        </is>
-      </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>['64', '83']</t>
-        </is>
-      </c>
-      <c r="Q245" t="n">
-        <v>4</v>
-      </c>
-      <c r="R245" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S245" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="T245" t="n">
+      <c r="AW245" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY245" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB245" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC245" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE245" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF245" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI245" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ245" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK245" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM245" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN245" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO245" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP245" t="n">
         <v>1.53</v>
-      </c>
-      <c r="U245" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="V245" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W245" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X245" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y245" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z245" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA245" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB245" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AC245" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD245" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE245" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF245" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG245" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AH245" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI245" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ245" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK245" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL245" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM245" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN245" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AO245" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP245" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AQ245" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AR245" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS245" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT245" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AU245" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV245" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW245" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX245" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY245" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ245" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA245" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB245" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC245" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD245" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BE245" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF245" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BG245" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BH245" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BI245" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BJ245" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BK245" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BL245" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BM245" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BN245" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BO245" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BP245" t="n">
-        <v>1.44</v>
       </c>
     </row>
     <row r="246">
@@ -53971,7 +53971,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>7834565</v>
+        <v>7834570</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -53991,197 +53991,197 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I246" t="n">
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N246" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['73', '90+7']</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['64', '83']</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="R246" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S246" t="n">
-        <v>4.75</v>
+        <v>3.21</v>
       </c>
       <c r="T246" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U246" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="V246" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="W246" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="X246" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y246" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z246" t="n">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="AA246" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AB246" t="n">
-        <v>4.5</v>
+        <v>2.44</v>
       </c>
       <c r="AC246" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AD246" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE246" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF246" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AG246" t="n">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="AH246" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AI246" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AJ246" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AK246" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AL246" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AM246" t="n">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="AN246" t="n">
-        <v>2.27</v>
+        <v>0.73</v>
       </c>
       <c r="AO246" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP246" t="n">
-        <v>2.23</v>
+        <v>0.75</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="AR246" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AS246" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AT246" t="n">
-        <v>2.96</v>
+        <v>2.51</v>
       </c>
       <c r="AU246" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV246" t="n">
         <v>5</v>
       </c>
-      <c r="AV246" t="n">
+      <c r="AW246" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY246" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA246" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB246" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC246" t="n">
         <v>4</v>
       </c>
-      <c r="AW246" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX246" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY246" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ246" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA246" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB246" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC246" t="n">
-        <v>17</v>
-      </c>
       <c r="BD246" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="BE246" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF246" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="BG246" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BH246" t="n">
-        <v>4.6</v>
+        <v>3.78</v>
       </c>
       <c r="BI246" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BJ246" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BK246" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BL246" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="BM246" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="BN246" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BO246" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="BP246" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="247">
@@ -54330,10 +54330,10 @@
         <v>1.73</v>
       </c>
       <c r="AS247" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AT247" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="AU247" t="n">
         <v>6</v>
@@ -54545,13 +54545,13 @@
         <v>1</v>
       </c>
       <c r="AR248" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AS248" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AT248" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AU248" t="n">
         <v>4</v>
@@ -54625,7 +54625,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>7834562</v>
+        <v>7834564</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -54645,197 +54645,197 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M249" t="n">
         <v>1</v>
       </c>
       <c r="N249" t="n">
+        <v>2</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R249" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S249" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T249" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U249" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V249" t="n">
         <v>3</v>
       </c>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>['27', '46']</t>
-        </is>
-      </c>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="Q249" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R249" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S249" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T249" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U249" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V249" t="n">
-        <v>2.95</v>
-      </c>
       <c r="W249" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X249" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="Y249" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z249" t="n">
         <v>1.85</v>
       </c>
       <c r="AA249" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AB249" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AC249" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD249" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE249" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF249" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="AG249" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH249" t="n">
         <v>1.66</v>
       </c>
       <c r="AI249" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AJ249" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AK249" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL249" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM249" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AN249" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AO249" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR249" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS249" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AT249" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="AU249" t="n">
         <v>7</v>
       </c>
       <c r="AV249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW249" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AX249" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY249" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AZ249" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA249" t="n">
         <v>10</v>
       </c>
-      <c r="BA249" t="n">
-        <v>6</v>
-      </c>
       <c r="BB249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC249" t="n">
         <v>10</v>
       </c>
       <c r="BD249" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BE249" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="BF249" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="BG249" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BH249" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BI249" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="BJ249" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BK249" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="BL249" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="BM249" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="BN249" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO249" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="BP249" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="250">
@@ -54843,7 +54843,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>7834564</v>
+        <v>7834562</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -54863,197 +54863,197 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
         <v>1</v>
       </c>
       <c r="N250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['27', '46']</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="R250" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="S250" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T250" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U250" t="n">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="V250" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="W250" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X250" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="Y250" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z250" t="n">
         <v>1.85</v>
       </c>
       <c r="AA250" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AB250" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AC250" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AD250" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE250" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF250" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="AG250" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH250" t="n">
         <v>1.66</v>
       </c>
       <c r="AI250" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AJ250" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AK250" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL250" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL250" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AM250" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AN250" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AO250" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AS250" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AT250" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="AU250" t="n">
         <v>7</v>
       </c>
       <c r="AV250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW250" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AX250" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY250" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AZ250" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA250" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB250" t="n">
         <v>4</v>
-      </c>
-      <c r="BA250" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB250" t="n">
-        <v>0</v>
       </c>
       <c r="BC250" t="n">
         <v>10</v>
       </c>
       <c r="BD250" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="BE250" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF250" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="BG250" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BH250" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BI250" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="BJ250" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="BK250" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="BL250" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="BM250" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="BN250" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO250" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="BP250" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="251">
@@ -55199,13 +55199,13 @@
         <v>1</v>
       </c>
       <c r="AR251" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AS251" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT251" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="AU251" t="n">
         <v>3</v>
@@ -55420,10 +55420,10 @@
         <v>1.54</v>
       </c>
       <c r="AS252" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AT252" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AU252" t="n">
         <v>5</v>
@@ -55638,10 +55638,10 @@
         <v>1.94</v>
       </c>
       <c r="AS253" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AT253" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AU253" t="n">
         <v>2</v>
@@ -55853,13 +55853,13 @@
         <v>1.29</v>
       </c>
       <c r="AR254" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AS254" t="n">
         <v>1.42</v>
       </c>
       <c r="AT254" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="AU254" t="n">
         <v>7</v>
@@ -55933,7 +55933,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>7834571</v>
+        <v>7834575</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -55953,35 +55953,35 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M255" t="n">
         <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>['15', '58', '90+1']</t>
+          <t>['90+16']</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
@@ -55990,160 +55990,160 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="R255" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S255" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="T255" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="U255" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="V255" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="W255" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X255" t="n">
-        <v>9.199999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="Y255" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Z255" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AA255" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AB255" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AC255" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD255" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AE255" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AF255" t="n">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="AG255" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="AH255" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI255" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AJ255" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AK255" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL255" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL255" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AM255" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AN255" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AO255" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="AP255" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AQ255" t="n">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR255" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AS255" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="AT255" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="AU255" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV255" t="n">
         <v>1</v>
       </c>
       <c r="AW255" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AX255" t="n">
         <v>4</v>
       </c>
       <c r="AY255" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AZ255" t="n">
         <v>5</v>
       </c>
       <c r="BA255" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB255" t="n">
         <v>2</v>
       </c>
       <c r="BC255" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD255" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BE255" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="BF255" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="BG255" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="BH255" t="n">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="BI255" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="BJ255" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="BK255" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="BL255" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="BM255" t="n">
-        <v>2.56</v>
+        <v>2.07</v>
       </c>
       <c r="BN255" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="BO255" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="BP255" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="256">
@@ -56151,7 +56151,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>7834575</v>
+        <v>7834571</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -56171,35 +56171,35 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M256" t="n">
         <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>['90+16']</t>
+          <t>['15', '58', '90+1']</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -56208,160 +56208,160 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="R256" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S256" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T256" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U256" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V256" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W256" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X256" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z256" t="n">
         <v>2.05</v>
       </c>
-      <c r="S256" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T256" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U256" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V256" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="W256" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X256" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="Y256" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z256" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AA256" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="AB256" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU256" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW256" t="n">
         <v>4</v>
-      </c>
-      <c r="AC256" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD256" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE256" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF256" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG256" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH256" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI256" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AJ256" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AK256" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AL256" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM256" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AN256" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO256" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP256" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AQ256" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AR256" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AS256" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AT256" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AU256" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV256" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW256" t="n">
-        <v>21</v>
       </c>
       <c r="AX256" t="n">
         <v>4</v>
       </c>
       <c r="AY256" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AZ256" t="n">
         <v>5</v>
       </c>
       <c r="BA256" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB256" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC256" t="n">
         <v>6</v>
       </c>
-      <c r="BB256" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC256" t="n">
-        <v>8</v>
-      </c>
       <c r="BD256" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BE256" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="BF256" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="BG256" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BH256" t="n">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="BI256" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="BJ256" t="n">
-        <v>2.83</v>
+        <v>2.2</v>
       </c>
       <c r="BK256" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="BL256" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="BM256" t="n">
-        <v>2.07</v>
+        <v>2.56</v>
       </c>
       <c r="BN256" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="BO256" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="BP256" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="257">
@@ -56507,13 +56507,13 @@
         <v>1.21</v>
       </c>
       <c r="AR257" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AS257" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT257" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AU257" t="n">
         <v>3</v>
@@ -56725,13 +56725,13 @@
         <v>0.36</v>
       </c>
       <c r="AR258" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AS258" t="n">
         <v>1.11</v>
       </c>
       <c r="AT258" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AU258" t="n">
         <v>7</v>
@@ -56943,13 +56943,13 @@
         <v>2.17</v>
       </c>
       <c r="AR259" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS259" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AU259" t="n">
         <v>5</v>
@@ -57023,7 +57023,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>7834580</v>
+        <v>7834578</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -57043,12 +57043,12 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I260" t="n">
@@ -57064,176 +57064,176 @@
         <v>1</v>
       </c>
       <c r="M260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>['72', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>3.53</v>
+        <v>5.96</v>
       </c>
       <c r="R260" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S260" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="T260" t="n">
         <v>1.4</v>
       </c>
       <c r="U260" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V260" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="W260" t="n">
         <v>1.33</v>
       </c>
       <c r="X260" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Y260" t="n">
         <v>1.06</v>
       </c>
       <c r="Z260" t="n">
-        <v>2.33</v>
+        <v>4.85</v>
       </c>
       <c r="AA260" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB260" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC260" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD260" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AE260" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AF260" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AG260" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="AH260" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AI260" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AJ260" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AK260" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL260" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AM260" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AN260" t="n">
-        <v>1.38</v>
+        <v>2.25</v>
       </c>
       <c r="AO260" t="n">
-        <v>0.36</v>
+        <v>2.09</v>
       </c>
       <c r="AP260" t="n">
-        <v>1.29</v>
+        <v>2.31</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.58</v>
+        <v>1.92</v>
       </c>
       <c r="AR260" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="AS260" t="n">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="AT260" t="n">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="AU260" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV260" t="n">
         <v>3</v>
       </c>
       <c r="AW260" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX260" t="n">
         <v>5</v>
       </c>
       <c r="AY260" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ260" t="n">
         <v>8</v>
       </c>
       <c r="BA260" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BB260" t="n">
         <v>1</v>
       </c>
       <c r="BC260" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BD260" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="BE260" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BF260" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="BG260" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="BH260" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BI260" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="BJ260" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="BK260" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="BL260" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="BM260" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="BN260" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO260" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="BP260" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="261">
@@ -57241,7 +57241,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>7834578</v>
+        <v>7834580</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -57261,12 +57261,12 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="I261" t="n">
@@ -57282,176 +57282,176 @@
         <v>1</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72', '85']</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>5.96</v>
+        <v>3.53</v>
       </c>
       <c r="R261" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S261" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="T261" t="n">
         <v>1.4</v>
       </c>
       <c r="U261" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V261" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="W261" t="n">
         <v>1.33</v>
       </c>
       <c r="X261" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="Y261" t="n">
         <v>1.06</v>
       </c>
       <c r="Z261" t="n">
-        <v>4.85</v>
+        <v>2.33</v>
       </c>
       <c r="AA261" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC261" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD261" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AE261" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AF261" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AG261" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="AH261" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AI261" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AJ261" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AK261" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL261" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AM261" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AN261" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="AO261" t="n">
-        <v>2.09</v>
+        <v>0.36</v>
       </c>
       <c r="AP261" t="n">
-        <v>2.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.92</v>
+        <v>0.58</v>
       </c>
       <c r="AR261" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AS261" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="AT261" t="n">
-        <v>3.02</v>
+        <v>2.39</v>
       </c>
       <c r="AU261" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV261" t="n">
         <v>3</v>
       </c>
       <c r="AW261" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX261" t="n">
         <v>5</v>
       </c>
       <c r="AY261" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ261" t="n">
         <v>8</v>
       </c>
       <c r="BA261" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BB261" t="n">
         <v>1</v>
       </c>
       <c r="BC261" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BD261" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="BE261" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF261" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="BG261" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BH261" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BI261" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="BJ261" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="BK261" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="BL261" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="BM261" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="BN261" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="BO261" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="BP261" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="262">
@@ -57459,7 +57459,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>7834579</v>
+        <v>7834576</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -57479,197 +57479,197 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K262" t="n">
         <v>1</v>
       </c>
       <c r="L262" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>['10', '66', '90+4']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R262" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="S262" t="n">
-        <v>3.92</v>
+        <v>6.15</v>
       </c>
       <c r="T262" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U262" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="V262" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="W262" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="X262" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y262" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z262" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AA262" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="AB262" t="n">
-        <v>3.14</v>
+        <v>6</v>
       </c>
       <c r="AC262" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AD262" t="n">
-        <v>6.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE262" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AF262" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="AG262" t="n">
-        <v>2.69</v>
+        <v>1.99</v>
       </c>
       <c r="AH262" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AI262" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AJ262" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AK262" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AL262" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AM262" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AN262" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AO262" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AQ262" t="n">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
       <c r="AR262" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AS262" t="n">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AT262" t="n">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="AU262" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV262" t="n">
         <v>5</v>
       </c>
       <c r="AW262" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AX262" t="n">
         <v>12</v>
       </c>
       <c r="AY262" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AZ262" t="n">
         <v>17</v>
       </c>
       <c r="BA262" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BB262" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC262" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD262" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="BE262" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BF262" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="BG262" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="BH262" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI262" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BJ262" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="BK262" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="BL262" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="BM262" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="BN262" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="BO262" t="n">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="BP262" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="263">
@@ -57677,7 +57677,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="n">
-        <v>7834576</v>
+        <v>7834579</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -57697,197 +57697,197 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K263" t="n">
         <v>1</v>
       </c>
       <c r="L263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['10', '66', '90+4']</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="R263" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="S263" t="n">
-        <v>6.15</v>
+        <v>3.92</v>
       </c>
       <c r="T263" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V263" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W263" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X263" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK263" t="n">
         <v>1.36</v>
       </c>
-      <c r="U263" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V263" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W263" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X263" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y263" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z263" t="n">
+      <c r="AL263" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM263" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA263" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB263" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC263" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD263" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE263" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF263" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AG263" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AH263" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AI263" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AJ263" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK263" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AL263" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AM263" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AN263" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AO263" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AP263" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="AQ263" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR263" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="AT263" t="n">
-        <v>3.06</v>
+        <v>2.49</v>
       </c>
       <c r="AU263" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV263" t="n">
         <v>5</v>
       </c>
       <c r="AW263" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AX263" t="n">
         <v>12</v>
       </c>
       <c r="AY263" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AZ263" t="n">
         <v>17</v>
       </c>
       <c r="BA263" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BB263" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC263" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE263" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF263" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG263" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH263" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI263" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO263" t="n">
         <v>3</v>
       </c>
-      <c r="BC263" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD263" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BE263" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF263" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG263" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BH263" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI263" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BJ263" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BK263" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BL263" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BM263" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BN263" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BO263" t="n">
-        <v>2.31</v>
-      </c>
       <c r="BP263" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="264">
@@ -58036,10 +58036,10 @@
         <v>1.81</v>
       </c>
       <c r="AS264" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AT264" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AU264" t="n">
         <v>5</v>
@@ -58251,13 +58251,13 @@
         <v>0.93</v>
       </c>
       <c r="AR265" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AS265" t="n">
         <v>1.11</v>
       </c>
       <c r="AT265" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AU265" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP265"/>
+  <dimension ref="A1:BP266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.29</v>
@@ -3530,7 +3530,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
@@ -8980,7 +8980,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR39" t="n">
         <v>1.72</v>
@@ -11814,7 +11814,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR52" t="n">
         <v>2.07</v>
@@ -13119,7 +13119,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ58" t="n">
         <v>1</v>
@@ -16174,7 +16174,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR72" t="n">
         <v>1.11</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.08</v>
@@ -21621,7 +21621,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.92</v>
@@ -22278,7 +22278,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR100" t="n">
         <v>1.61</v>
@@ -27943,7 +27943,7 @@
         <v>1</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.21</v>
@@ -30344,7 +30344,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR137" t="n">
         <v>1.59</v>
@@ -30995,7 +30995,7 @@
         <v>1.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.64</v>
@@ -33829,7 +33829,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.93</v>
@@ -34704,7 +34704,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR157" t="n">
         <v>1.39</v>
@@ -37320,7 +37320,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR169" t="n">
         <v>1.64</v>
@@ -38843,7 +38843,7 @@
         <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ176" t="n">
         <v>1</v>
@@ -40154,7 +40154,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR182" t="n">
         <v>1.55</v>
@@ -43857,7 +43857,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP199" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.5</v>
@@ -44296,7 +44296,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR201" t="n">
         <v>1.36</v>
@@ -46909,7 +46909,7 @@
         <v>1</v>
       </c>
       <c r="AP213" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.92</v>
@@ -49525,7 +49525,7 @@
         <v>0.4</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.58</v>
@@ -49746,7 +49746,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ226" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR226" t="n">
         <v>1.71</v>
@@ -53670,7 +53670,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ244" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR244" t="n">
         <v>1.87</v>
@@ -54321,7 +54321,7 @@
         <v>0.92</v>
       </c>
       <c r="AP247" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ247" t="n">
         <v>0.85</v>
@@ -58324,6 +58324,224 @@
       </c>
       <c r="BP265" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>7834423</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>45941.79166666666</v>
+      </c>
+      <c r="F266" t="n">
+        <v>12</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>2</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>2</v>
+      </c>
+      <c r="L266" t="n">
+        <v>4</v>
+      </c>
+      <c r="M266" t="n">
+        <v>1</v>
+      </c>
+      <c r="N266" t="n">
+        <v>5</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>['27', '44', '49', '56']</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R266" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S266" t="n">
+        <v>11</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U266" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V266" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X266" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI266" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -754,19 +754,19 @@
     <t>['90']</t>
   </si>
   <si>
-    <t>['63']</t>
+    <t>['8', '61']</t>
   </si>
   <si>
-    <t>['8', '61']</t>
+    <t>['63']</t>
   </si>
   <si>
     <t>['45+2', '67', '89']</t>
   </si>
   <si>
-    <t>['78']</t>
+    <t>['33', '89']</t>
   </si>
   <si>
-    <t>['33', '89']</t>
+    <t>['78']</t>
   </si>
   <si>
     <t>['30', '78']</t>
@@ -802,10 +802,10 @@
     <t>['18', '72', '90+5']</t>
   </si>
   <si>
-    <t>['6', '52', '68', '90+7']</t>
+    <t>['15', '34']</t>
   </si>
   <si>
-    <t>['15', '34']</t>
+    <t>['6', '52', '68', '90+7']</t>
   </si>
   <si>
     <t>['45']</t>
@@ -1075,10 +1075,10 @@
     <t>['11', '85']</t>
   </si>
   <si>
-    <t>['26', '34', '72']</t>
+    <t>['70', '74', '89']</t>
   </si>
   <si>
-    <t>['70', '74', '89']</t>
+    <t>['26', '34', '72']</t>
   </si>
   <si>
     <t>['72', '85']</t>
@@ -23538,7 +23538,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -49658,7 +49658,7 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>7834560</v>
+        <v>7834552</v>
       </c>
       <c r="C235" t="s">
         <v>68</v>
@@ -49673,25 +49673,25 @@
         <v>25</v>
       </c>
       <c r="G235" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H235" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235">
         <v>1</v>
       </c>
       <c r="L235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N235">
         <v>2</v>
@@ -49700,163 +49700,163 @@
         <v>246</v>
       </c>
       <c r="P235" t="s">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="Q235">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R235">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S235">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T235">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U235">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V235">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="W235">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X235">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Y235">
         <v>1.01</v>
       </c>
       <c r="Z235">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA235">
         <v>3.1</v>
       </c>
       <c r="AB235">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="AC235">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD235">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AE235">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AF235">
-        <v>3.06</v>
+        <v>2.67</v>
       </c>
       <c r="AG235">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AH235">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI235">
         <v>1.91</v>
       </c>
       <c r="AJ235">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AK235">
         <v>1.38</v>
       </c>
       <c r="AL235">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AM235">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AN235">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AO235">
-        <v>0.91</v>
+        <v>1.73</v>
       </c>
       <c r="AP235">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AQ235">
-        <v>0.92</v>
+        <v>1.54</v>
       </c>
       <c r="AR235">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AS235">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AT235">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="AU235">
+        <v>4</v>
+      </c>
+      <c r="AV235">
         <v>3</v>
       </c>
-      <c r="AV235">
-        <v>2</v>
-      </c>
       <c r="AW235">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AX235">
+        <v>18</v>
+      </c>
+      <c r="AY235">
+        <v>12</v>
+      </c>
+      <c r="AZ235">
+        <v>21</v>
+      </c>
+      <c r="BA235">
         <v>3</v>
       </c>
-      <c r="AY235">
-        <v>14</v>
-      </c>
-      <c r="AZ235">
-        <v>5</v>
-      </c>
-      <c r="BA235">
-        <v>7</v>
-      </c>
       <c r="BB235">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BC235">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD235">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="BE235">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="BF235">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="BG235">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BH235">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="BI235">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="BJ235">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="BK235">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="BL235">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BM235">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BN235">
         <v>1.64</v>
       </c>
       <c r="BO235">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="BP235">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="236" spans="1:68">
@@ -49864,7 +49864,7 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>7834552</v>
+        <v>7834560</v>
       </c>
       <c r="C236" t="s">
         <v>68</v>
@@ -49879,25 +49879,25 @@
         <v>25</v>
       </c>
       <c r="G236" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H236" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236">
         <v>1</v>
       </c>
       <c r="L236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N236">
         <v>2</v>
@@ -49906,163 +49906,163 @@
         <v>247</v>
       </c>
       <c r="P236" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="Q236">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="R236">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S236">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T236">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U236">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V236">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="W236">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X236">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Y236">
         <v>1.01</v>
       </c>
       <c r="Z236">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA236">
         <v>3.1</v>
       </c>
       <c r="AB236">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="AC236">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD236">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AE236">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF236">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="AG236">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AH236">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI236">
         <v>1.91</v>
       </c>
       <c r="AJ236">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AK236">
         <v>1.38</v>
       </c>
       <c r="AL236">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AM236">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AN236">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AO236">
-        <v>1.73</v>
+        <v>0.91</v>
       </c>
       <c r="AP236">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AQ236">
-        <v>1.54</v>
+        <v>0.92</v>
       </c>
       <c r="AR236">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AS236">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AT236">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="AU236">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV236">
+        <v>2</v>
+      </c>
+      <c r="AW236">
+        <v>11</v>
+      </c>
+      <c r="AX236">
         <v>3</v>
       </c>
-      <c r="AW236">
+      <c r="AY236">
+        <v>14</v>
+      </c>
+      <c r="AZ236">
+        <v>5</v>
+      </c>
+      <c r="BA236">
+        <v>7</v>
+      </c>
+      <c r="BB236">
+        <v>1</v>
+      </c>
+      <c r="BC236">
         <v>8</v>
       </c>
-      <c r="AX236">
-        <v>18</v>
-      </c>
-      <c r="AY236">
-        <v>12</v>
-      </c>
-      <c r="AZ236">
-        <v>21</v>
-      </c>
-      <c r="BA236">
-        <v>3</v>
-      </c>
-      <c r="BB236">
-        <v>9</v>
-      </c>
-      <c r="BC236">
-        <v>12</v>
-      </c>
       <c r="BD236">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="BE236">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF236">
+        <v>1.97</v>
+      </c>
+      <c r="BG236">
+        <v>1.21</v>
+      </c>
+      <c r="BH236">
+        <v>3.32</v>
+      </c>
+      <c r="BI236">
+        <v>1.49</v>
+      </c>
+      <c r="BJ236">
+        <v>2.65</v>
+      </c>
+      <c r="BK236">
+        <v>1.81</v>
+      </c>
+      <c r="BL236">
         <v>1.85</v>
       </c>
-      <c r="BG236">
-        <v>1.26</v>
-      </c>
-      <c r="BH236">
-        <v>3.4</v>
-      </c>
-      <c r="BI236">
-        <v>1.4</v>
-      </c>
-      <c r="BJ236">
-        <v>2.58</v>
-      </c>
-      <c r="BK236">
-        <v>1.96</v>
-      </c>
-      <c r="BL236">
-        <v>1.9</v>
-      </c>
       <c r="BM236">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BN236">
         <v>1.64</v>
       </c>
       <c r="BO236">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="BP236">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="237" spans="1:68">
@@ -50482,7 +50482,7 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>7834558</v>
+        <v>7834551</v>
       </c>
       <c r="C239" t="s">
         <v>68</v>
@@ -50497,28 +50497,28 @@
         <v>25</v>
       </c>
       <c r="G239" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H239" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239">
         <v>0</v>
       </c>
       <c r="K239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M239">
         <v>0</v>
       </c>
       <c r="N239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O239" t="s">
         <v>249</v>
@@ -50527,160 +50527,160 @@
         <v>93</v>
       </c>
       <c r="Q239">
+        <v>2.95</v>
+      </c>
+      <c r="R239">
+        <v>2</v>
+      </c>
+      <c r="S239">
+        <v>3.7</v>
+      </c>
+      <c r="T239">
+        <v>1.53</v>
+      </c>
+      <c r="U239">
+        <v>2.52</v>
+      </c>
+      <c r="V239">
+        <v>3.3</v>
+      </c>
+      <c r="W239">
+        <v>1.28</v>
+      </c>
+      <c r="X239">
+        <v>10</v>
+      </c>
+      <c r="Y239">
+        <v>1.05</v>
+      </c>
+      <c r="Z239">
+        <v>2.47</v>
+      </c>
+      <c r="AA239">
+        <v>2.88</v>
+      </c>
+      <c r="AB239">
+        <v>3.25</v>
+      </c>
+      <c r="AC239">
+        <v>1.08</v>
+      </c>
+      <c r="AD239">
+        <v>6.5</v>
+      </c>
+      <c r="AE239">
+        <v>1.5</v>
+      </c>
+      <c r="AF239">
+        <v>2.65</v>
+      </c>
+      <c r="AG239">
+        <v>2.5</v>
+      </c>
+      <c r="AH239">
+        <v>1.52</v>
+      </c>
+      <c r="AI239">
+        <v>2.06</v>
+      </c>
+      <c r="AJ239">
+        <v>1.71</v>
+      </c>
+      <c r="AK239">
+        <v>1.37</v>
+      </c>
+      <c r="AL239">
+        <v>1.29</v>
+      </c>
+      <c r="AM239">
+        <v>1.68</v>
+      </c>
+      <c r="AN239">
+        <v>1.9</v>
+      </c>
+      <c r="AO239">
+        <v>1.5</v>
+      </c>
+      <c r="AP239">
+        <v>2.08</v>
+      </c>
+      <c r="AQ239">
+        <v>1.29</v>
+      </c>
+      <c r="AR239">
+        <v>1.68</v>
+      </c>
+      <c r="AS239">
+        <v>1.44</v>
+      </c>
+      <c r="AT239">
+        <v>3.12</v>
+      </c>
+      <c r="AU239">
+        <v>3</v>
+      </c>
+      <c r="AV239">
+        <v>1</v>
+      </c>
+      <c r="AW239">
+        <v>5</v>
+      </c>
+      <c r="AX239">
+        <v>11</v>
+      </c>
+      <c r="AY239">
+        <v>8</v>
+      </c>
+      <c r="AZ239">
+        <v>12</v>
+      </c>
+      <c r="BA239">
         <v>4</v>
       </c>
-      <c r="R239">
-        <v>2.05</v>
-      </c>
-      <c r="S239">
-        <v>2.72</v>
-      </c>
-      <c r="T239">
-        <v>1.4</v>
-      </c>
-      <c r="U239">
-        <v>2.57</v>
-      </c>
-      <c r="V239">
-        <v>3</v>
-      </c>
-      <c r="W239">
-        <v>1.32</v>
-      </c>
-      <c r="X239">
-        <v>8.1</v>
-      </c>
-      <c r="Y239">
-        <v>1.06</v>
-      </c>
-      <c r="Z239">
-        <v>3.8</v>
-      </c>
-      <c r="AA239">
-        <v>3.38</v>
-      </c>
-      <c r="AB239">
-        <v>1.95</v>
-      </c>
-      <c r="AC239">
-        <v>1.02</v>
-      </c>
-      <c r="AD239">
-        <v>9.5</v>
-      </c>
-      <c r="AE239">
-        <v>1.37</v>
-      </c>
-      <c r="AF239">
-        <v>3.1</v>
-      </c>
-      <c r="AG239">
-        <v>2.16</v>
-      </c>
-      <c r="AH239">
-        <v>1.72</v>
-      </c>
-      <c r="AI239">
-        <v>2</v>
-      </c>
-      <c r="AJ239">
-        <v>1.85</v>
-      </c>
-      <c r="AK239">
-        <v>1.75</v>
-      </c>
-      <c r="AL239">
-        <v>1.33</v>
-      </c>
-      <c r="AM239">
+      <c r="BB239">
+        <v>2</v>
+      </c>
+      <c r="BC239">
+        <v>6</v>
+      </c>
+      <c r="BD239">
+        <v>1.67</v>
+      </c>
+      <c r="BE239">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF239">
+        <v>2.6</v>
+      </c>
+      <c r="BG239">
+        <v>1.27</v>
+      </c>
+      <c r="BH239">
+        <v>3.14</v>
+      </c>
+      <c r="BI239">
+        <v>1.58</v>
+      </c>
+      <c r="BJ239">
+        <v>2.45</v>
+      </c>
+      <c r="BK239">
+        <v>2.3</v>
+      </c>
+      <c r="BL239">
+        <v>1.77</v>
+      </c>
+      <c r="BM239">
+        <v>2.5</v>
+      </c>
+      <c r="BN239">
+        <v>1.46</v>
+      </c>
+      <c r="BO239">
+        <v>3.42</v>
+      </c>
+      <c r="BP239">
         <v>1.26</v>
-      </c>
-      <c r="AN239">
-        <v>2.18</v>
-      </c>
-      <c r="AO239">
-        <v>2.3</v>
-      </c>
-      <c r="AP239">
-        <v>2.31</v>
-      </c>
-      <c r="AQ239">
-        <v>2.17</v>
-      </c>
-      <c r="AR239">
-        <v>1.52</v>
-      </c>
-      <c r="AS239">
-        <v>1.38</v>
-      </c>
-      <c r="AT239">
-        <v>2.9</v>
-      </c>
-      <c r="AU239">
-        <v>5</v>
-      </c>
-      <c r="AV239">
-        <v>4</v>
-      </c>
-      <c r="AW239">
-        <v>7</v>
-      </c>
-      <c r="AX239">
-        <v>7</v>
-      </c>
-      <c r="AY239">
-        <v>12</v>
-      </c>
-      <c r="AZ239">
-        <v>11</v>
-      </c>
-      <c r="BA239">
-        <v>1</v>
-      </c>
-      <c r="BB239">
-        <v>4</v>
-      </c>
-      <c r="BC239">
-        <v>5</v>
-      </c>
-      <c r="BD239">
-        <v>2.05</v>
-      </c>
-      <c r="BE239">
-        <v>7</v>
-      </c>
-      <c r="BF239">
-        <v>2.08</v>
-      </c>
-      <c r="BG239">
-        <v>1.3</v>
-      </c>
-      <c r="BH239">
-        <v>3.12</v>
-      </c>
-      <c r="BI239">
-        <v>1.52</v>
-      </c>
-      <c r="BJ239">
-        <v>2.33</v>
-      </c>
-      <c r="BK239">
-        <v>1.92</v>
-      </c>
-      <c r="BL239">
-        <v>1.82</v>
-      </c>
-      <c r="BM239">
-        <v>2.41</v>
-      </c>
-      <c r="BN239">
-        <v>1.5</v>
-      </c>
-      <c r="BO239">
-        <v>3.15</v>
-      </c>
-      <c r="BP239">
-        <v>1.3</v>
       </c>
     </row>
     <row r="240" spans="1:68">
@@ -50688,7 +50688,7 @@
         <v>239</v>
       </c>
       <c r="B240">
-        <v>7834551</v>
+        <v>7834558</v>
       </c>
       <c r="C240" t="s">
         <v>68</v>
@@ -50703,28 +50703,28 @@
         <v>25</v>
       </c>
       <c r="G240" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H240" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J240">
         <v>0</v>
       </c>
       <c r="K240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M240">
         <v>0</v>
       </c>
       <c r="N240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O240" t="s">
         <v>250</v>
@@ -50733,160 +50733,160 @@
         <v>93</v>
       </c>
       <c r="Q240">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R240">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S240">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="T240">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="U240">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="V240">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="W240">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X240">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="Y240">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z240">
-        <v>2.47</v>
+        <v>3.8</v>
       </c>
       <c r="AA240">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="AB240">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC240">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AD240">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE240">
+        <v>1.37</v>
+      </c>
+      <c r="AF240">
+        <v>3.1</v>
+      </c>
+      <c r="AG240">
+        <v>2.16</v>
+      </c>
+      <c r="AH240">
+        <v>1.72</v>
+      </c>
+      <c r="AI240">
+        <v>2</v>
+      </c>
+      <c r="AJ240">
+        <v>1.85</v>
+      </c>
+      <c r="AK240">
+        <v>1.75</v>
+      </c>
+      <c r="AL240">
+        <v>1.33</v>
+      </c>
+      <c r="AM240">
+        <v>1.26</v>
+      </c>
+      <c r="AN240">
+        <v>2.18</v>
+      </c>
+      <c r="AO240">
+        <v>2.3</v>
+      </c>
+      <c r="AP240">
+        <v>2.31</v>
+      </c>
+      <c r="AQ240">
+        <v>2.17</v>
+      </c>
+      <c r="AR240">
+        <v>1.52</v>
+      </c>
+      <c r="AS240">
+        <v>1.38</v>
+      </c>
+      <c r="AT240">
+        <v>2.9</v>
+      </c>
+      <c r="AU240">
+        <v>5</v>
+      </c>
+      <c r="AV240">
+        <v>4</v>
+      </c>
+      <c r="AW240">
+        <v>7</v>
+      </c>
+      <c r="AX240">
+        <v>7</v>
+      </c>
+      <c r="AY240">
+        <v>12</v>
+      </c>
+      <c r="AZ240">
+        <v>11</v>
+      </c>
+      <c r="BA240">
+        <v>1</v>
+      </c>
+      <c r="BB240">
+        <v>4</v>
+      </c>
+      <c r="BC240">
+        <v>5</v>
+      </c>
+      <c r="BD240">
+        <v>2.05</v>
+      </c>
+      <c r="BE240">
+        <v>7</v>
+      </c>
+      <c r="BF240">
+        <v>2.08</v>
+      </c>
+      <c r="BG240">
+        <v>1.3</v>
+      </c>
+      <c r="BH240">
+        <v>3.12</v>
+      </c>
+      <c r="BI240">
+        <v>1.52</v>
+      </c>
+      <c r="BJ240">
+        <v>2.33</v>
+      </c>
+      <c r="BK240">
+        <v>1.92</v>
+      </c>
+      <c r="BL240">
+        <v>1.82</v>
+      </c>
+      <c r="BM240">
+        <v>2.41</v>
+      </c>
+      <c r="BN240">
         <v>1.5</v>
       </c>
-      <c r="AF240">
-        <v>2.65</v>
-      </c>
-      <c r="AG240">
-        <v>2.5</v>
-      </c>
-      <c r="AH240">
-        <v>1.52</v>
-      </c>
-      <c r="AI240">
-        <v>2.06</v>
-      </c>
-      <c r="AJ240">
-        <v>1.71</v>
-      </c>
-      <c r="AK240">
-        <v>1.37</v>
-      </c>
-      <c r="AL240">
-        <v>1.29</v>
-      </c>
-      <c r="AM240">
-        <v>1.68</v>
-      </c>
-      <c r="AN240">
-        <v>1.9</v>
-      </c>
-      <c r="AO240">
-        <v>1.5</v>
-      </c>
-      <c r="AP240">
-        <v>2.08</v>
-      </c>
-      <c r="AQ240">
-        <v>1.29</v>
-      </c>
-      <c r="AR240">
-        <v>1.68</v>
-      </c>
-      <c r="AS240">
-        <v>1.44</v>
-      </c>
-      <c r="AT240">
-        <v>3.12</v>
-      </c>
-      <c r="AU240">
-        <v>3</v>
-      </c>
-      <c r="AV240">
-        <v>1</v>
-      </c>
-      <c r="AW240">
-        <v>5</v>
-      </c>
-      <c r="AX240">
-        <v>11</v>
-      </c>
-      <c r="AY240">
-        <v>8</v>
-      </c>
-      <c r="AZ240">
-        <v>12</v>
-      </c>
-      <c r="BA240">
-        <v>4</v>
-      </c>
-      <c r="BB240">
-        <v>2</v>
-      </c>
-      <c r="BC240">
-        <v>6</v>
-      </c>
-      <c r="BD240">
-        <v>1.67</v>
-      </c>
-      <c r="BE240">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF240">
-        <v>2.6</v>
-      </c>
-      <c r="BG240">
-        <v>1.27</v>
-      </c>
-      <c r="BH240">
-        <v>3.14</v>
-      </c>
-      <c r="BI240">
-        <v>1.58</v>
-      </c>
-      <c r="BJ240">
-        <v>2.45</v>
-      </c>
-      <c r="BK240">
-        <v>2.3</v>
-      </c>
-      <c r="BL240">
-        <v>1.77</v>
-      </c>
-      <c r="BM240">
-        <v>2.5</v>
-      </c>
-      <c r="BN240">
-        <v>1.46</v>
-      </c>
       <c r="BO240">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="BP240">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="241" spans="1:68">
@@ -51718,7 +51718,7 @@
         <v>244</v>
       </c>
       <c r="B245">
-        <v>7834565</v>
+        <v>7834570</v>
       </c>
       <c r="C245" t="s">
         <v>68</v>
@@ -51733,190 +51733,190 @@
         <v>26</v>
       </c>
       <c r="G245" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H245" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I245">
         <v>0</v>
       </c>
       <c r="J245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N245">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O245" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="P245" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="Q245">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="R245">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S245">
-        <v>4.75</v>
+        <v>3.21</v>
       </c>
       <c r="T245">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="U245">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="V245">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="W245">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="X245">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y245">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z245">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="AA245">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AB245">
-        <v>4.5</v>
+        <v>2.44</v>
       </c>
       <c r="AC245">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AD245">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="AE245">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF245">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AG245">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="AH245">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AI245">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AJ245">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AK245">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AL245">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AM245">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="AN245">
-        <v>2.27</v>
+        <v>0.73</v>
       </c>
       <c r="AO245">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP245">
-        <v>2.23</v>
+        <v>0.75</v>
       </c>
       <c r="AQ245">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="AR245">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AS245">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT245">
-        <v>2.93</v>
+        <v>2.51</v>
       </c>
       <c r="AU245">
+        <v>4</v>
+      </c>
+      <c r="AV245">
         <v>5</v>
       </c>
-      <c r="AV245">
+      <c r="AW245">
+        <v>8</v>
+      </c>
+      <c r="AX245">
+        <v>6</v>
+      </c>
+      <c r="AY245">
+        <v>12</v>
+      </c>
+      <c r="AZ245">
+        <v>11</v>
+      </c>
+      <c r="BA245">
+        <v>3</v>
+      </c>
+      <c r="BB245">
+        <v>1</v>
+      </c>
+      <c r="BC245">
         <v>4</v>
       </c>
-      <c r="AW245">
-        <v>9</v>
-      </c>
-      <c r="AX245">
-        <v>9</v>
-      </c>
-      <c r="AY245">
-        <v>14</v>
-      </c>
-      <c r="AZ245">
-        <v>13</v>
-      </c>
-      <c r="BA245">
-        <v>12</v>
-      </c>
-      <c r="BB245">
-        <v>5</v>
-      </c>
-      <c r="BC245">
-        <v>17</v>
-      </c>
       <c r="BD245">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="BE245">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF245">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="BG245">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BH245">
-        <v>4.6</v>
+        <v>3.78</v>
       </c>
       <c r="BI245">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BJ245">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BK245">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BL245">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="BM245">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="BN245">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BO245">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="BP245">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="246" spans="1:68">
@@ -51924,7 +51924,7 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>7834570</v>
+        <v>7834565</v>
       </c>
       <c r="C246" t="s">
         <v>68</v>
@@ -51939,190 +51939,190 @@
         <v>26</v>
       </c>
       <c r="G246" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H246" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I246">
         <v>0</v>
       </c>
       <c r="J246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N246">
+        <v>2</v>
+      </c>
+      <c r="O246" t="s">
+        <v>193</v>
+      </c>
+      <c r="P246" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q246">
+        <v>2.31</v>
+      </c>
+      <c r="R246">
+        <v>2.15</v>
+      </c>
+      <c r="S246">
+        <v>4.75</v>
+      </c>
+      <c r="T246">
+        <v>1.36</v>
+      </c>
+      <c r="U246">
+        <v>2.78</v>
+      </c>
+      <c r="V246">
+        <v>2.75</v>
+      </c>
+      <c r="W246">
+        <v>1.36</v>
+      </c>
+      <c r="X246">
+        <v>7</v>
+      </c>
+      <c r="Y246">
+        <v>1.04</v>
+      </c>
+      <c r="Z246">
+        <v>1.81</v>
+      </c>
+      <c r="AA246">
+        <v>3.58</v>
+      </c>
+      <c r="AB246">
+        <v>4.5</v>
+      </c>
+      <c r="AC246">
+        <v>1</v>
+      </c>
+      <c r="AD246">
+        <v>10.5</v>
+      </c>
+      <c r="AE246">
+        <v>1.33</v>
+      </c>
+      <c r="AF246">
+        <v>3.55</v>
+      </c>
+      <c r="AG246">
+        <v>2</v>
+      </c>
+      <c r="AH246">
+        <v>1.77</v>
+      </c>
+      <c r="AI246">
+        <v>1.85</v>
+      </c>
+      <c r="AJ246">
+        <v>2</v>
+      </c>
+      <c r="AK246">
+        <v>1.2</v>
+      </c>
+      <c r="AL246">
+        <v>1.25</v>
+      </c>
+      <c r="AM246">
+        <v>2.02</v>
+      </c>
+      <c r="AN246">
+        <v>2.27</v>
+      </c>
+      <c r="AO246">
+        <v>1.08</v>
+      </c>
+      <c r="AP246">
+        <v>2.23</v>
+      </c>
+      <c r="AQ246">
+        <v>1.08</v>
+      </c>
+      <c r="AR246">
+        <v>1.7</v>
+      </c>
+      <c r="AS246">
+        <v>1.23</v>
+      </c>
+      <c r="AT246">
+        <v>2.93</v>
+      </c>
+      <c r="AU246">
+        <v>5</v>
+      </c>
+      <c r="AV246">
         <v>4</v>
       </c>
-      <c r="O246" t="s">
-        <v>253</v>
-      </c>
-      <c r="P246" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q246">
-        <v>4</v>
-      </c>
-      <c r="R246">
-        <v>1.95</v>
-      </c>
-      <c r="S246">
-        <v>3.21</v>
-      </c>
-      <c r="T246">
+      <c r="AW246">
+        <v>9</v>
+      </c>
+      <c r="AX246">
+        <v>9</v>
+      </c>
+      <c r="AY246">
+        <v>14</v>
+      </c>
+      <c r="AZ246">
+        <v>13</v>
+      </c>
+      <c r="BA246">
+        <v>12</v>
+      </c>
+      <c r="BB246">
+        <v>5</v>
+      </c>
+      <c r="BC246">
+        <v>17</v>
+      </c>
+      <c r="BD246">
+        <v>1.66</v>
+      </c>
+      <c r="BE246">
+        <v>8</v>
+      </c>
+      <c r="BF246">
+        <v>2.65</v>
+      </c>
+      <c r="BG246">
+        <v>1.13</v>
+      </c>
+      <c r="BH246">
+        <v>4.6</v>
+      </c>
+      <c r="BI246">
+        <v>1.32</v>
+      </c>
+      <c r="BJ246">
+        <v>3.1</v>
+      </c>
+      <c r="BK246">
+        <v>1.54</v>
+      </c>
+      <c r="BL246">
+        <v>2.3</v>
+      </c>
+      <c r="BM246">
+        <v>1.9</v>
+      </c>
+      <c r="BN246">
+        <v>1.85</v>
+      </c>
+      <c r="BO246">
+        <v>2.33</v>
+      </c>
+      <c r="BP246">
         <v>1.53</v>
-      </c>
-      <c r="U246">
-        <v>2.35</v>
-      </c>
-      <c r="V246">
-        <v>3.3</v>
-      </c>
-      <c r="W246">
-        <v>1.26</v>
-      </c>
-      <c r="X246">
-        <v>8</v>
-      </c>
-      <c r="Y246">
-        <v>1.01</v>
-      </c>
-      <c r="Z246">
-        <v>3.3</v>
-      </c>
-      <c r="AA246">
-        <v>3.08</v>
-      </c>
-      <c r="AB246">
-        <v>2.44</v>
-      </c>
-      <c r="AC246">
-        <v>1.12</v>
-      </c>
-      <c r="AD246">
-        <v>7.5</v>
-      </c>
-      <c r="AE246">
-        <v>1.46</v>
-      </c>
-      <c r="AF246">
-        <v>2.7</v>
-      </c>
-      <c r="AG246">
-        <v>2.51</v>
-      </c>
-      <c r="AH246">
-        <v>1.51</v>
-      </c>
-      <c r="AI246">
-        <v>2.1</v>
-      </c>
-      <c r="AJ246">
-        <v>1.75</v>
-      </c>
-      <c r="AK246">
-        <v>1.63</v>
-      </c>
-      <c r="AL246">
-        <v>1.3</v>
-      </c>
-      <c r="AM246">
-        <v>1.28</v>
-      </c>
-      <c r="AN246">
-        <v>0.73</v>
-      </c>
-      <c r="AO246">
-        <v>1</v>
-      </c>
-      <c r="AP246">
-        <v>0.75</v>
-      </c>
-      <c r="AQ246">
-        <v>0.93</v>
-      </c>
-      <c r="AR246">
-        <v>1.41</v>
-      </c>
-      <c r="AS246">
-        <v>1.1</v>
-      </c>
-      <c r="AT246">
-        <v>2.51</v>
-      </c>
-      <c r="AU246">
-        <v>4</v>
-      </c>
-      <c r="AV246">
-        <v>5</v>
-      </c>
-      <c r="AW246">
-        <v>8</v>
-      </c>
-      <c r="AX246">
-        <v>6</v>
-      </c>
-      <c r="AY246">
-        <v>12</v>
-      </c>
-      <c r="AZ246">
-        <v>11</v>
-      </c>
-      <c r="BA246">
-        <v>3</v>
-      </c>
-      <c r="BB246">
-        <v>1</v>
-      </c>
-      <c r="BC246">
-        <v>4</v>
-      </c>
-      <c r="BD246">
-        <v>2.35</v>
-      </c>
-      <c r="BE246">
-        <v>8.6</v>
-      </c>
-      <c r="BF246">
-        <v>1.82</v>
-      </c>
-      <c r="BG246">
-        <v>1.21</v>
-      </c>
-      <c r="BH246">
-        <v>3.78</v>
-      </c>
-      <c r="BI246">
-        <v>1.4</v>
-      </c>
-      <c r="BJ246">
-        <v>3.05</v>
-      </c>
-      <c r="BK246">
-        <v>1.53</v>
-      </c>
-      <c r="BL246">
-        <v>2.13</v>
-      </c>
-      <c r="BM246">
-        <v>2.07</v>
-      </c>
-      <c r="BN246">
-        <v>1.71</v>
-      </c>
-      <c r="BO246">
-        <v>2.57</v>
-      </c>
-      <c r="BP246">
-        <v>1.44</v>
       </c>
     </row>
     <row r="247" spans="1:68">
@@ -54396,7 +54396,7 @@
         <v>257</v>
       </c>
       <c r="B258">
-        <v>7834572</v>
+        <v>7834574</v>
       </c>
       <c r="C258" t="s">
         <v>68</v>
@@ -54411,28 +54411,28 @@
         <v>27</v>
       </c>
       <c r="G258" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H258" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J258">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K258">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L258">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M258">
         <v>3</v>
       </c>
       <c r="N258">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O258" t="s">
         <v>262</v>
@@ -54441,157 +54441,157 @@
         <v>353</v>
       </c>
       <c r="Q258">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="R258">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S258">
-        <v>4.68</v>
+        <v>3</v>
       </c>
       <c r="T258">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="U258">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="V258">
-        <v>2.96</v>
+        <v>3.66</v>
       </c>
       <c r="W258">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="X258">
+        <v>9</v>
+      </c>
+      <c r="Y258">
+        <v>1.01</v>
+      </c>
+      <c r="Z258">
+        <v>3.5</v>
+      </c>
+      <c r="AA258">
+        <v>3</v>
+      </c>
+      <c r="AB258">
+        <v>2.25</v>
+      </c>
+      <c r="AC258">
+        <v>1.12</v>
+      </c>
+      <c r="AD258">
+        <v>6.75</v>
+      </c>
+      <c r="AE258">
+        <v>1.55</v>
+      </c>
+      <c r="AF258">
+        <v>2.38</v>
+      </c>
+      <c r="AG258">
+        <v>2.6</v>
+      </c>
+      <c r="AH258">
+        <v>1.45</v>
+      </c>
+      <c r="AI258">
+        <v>2.3</v>
+      </c>
+      <c r="AJ258">
+        <v>1.65</v>
+      </c>
+      <c r="AK258">
+        <v>1.35</v>
+      </c>
+      <c r="AL258">
+        <v>1.33</v>
+      </c>
+      <c r="AM258">
+        <v>1.26</v>
+      </c>
+      <c r="AN258">
+        <v>1.85</v>
+      </c>
+      <c r="AO258">
+        <v>2.09</v>
+      </c>
+      <c r="AP258">
+        <v>1.71</v>
+      </c>
+      <c r="AQ258">
+        <v>2.17</v>
+      </c>
+      <c r="AR258">
+        <v>1.37</v>
+      </c>
+      <c r="AS258">
+        <v>1.39</v>
+      </c>
+      <c r="AT258">
+        <v>2.76</v>
+      </c>
+      <c r="AU258">
+        <v>5</v>
+      </c>
+      <c r="AV258">
         <v>7</v>
       </c>
-      <c r="Y258">
-        <v>1.08</v>
-      </c>
-      <c r="Z258">
-        <v>1.69</v>
-      </c>
-      <c r="AA258">
-        <v>3.75</v>
-      </c>
-      <c r="AB258">
-        <v>4.8</v>
-      </c>
-      <c r="AC258">
-        <v>1.06</v>
-      </c>
-      <c r="AD258">
-        <v>10</v>
-      </c>
-      <c r="AE258">
-        <v>1.28</v>
-      </c>
-      <c r="AF258">
-        <v>3.3</v>
-      </c>
-      <c r="AG258">
-        <v>2.01</v>
-      </c>
-      <c r="AH258">
-        <v>1.88</v>
-      </c>
-      <c r="AI258">
-        <v>1.96</v>
-      </c>
-      <c r="AJ258">
-        <v>1.75</v>
-      </c>
-      <c r="AK258">
-        <v>1.25</v>
-      </c>
-      <c r="AL258">
-        <v>1.3</v>
-      </c>
-      <c r="AM258">
-        <v>2</v>
-      </c>
-      <c r="AN258">
-        <v>1.46</v>
-      </c>
-      <c r="AO258">
-        <v>0.38</v>
-      </c>
-      <c r="AP258">
-        <v>1.57</v>
-      </c>
-      <c r="AQ258">
-        <v>0.36</v>
-      </c>
-      <c r="AR258">
-        <v>1.55</v>
-      </c>
-      <c r="AS258">
-        <v>1.11</v>
-      </c>
-      <c r="AT258">
-        <v>2.66</v>
-      </c>
-      <c r="AU258">
+      <c r="AW258">
         <v>7</v>
       </c>
-      <c r="AV258">
-        <v>3</v>
-      </c>
-      <c r="AW258">
-        <v>6</v>
-      </c>
       <c r="AX258">
+        <v>7</v>
+      </c>
+      <c r="AY258">
+        <v>12</v>
+      </c>
+      <c r="AZ258">
+        <v>14</v>
+      </c>
+      <c r="BA258">
         <v>4</v>
       </c>
-      <c r="AY258">
-        <v>13</v>
-      </c>
-      <c r="AZ258">
+      <c r="BB258">
         <v>7</v>
       </c>
-      <c r="BA258">
-        <v>5</v>
-      </c>
-      <c r="BB258">
-        <v>0</v>
-      </c>
       <c r="BC258">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BD258">
-        <v>1.49</v>
+        <v>2.33</v>
       </c>
       <c r="BE258">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BF258">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="BG258">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BH258">
         <v>3.1</v>
       </c>
       <c r="BI258">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="BJ258">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="BK258">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="BL258">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BM258">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="BN258">
         <v>1.5</v>
       </c>
       <c r="BO258">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BP258">
         <v>1.29</v>
@@ -54602,7 +54602,7 @@
         <v>258</v>
       </c>
       <c r="B259">
-        <v>7834574</v>
+        <v>7834572</v>
       </c>
       <c r="C259" t="s">
         <v>68</v>
@@ -54617,28 +54617,28 @@
         <v>27</v>
       </c>
       <c r="G259" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H259" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I259">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K259">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L259">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M259">
         <v>3</v>
       </c>
       <c r="N259">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O259" t="s">
         <v>263</v>
@@ -54647,157 +54647,157 @@
         <v>354</v>
       </c>
       <c r="Q259">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="R259">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S259">
+        <v>4.68</v>
+      </c>
+      <c r="T259">
+        <v>1.36</v>
+      </c>
+      <c r="U259">
+        <v>2.9</v>
+      </c>
+      <c r="V259">
+        <v>2.96</v>
+      </c>
+      <c r="W259">
+        <v>1.38</v>
+      </c>
+      <c r="X259">
+        <v>7</v>
+      </c>
+      <c r="Y259">
+        <v>1.08</v>
+      </c>
+      <c r="Z259">
+        <v>1.69</v>
+      </c>
+      <c r="AA259">
+        <v>3.75</v>
+      </c>
+      <c r="AB259">
+        <v>4.8</v>
+      </c>
+      <c r="AC259">
+        <v>1.06</v>
+      </c>
+      <c r="AD259">
+        <v>10</v>
+      </c>
+      <c r="AE259">
+        <v>1.28</v>
+      </c>
+      <c r="AF259">
+        <v>3.3</v>
+      </c>
+      <c r="AG259">
+        <v>2.01</v>
+      </c>
+      <c r="AH259">
+        <v>1.88</v>
+      </c>
+      <c r="AI259">
+        <v>1.96</v>
+      </c>
+      <c r="AJ259">
+        <v>1.75</v>
+      </c>
+      <c r="AK259">
+        <v>1.25</v>
+      </c>
+      <c r="AL259">
+        <v>1.3</v>
+      </c>
+      <c r="AM259">
+        <v>2</v>
+      </c>
+      <c r="AN259">
+        <v>1.46</v>
+      </c>
+      <c r="AO259">
+        <v>0.38</v>
+      </c>
+      <c r="AP259">
+        <v>1.57</v>
+      </c>
+      <c r="AQ259">
+        <v>0.36</v>
+      </c>
+      <c r="AR259">
+        <v>1.55</v>
+      </c>
+      <c r="AS259">
+        <v>1.11</v>
+      </c>
+      <c r="AT259">
+        <v>2.66</v>
+      </c>
+      <c r="AU259">
+        <v>7</v>
+      </c>
+      <c r="AV259">
         <v>3</v>
       </c>
-      <c r="T259">
-        <v>1.59</v>
-      </c>
-      <c r="U259">
-        <v>2.31</v>
-      </c>
-      <c r="V259">
-        <v>3.66</v>
-      </c>
-      <c r="W259">
-        <v>1.25</v>
-      </c>
-      <c r="X259">
-        <v>9</v>
-      </c>
-      <c r="Y259">
-        <v>1.01</v>
-      </c>
-      <c r="Z259">
-        <v>3.5</v>
-      </c>
-      <c r="AA259">
-        <v>3</v>
-      </c>
-      <c r="AB259">
-        <v>2.25</v>
-      </c>
-      <c r="AC259">
-        <v>1.12</v>
-      </c>
-      <c r="AD259">
-        <v>6.75</v>
-      </c>
-      <c r="AE259">
-        <v>1.55</v>
-      </c>
-      <c r="AF259">
-        <v>2.38</v>
-      </c>
-      <c r="AG259">
-        <v>2.6</v>
-      </c>
-      <c r="AH259">
-        <v>1.45</v>
-      </c>
-      <c r="AI259">
-        <v>2.3</v>
-      </c>
-      <c r="AJ259">
-        <v>1.65</v>
-      </c>
-      <c r="AK259">
-        <v>1.35</v>
-      </c>
-      <c r="AL259">
-        <v>1.33</v>
-      </c>
-      <c r="AM259">
-        <v>1.26</v>
-      </c>
-      <c r="AN259">
-        <v>1.85</v>
-      </c>
-      <c r="AO259">
-        <v>2.09</v>
-      </c>
-      <c r="AP259">
-        <v>1.71</v>
-      </c>
-      <c r="AQ259">
-        <v>2.17</v>
-      </c>
-      <c r="AR259">
-        <v>1.37</v>
-      </c>
-      <c r="AS259">
-        <v>1.39</v>
-      </c>
-      <c r="AT259">
-        <v>2.76</v>
-      </c>
-      <c r="AU259">
+      <c r="AW259">
+        <v>6</v>
+      </c>
+      <c r="AX259">
+        <v>4</v>
+      </c>
+      <c r="AY259">
+        <v>13</v>
+      </c>
+      <c r="AZ259">
+        <v>7</v>
+      </c>
+      <c r="BA259">
         <v>5</v>
       </c>
-      <c r="AV259">
-        <v>7</v>
-      </c>
-      <c r="AW259">
-        <v>7</v>
-      </c>
-      <c r="AX259">
-        <v>7</v>
-      </c>
-      <c r="AY259">
-        <v>12</v>
-      </c>
-      <c r="AZ259">
-        <v>14</v>
-      </c>
-      <c r="BA259">
-        <v>4</v>
-      </c>
       <c r="BB259">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BC259">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BD259">
-        <v>2.33</v>
+        <v>1.49</v>
       </c>
       <c r="BE259">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF259">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="BG259">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BH259">
         <v>3.1</v>
       </c>
       <c r="BI259">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="BJ259">
-        <v>2.17</v>
+        <v>2.39</v>
       </c>
       <c r="BK259">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="BL259">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BM259">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="BN259">
         <v>1.5</v>
       </c>
       <c r="BO259">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BP259">
         <v>1.29</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie A_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP266"/>
+  <dimension ref="A1:BP270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.29</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.38</v>
@@ -3966,7 +3966,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.17</v>
@@ -4402,7 +4402,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.58</v>
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
@@ -6582,7 +6582,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR28" t="n">
         <v>1.33</v>
@@ -7018,7 +7018,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR30" t="n">
         <v>0.67</v>
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.08</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
         <v>1.02</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.93</v>
@@ -9852,7 +9852,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR43" t="n">
         <v>1.42</v>
@@ -10070,7 +10070,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR44" t="n">
         <v>1.21</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.64</v>
@@ -12465,7 +12465,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.58</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.93</v>
@@ -13119,7 +13119,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ58" t="n">
         <v>1</v>
@@ -13776,7 +13776,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR61" t="n">
         <v>1.74</v>
@@ -14430,7 +14430,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -15520,7 +15520,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR69" t="n">
         <v>1.32</v>
@@ -16389,7 +16389,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ73" t="n">
         <v>1</v>
@@ -16610,7 +16610,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR74" t="n">
         <v>1.05</v>
@@ -17261,7 +17261,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.54</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.08</v>
@@ -17915,10 +17915,10 @@
         <v>0.75</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR80" t="n">
         <v>1.99</v>
@@ -21403,10 +21403,10 @@
         <v>0.6</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR96" t="n">
         <v>1.67</v>
@@ -21621,10 +21621,10 @@
         <v>1.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR97" t="n">
         <v>1.63</v>
@@ -22714,7 +22714,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR102" t="n">
         <v>1.25</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5</v>
@@ -24673,7 +24673,7 @@
         <v>0.5</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ111" t="n">
         <v>1</v>
@@ -25984,7 +25984,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR117" t="n">
         <v>2</v>
@@ -27074,7 +27074,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR122" t="n">
         <v>1.44</v>
@@ -27943,7 +27943,7 @@
         <v>1</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.21</v>
@@ -28382,7 +28382,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR128" t="n">
         <v>1.65</v>
@@ -28597,7 +28597,7 @@
         <v>0.43</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.36</v>
@@ -29687,7 +29687,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.86</v>
@@ -30562,7 +30562,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
         <v>1.43</v>
@@ -30777,7 +30777,7 @@
         <v>1.14</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.29</v>
@@ -30995,7 +30995,7 @@
         <v>1.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.64</v>
@@ -32306,7 +32306,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR146" t="n">
         <v>1.49</v>
@@ -32524,7 +32524,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR147" t="n">
         <v>1.53</v>
@@ -32957,7 +32957,7 @@
         <v>0.75</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ149" t="n">
         <v>1</v>
@@ -33175,7 +33175,7 @@
         <v>0.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.36</v>
@@ -33396,7 +33396,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR151" t="n">
         <v>1.5</v>
@@ -33611,7 +33611,7 @@
         <v>0.75</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.86</v>
@@ -33829,7 +33829,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.93</v>
@@ -35355,7 +35355,7 @@
         <v>1.14</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ160" t="n">
         <v>1</v>
@@ -35573,7 +35573,7 @@
         <v>0.57</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.85</v>
@@ -36227,7 +36227,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.54</v>
@@ -36448,7 +36448,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR165" t="n">
         <v>1.44</v>
@@ -36666,7 +36666,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR166" t="n">
         <v>1.9</v>
@@ -37974,7 +37974,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR172" t="n">
         <v>1.43</v>
@@ -38843,7 +38843,7 @@
         <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ176" t="n">
         <v>1</v>
@@ -39718,7 +39718,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR180" t="n">
         <v>1.39</v>
@@ -40369,7 +40369,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.08</v>
@@ -41244,7 +41244,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR187" t="n">
         <v>1.86</v>
@@ -41459,7 +41459,7 @@
         <v>2.38</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ188" t="n">
         <v>2.17</v>
@@ -41677,7 +41677,7 @@
         <v>1.67</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.54</v>
@@ -42334,7 +42334,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR192" t="n">
         <v>1.67</v>
@@ -43857,7 +43857,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP199" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.5</v>
@@ -44511,10 +44511,10 @@
         <v>1.3</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR202" t="n">
         <v>1.75</v>
@@ -45601,7 +45601,7 @@
         <v>1.33</v>
       </c>
       <c r="AP207" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ207" t="n">
         <v>1</v>
@@ -46255,7 +46255,7 @@
         <v>0.7</v>
       </c>
       <c r="AP210" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.85</v>
@@ -46909,10 +46909,10 @@
         <v>1</v>
       </c>
       <c r="AP213" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR213" t="n">
         <v>1.6</v>
@@ -47784,7 +47784,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ217" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR217" t="n">
         <v>1.31</v>
@@ -48653,7 +48653,7 @@
         <v>1.45</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ221" t="n">
         <v>1.21</v>
@@ -49089,7 +49089,7 @@
         <v>0.75</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.64</v>
@@ -49525,7 +49525,7 @@
         <v>0.4</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.58</v>
@@ -49743,7 +49743,7 @@
         <v>0.4</v>
       </c>
       <c r="AP226" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.38</v>
@@ -50179,7 +50179,7 @@
         <v>1.08</v>
       </c>
       <c r="AP228" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ228" t="n">
         <v>1</v>
@@ -50618,7 +50618,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR230" t="n">
         <v>1.67</v>
@@ -51926,7 +51926,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ236" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR236" t="n">
         <v>1.25</v>
@@ -53234,7 +53234,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR242" t="n">
         <v>1.55</v>
@@ -53885,7 +53885,7 @@
         <v>1</v>
       </c>
       <c r="AP245" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ245" t="n">
         <v>0.93</v>
@@ -54103,10 +54103,10 @@
         <v>1.08</v>
       </c>
       <c r="AP246" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR246" t="n">
         <v>1.7</v>
@@ -54321,7 +54321,7 @@
         <v>0.92</v>
       </c>
       <c r="AP247" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ247" t="n">
         <v>0.85</v>
@@ -54975,7 +54975,7 @@
         <v>1.08</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ250" t="n">
         <v>1</v>
@@ -57158,7 +57158,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ260" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR260" t="n">
         <v>1.51</v>
@@ -58245,7 +58245,7 @@
         <v>1</v>
       </c>
       <c r="AP265" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ265" t="n">
         <v>0.93</v>
@@ -58463,7 +58463,7 @@
         <v>0.42</v>
       </c>
       <c r="AP266" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ266" t="n">
         <v>0.38</v>
@@ -58542,6 +58542,878 @@
       </c>
       <c r="BP266" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>7834583</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>45945.79166666666</v>
+      </c>
+      <c r="F267" t="n">
+        <v>28</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" t="n">
+        <v>2</v>
+      </c>
+      <c r="L267" t="n">
+        <v>5</v>
+      </c>
+      <c r="M267" t="n">
+        <v>1</v>
+      </c>
+      <c r="N267" t="n">
+        <v>6</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>['45+5', '58', '73', '84', '89']</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S267" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U267" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V267" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W267" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X267" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY267" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA267" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB267" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE267" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI267" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM267" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN267" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO267" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BP267" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>7834582</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>45945.8125</v>
+      </c>
+      <c r="F268" t="n">
+        <v>28</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>1</v>
+      </c>
+      <c r="K268" t="n">
+        <v>1</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
+        <v>3</v>
+      </c>
+      <c r="N268" t="n">
+        <v>3</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>['40', '70', '80']</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R268" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S268" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T268" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U268" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V268" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W268" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X268" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA268" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB268" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BI268" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO268" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BP268" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>7834585</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>45945.83333333334</v>
+      </c>
+      <c r="F269" t="n">
+        <v>28</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>2</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" t="n">
+        <v>3</v>
+      </c>
+      <c r="L269" t="n">
+        <v>3</v>
+      </c>
+      <c r="M269" t="n">
+        <v>1</v>
+      </c>
+      <c r="N269" t="n">
+        <v>4</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>['26', '45+4', '49']</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R269" t="n">
+        <v>2</v>
+      </c>
+      <c r="S269" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U269" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V269" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X269" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU269" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY269" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA269" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI269" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM269" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN269" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO269" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP269" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>7834590</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>45945.83333333334</v>
+      </c>
+      <c r="F270" t="n">
+        <v>28</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1</v>
+      </c>
+      <c r="M270" t="n">
+        <v>1</v>
+      </c>
+      <c r="N270" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>3</v>
+      </c>
+      <c r="R270" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S270" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U270" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V270" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W270" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X270" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA270" t="